--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -251,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -327,6 +327,9 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -335,6 +338,12 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -778,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-08 19:46 KST</t>
+          <t>2026-09-08 20:57 KST</t>
         </is>
       </c>
     </row>
@@ -789,9 +798,9 @@
           <t>MARKET SIGNAL</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>AI 반도체 주도 랠리와 경기 둔화 우려의 교차</t>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>반도체 주도 랠리와 금리 인상 우려 사이의 변동성 장세</t>
         </is>
       </c>
     </row>
@@ -886,28 +895,28 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="28" t="n">
         <v>-98706</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>31848</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>32918</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <v>-0.76</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="28" t="n">
         <v>-1.02</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="28" t="n">
         <v>-0.58</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="29" t="n">
         <v>6.77</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="29" t="n">
         <v>6.74</v>
       </c>
     </row>
@@ -917,13 +926,13 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="29" t="n">
         <v>3387</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>-99</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="28" t="n">
         <v>-3471</v>
       </c>
     </row>
@@ -956,83 +965,83 @@
           <t>US 상승 섹터</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>반도체 +5.22%</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>기술 +1.4%</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>산업재 +0.82%</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="31" customHeight="1" s="15">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>US 하락 섹터</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>임의소비재 -2.66%</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>헬스케어 -2.08%</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>에너지 -1.74%</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="31" customHeight="1" s="15">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>KR 상승 섹터</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>건설 +7.86%</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>기계·장비 +7.43%</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>전기·전자 +5.93%</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="31" customHeight="1" s="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>KR 하락 섹터</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>음식료·담배 -3.39%</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>IT 서비스 -1.75%</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>화학 -1.32%</t>
         </is>
@@ -1101,32 +1110,32 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="15">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>실업률</t>
         </is>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>4.1</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="30" t="n">
         <v>4.1</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <v>4.1</v>
       </c>
-      <c r="G19" s="29" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1137,67 +1146,75 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+    <row r="20" ht="31" customHeight="1" s="15">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>비농업고용지수</t>
         </is>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>162</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="30" t="n">
         <v>-23</v>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>Kpers</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>예상 상회</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44.5" customHeight="1" s="15">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>KOR</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>국내총생산(GDP) 전분기 대비</t>
         </is>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.6</v>
       </c>
-      <c r="E21" s="29" t="inlineStr"/>
-      <c r="F21" s="29" t="n">
+      <c r="E21" s="30" t="inlineStr"/>
+      <c r="F21" s="30" t="n">
         <v>1.8</v>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>이전比 하회</t>
+        </is>
+      </c>
     </row>
     <row r="22"/>
     <row r="23">
@@ -1258,60 +1275,68 @@
       </c>
     </row>
     <row r="25" ht="58" customHeight="1" s="15">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="29" t="n">
         <v>4.61</v>
       </c>
-      <c r="C25" s="29" t="inlineStr"/>
-      <c r="D25" s="28" t="n">
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="n">
         <v>1.07</v>
       </c>
-      <c r="E25" s="29" t="inlineStr"/>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>기계·장비, 전기·전자</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 및 대형주로 이어지며, 미국 지수 약세에도 불구하고 외국인과 기관의 강력한 매수세를 유도함.</t>
+          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1" s="15">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="28" t="n">
         <v>-0.58</v>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>231▲/634▼</t>
         </is>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="28" t="n">
         <v>-1.25</v>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>506▲/1141▼ 상한6</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>전기·가스, 건설</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시켰고, 국내 GDP 성장률 둔화와 맞물려 지수 하락을 견인함.</t>
+          <t>미국 국채금리 급등과 UBS의 금리 인상 전망 제기로 인한 투자 심리 위축이 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
         </is>
       </c>
     </row>
@@ -1351,21 +1376,21 @@
     <row r="30" ht="31" customHeight="1" s="15">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경: 미국 비농업 고용지수(162K)가 예상치(55K)를 상회하며 금리 인하 경로 불확실성이 커졌고, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 신호가 뚜렷함.</t>
+          <t>- 미국 비농업 고용지표(162K)가 예상치를 상회하고 국내 2분기 GDP(0.6%)가 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 커짐.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="15">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으나, 개인은 전 섹터에서 매도 우위를 보이며 차익 실현에 집중함.</t>
+          <t>- 수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수가 집중되었으나, 개인은 전반적인 차익 실현 매도를 지속함.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="15">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>- 종합 관점: AI 반도체 모멘텀이 시장을 견인했으나, 매크로 불확실성과 경기 둔화 우려가 상존하며 수급 쏠림 현상이 심화된 한 주였음.</t>
+          <t>- 반도체 중심의 수급 쏠림이 뚜렷한 가운데, 금리 인상 우려와 경기 둔화 신호가 맞물리며 지수 상단이 제한되는 흐름을 보임.</t>
         </is>
       </c>
     </row>
@@ -1452,34 +1477,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D36" s="28" t="n">
-        <v>43839</v>
-      </c>
-      <c r="E36" s="28" t="n">
-        <v>20501</v>
-      </c>
-      <c r="F36" s="28" t="n">
-        <v>23338</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>-53897</v>
-      </c>
-      <c r="H36" s="29" t="n">
+      <c r="D36" s="29" t="n">
+        <v>45121</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>21100</v>
+      </c>
+      <c r="F36" s="29" t="n">
+        <v>24020</v>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>-55192</v>
+      </c>
+      <c r="H36" s="30" t="n">
         <v>1816.7</v>
       </c>
-      <c r="I36" s="29" t="n">
-        <v>247447.2</v>
-      </c>
-      <c r="J36" s="29" t="n">
-        <v>0</v>
+      <c r="I36" s="30" t="n">
+        <v>240284.8</v>
+      </c>
+      <c r="J36" s="30" t="n">
+        <v>-7162.4</v>
       </c>
     </row>
     <row r="37">
@@ -1488,34 +1513,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D37" s="28" t="n">
-        <v>28819</v>
-      </c>
-      <c r="E37" s="28" t="n">
-        <v>19070</v>
-      </c>
-      <c r="F37" s="28" t="n">
-        <v>9749</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>-51831</v>
-      </c>
-      <c r="H37" s="29" t="n">
+      <c r="D37" s="29" t="n">
+        <v>29092</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>19197</v>
+      </c>
+      <c r="F37" s="29" t="n">
+        <v>9895</v>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>-52130</v>
+      </c>
+      <c r="H37" s="30" t="n">
         <v>3364.2</v>
       </c>
-      <c r="I37" s="29" t="n">
-        <v>225804.3</v>
-      </c>
-      <c r="J37" s="29" t="n">
-        <v>0</v>
+      <c r="I37" s="30" t="n">
+        <v>223759.5</v>
+      </c>
+      <c r="J37" s="30" t="n">
+        <v>-2044.8</v>
       </c>
     </row>
     <row r="38">
@@ -1524,34 +1549,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D38" s="28" t="n">
-        <v>5236</v>
-      </c>
-      <c r="E38" s="28" t="n">
-        <v>3060</v>
-      </c>
-      <c r="F38" s="28" t="n">
-        <v>2175</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>-5105</v>
-      </c>
-      <c r="H38" s="29" t="n">
+      <c r="D38" s="29" t="n">
+        <v>5294</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F38" s="29" t="n">
+        <v>2223</v>
+      </c>
+      <c r="G38" s="28" t="n">
+        <v>-5184</v>
+      </c>
+      <c r="H38" s="30" t="n">
         <v>365.7</v>
       </c>
-      <c r="I38" s="29" t="n">
-        <v>32812</v>
-      </c>
-      <c r="J38" s="29" t="n">
-        <v>0</v>
+      <c r="I38" s="30" t="n">
+        <v>32891.8</v>
+      </c>
+      <c r="J38" s="30" t="n">
+        <v>79.8</v>
       </c>
     </row>
     <row r="39">
@@ -1560,70 +1585,70 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D39" s="28" t="n">
+      <c r="D39" s="29" t="n">
         <v>2338</v>
       </c>
-      <c r="E39" s="28" t="n">
+      <c r="E39" s="29" t="n">
         <v>740</v>
       </c>
-      <c r="F39" s="28" t="n">
+      <c r="F39" s="29" t="n">
         <v>1598</v>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="28" t="n">
         <v>-2361</v>
       </c>
-      <c r="H39" s="29" t="n">
+      <c r="H39" s="30" t="n">
         <v>206.2</v>
       </c>
-      <c r="I39" s="29" t="n">
-        <v>29143.8</v>
-      </c>
-      <c r="J39" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="I39" s="30" t="n">
+        <v>28477.7</v>
+      </c>
+      <c r="J39" s="30" t="n">
+        <v>-666.1</v>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1" s="15">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D40" s="28" t="n">
-        <v>2266</v>
+      <c r="D40" s="29" t="n">
+        <v>2138</v>
       </c>
       <c r="E40" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="F40" s="28" t="n">
-        <v>2208</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>-2304</v>
-      </c>
-      <c r="H40" s="29" t="n">
+        <v>-81</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>2220</v>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>-2125</v>
+      </c>
+      <c r="H40" s="30" t="n">
         <v>900.5</v>
       </c>
-      <c r="I40" s="29" t="n">
-        <v>19475.5</v>
-      </c>
-      <c r="J40" s="29" t="n">
-        <v>0</v>
+      <c r="I40" s="30" t="n">
+        <v>19469.6</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <v>-5.9</v>
       </c>
     </row>
     <row r="41">
@@ -1632,34 +1657,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="D41" s="28" t="n">
-        <v>1369</v>
-      </c>
-      <c r="E41" s="28" t="n">
-        <v>816</v>
-      </c>
-      <c r="F41" s="28" t="n">
-        <v>553</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>-1351</v>
-      </c>
-      <c r="H41" s="29" t="n">
+      <c r="D41" s="29" t="n">
+        <v>1581</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>581</v>
+      </c>
+      <c r="G41" s="28" t="n">
+        <v>-1560</v>
+      </c>
+      <c r="H41" s="30" t="n">
         <v>485.3</v>
       </c>
-      <c r="I41" s="29" t="n">
-        <v>44346.7</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>0</v>
+      <c r="I41" s="30" t="n">
+        <v>43511.4</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>-835.3</v>
       </c>
     </row>
     <row r="42">
@@ -1668,34 +1693,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D42" s="28" t="n">
-        <v>1309</v>
-      </c>
-      <c r="E42" s="28" t="n">
-        <v>765</v>
-      </c>
-      <c r="F42" s="28" t="n">
-        <v>543</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>-1290</v>
-      </c>
-      <c r="H42" s="29" t="n">
+      <c r="D42" s="29" t="n">
+        <v>1182</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>640</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>541</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>-1175</v>
+      </c>
+      <c r="H42" s="30" t="n">
         <v>422.1</v>
       </c>
-      <c r="I42" s="29" t="n">
-        <v>10675.8</v>
-      </c>
-      <c r="J42" s="29" t="n">
-        <v>0</v>
+      <c r="I42" s="30" t="n">
+        <v>10178.7</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>-497.1</v>
       </c>
     </row>
     <row r="43">
@@ -1704,34 +1729,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D43" s="28" t="n">
-        <v>867</v>
-      </c>
-      <c r="E43" s="28" t="n">
-        <v>702</v>
-      </c>
-      <c r="F43" s="28" t="n">
-        <v>165</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>-880</v>
-      </c>
-      <c r="H43" s="29" t="n">
+      <c r="D43" s="29" t="n">
+        <v>852</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <v>687</v>
+      </c>
+      <c r="F43" s="29" t="n">
+        <v>166</v>
+      </c>
+      <c r="G43" s="28" t="n">
+        <v>-863</v>
+      </c>
+      <c r="H43" s="30" t="n">
         <v>144</v>
       </c>
-      <c r="I43" s="29" t="n">
-        <v>6126.4</v>
-      </c>
-      <c r="J43" s="29" t="n">
-        <v>0</v>
+      <c r="I43" s="30" t="n">
+        <v>5502.2</v>
+      </c>
+      <c r="J43" s="30" t="n">
+        <v>-624.2</v>
       </c>
     </row>
     <row r="44">
@@ -1740,34 +1765,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>대우건설</t>
         </is>
       </c>
-      <c r="D44" s="28" t="n">
+      <c r="D44" s="29" t="n">
         <v>813</v>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="E44" s="29" t="n">
         <v>369</v>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="29" t="n">
         <v>444</v>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="28" t="n">
         <v>-812</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="30" t="n">
         <v>164.4</v>
       </c>
-      <c r="I44" s="29" t="n">
-        <v>5739.7</v>
-      </c>
-      <c r="J44" s="29" t="n">
-        <v>0</v>
+      <c r="I44" s="30" t="n">
+        <v>6222.6</v>
+      </c>
+      <c r="J44" s="30" t="n">
+        <v>482.9</v>
       </c>
     </row>
     <row r="45">
@@ -1776,34 +1801,34 @@
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>현대건설</t>
         </is>
       </c>
-      <c r="D45" s="28" t="n">
-        <v>720</v>
-      </c>
-      <c r="E45" s="27" t="n">
-        <v>-287</v>
-      </c>
-      <c r="F45" s="28" t="n">
-        <v>1007</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>-724</v>
-      </c>
-      <c r="H45" s="29" t="n">
+      <c r="D45" s="29" t="n">
+        <v>754</v>
+      </c>
+      <c r="E45" s="28" t="n">
+        <v>-258</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>1011</v>
+      </c>
+      <c r="G45" s="28" t="n">
+        <v>-760</v>
+      </c>
+      <c r="H45" s="30" t="n">
         <v>292.4</v>
       </c>
-      <c r="I45" s="29" t="n">
-        <v>8468.6</v>
-      </c>
-      <c r="J45" s="29" t="n">
-        <v>0</v>
+      <c r="I45" s="30" t="n">
+        <v>8765.6</v>
+      </c>
+      <c r="J45" s="30" t="n">
+        <v>297</v>
       </c>
     </row>
     <row r="46">
@@ -1812,34 +1837,34 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D46" s="27" t="n">
-        <v>-1900</v>
-      </c>
-      <c r="E46" s="27" t="n">
-        <v>-1420</v>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>-480</v>
-      </c>
-      <c r="G46" s="28" t="n">
-        <v>1869</v>
-      </c>
-      <c r="H46" s="29" t="n">
+      <c r="D46" s="28" t="n">
+        <v>-3070</v>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>-2520</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G46" s="29" t="n">
+        <v>3076</v>
+      </c>
+      <c r="H46" s="30" t="n">
         <v>686.4</v>
       </c>
-      <c r="I46" s="29" t="n">
-        <v>38810</v>
-      </c>
-      <c r="J46" s="29" t="n">
-        <v>0</v>
+      <c r="I46" s="30" t="n">
+        <v>36009</v>
+      </c>
+      <c r="J46" s="30" t="n">
+        <v>-2801</v>
       </c>
     </row>
     <row r="47">
@@ -1848,34 +1873,34 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D47" s="27" t="n">
-        <v>-1526</v>
-      </c>
-      <c r="E47" s="27" t="n">
-        <v>-657</v>
-      </c>
-      <c r="F47" s="27" t="n">
-        <v>-870</v>
-      </c>
-      <c r="G47" s="28" t="n">
-        <v>1555</v>
-      </c>
-      <c r="H47" s="29" t="n">
+      <c r="D47" s="28" t="n">
+        <v>-1568</v>
+      </c>
+      <c r="E47" s="28" t="n">
+        <v>-695</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>-873</v>
+      </c>
+      <c r="G47" s="29" t="n">
+        <v>1591</v>
+      </c>
+      <c r="H47" s="30" t="n">
         <v>284</v>
       </c>
-      <c r="I47" s="29" t="n">
-        <v>13527.9</v>
-      </c>
-      <c r="J47" s="29" t="n">
-        <v>0</v>
+      <c r="I47" s="30" t="n">
+        <v>13231</v>
+      </c>
+      <c r="J47" s="30" t="n">
+        <v>-296.9</v>
       </c>
     </row>
     <row r="48">
@@ -1884,34 +1909,34 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="D48" s="27" t="n">
-        <v>-944</v>
-      </c>
-      <c r="E48" s="27" t="n">
-        <v>-113</v>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>-831</v>
-      </c>
-      <c r="G48" s="28" t="n">
-        <v>942</v>
-      </c>
-      <c r="H48" s="29" t="n">
+      <c r="D48" s="28" t="n">
+        <v>-968</v>
+      </c>
+      <c r="E48" s="28" t="n">
+        <v>-135</v>
+      </c>
+      <c r="F48" s="28" t="n">
+        <v>-833</v>
+      </c>
+      <c r="G48" s="29" t="n">
+        <v>966</v>
+      </c>
+      <c r="H48" s="30" t="n">
         <v>96.5</v>
       </c>
-      <c r="I48" s="29" t="n">
-        <v>8359.200000000001</v>
-      </c>
-      <c r="J48" s="29" t="n">
-        <v>0</v>
+      <c r="I48" s="30" t="n">
+        <v>8138.3</v>
+      </c>
+      <c r="J48" s="30" t="n">
+        <v>-220.9</v>
       </c>
     </row>
     <row r="49">
@@ -1920,70 +1945,70 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="29" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="D49" s="27" t="n">
-        <v>-751</v>
-      </c>
-      <c r="E49" s="27" t="n">
-        <v>-528</v>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>-223</v>
-      </c>
-      <c r="G49" s="28" t="n">
-        <v>564</v>
-      </c>
-      <c r="H49" s="29" t="n">
+      <c r="D49" s="28" t="n">
+        <v>-783</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>-551</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>-232</v>
+      </c>
+      <c r="G49" s="29" t="n">
+        <v>626</v>
+      </c>
+      <c r="H49" s="30" t="n">
         <v>125.5</v>
       </c>
-      <c r="I49" s="29" t="n">
-        <v>12830.3</v>
-      </c>
-      <c r="J49" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="I49" s="30" t="n">
+        <v>12546.7</v>
+      </c>
+      <c r="J49" s="30" t="n">
+        <v>-283.6</v>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1" s="15">
       <c r="A50" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="29" t="inlineStr">
-        <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="D50" s="27" t="n">
-        <v>-588</v>
-      </c>
-      <c r="E50" s="27" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>-585</v>
-      </c>
-      <c r="G50" s="28" t="n">
-        <v>590</v>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>14894.9</v>
-      </c>
-      <c r="J50" s="29" t="n">
-        <v>0</v>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>-679</v>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>-292</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>-386</v>
+      </c>
+      <c r="G50" s="29" t="n">
+        <v>764</v>
+      </c>
+      <c r="H50" s="30" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="I50" s="30" t="n">
+        <v>31440</v>
+      </c>
+      <c r="J50" s="30" t="n">
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="51">
@@ -1992,70 +2017,70 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션</t>
-        </is>
-      </c>
-      <c r="D51" s="27" t="n">
-        <v>-572</v>
-      </c>
-      <c r="E51" s="27" t="n">
-        <v>-204</v>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>-368</v>
-      </c>
-      <c r="G51" s="28" t="n">
-        <v>658</v>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>419.2</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>32626.9</v>
-      </c>
-      <c r="J51" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>-629</v>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>-46</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>-583</v>
+      </c>
+      <c r="G51" s="29" t="n">
+        <v>634</v>
+      </c>
+      <c r="H51" s="30" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="I51" s="30" t="n">
+        <v>14504.2</v>
+      </c>
+      <c r="J51" s="30" t="n">
+        <v>-390.7</v>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1" s="15">
       <c r="A52" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B52" s="29" t="n">
+      <c r="B52" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
-        </is>
-      </c>
-      <c r="D52" s="27" t="n">
-        <v>-535</v>
-      </c>
-      <c r="E52" s="27" t="n">
-        <v>-555</v>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="n">
+        <v>-593</v>
+      </c>
+      <c r="E52" s="28" t="n">
+        <v>-468</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="G52" s="28" t="n">
-        <v>537</v>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>12094.3</v>
-      </c>
-      <c r="J52" s="29" t="n">
-        <v>0</v>
+        <v>-125</v>
+      </c>
+      <c r="G52" s="29" t="n">
+        <v>588</v>
+      </c>
+      <c r="H52" s="30" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="I52" s="30" t="n">
+        <v>6895.6</v>
+      </c>
+      <c r="J52" s="30" t="n">
+        <v>-292.3</v>
       </c>
     </row>
     <row r="53">
@@ -2064,70 +2089,70 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n">
+      <c r="B53" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="D53" s="27" t="n">
-        <v>-530</v>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="n">
+        <v>-582</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>108</v>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>-638</v>
-      </c>
-      <c r="G53" s="28" t="n">
-        <v>575</v>
-      </c>
-      <c r="H53" s="29" t="n">
-        <v>314.6</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>14493.4</v>
-      </c>
-      <c r="J53" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>-195</v>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>-386</v>
+      </c>
+      <c r="G53" s="29" t="n">
+        <v>571</v>
+      </c>
+      <c r="H53" s="30" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="I53" s="30" t="n">
+        <v>9333.9</v>
+      </c>
+      <c r="J53" s="30" t="n">
+        <v>-1092.4</v>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1" s="15">
       <c r="A54" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="B54" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>레인보우로보틱스</t>
-        </is>
-      </c>
-      <c r="D54" s="27" t="n">
-        <v>-503</v>
-      </c>
-      <c r="E54" s="27" t="n">
-        <v>-385</v>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>-118</v>
-      </c>
-      <c r="G54" s="28" t="n">
-        <v>494</v>
-      </c>
-      <c r="H54" s="29" t="n">
-        <v>222.6</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>7187.9</v>
-      </c>
-      <c r="J54" s="29" t="n">
-        <v>0</v>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>-524</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>-559</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="G54" s="29" t="n">
+        <v>528</v>
+      </c>
+      <c r="H54" s="30" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="I54" s="30" t="n">
+        <v>11659.9</v>
+      </c>
+      <c r="J54" s="30" t="n">
+        <v>-434.4</v>
       </c>
     </row>
     <row r="55">
@@ -2136,34 +2161,34 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>OCI홀딩스</t>
-        </is>
-      </c>
-      <c r="D55" s="27" t="n">
-        <v>-465</v>
-      </c>
-      <c r="E55" s="27" t="n">
-        <v>-29</v>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>-436</v>
-      </c>
-      <c r="G55" s="28" t="n">
-        <v>497</v>
-      </c>
-      <c r="H55" s="29" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="I55" s="29" t="n">
-        <v>3613.5</v>
-      </c>
-      <c r="J55" s="29" t="n">
-        <v>0</v>
+      <c r="C55" s="30" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>-511</v>
+      </c>
+      <c r="E55" s="29" t="n">
+        <v>132</v>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G55" s="29" t="n">
+        <v>559</v>
+      </c>
+      <c r="H55" s="30" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="I55" s="30" t="n">
+        <v>13946.5</v>
+      </c>
+      <c r="J55" s="30" t="n">
+        <v>-546.9</v>
       </c>
     </row>
     <row r="56"/>
@@ -2210,14 +2235,14 @@
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 43,839억 원으로 수급 집중도가 가장 높음.</t>
+          <t>주가 상승에도 대차잔고가 2,044.8억 감소하며 숏커버링 여지 확인됨.</t>
         </is>
       </c>
     </row>
@@ -2227,14 +2252,14 @@
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 28,819억 원으로 AI 메모리 모멘텀 지속.</t>
+          <t>기관 순매수 2,220억이 집중되었으며 원전 수주 기대감이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -2244,14 +2269,14 @@
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 -1,900억 원으로 수급 이탈이 뚜렷함.</t>
+          <t>주간 순매도 -3,070억을 기록하며 수급 이탈이 관찰됨.</t>
         </is>
       </c>
     </row>
@@ -2261,14 +2286,14 @@
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 -1,526억 원으로 수급 약세 지속.</t>
+          <t>주가 급등에 따른 대차잔고 482.9억 증가로 하방 압력 관찰됨.</t>
         </is>
       </c>
     </row>
@@ -2308,28 +2333,28 @@
     <row r="66" ht="15" customHeight="1" s="15">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>- AI 반도체 중심의 강력한 외국인·기관 매수세가 유입되며 주초 시장 급등을 견인함.</t>
+          <t>- 주초 외국인과 기관의 강력한 동반 매수세로 KOSPI가 4.61% 급등하며 Risk-On 국면을 연출함.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한함.</t>
+          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장 상단을 제한함.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="15">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>- 국내 2분기 GDP 성장률(0.6%)이 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
+          <t>- 주 후반 국내 2분기 GDP 성장률이 0.6%로 둔화하며 경기 우려가 부각됨.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- 개인의 대규모 차익 실현 매도세가 지수 하락 압력으로 작용하며 변동성이 확대됨.</t>
+          <t>- 반도체 섹터는 미국 모멘텀을 이어받았으나, 금리 인상 우려와 밸류에이션 부담으로 지수 변동성이 확대됨.</t>
         </is>
       </c>
     </row>
@@ -2357,21 +2382,21 @@
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 및 기계·장비 섹터가 AI 반도체와 원전 모멘텀을 바탕으로 시장 상승을 주도함.</t>
+          <t>- 전기·전자 및 기계·장비 섹터가 반도체와 원전 모멘텀을 바탕으로 주간 상승률 상위를 기록함.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>- 건설 섹터는 대형 원전 건설 협의 기대감으로 주간 7.86% 상승하며 강세를 지속함.</t>
+          <t>- 건설 및 전기·가스 섹터는 대형 원전 수주 기대감으로 주 후반 강세를 보임.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="15">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>- 음식료·담배 및 IT 서비스 섹터는 차익 실현 매물 출회로 약세 전환함.</t>
+          <t>- IT 서비스 및 음식료·담배 섹터는 차익 실현 매물과 경기 둔화 우려로 약세를 보임.</t>
         </is>
       </c>
     </row>
@@ -2400,38 +2425,38 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="15">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr"/>
+      <c r="C77" s="30" t="inlineStr"/>
       <c r="D77" s="14" t="inlineStr"/>
-      <c r="E77" s="28" t="inlineStr"/>
+      <c r="E77" s="29" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
+          <t>외국인·기관 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
         </is>
       </c>
     </row>
     <row r="78" ht="31" customHeight="1" s="15">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>네오오토</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2441,7 +2466,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E78" s="28" t="n">
+      <c r="E78" s="29" t="n">
         <v>40.59</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -2451,17 +2476,17 @@
       </c>
     </row>
     <row r="79" ht="31" customHeight="1" s="15">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" s="30" t="inlineStr">
         <is>
           <t>필옵틱스</t>
         </is>
       </c>
-      <c r="C79" s="29" t="inlineStr">
+      <c r="C79" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2471,7 +2496,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E79" s="28" t="n">
+      <c r="E79" s="29" t="n">
         <v>37.21</v>
       </c>
       <c r="F79" s="17" t="inlineStr">
@@ -2481,17 +2506,17 @@
       </c>
     </row>
     <row r="80" ht="31" customHeight="1" s="15">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>나무가</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2501,7 +2526,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E80" s="28" t="n">
+      <c r="E80" s="29" t="n">
         <v>10.23</v>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -2511,17 +2536,17 @@
       </c>
     </row>
     <row r="81" ht="31" customHeight="1" s="15">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" s="30" t="inlineStr">
         <is>
           <t>두산퓨얼셀</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
+      <c r="C81" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2531,7 +2556,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E81" s="28" t="n">
+      <c r="E81" s="29" t="n">
         <v>12.31</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
@@ -2541,17 +2566,17 @@
       </c>
     </row>
     <row r="82" ht="31" customHeight="1" s="15">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2561,7 +2586,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E82" s="28" t="n">
+      <c r="E82" s="29" t="n">
         <v>15.02</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -2571,17 +2596,17 @@
       </c>
     </row>
     <row r="83" ht="31" customHeight="1" s="15">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
+      <c r="C83" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2591,7 +2616,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E83" s="28" t="n">
+      <c r="E83" s="29" t="n">
         <v>13.01</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
@@ -2601,17 +2626,17 @@
       </c>
     </row>
     <row r="84" ht="31" customHeight="1" s="15">
-      <c r="A84" s="29" t="inlineStr">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
+      <c r="C84" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2621,7 +2646,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E84" s="28" t="n">
+      <c r="E84" s="29" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -2631,17 +2656,17 @@
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" s="15">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" s="30" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C85" s="29" t="inlineStr">
+      <c r="C85" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2651,7 +2676,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E85" s="28" t="n">
+      <c r="E85" s="29" t="n">
         <v>5.48</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
@@ -2661,37 +2686,37 @@
       </c>
     </row>
     <row r="86" ht="31" customHeight="1" s="15">
-      <c r="A86" s="29" t="inlineStr">
+      <c r="A86" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr"/>
+      <c r="C86" s="30" t="inlineStr"/>
       <c r="D86" s="14" t="inlineStr"/>
-      <c r="E86" s="28" t="inlineStr"/>
+      <c r="E86" s="29" t="inlineStr"/>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>2분기 GDP 성장률 0.6% 발표 및 경기 둔화 우려 부각으로 KOSPI 0.58% 하락.</t>
+          <t>국내 2분기 GDP 성장률 0.6% 발표 및 금리 인상 우려로 KOSPI 0.58% 하락</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" s="30" t="inlineStr">
         <is>
           <t>빛과전자</t>
         </is>
       </c>
-      <c r="C87" s="29" t="inlineStr">
+      <c r="C87" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2701,7 +2726,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E87" s="28" t="n">
+      <c r="E87" s="29" t="n">
         <v>34.07</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
@@ -2711,17 +2736,17 @@
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="15">
-      <c r="A88" s="29" t="inlineStr">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="B88" s="30" t="inlineStr">
         <is>
           <t>오르비텍</t>
         </is>
       </c>
-      <c r="C88" s="29" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2731,7 +2756,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E88" s="28" t="n">
+      <c r="E88" s="29" t="n">
         <v>39.88</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -2741,17 +2766,17 @@
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" s="15">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <t>서전기전</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
@@ -2761,7 +2786,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E89" s="28" t="n">
+      <c r="E89" s="29" t="n">
         <v>37.07</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
@@ -2771,17 +2796,17 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" s="29" t="inlineStr">
+      <c r="A90" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
         <is>
           <t>한전기술</t>
         </is>
       </c>
-      <c r="C90" s="29" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2791,7 +2816,7 @@
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E90" s="28" t="n">
+      <c r="E90" s="29" t="n">
         <v>32.53</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -2801,17 +2826,17 @@
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="A91" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B91" s="30" t="inlineStr">
         <is>
           <t>현대약품</t>
         </is>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2821,7 +2846,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E91" s="28" t="n">
+      <c r="E91" s="29" t="n">
         <v>31.32</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -2831,17 +2856,17 @@
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="15">
-      <c r="A92" s="29" t="inlineStr">
+      <c r="A92" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B92" s="30" t="inlineStr">
         <is>
           <t>대우건설</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
@@ -2851,7 +2876,7 @@
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E92" s="28" t="n">
+      <c r="E92" s="29" t="n">
         <v>18.52</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -2893,62 +2918,75 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="15">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="96" ht="31" customHeight="1" s="15">
+      <c r="A96" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="15">
-      <c r="A97" s="10" t="inlineStr">
+          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="31" customHeight="1" s="15">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>상승 시나리오</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 압력이 지속될 경우, 경기 방어주 및 원전 관련주로의 수급 로테이션이 강화될 것임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="31" customHeight="1" s="15">
+      <c r="A98" s="32" t="inlineStr">
         <is>
           <t>하방 시나리오</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>물가 지표가 예상치를 상회하여 국채 금리가 추가 상승하면 경기 둔화 우려가 부각되며 지수 조정이 심화될 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="15">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>판별 신호</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>판별 신호: 9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 증감률.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="31" customHeight="1" s="15">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>판별 신호: 미국 생산자물가지수(PPI) 및 소비자물가지수(CPI)의 전월 대비 등락폭.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="15">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>핵심 이벤트: 9월 10일 미국 생산자물가지수(PPI), 9월 11일 미국 소비자물가지수(CPI), 9월 15일 국내 무역수지.</t>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>핵심 이벤트: 9월 10일 미국 PPI, 9월 11일 미국 CPI, 9월 15일 국내 무역수지.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="47">
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="F78:J78"/>
     <mergeCell ref="B98:J98"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="F87:J87"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C62:J62"/>
     <mergeCell ref="C58:J58"/>
     <mergeCell ref="G25:J25"/>
@@ -2978,6 +3016,8 @@
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="B97:J97"/>
     <mergeCell ref="C61:J61"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="B100:J100"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="F92:J92"/>
@@ -2998,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -3030,7 +3070,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:46 KST</t>
+          <t>2026-09-08 20:57 KST</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3082,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI 반도체 주도 랠리와 경기 둔화 우려의 교차</t>
+          <t>반도체 주도 랠리와 금리 인상 우려 사이의 변동성 장세</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3306,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 및 대형주로 이어지며, 미국 지수 약세에도 불구하고 외국인과 기관의 강력한 매수세를 유도함.</t>
+          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3321,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시켰고, 국내 GDP 성장률 둔화와 맞물려 지수 하락을 견인함.</t>
+          <t>미국 국채금리 급등과 UBS의 금리 인상 전망 제기로 인한 투자 심리 위축이 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3341,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>매크로 환경: 미국 비농업 고용지수(162K)가 예상치(55K)를 상회하며 금리 인하 경로 불확실성이 커졌고, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 신호가 뚜렷함.</t>
+          <t>미국 비농업 고용지표(162K)가 예상치를 상회하고 국내 2분기 GDP(0.6%)가 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 커짐.</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3353,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으나, 개인은 전 섹터에서 매도 우위를 보이며 차익 실현에 집중함.</t>
+          <t>수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수가 집중되었으나, 개인은 전반적인 차익 실현 매도를 지속함.</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3365,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>종합 관점: AI 반도체 모멘텀이 시장을 견인했으나, 매크로 불확실성과 경기 둔화 우려가 상존하며 수급 쏠림 현상이 심화된 한 주였음.</t>
+          <t>반도체 중심의 수급 쏠림이 뚜렷한 가운데, 금리 인상 우려와 경기 둔화 신호가 맞물리며 지수 상단이 제한되는 흐름을 보임.</t>
         </is>
       </c>
     </row>
@@ -3351,25 +3391,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>43839</v>
+        <v>45121</v>
       </c>
       <c r="E31" t="n">
-        <v>20501</v>
+        <v>21100</v>
       </c>
       <c r="F31" t="n">
-        <v>23338</v>
+        <v>24020</v>
       </c>
       <c r="G31" t="n">
-        <v>-53897</v>
+        <v>-55192</v>
       </c>
       <c r="H31" t="n">
         <v>1816.7</v>
       </c>
       <c r="I31" t="n">
-        <v>247447.2</v>
+        <v>240284.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-7162.4</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="15">
@@ -3387,25 +3427,25 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28819</v>
+        <v>29092</v>
       </c>
       <c r="E32" t="n">
-        <v>19070</v>
+        <v>19197</v>
       </c>
       <c r="F32" t="n">
-        <v>9749</v>
+        <v>9895</v>
       </c>
       <c r="G32" t="n">
-        <v>-51831</v>
+        <v>-52130</v>
       </c>
       <c r="H32" t="n">
         <v>3364.2</v>
       </c>
       <c r="I32" t="n">
-        <v>225804.3</v>
+        <v>223759.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-2044.8</v>
       </c>
     </row>
     <row r="33">
@@ -3423,25 +3463,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5236</v>
+        <v>5294</v>
       </c>
       <c r="E33" t="n">
-        <v>3060</v>
+        <v>3070</v>
       </c>
       <c r="F33" t="n">
-        <v>2175</v>
+        <v>2223</v>
       </c>
       <c r="G33" t="n">
-        <v>-5105</v>
+        <v>-5184</v>
       </c>
       <c r="H33" t="n">
         <v>365.7</v>
       </c>
       <c r="I33" t="n">
-        <v>32812</v>
+        <v>32891.8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="15">
@@ -3474,10 +3514,10 @@
         <v>206.2</v>
       </c>
       <c r="I34" t="n">
-        <v>29143.8</v>
+        <v>28477.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-666.1</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="15">
@@ -3495,25 +3535,25 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2266</v>
+        <v>2138</v>
       </c>
       <c r="E35" t="n">
-        <v>58</v>
+        <v>-81</v>
       </c>
       <c r="F35" t="n">
-        <v>2208</v>
+        <v>2220</v>
       </c>
       <c r="G35" t="n">
-        <v>-2304</v>
+        <v>-2125</v>
       </c>
       <c r="H35" t="n">
         <v>900.5</v>
       </c>
       <c r="I35" t="n">
-        <v>19475.5</v>
+        <v>19469.6</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="15">
@@ -3531,25 +3571,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1369</v>
+        <v>1581</v>
       </c>
       <c r="E36" t="n">
-        <v>816</v>
+        <v>1000</v>
       </c>
       <c r="F36" t="n">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="G36" t="n">
-        <v>-1351</v>
+        <v>-1560</v>
       </c>
       <c r="H36" t="n">
         <v>485.3</v>
       </c>
       <c r="I36" t="n">
-        <v>44346.7</v>
+        <v>43511.4</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-835.3</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="15">
@@ -3567,25 +3607,25 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1309</v>
+        <v>1182</v>
       </c>
       <c r="E37" t="n">
-        <v>765</v>
+        <v>640</v>
       </c>
       <c r="F37" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G37" t="n">
-        <v>-1290</v>
+        <v>-1175</v>
       </c>
       <c r="H37" t="n">
         <v>422.1</v>
       </c>
       <c r="I37" t="n">
-        <v>10675.8</v>
+        <v>10178.7</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-497.1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="15">
@@ -3603,25 +3643,25 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="E38" t="n">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="F38" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G38" t="n">
-        <v>-880</v>
+        <v>-863</v>
       </c>
       <c r="H38" t="n">
         <v>144</v>
       </c>
       <c r="I38" t="n">
-        <v>6126.4</v>
+        <v>5502.2</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-624.2</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
@@ -3654,10 +3694,10 @@
         <v>164.4</v>
       </c>
       <c r="I39" t="n">
-        <v>5739.7</v>
+        <v>6222.6</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>482.9</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="15">
@@ -3675,25 +3715,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>720</v>
+        <v>754</v>
       </c>
       <c r="E40" t="n">
-        <v>-287</v>
+        <v>-258</v>
       </c>
       <c r="F40" t="n">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="G40" t="n">
-        <v>-724</v>
+        <v>-760</v>
       </c>
       <c r="H40" t="n">
         <v>292.4</v>
       </c>
       <c r="I40" t="n">
-        <v>8468.6</v>
+        <v>8765.6</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="15">
@@ -3711,25 +3751,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1900</v>
+        <v>-3070</v>
       </c>
       <c r="E41" t="n">
-        <v>-1420</v>
+        <v>-2520</v>
       </c>
       <c r="F41" t="n">
-        <v>-480</v>
+        <v>-550</v>
       </c>
       <c r="G41" t="n">
-        <v>1869</v>
+        <v>3076</v>
       </c>
       <c r="H41" t="n">
         <v>686.4</v>
       </c>
       <c r="I41" t="n">
-        <v>38810</v>
+        <v>36009</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-2801</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
@@ -3747,25 +3787,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1526</v>
+        <v>-1568</v>
       </c>
       <c r="E42" t="n">
-        <v>-657</v>
+        <v>-695</v>
       </c>
       <c r="F42" t="n">
-        <v>-870</v>
+        <v>-873</v>
       </c>
       <c r="G42" t="n">
-        <v>1555</v>
+        <v>1591</v>
       </c>
       <c r="H42" t="n">
         <v>284</v>
       </c>
       <c r="I42" t="n">
-        <v>13527.9</v>
+        <v>13231</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
@@ -3783,25 +3823,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-944</v>
+        <v>-968</v>
       </c>
       <c r="E43" t="n">
-        <v>-113</v>
+        <v>-135</v>
       </c>
       <c r="F43" t="n">
-        <v>-831</v>
+        <v>-833</v>
       </c>
       <c r="G43" t="n">
-        <v>942</v>
+        <v>966</v>
       </c>
       <c r="H43" t="n">
         <v>96.5</v>
       </c>
       <c r="I43" t="n">
-        <v>8359.200000000001</v>
+        <v>8138.3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
@@ -3819,25 +3859,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-751</v>
+        <v>-783</v>
       </c>
       <c r="E44" t="n">
-        <v>-528</v>
+        <v>-551</v>
       </c>
       <c r="F44" t="n">
-        <v>-223</v>
+        <v>-232</v>
       </c>
       <c r="G44" t="n">
-        <v>564</v>
+        <v>626</v>
       </c>
       <c r="H44" t="n">
         <v>125.5</v>
       </c>
       <c r="I44" t="n">
-        <v>12830.3</v>
+        <v>12546.7</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-283.6</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
@@ -3851,29 +3891,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-588</v>
+        <v>-679</v>
       </c>
       <c r="E45" t="n">
-        <v>-3</v>
+        <v>-292</v>
       </c>
       <c r="F45" t="n">
-        <v>-585</v>
+        <v>-386</v>
       </c>
       <c r="G45" t="n">
-        <v>590</v>
+        <v>764</v>
       </c>
       <c r="H45" t="n">
-        <v>133.3</v>
+        <v>419.2</v>
       </c>
       <c r="I45" t="n">
-        <v>14894.9</v>
+        <v>31440</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
@@ -3887,29 +3927,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-572</v>
+        <v>-629</v>
       </c>
       <c r="E46" t="n">
-        <v>-204</v>
+        <v>-46</v>
       </c>
       <c r="F46" t="n">
-        <v>-368</v>
+        <v>-583</v>
       </c>
       <c r="G46" t="n">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="H46" t="n">
-        <v>419.2</v>
+        <v>133.3</v>
       </c>
       <c r="I46" t="n">
-        <v>32626.9</v>
+        <v>14504.2</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-390.7</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
@@ -3923,29 +3963,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-535</v>
+        <v>-593</v>
       </c>
       <c r="E47" t="n">
-        <v>-555</v>
+        <v>-468</v>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>-125</v>
       </c>
       <c r="G47" t="n">
-        <v>537</v>
+        <v>588</v>
       </c>
       <c r="H47" t="n">
-        <v>146.9</v>
+        <v>222.6</v>
       </c>
       <c r="I47" t="n">
-        <v>12094.3</v>
+        <v>6895.6</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
@@ -3959,29 +3999,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-530</v>
+        <v>-582</v>
       </c>
       <c r="E48" t="n">
-        <v>108</v>
+        <v>-195</v>
       </c>
       <c r="F48" t="n">
-        <v>-638</v>
+        <v>-386</v>
       </c>
       <c r="G48" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H48" t="n">
-        <v>314.6</v>
+        <v>563.7</v>
       </c>
       <c r="I48" t="n">
-        <v>14493.4</v>
+        <v>9333.9</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-1092.4</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="15">
@@ -3995,29 +4035,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-503</v>
+        <v>-524</v>
       </c>
       <c r="E49" t="n">
-        <v>-385</v>
+        <v>-559</v>
       </c>
       <c r="F49" t="n">
-        <v>-118</v>
+        <v>35</v>
       </c>
       <c r="G49" t="n">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="H49" t="n">
-        <v>222.6</v>
+        <v>146.9</v>
       </c>
       <c r="I49" t="n">
-        <v>7187.9</v>
+        <v>11659.9</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="15">
@@ -4031,29 +4071,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-465</v>
+        <v>-511</v>
       </c>
       <c r="E50" t="n">
-        <v>-29</v>
+        <v>132</v>
       </c>
       <c r="F50" t="n">
-        <v>-436</v>
+        <v>-643</v>
       </c>
       <c r="G50" t="n">
-        <v>497</v>
+        <v>559</v>
       </c>
       <c r="H50" t="n">
-        <v>37.7</v>
+        <v>314.6</v>
       </c>
       <c r="I50" t="n">
-        <v>3613.5</v>
+        <v>13946.5</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
@@ -4071,12 +4111,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>주간 순매수 43,839억 원으로 수급 집중도가 가장 높음.</t>
+          <t>주가 상승에도 대차잔고가 2,044.8억 감소하며 숏커버링 여지 확인됨.</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4128,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>주간 순매수 28,819억 원으로 AI 메모리 모멘텀 지속.</t>
+          <t>기관 순매수 2,220억이 집중되었으며 원전 수주 기대감이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4150,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>주간 순매수 -1,900억 원으로 수급 이탈이 뚜렷함.</t>
+          <t>주간 순매도 -3,070억을 기록하며 수급 이탈이 관찰됨.</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4162,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 순매수 -1,526억 원으로 수급 약세 지속.</t>
+          <t>주가 급등에 따른 대차잔고 482.9억 증가로 하방 압력 관찰됨.</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4186,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AI 반도체 중심의 강력한 외국인·기관 매수세가 유입되며 주초 시장 급등을 견인함.</t>
+          <t>주초 외국인과 기관의 강력한 동반 매수세로 KOSPI가 4.61% 급등하며 Risk-On 국면을 연출함.</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4198,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한함.</t>
+          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장 상단을 제한함.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4210,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률(0.6%)이 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
+          <t>주 후반 국내 2분기 GDP 성장률이 0.6%로 둔화하며 경기 우려가 부각됨.</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4222,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>개인의 대규모 차익 실현 매도세가 지수 하락 압력으로 작용하며 변동성이 확대됨.</t>
+          <t>반도체 섹터는 미국 모멘텀을 이어받았으나, 금리 인상 우려와 밸류에이션 부담으로 지수 변동성이 확대됨.</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4241,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전기·전자 및 기계·장비 섹터가 AI 반도체와 원전 모멘텀을 바탕으로 시장 상승을 주도함.</t>
+          <t>전기·전자 및 기계·장비 섹터가 반도체와 원전 모멘텀을 바탕으로 주간 상승률 상위를 기록함.</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4253,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>건설 섹터는 대형 원전 건설 협의 기대감으로 주간 7.86% 상승하며 강세를 지속함.</t>
+          <t>건설 및 전기·가스 섹터는 대형 원전 수주 기대감으로 주 후반 강세를 보임.</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4265,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>음식료·담배 및 IT 서비스 섹터는 차익 실현 매물 출회로 약세 전환함.</t>
+          <t>IT 서비스 및 음식료·담배 섹터는 차익 실현 매물과 경기 둔화 우려로 약세를 보임.</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4289,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
+          <t>외국인·기관 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4530,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2분기 GDP 성장률 0.6% 발표 및 경기 둔화 우려 부각으로 KOSPI 0.58% 하락.</t>
+          <t>국내 2분기 GDP 성장률 0.6% 발표 및 금리 인상 우려로 KOSPI 0.58% 하락</t>
         </is>
       </c>
     </row>
@@ -4677,47 +4717,58 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것.</t>
+          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것임.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>물가 지표가 예상치를 상회하여 국채 금리가 추가 상승하면 경기 둔화 우려가 부각되며 지수 조정이 심화될 것.</t>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 압력이 지속될 경우, 경기 방어주 및 원전 관련주로의 수급 로테이션이 강화될 것임.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>판별 신호: 9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 증감률.</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
+          <t>판별 신호</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>판별 신호: 미국 생산자물가지수(PPI) 및 소비자물가지수(CPI)의 전월 대비 등락폭.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="15">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>핵심 이벤트: 9월 10일 미국 생산자물가지수(PPI), 9월 11일 미국 소비자물가지수(CPI), 9월 15일 국내 무역수지.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="15"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>핵심 이벤트: 9월 10일 미국 PPI, 9월 11일 미국 CPI, 9월 15일 국내 무역수지.</t>
+        </is>
+      </c>
+    </row>
     <row r="88" ht="15" customHeight="1" s="15"/>
     <row r="89" ht="15" customHeight="1" s="15"/>
     <row r="90" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-08 20:57 KST</t>
+          <t>2026-09-08 21:31 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체 주도 랠리와 금리 인상 우려 사이의 변동성 장세</t>
+          <t>반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
+          <t>미국 반도체 지수 급등과 마이크론 강세가 국내 반도체 대형주로 이어지며 외국인·기관의 대규모 매수세와 함께 KOSPI 4.61% 급등을 견인함.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 UBS의 금리 인상 전망 제기로 인한 투자 심리 위축이 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
+          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 둔화까지 겹쳐 지수가 0.58% 하락함.</t>
         </is>
       </c>
     </row>
@@ -1376,21 +1376,21 @@
     <row r="30" ht="31" customHeight="1" s="15">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>- 미국 비농업 고용지표(162K)가 예상치를 상회하고 국내 2분기 GDP(0.6%)가 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 커짐.</t>
+          <t>- 미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회해 금리 인하 경로의 불확실성이 커졌고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경을 압박함.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="15">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수가 집중되었으나, 개인은 전반적인 차익 실현 매도를 지속함.</t>
+          <t>- 수급 측면에서 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주간 5.93% 상승했고, 기계·장비 섹터 역시 기관(2,736억) 매수와 함께 7.43% 상승하며 주도 섹터로 자리매김함.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="15">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 중심의 수급 쏠림이 뚜렷한 가운데, 금리 인상 우려와 경기 둔화 신호가 맞물리며 지수 상단이 제한되는 흐름을 보임.</t>
+          <t>- 매크로 지표의 둔화 신호에도 불구하고 반도체와 원전 등 특정 섹터로의 수급 쏠림이 뚜렷해, 향후 지수 방향성은 매크로 데이터의 추가 확인과 주도 섹터의 수급 연속성에 좌우될 전망임.</t>
         </is>
       </c>
     </row>
@@ -1842,29 +1842,29 @@
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D46" s="28" t="n">
-        <v>-3070</v>
+        <v>-1568</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>-2520</v>
+        <v>-695</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>-550</v>
+        <v>-873</v>
       </c>
       <c r="G46" s="29" t="n">
-        <v>3076</v>
+        <v>1591</v>
       </c>
       <c r="H46" s="30" t="n">
-        <v>686.4</v>
+        <v>284</v>
       </c>
       <c r="I46" s="30" t="n">
-        <v>36009</v>
+        <v>13231</v>
       </c>
       <c r="J46" s="30" t="n">
-        <v>-2801</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="47">
@@ -1878,29 +1878,29 @@
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="D47" s="28" t="n">
-        <v>-1568</v>
+        <v>-968</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>-695</v>
+        <v>-135</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>-873</v>
+        <v>-833</v>
       </c>
       <c r="G47" s="29" t="n">
-        <v>1591</v>
+        <v>966</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>284</v>
+        <v>96.5</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>13231</v>
+        <v>8138.3</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>-296.9</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="48">
@@ -1914,32 +1914,32 @@
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D48" s="28" t="n">
-        <v>-968</v>
+        <v>-783</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>-135</v>
+        <v>-551</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>-833</v>
+        <v>-232</v>
       </c>
       <c r="G48" s="29" t="n">
-        <v>966</v>
+        <v>626</v>
       </c>
       <c r="H48" s="30" t="n">
-        <v>96.5</v>
+        <v>125.5</v>
       </c>
       <c r="I48" s="30" t="n">
-        <v>8138.3</v>
+        <v>12546.7</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>-220.9</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>-283.6</v>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1" s="15">
       <c r="A49" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -1948,34 +1948,34 @@
       <c r="B49" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="30" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D49" s="28" t="n">
-        <v>-783</v>
+        <v>-679</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>-551</v>
+        <v>-292</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>-232</v>
+        <v>-386</v>
       </c>
       <c r="G49" s="29" t="n">
-        <v>626</v>
+        <v>764</v>
       </c>
       <c r="H49" s="30" t="n">
-        <v>125.5</v>
+        <v>419.2</v>
       </c>
       <c r="I49" s="30" t="n">
-        <v>12546.7</v>
+        <v>31440</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>-283.6</v>
-      </c>
-    </row>
-    <row r="50" ht="31" customHeight="1" s="15">
+        <v>-1186.9</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -1984,34 +1984,34 @@
       <c r="B50" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션</t>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>-679</v>
+        <v>-629</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>-292</v>
+        <v>-46</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>-386</v>
+        <v>-583</v>
       </c>
       <c r="G50" s="29" t="n">
-        <v>764</v>
+        <v>634</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>419.2</v>
+        <v>133.3</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>31440</v>
+        <v>14504.2</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>-1186.9</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>-390.7</v>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1" s="15">
       <c r="A51" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2020,34 +2020,34 @@
       <c r="B51" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C51" s="30" t="inlineStr">
-        <is>
-          <t>에이피알</t>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>-629</v>
+        <v>-593</v>
       </c>
       <c r="E51" s="28" t="n">
-        <v>-46</v>
+        <v>-468</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>-583</v>
+        <v>-125</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>634</v>
+        <v>588</v>
       </c>
       <c r="H51" s="30" t="n">
-        <v>133.3</v>
+        <v>222.6</v>
       </c>
       <c r="I51" s="30" t="n">
-        <v>14504.2</v>
+        <v>6895.6</v>
       </c>
       <c r="J51" s="30" t="n">
-        <v>-390.7</v>
-      </c>
-    </row>
-    <row r="52" ht="31" customHeight="1" s="15">
+        <v>-292.3</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2056,34 +2056,34 @@
       <c r="B52" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>레인보우로보틱스</t>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D52" s="28" t="n">
-        <v>-593</v>
+        <v>-582</v>
       </c>
       <c r="E52" s="28" t="n">
-        <v>-468</v>
+        <v>-195</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>-125</v>
+        <v>-386</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="H52" s="30" t="n">
-        <v>222.6</v>
+        <v>563.7</v>
       </c>
       <c r="I52" s="30" t="n">
-        <v>6895.6</v>
+        <v>9333.9</v>
       </c>
       <c r="J52" s="30" t="n">
-        <v>-292.3</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>-1092.4</v>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1" s="15">
       <c r="A53" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2092,34 +2092,34 @@
       <c r="B53" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C53" s="30" t="inlineStr">
-        <is>
-          <t>LG이노텍</t>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-582</v>
+        <v>-524</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>-195</v>
-      </c>
-      <c r="F53" s="28" t="n">
-        <v>-386</v>
+        <v>-559</v>
+      </c>
+      <c r="F53" s="29" t="n">
+        <v>35</v>
       </c>
       <c r="G53" s="29" t="n">
-        <v>571</v>
+        <v>528</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>563.7</v>
+        <v>146.9</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>9333.9</v>
+        <v>11659.9</v>
       </c>
       <c r="J53" s="30" t="n">
-        <v>-1092.4</v>
-      </c>
-    </row>
-    <row r="54" ht="31" customHeight="1" s="15">
+        <v>-434.4</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2128,31 +2128,31 @@
       <c r="B54" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D54" s="28" t="n">
-        <v>-524</v>
-      </c>
-      <c r="E54" s="28" t="n">
-        <v>-559</v>
-      </c>
-      <c r="F54" s="29" t="n">
-        <v>35</v>
+        <v>-511</v>
+      </c>
+      <c r="E54" s="29" t="n">
+        <v>132</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>-643</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="H54" s="30" t="n">
-        <v>146.9</v>
+        <v>314.6</v>
       </c>
       <c r="I54" s="30" t="n">
-        <v>11659.9</v>
+        <v>13946.5</v>
       </c>
       <c r="J54" s="30" t="n">
-        <v>-434.4</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="55">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D55" s="28" t="n">
-        <v>-511</v>
-      </c>
-      <c r="E55" s="29" t="n">
-        <v>132</v>
+        <v>-478</v>
+      </c>
+      <c r="E55" s="28" t="n">
+        <v>-42</v>
       </c>
       <c r="F55" s="28" t="n">
-        <v>-643</v>
+        <v>-437</v>
       </c>
       <c r="G55" s="29" t="n">
-        <v>559</v>
+        <v>507</v>
       </c>
       <c r="H55" s="30" t="n">
-        <v>314.6</v>
+        <v>37.7</v>
       </c>
       <c r="I55" s="30" t="n">
-        <v>13946.5</v>
+        <v>3421.8</v>
       </c>
       <c r="J55" s="30" t="n">
-        <v>-546.9</v>
+        <v>-191.7</v>
       </c>
     </row>
     <row r="56"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>주가 상승에도 대차잔고가 2,044.8억 감소하며 숏커버링 여지 확인됨.</t>
+          <t>주간 순매수 상위 종목이며 대차잔고가 2,044.8억 감소하여 숏커버 여지가 있음.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>기관 순매수 2,220억이 집중되었으며 원전 수주 기대감이 지속됨.</t>
+          <t>기관 순매수 2,220억이 집중되었으며 원전 모멘텀이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>주간 순매도 -3,070억을 기록하며 수급 이탈이 관찰됨.</t>
+          <t>주간 순매도 1,568억으로 수급 이탈이 뚜렷함.</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B62" s="30" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주가 급등에 따른 대차잔고 482.9억 증가로 하방 압력 관찰됨.</t>
+          <t>주간 순매도 968억으로 수급이 악화됨.</t>
         </is>
       </c>
     </row>
@@ -2330,31 +2330,31 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="15">
+    <row r="66" ht="31" customHeight="1" s="15">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>- 주초 외국인과 기관의 강력한 동반 매수세로 KOSPI가 4.61% 급등하며 Risk-On 국면을 연출함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="15">
+          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 국면을 연출함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장 상단을 제한함.</t>
+          <t>- 반도체 및 기계·장비 섹터가 지수 상승을 견인했으나, 주 후반 경기 둔화 우려와 금리 인상 경계감이 부각되며 상승분을 일부 반납함.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="15">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>- 주 후반 국내 2분기 GDP 성장률이 0.6%로 둔화하며 경기 우려가 부각됨.</t>
+          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장의 밸류에이션 부담을 가중시킴.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 섹터는 미국 모멘텀을 이어받았으나, 금리 인상 우려와 밸류에이션 부담으로 지수 변동성이 확대됨.</t>
+          <t>- 개인 투자자는 주간 내내 차익 실현 매물을 쏟아내며 외국인·기관의 매수 물량을 받아내는 양상을 보임.</t>
         </is>
       </c>
     </row>
@@ -2382,50 +2382,63 @@
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 및 기계·장비 섹터가 반도체와 원전 모멘텀을 바탕으로 주간 상승률 상위를 기록함.</t>
+          <t>- 반도체 및 기계·장비 섹터는 AI 모멘텀과 원전 수주 기대감으로 주간 내내 강세를 유지하며 시장 주도력을 확보함.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>- 건설 및 전기·가스 섹터는 대형 원전 수주 기대감으로 주 후반 강세를 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="15">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t>- IT 서비스 및 음식료·담배 섹터는 차익 실현 매물과 경기 둔화 우려로 약세를 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+          <t>- 음식료·담배 및 부동산 섹터는 환율 하락에 따른 수출 우려와 고금리 부담으로 인해 약세 흐름이 지속됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="18" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="15">
+    <row r="76" ht="31" customHeight="1" s="15">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr"/>
+      <c r="D76" s="14" t="inlineStr"/>
+      <c r="E76" s="29" t="inlineStr"/>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>외국인과 기관의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="31" customHeight="1" s="15">
       <c r="A77" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2433,15 +2446,25 @@
       </c>
       <c r="B77" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr"/>
-      <c r="D77" s="14" t="inlineStr"/>
-      <c r="E77" s="29" t="inlineStr"/>
+          <t>네오오토</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="n">
+        <v>40.59</v>
+      </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>외국인·기관 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2476,7 @@
       </c>
       <c r="B78" s="30" t="inlineStr">
         <is>
-          <t>네오오토</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
@@ -2467,11 +2490,11 @@
         </is>
       </c>
       <c r="E78" s="29" t="n">
-        <v>40.59</v>
+        <v>37.21</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2506,7 @@
       </c>
       <c r="B79" s="30" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
@@ -2497,11 +2520,11 @@
         </is>
       </c>
       <c r="E79" s="29" t="n">
-        <v>37.21</v>
+        <v>10.23</v>
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2536,12 @@
       </c>
       <c r="B80" s="30" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -2527,11 +2550,11 @@
         </is>
       </c>
       <c r="E80" s="29" t="n">
-        <v>10.23</v>
+        <v>12.31</v>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2566,7 @@
       </c>
       <c r="B81" s="30" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C81" s="30" t="inlineStr">
@@ -2553,15 +2576,15 @@
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E81" s="29" t="n">
-        <v>12.31</v>
+        <v>15.02</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2596,7 @@
       </c>
       <c r="B82" s="30" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
@@ -2587,11 +2610,11 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>15.02</v>
+        <v>13.01</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2626,7 @@
       </c>
       <c r="B83" s="30" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
@@ -2617,11 +2640,11 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>13.01</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2656,7 @@
       </c>
       <c r="B84" s="30" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
@@ -2647,45 +2670,35 @@
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" s="15">
       <c r="A85" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" s="30" t="inlineStr">
         <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="C85" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E85" s="29" t="n">
-        <v>5.48</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr"/>
+      <c r="D85" s="14" t="inlineStr"/>
+      <c r="E85" s="29" t="inlineStr"/>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="31" customHeight="1" s="15">
+          <t>2분기 GDP 성장률 0.6%로 둔화 및 국채 금리 급등에 따른 투자 심리 위축으로 KOSPI 0.58% 하락</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -2693,15 +2706,25 @@
       </c>
       <c r="B86" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C86" s="30" t="inlineStr"/>
-      <c r="D86" s="14" t="inlineStr"/>
-      <c r="E86" s="29" t="inlineStr"/>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="n">
+        <v>34.07</v>
+      </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률 0.6% 발표 및 금리 인상 우려로 KOSPI 0.58% 하락</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2736,7 @@
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
@@ -2727,15 +2750,15 @@
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>34.07</v>
+        <v>39.88</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="31" customHeight="1" s="15">
       <c r="A88" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -2743,7 +2766,7 @@
       </c>
       <c r="B88" s="30" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
@@ -2757,15 +2780,15 @@
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>39.88</v>
+        <v>37.07</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="31" customHeight="1" s="15">
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="15">
       <c r="A89" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -2773,12 +2796,12 @@
       </c>
       <c r="B89" s="30" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -2787,11 +2810,11 @@
         </is>
       </c>
       <c r="E89" s="29" t="n">
-        <v>37.07</v>
+        <v>32.53</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2826,7 @@
       </c>
       <c r="B90" s="30" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
@@ -2813,15 +2836,15 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>32.53</v>
+        <v>31.32</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2856,7 @@
       </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
@@ -2847,122 +2870,104 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>31.32</v>
+        <v>18.52</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="15">
-      <c r="A92" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B92" s="30" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="C92" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D92" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E92" s="29" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>다음 주 프리뷰</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+    </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>다음 주 프리뷰</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr"/>
-      <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
+    <row r="95" ht="31" customHeight="1" s="15">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>상승 시나리오</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>반도체 및 원전 관련주가 외국인 수급을 유지하면 지수 하방 경직성 확보 및 완만한 상승세 지속</t>
+        </is>
+      </c>
+    </row>
     <row r="96" ht="31" customHeight="1" s="15">
-      <c r="A96" s="31" t="inlineStr">
-        <is>
-          <t>상승 시나리오</t>
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것임.</t>
+          <t>미국 물가지표(PPI, CPI)가 예상치를 상회하여 금리 인상 우려가 심화되면 지수 조정 압력 확대</t>
         </is>
       </c>
     </row>
     <row r="97" ht="31" customHeight="1" s="15">
-      <c r="A97" s="31" t="inlineStr">
-        <is>
-          <t>상승 시나리오</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>물가 지표가 예상치를 상회하여 금리 인상 압력이 지속될 경우, 경기 방어주 및 원전 관련주로의 수급 로테이션이 강화될 것임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="31" customHeight="1" s="15">
-      <c r="A98" s="32" t="inlineStr">
-        <is>
-          <t>하방 시나리오</t>
+          <t>9월 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과가 금리 경로에 미칠 영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="15">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="15">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>판별 신호: 미국 생산자물가지수(PPI) 및 소비자물가지수(CPI)의 전월 대비 등락폭.</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2979,7 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>핵심 이벤트: 9월 10일 미국 PPI, 9월 11일 미국 CPI, 9월 15일 국내 무역수지.</t>
+          <t>국내 무역수지</t>
         </is>
       </c>
     </row>
@@ -3003,6 +3008,7 @@
     <mergeCell ref="F86:J86"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="F80:J80"/>
+    <mergeCell ref="F76:J76"/>
     <mergeCell ref="B65:J65"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="F79:J79"/>
@@ -3014,15 +3020,14 @@
     <mergeCell ref="F90:J90"/>
     <mergeCell ref="C60:J60"/>
     <mergeCell ref="A69:J69"/>
+    <mergeCell ref="B94:J94"/>
     <mergeCell ref="B97:J97"/>
     <mergeCell ref="C61:J61"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F92:J92"/>
     <mergeCell ref="F77:J77"/>
-    <mergeCell ref="A74:J74"/>
     <mergeCell ref="F82:J82"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="B96:J96"/>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:57 KST</t>
+          <t>2026-09-08 21:31 KST</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3087,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반도체 주도 랠리와 금리 인상 우려 사이의 변동성 장세</t>
+          <t>반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3311,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
+          <t>미국 반도체 지수 급등과 마이크론 강세가 국내 반도체 대형주로 이어지며 외국인·기관의 대규모 매수세와 함께 KOSPI 4.61% 급등을 견인함.</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 UBS의 금리 인상 전망 제기로 인한 투자 심리 위축이 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
+          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 둔화까지 겹쳐 지수가 0.58% 하락함.</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3346,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>미국 비농업 고용지표(162K)가 예상치를 상회하고 국내 2분기 GDP(0.6%)가 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 커짐.</t>
+          <t>미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회해 금리 인하 경로의 불확실성이 커졌고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경을 압박함.</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3358,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수가 집중되었으나, 개인은 전반적인 차익 실현 매도를 지속함.</t>
+          <t>수급 측면에서 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주간 5.93% 상승했고, 기계·장비 섹터 역시 기관(2,736억) 매수와 함께 7.43% 상승하며 주도 섹터로 자리매김함.</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3370,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>반도체 중심의 수급 쏠림이 뚜렷한 가운데, 금리 인상 우려와 경기 둔화 신호가 맞물리며 지수 상단이 제한되는 흐름을 보임.</t>
+          <t>매크로 지표의 둔화 신호에도 불구하고 반도체와 원전 등 특정 섹터로의 수급 쏠림이 뚜렷해, 향후 지수 방향성은 매크로 데이터의 추가 확인과 주도 섹터의 수급 연속성에 좌우될 전망임.</t>
         </is>
       </c>
     </row>
@@ -3747,29 +3752,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3070</v>
+        <v>-1568</v>
       </c>
       <c r="E41" t="n">
-        <v>-2520</v>
+        <v>-695</v>
       </c>
       <c r="F41" t="n">
-        <v>-550</v>
+        <v>-873</v>
       </c>
       <c r="G41" t="n">
-        <v>3076</v>
+        <v>1591</v>
       </c>
       <c r="H41" t="n">
-        <v>686.4</v>
+        <v>284</v>
       </c>
       <c r="I41" t="n">
-        <v>36009</v>
+        <v>13231</v>
       </c>
       <c r="J41" t="n">
-        <v>-2801</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
@@ -3783,29 +3788,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1568</v>
+        <v>-968</v>
       </c>
       <c r="E42" t="n">
-        <v>-695</v>
+        <v>-135</v>
       </c>
       <c r="F42" t="n">
-        <v>-873</v>
+        <v>-833</v>
       </c>
       <c r="G42" t="n">
-        <v>1591</v>
+        <v>966</v>
       </c>
       <c r="H42" t="n">
-        <v>284</v>
+        <v>96.5</v>
       </c>
       <c r="I42" t="n">
-        <v>13231</v>
+        <v>8138.3</v>
       </c>
       <c r="J42" t="n">
-        <v>-296.9</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
@@ -3819,29 +3824,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-968</v>
+        <v>-783</v>
       </c>
       <c r="E43" t="n">
-        <v>-135</v>
+        <v>-551</v>
       </c>
       <c r="F43" t="n">
-        <v>-833</v>
+        <v>-232</v>
       </c>
       <c r="G43" t="n">
-        <v>966</v>
+        <v>626</v>
       </c>
       <c r="H43" t="n">
-        <v>96.5</v>
+        <v>125.5</v>
       </c>
       <c r="I43" t="n">
-        <v>8138.3</v>
+        <v>12546.7</v>
       </c>
       <c r="J43" t="n">
-        <v>-220.9</v>
+        <v>-283.6</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
@@ -3855,29 +3860,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-783</v>
+        <v>-679</v>
       </c>
       <c r="E44" t="n">
-        <v>-551</v>
+        <v>-292</v>
       </c>
       <c r="F44" t="n">
-        <v>-232</v>
+        <v>-386</v>
       </c>
       <c r="G44" t="n">
-        <v>626</v>
+        <v>764</v>
       </c>
       <c r="H44" t="n">
-        <v>125.5</v>
+        <v>419.2</v>
       </c>
       <c r="I44" t="n">
-        <v>12546.7</v>
+        <v>31440</v>
       </c>
       <c r="J44" t="n">
-        <v>-283.6</v>
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
@@ -3891,29 +3896,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-679</v>
+        <v>-629</v>
       </c>
       <c r="E45" t="n">
-        <v>-292</v>
+        <v>-46</v>
       </c>
       <c r="F45" t="n">
-        <v>-386</v>
+        <v>-583</v>
       </c>
       <c r="G45" t="n">
-        <v>764</v>
+        <v>634</v>
       </c>
       <c r="H45" t="n">
-        <v>419.2</v>
+        <v>133.3</v>
       </c>
       <c r="I45" t="n">
-        <v>31440</v>
+        <v>14504.2</v>
       </c>
       <c r="J45" t="n">
-        <v>-1186.9</v>
+        <v>-390.7</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
@@ -3927,29 +3932,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-629</v>
+        <v>-593</v>
       </c>
       <c r="E46" t="n">
-        <v>-46</v>
+        <v>-468</v>
       </c>
       <c r="F46" t="n">
-        <v>-583</v>
+        <v>-125</v>
       </c>
       <c r="G46" t="n">
-        <v>634</v>
+        <v>588</v>
       </c>
       <c r="H46" t="n">
-        <v>133.3</v>
+        <v>222.6</v>
       </c>
       <c r="I46" t="n">
-        <v>14504.2</v>
+        <v>6895.6</v>
       </c>
       <c r="J46" t="n">
-        <v>-390.7</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
@@ -3963,29 +3968,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-593</v>
+        <v>-582</v>
       </c>
       <c r="E47" t="n">
-        <v>-468</v>
+        <v>-195</v>
       </c>
       <c r="F47" t="n">
-        <v>-125</v>
+        <v>-386</v>
       </c>
       <c r="G47" t="n">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="H47" t="n">
-        <v>222.6</v>
+        <v>563.7</v>
       </c>
       <c r="I47" t="n">
-        <v>6895.6</v>
+        <v>9333.9</v>
       </c>
       <c r="J47" t="n">
-        <v>-292.3</v>
+        <v>-1092.4</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
@@ -3999,29 +4004,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-582</v>
+        <v>-524</v>
       </c>
       <c r="E48" t="n">
-        <v>-195</v>
+        <v>-559</v>
       </c>
       <c r="F48" t="n">
-        <v>-386</v>
+        <v>35</v>
       </c>
       <c r="G48" t="n">
-        <v>571</v>
+        <v>528</v>
       </c>
       <c r="H48" t="n">
-        <v>563.7</v>
+        <v>146.9</v>
       </c>
       <c r="I48" t="n">
-        <v>9333.9</v>
+        <v>11659.9</v>
       </c>
       <c r="J48" t="n">
-        <v>-1092.4</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="15">
@@ -4035,29 +4040,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-524</v>
+        <v>-511</v>
       </c>
       <c r="E49" t="n">
-        <v>-559</v>
+        <v>132</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>-643</v>
       </c>
       <c r="G49" t="n">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="H49" t="n">
-        <v>146.9</v>
+        <v>314.6</v>
       </c>
       <c r="I49" t="n">
-        <v>11659.9</v>
+        <v>13946.5</v>
       </c>
       <c r="J49" t="n">
-        <v>-434.4</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="15">
@@ -4071,29 +4076,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-511</v>
+        <v>-478</v>
       </c>
       <c r="E50" t="n">
-        <v>132</v>
+        <v>-42</v>
       </c>
       <c r="F50" t="n">
-        <v>-643</v>
+        <v>-437</v>
       </c>
       <c r="G50" t="n">
-        <v>559</v>
+        <v>507</v>
       </c>
       <c r="H50" t="n">
-        <v>314.6</v>
+        <v>37.7</v>
       </c>
       <c r="I50" t="n">
-        <v>13946.5</v>
+        <v>3421.8</v>
       </c>
       <c r="J50" t="n">
-        <v>-546.9</v>
+        <v>-191.7</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
@@ -4116,7 +4121,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>주가 상승에도 대차잔고가 2,044.8억 감소하며 숏커버링 여지 확인됨.</t>
+          <t>주간 순매수 상위 종목이며 대차잔고가 2,044.8억 감소하여 숏커버 여지가 있음.</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4138,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>기관 순매수 2,220억이 집중되었으며 원전 수주 기대감이 지속됨.</t>
+          <t>기관 순매수 2,220억이 집중되었으며 원전 모멘텀이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4150,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>주간 순매도 -3,070억을 기록하며 수급 이탈이 관찰됨.</t>
+          <t>주간 순매도 1,568억으로 수급 이탈이 뚜렷함.</t>
         </is>
       </c>
     </row>
@@ -4162,12 +4167,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주가 급등에 따른 대차잔고 482.9억 증가로 하방 압력 관찰됨.</t>
+          <t>주간 순매도 968억으로 수급이 악화됨.</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4191,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>주초 외국인과 기관의 강력한 동반 매수세로 KOSPI가 4.61% 급등하며 Risk-On 국면을 연출함.</t>
+          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 국면을 연출함.</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4203,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장 상단을 제한함.</t>
+          <t>반도체 및 기계·장비 섹터가 지수 상승을 견인했으나, 주 후반 경기 둔화 우려와 금리 인상 경계감이 부각되며 상승분을 일부 반납함.</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4215,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>주 후반 국내 2분기 GDP 성장률이 0.6%로 둔화하며 경기 우려가 부각됨.</t>
+          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장의 밸류에이션 부담을 가중시킴.</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>반도체 섹터는 미국 모멘텀을 이어받았으나, 금리 인상 우려와 밸류에이션 부담으로 지수 변동성이 확대됨.</t>
+          <t>개인 투자자는 주간 내내 차익 실현 매물을 쏟아내며 외국인·기관의 매수 물량을 받아내는 양상을 보임.</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4246,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전기·전자 및 기계·장비 섹터가 반도체와 원전 모멘텀을 바탕으로 주간 상승률 상위를 기록함.</t>
+          <t>반도체 및 기계·장비 섹터는 AI 모멘텀과 원전 수주 기대감으로 주간 내내 강세를 유지하며 시장 주도력을 확보함.</t>
         </is>
       </c>
     </row>
@@ -4253,26 +4258,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>건설 및 전기·가스 섹터는 대형 원전 수주 기대감으로 주 후반 강세를 보임.</t>
+          <t>음식료·담배 및 부동산 섹터는 환율 하락에 따른 수출 우려와 고금리 부담으로 인해 약세 흐름이 지속됨.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>IT 서비스 및 음식료·담배 섹터는 차익 실현 매물과 경기 둔화 우려로 약세를 보임.</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>외국인과 기관의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
         </is>
       </c>
     </row>
@@ -4284,12 +4294,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>네오오토</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>40.59</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>외국인·기관 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4322,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네오오토</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4313,11 +4334,11 @@
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>40.59</v>
+        <v>37.21</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4350,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4341,11 +4362,11 @@
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>37.21</v>
+        <v>10.23</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4357,23 +4378,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>10.23</v>
+        <v>12.31</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4406,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4394,14 +4415,14 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>12.31</v>
+        <v>15.02</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4434,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4425,11 +4446,11 @@
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>15.02</v>
+        <v>13.01</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4462,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4453,11 +4474,11 @@
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>13.01</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4490,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4481,39 +4502,28 @@
         <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>8.859999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="15">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>4</v>
-      </c>
-      <c r="E74" t="n">
-        <v>5.48</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>2분기 GDP 성장률 0.6%로 둔화 및 국채 금리 급등에 따른 투자 심리 위축으로 KOSPI 0.58% 하락</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4535,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34.07</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률 0.6% 발표 및 금리 인상 우려로 KOSPI 0.58% 하락</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4563,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4554,11 +4575,11 @@
         <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>34.07</v>
+        <v>39.88</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4591,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4582,11 +4603,11 @@
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>39.88</v>
+        <v>37.07</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -4598,23 +4619,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>37.07</v>
+        <v>32.53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4647,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4635,14 +4656,14 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>32.53</v>
+        <v>31.32</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4675,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4666,94 +4687,78 @@
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>31.32</v>
+        <v>18.52</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="15">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>4</v>
-      </c>
-      <c r="E81" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="15">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>상승 시나리오</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>반도체 및 원전 관련주가 외국인 수급을 유지하면 지수 하방 경직성 확보 및 완만한 상승세 지속</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>미국 PPI 및 CPI 발표 결과에 따라 금리 인상 우려가 완화되면 반도체 중심의 상승세가 재개될 것임.</t>
+          <t>미국 물가지표(PPI, CPI)가 예상치를 상회하여 금리 인상 우려가 심화되면 지수 조정 압력 확대</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>물가 지표가 예상치를 상회하여 금리 인상 압력이 지속될 경우, 경기 방어주 및 원전 관련주로의 수급 로테이션이 강화될 것임.</t>
+          <t>9월 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과가 금리 경로에 미칠 영향</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>판별 신호: 미국 생산자물가지수(PPI) 및 소비자물가지수(CPI)의 전월 대비 등락폭.</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4770,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>핵심 이벤트: 9월 10일 미국 PPI, 9월 11일 미국 CPI, 9월 15일 국내 무역수지.</t>
+          <t>국내 무역수지</t>
         </is>
       </c>
     </row>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-08 21:31 KST</t>
+          <t>2026-09-08 21:43 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
+          <t>반도체 주도 수급 쏠림과 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 급등과 마이크론 강세가 국내 반도체 대형주로 이어지며 외국인·기관의 대규모 매수세와 함께 KOSPI 4.61% 급등을 견인함.</t>
+          <t>미국 필라델피아 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 기대 후퇴로 지수 상단은 제한됨.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 둔화까지 겹쳐 지수가 0.58% 하락함.</t>
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 0.6% 발표와 맞물려 지수 하락을 견인함.</t>
         </is>
       </c>
     </row>
@@ -1376,21 +1376,21 @@
     <row r="30" ht="31" customHeight="1" s="15">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>- 미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회해 금리 인하 경로의 불확실성이 커졌고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경을 압박함.</t>
+          <t>- 매크로 환경은 미국 고용지표가 16만 2천 명 증가하며 견조함을 보였으나, 국내 2분기 GDP 성장률이 0.6%로 이전치 1.8%를 하회하며 경기 둔화 우려가 상존함.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="15">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주간 5.93% 상승했고, 기계·장비 섹터 역시 기관(2,736억) 매수와 함께 7.43% 상승하며 주도 섹터로 자리매김함.</t>
+          <t>- 수급 구도는 전기·전자 섹터에 외국인 32,305억, 기관 25,821억의 대규모 순매수가 집중되며 반도체 쏠림 현상이 뚜렷했음.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="15">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 지표의 둔화 신호에도 불구하고 반도체와 원전 등 특정 섹터로의 수급 쏠림이 뚜렷해, 향후 지수 방향성은 매크로 데이터의 추가 확인과 주도 섹터의 수급 연속성에 좌우될 전망임.</t>
+          <t>- 종합적으로 반도체 중심의 수급 주도력은 강력하나, 매크로 지표의 엇박자와 개인의 차익 실현 매물이 지수 변동성을 키우는 국면임.</t>
         </is>
       </c>
     </row>
@@ -1842,29 +1842,29 @@
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D46" s="28" t="n">
-        <v>-1568</v>
+        <v>-3070</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>-695</v>
+        <v>-2520</v>
       </c>
       <c r="F46" s="28" t="n">
-        <v>-873</v>
+        <v>-550</v>
       </c>
       <c r="G46" s="29" t="n">
-        <v>1591</v>
+        <v>3076</v>
       </c>
       <c r="H46" s="30" t="n">
-        <v>284</v>
+        <v>686.4</v>
       </c>
       <c r="I46" s="30" t="n">
-        <v>13231</v>
+        <v>36009</v>
       </c>
       <c r="J46" s="30" t="n">
-        <v>-296.9</v>
+        <v>-2801</v>
       </c>
     </row>
     <row r="47">
@@ -1878,29 +1878,29 @@
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D47" s="28" t="n">
-        <v>-968</v>
+        <v>-1568</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>-135</v>
+        <v>-695</v>
       </c>
       <c r="F47" s="28" t="n">
-        <v>-833</v>
+        <v>-873</v>
       </c>
       <c r="G47" s="29" t="n">
-        <v>966</v>
+        <v>1591</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>96.5</v>
+        <v>284</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>8138.3</v>
+        <v>13231</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>-220.9</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="48">
@@ -1914,32 +1914,32 @@
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="D48" s="28" t="n">
-        <v>-783</v>
+        <v>-968</v>
       </c>
       <c r="E48" s="28" t="n">
-        <v>-551</v>
+        <v>-135</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>-232</v>
+        <v>-833</v>
       </c>
       <c r="G48" s="29" t="n">
-        <v>626</v>
+        <v>966</v>
       </c>
       <c r="H48" s="30" t="n">
-        <v>125.5</v>
+        <v>96.5</v>
       </c>
       <c r="I48" s="30" t="n">
-        <v>12546.7</v>
+        <v>8138.3</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>-283.6</v>
-      </c>
-    </row>
-    <row r="49" ht="31" customHeight="1" s="15">
+        <v>-220.9</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -1948,34 +1948,34 @@
       <c r="B49" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션</t>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D49" s="28" t="n">
-        <v>-679</v>
+        <v>-783</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>-292</v>
+        <v>-551</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>-386</v>
+        <v>-232</v>
       </c>
       <c r="G49" s="29" t="n">
-        <v>764</v>
+        <v>626</v>
       </c>
       <c r="H49" s="30" t="n">
-        <v>419.2</v>
+        <v>125.5</v>
       </c>
       <c r="I49" s="30" t="n">
-        <v>31440</v>
+        <v>12546.7</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>-1186.9</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>-283.6</v>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1" s="15">
       <c r="A50" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -1984,34 +1984,34 @@
       <c r="B50" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="30" t="inlineStr">
-        <is>
-          <t>에이피알</t>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>-629</v>
+        <v>-679</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>-46</v>
+        <v>-292</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>-583</v>
+        <v>-386</v>
       </c>
       <c r="G50" s="29" t="n">
-        <v>634</v>
+        <v>764</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>133.3</v>
+        <v>419.2</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>14504.2</v>
+        <v>31440</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>-390.7</v>
-      </c>
-    </row>
-    <row r="51" ht="31" customHeight="1" s="15">
+        <v>-1186.9</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2020,34 +2020,34 @@
       <c r="B51" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>레인보우로보틱스</t>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>-593</v>
+        <v>-629</v>
       </c>
       <c r="E51" s="28" t="n">
-        <v>-468</v>
+        <v>-46</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>-125</v>
+        <v>-583</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="H51" s="30" t="n">
-        <v>222.6</v>
+        <v>133.3</v>
       </c>
       <c r="I51" s="30" t="n">
-        <v>6895.6</v>
+        <v>14504.2</v>
       </c>
       <c r="J51" s="30" t="n">
-        <v>-292.3</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>-390.7</v>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1" s="15">
       <c r="A52" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2056,34 +2056,34 @@
       <c r="B52" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C52" s="30" t="inlineStr">
-        <is>
-          <t>LG이노텍</t>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D52" s="28" t="n">
-        <v>-582</v>
+        <v>-593</v>
       </c>
       <c r="E52" s="28" t="n">
-        <v>-195</v>
+        <v>-468</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>-386</v>
+        <v>-125</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="H52" s="30" t="n">
-        <v>563.7</v>
+        <v>222.6</v>
       </c>
       <c r="I52" s="30" t="n">
-        <v>9333.9</v>
+        <v>6895.6</v>
       </c>
       <c r="J52" s="30" t="n">
-        <v>-1092.4</v>
-      </c>
-    </row>
-    <row r="53" ht="31" customHeight="1" s="15">
+        <v>-292.3</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2092,34 +2092,34 @@
       <c r="B53" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-524</v>
+        <v>-582</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>-559</v>
-      </c>
-      <c r="F53" s="29" t="n">
-        <v>35</v>
+        <v>-195</v>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>-386</v>
       </c>
       <c r="G53" s="29" t="n">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>146.9</v>
+        <v>563.7</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>11659.9</v>
+        <v>9333.9</v>
       </c>
       <c r="J53" s="30" t="n">
-        <v>-434.4</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>-1092.4</v>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1" s="15">
       <c r="A54" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2128,31 +2128,31 @@
       <c r="B54" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="30" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D54" s="28" t="n">
-        <v>-511</v>
-      </c>
-      <c r="E54" s="29" t="n">
-        <v>132</v>
-      </c>
-      <c r="F54" s="28" t="n">
-        <v>-643</v>
+        <v>-524</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>-559</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>35</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="H54" s="30" t="n">
-        <v>314.6</v>
+        <v>146.9</v>
       </c>
       <c r="I54" s="30" t="n">
-        <v>13946.5</v>
+        <v>11659.9</v>
       </c>
       <c r="J54" s="30" t="n">
-        <v>-546.9</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="55">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D55" s="28" t="n">
-        <v>-478</v>
-      </c>
-      <c r="E55" s="28" t="n">
-        <v>-42</v>
+        <v>-511</v>
+      </c>
+      <c r="E55" s="29" t="n">
+        <v>132</v>
       </c>
       <c r="F55" s="28" t="n">
-        <v>-437</v>
+        <v>-643</v>
       </c>
       <c r="G55" s="29" t="n">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="H55" s="30" t="n">
-        <v>37.7</v>
+        <v>314.6</v>
       </c>
       <c r="I55" s="30" t="n">
-        <v>3421.8</v>
+        <v>13946.5</v>
       </c>
       <c r="J55" s="30" t="n">
-        <v>-191.7</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="56"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 상위 종목이며 대차잔고가 2,044.8억 감소하여 숏커버 여지가 있음.</t>
+          <t>주가 상승에도 대차잔고 감소로 숏커버 여지가 있으며, 외국인과 기관의 순매수가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>기관 순매수 2,220억이 집중되었으며 원전 모멘텀이 지속됨.</t>
+          <t>원전 수주 기대감과 함께 기관 순매수 2,220억이 유입됨.</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>주간 순매도 1,568억으로 수급 이탈이 뚜렷함.</t>
+          <t>주가 하락세 속 외국인 -2,520억, 기관 -550억의 순매도가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주간 순매도 968억으로 수급이 악화됨.</t>
+          <t>주가 하락세 속 기관 -833억의 순매도가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -2333,28 +2333,28 @@
     <row r="66" ht="31" customHeight="1" s="15">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 국면을 연출함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="31" customHeight="1" s="15">
+          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 장세가 연출됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 및 기계·장비 섹터가 지수 상승을 견인했으나, 주 후반 경기 둔화 우려와 금리 인상 경계감이 부각되며 상승분을 일부 반납함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="15">
+          <t>- 반도체 섹터로의 수급 쏠림이 극대화되며 삼성전자와 SK하이닉스가 지수 상승을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="31" customHeight="1" s="15">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장의 밸류에이션 부담을 가중시킴.</t>
+          <t>- 주 후반 미국발 금리 인상 우려와 국내 2분기 GDP 성장률 0.6% 기록에 따른 경기 둔화 우려가 부각되며 상승분 일부를 반납함.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- 개인 투자자는 주간 내내 차익 실현 매물을 쏟아내며 외국인·기관의 매수 물량을 받아내는 양상을 보임.</t>
+          <t>- 개인 투자자의 대규모 차익 실현 매물이 출회되는 가운데, 원/달러 환율은 1,340원대에서 등락하며 변동성이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -2382,59 +2382,46 @@
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 및 기계·장비 섹터는 AI 모멘텀과 원전 수주 기대감으로 주간 내내 강세를 유지하며 시장 주도력을 확보함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="15">
+          <t>- 반도체·AI: 삼성전자와 SK하이닉스 중심의 수급 쏠림이 지속되며 주도 섹터 지위 공고화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="31" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>- 음식료·담배 및 부동산 섹터는 환율 하락에 따른 수출 우려와 고금리 부담으로 인해 약세 흐름이 지속됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+          <t>- 건설·원전: 미국 내 대형 원전 8기 건설 협의 및 가덕도 신공항 이슈로 건설 및 기계·장비 섹터가 강한 순환매 흐름 형성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="15">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>- 소비재·IT서비스: 환율 하락에 따른 수출 우려와 차익 실현 매물로 음식료 및 IT 서비스 섹터는 약세 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="18" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="31" customHeight="1" s="15">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr"/>
-      <c r="D76" s="14" t="inlineStr"/>
-      <c r="E76" s="29" t="inlineStr"/>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>외국인과 기관의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
         </is>
       </c>
     </row>
@@ -2446,25 +2433,15 @@
       </c>
       <c r="B77" s="30" t="inlineStr">
         <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="n">
-        <v>40.59</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr"/>
+      <c r="D77" s="14" t="inlineStr"/>
+      <c r="E77" s="29" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>KOSPI 4.61% 급등, 외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2453,7 @@
       </c>
       <c r="B78" s="30" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>네오오토</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
@@ -2490,11 +2467,11 @@
         </is>
       </c>
       <c r="E78" s="29" t="n">
-        <v>37.21</v>
+        <v>40.59</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2483,7 @@
       </c>
       <c r="B79" s="30" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
@@ -2520,11 +2497,11 @@
         </is>
       </c>
       <c r="E79" s="29" t="n">
-        <v>10.23</v>
+        <v>37.21</v>
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2513,12 @@
       </c>
       <c r="B80" s="30" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -2550,11 +2527,11 @@
         </is>
       </c>
       <c r="E80" s="29" t="n">
-        <v>12.31</v>
+        <v>10.23</v>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2543,7 @@
       </c>
       <c r="B81" s="30" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C81" s="30" t="inlineStr">
@@ -2576,15 +2553,15 @@
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E81" s="29" t="n">
-        <v>15.02</v>
+        <v>12.31</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2573,7 @@
       </c>
       <c r="B82" s="30" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
@@ -2610,11 +2587,11 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>13.01</v>
+        <v>15.02</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2603,7 @@
       </c>
       <c r="B83" s="30" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
@@ -2640,11 +2617,11 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>13.01</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2633,7 @@
       </c>
       <c r="B84" s="30" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
@@ -2670,61 +2647,61 @@
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>5.48</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" s="15">
       <c r="A85" s="30" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="31" customHeight="1" s="15">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B85" s="30" t="inlineStr">
+      <c r="B86" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C85" s="30" t="inlineStr"/>
-      <c r="D85" s="14" t="inlineStr"/>
-      <c r="E85" s="29" t="inlineStr"/>
-      <c r="F85" s="17" t="inlineStr">
-        <is>
-          <t>2분기 GDP 성장률 0.6%로 둔화 및 국채 금리 급등에 따른 투자 심리 위축으로 KOSPI 0.58% 하락</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="15">
-      <c r="A86" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B86" s="30" t="inlineStr">
-        <is>
-          <t>빛과전자</t>
-        </is>
-      </c>
-      <c r="C86" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D86" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E86" s="29" t="n">
-        <v>34.07</v>
-      </c>
+      <c r="C86" s="30" t="inlineStr"/>
+      <c r="D86" s="14" t="inlineStr"/>
+      <c r="E86" s="29" t="inlineStr"/>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>KOSPI 0.58% 하락, 2분기 GDP 성장률 0.6% 발표에 따른 경기 둔화 우려 부각.</t>
         </is>
       </c>
     </row>
@@ -2736,85 +2713,85 @@
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E87" s="29" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="15">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
           <t>오르비텍</t>
         </is>
       </c>
-      <c r="C87" s="30" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D88" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E87" s="29" t="n">
+      <c r="E88" s="29" t="n">
         <v>39.88</v>
       </c>
-      <c r="F87" s="17" t="inlineStr">
+      <c r="F88" s="17" t="inlineStr">
         <is>
           <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="31" customHeight="1" s="15">
-      <c r="A88" s="30" t="inlineStr">
+    <row r="89" ht="31" customHeight="1" s="15">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <t>서전기전</t>
         </is>
       </c>
-      <c r="C88" s="30" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
+      <c r="D89" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E88" s="29" t="n">
+      <c r="E89" s="29" t="n">
         <v>37.07</v>
       </c>
-      <c r="F88" s="17" t="inlineStr">
+      <c r="F89" s="17" t="inlineStr">
         <is>
           <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15">
-      <c r="A89" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B89" s="30" t="inlineStr">
-        <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E89" s="29" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="F89" s="17" t="inlineStr">
-        <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2803,7 @@
       </c>
       <c r="B90" s="30" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
@@ -2836,15 +2813,15 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>31.32</v>
+        <v>32.53</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2856,106 +2833,124 @@
       </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E91" s="29" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="15">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
           <t>대우건설</t>
         </is>
       </c>
-      <c r="C91" s="30" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="D92" s="14" t="inlineStr">
         <is>
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E91" s="29" t="n">
+      <c r="E92" s="29" t="n">
         <v>18.52</v>
       </c>
-      <c r="F91" s="17" t="inlineStr">
+      <c r="F92" s="17" t="inlineStr">
         <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr"/>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="3" t="inlineStr"/>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="31" customHeight="1" s="15">
-      <c r="A95" s="31" t="inlineStr">
+    <row r="96" ht="31" customHeight="1" s="15">
+      <c r="A96" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>반도체 및 원전 관련주가 외국인 수급을 유지하면 지수 하방 경직성 확보 및 완만한 상승세 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="31" customHeight="1" s="15">
-      <c r="A96" s="32" t="inlineStr">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>반도체 수급이 지속되고 미국 물가 지표가 안정적이면 지수 반등 시도</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="31" customHeight="1" s="15">
+      <c r="A97" s="32" t="inlineStr">
         <is>
           <t>하방 시나리오</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>미국 물가지표(PPI, CPI)가 예상치를 상회하여 금리 인상 우려가 심화되면 지수 조정 압력 확대</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="31" customHeight="1" s="15">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>판별 신호</t>
-        </is>
-      </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>9월 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과가 금리 경로에 미칠 영향</t>
+          <t>미국 물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 지수 조정</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="15">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>핵심 이벤트</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>9월 10일 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2962,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2974,24 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>국내 무역수지</t>
+          <t>미국 소비자물가지수(CPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="15">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>한국 무역수지</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="F78:J78"/>
     <mergeCell ref="B98:J98"/>
@@ -2992,6 +2999,7 @@
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="F87:J87"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B101:J101"/>
     <mergeCell ref="C62:J62"/>
     <mergeCell ref="C58:J58"/>
     <mergeCell ref="G25:J25"/>
@@ -3008,7 +3016,6 @@
     <mergeCell ref="F86:J86"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="F80:J80"/>
-    <mergeCell ref="F76:J76"/>
     <mergeCell ref="B65:J65"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="F79:J79"/>
@@ -3020,14 +3027,15 @@
     <mergeCell ref="F90:J90"/>
     <mergeCell ref="C60:J60"/>
     <mergeCell ref="A69:J69"/>
-    <mergeCell ref="B94:J94"/>
     <mergeCell ref="B97:J97"/>
     <mergeCell ref="C61:J61"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F92:J92"/>
     <mergeCell ref="F77:J77"/>
+    <mergeCell ref="A74:J74"/>
     <mergeCell ref="F82:J82"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="B96:J96"/>
@@ -3043,7 +3051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -3075,7 +3083,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 21:31 KST</t>
+          <t>2026-09-08 21:43 KST</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3095,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
+          <t>반도체 주도 수급 쏠림과 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3319,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 급등과 마이크론 강세가 국내 반도체 대형주로 이어지며 외국인·기관의 대규모 매수세와 함께 KOSPI 4.61% 급등을 견인함.</t>
+          <t>미국 필라델피아 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 기대 후퇴로 지수 상단은 제한됨.</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3334,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>미국 국채 금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 둔화까지 겹쳐 지수가 0.58% 하락함.</t>
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 0.6% 발표와 맞물려 지수 하락을 견인함.</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3354,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회해 금리 인하 경로의 불확실성이 커졌고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경을 압박함.</t>
+          <t>매크로 환경은 미국 고용지표가 16만 2천 명 증가하며 견조함을 보였으나, 국내 2분기 GDP 성장률이 0.6%로 이전치 1.8%를 하회하며 경기 둔화 우려가 상존함.</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3366,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>수급 측면에서 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주간 5.93% 상승했고, 기계·장비 섹터 역시 기관(2,736억) 매수와 함께 7.43% 상승하며 주도 섹터로 자리매김함.</t>
+          <t>수급 구도는 전기·전자 섹터에 외국인 32,305억, 기관 25,821억의 대규모 순매수가 집중되며 반도체 쏠림 현상이 뚜렷했음.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>매크로 지표의 둔화 신호에도 불구하고 반도체와 원전 등 특정 섹터로의 수급 쏠림이 뚜렷해, 향후 지수 방향성은 매크로 데이터의 추가 확인과 주도 섹터의 수급 연속성에 좌우될 전망임.</t>
+          <t>종합적으로 반도체 중심의 수급 주도력은 강력하나, 매크로 지표의 엇박자와 개인의 차익 실현 매물이 지수 변동성을 키우는 국면임.</t>
         </is>
       </c>
     </row>
@@ -3752,29 +3760,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1568</v>
+        <v>-3070</v>
       </c>
       <c r="E41" t="n">
-        <v>-695</v>
+        <v>-2520</v>
       </c>
       <c r="F41" t="n">
-        <v>-873</v>
+        <v>-550</v>
       </c>
       <c r="G41" t="n">
-        <v>1591</v>
+        <v>3076</v>
       </c>
       <c r="H41" t="n">
-        <v>284</v>
+        <v>686.4</v>
       </c>
       <c r="I41" t="n">
-        <v>13231</v>
+        <v>36009</v>
       </c>
       <c r="J41" t="n">
-        <v>-296.9</v>
+        <v>-2801</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
@@ -3788,29 +3796,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-968</v>
+        <v>-1568</v>
       </c>
       <c r="E42" t="n">
-        <v>-135</v>
+        <v>-695</v>
       </c>
       <c r="F42" t="n">
-        <v>-833</v>
+        <v>-873</v>
       </c>
       <c r="G42" t="n">
-        <v>966</v>
+        <v>1591</v>
       </c>
       <c r="H42" t="n">
-        <v>96.5</v>
+        <v>284</v>
       </c>
       <c r="I42" t="n">
-        <v>8138.3</v>
+        <v>13231</v>
       </c>
       <c r="J42" t="n">
-        <v>-220.9</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
@@ -3824,29 +3832,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-783</v>
+        <v>-968</v>
       </c>
       <c r="E43" t="n">
-        <v>-551</v>
+        <v>-135</v>
       </c>
       <c r="F43" t="n">
-        <v>-232</v>
+        <v>-833</v>
       </c>
       <c r="G43" t="n">
-        <v>626</v>
+        <v>966</v>
       </c>
       <c r="H43" t="n">
-        <v>125.5</v>
+        <v>96.5</v>
       </c>
       <c r="I43" t="n">
-        <v>12546.7</v>
+        <v>8138.3</v>
       </c>
       <c r="J43" t="n">
-        <v>-283.6</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
@@ -3860,29 +3868,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-679</v>
+        <v>-783</v>
       </c>
       <c r="E44" t="n">
-        <v>-292</v>
+        <v>-551</v>
       </c>
       <c r="F44" t="n">
-        <v>-386</v>
+        <v>-232</v>
       </c>
       <c r="G44" t="n">
-        <v>764</v>
+        <v>626</v>
       </c>
       <c r="H44" t="n">
-        <v>419.2</v>
+        <v>125.5</v>
       </c>
       <c r="I44" t="n">
-        <v>31440</v>
+        <v>12546.7</v>
       </c>
       <c r="J44" t="n">
-        <v>-1186.9</v>
+        <v>-283.6</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
@@ -3896,29 +3904,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-629</v>
+        <v>-679</v>
       </c>
       <c r="E45" t="n">
-        <v>-46</v>
+        <v>-292</v>
       </c>
       <c r="F45" t="n">
-        <v>-583</v>
+        <v>-386</v>
       </c>
       <c r="G45" t="n">
-        <v>634</v>
+        <v>764</v>
       </c>
       <c r="H45" t="n">
-        <v>133.3</v>
+        <v>419.2</v>
       </c>
       <c r="I45" t="n">
-        <v>14504.2</v>
+        <v>31440</v>
       </c>
       <c r="J45" t="n">
-        <v>-390.7</v>
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
@@ -3932,29 +3940,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-593</v>
+        <v>-629</v>
       </c>
       <c r="E46" t="n">
-        <v>-468</v>
+        <v>-46</v>
       </c>
       <c r="F46" t="n">
-        <v>-125</v>
+        <v>-583</v>
       </c>
       <c r="G46" t="n">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="H46" t="n">
-        <v>222.6</v>
+        <v>133.3</v>
       </c>
       <c r="I46" t="n">
-        <v>6895.6</v>
+        <v>14504.2</v>
       </c>
       <c r="J46" t="n">
-        <v>-292.3</v>
+        <v>-390.7</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
@@ -3968,29 +3976,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-582</v>
+        <v>-593</v>
       </c>
       <c r="E47" t="n">
-        <v>-195</v>
+        <v>-468</v>
       </c>
       <c r="F47" t="n">
-        <v>-386</v>
+        <v>-125</v>
       </c>
       <c r="G47" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="H47" t="n">
-        <v>563.7</v>
+        <v>222.6</v>
       </c>
       <c r="I47" t="n">
-        <v>9333.9</v>
+        <v>6895.6</v>
       </c>
       <c r="J47" t="n">
-        <v>-1092.4</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
@@ -4004,29 +4012,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-524</v>
+        <v>-582</v>
       </c>
       <c r="E48" t="n">
-        <v>-559</v>
+        <v>-195</v>
       </c>
       <c r="F48" t="n">
-        <v>35</v>
+        <v>-386</v>
       </c>
       <c r="G48" t="n">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="H48" t="n">
-        <v>146.9</v>
+        <v>563.7</v>
       </c>
       <c r="I48" t="n">
-        <v>11659.9</v>
+        <v>9333.9</v>
       </c>
       <c r="J48" t="n">
-        <v>-434.4</v>
+        <v>-1092.4</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="15">
@@ -4040,29 +4048,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-511</v>
+        <v>-524</v>
       </c>
       <c r="E49" t="n">
-        <v>132</v>
+        <v>-559</v>
       </c>
       <c r="F49" t="n">
-        <v>-643</v>
+        <v>35</v>
       </c>
       <c r="G49" t="n">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="H49" t="n">
-        <v>314.6</v>
+        <v>146.9</v>
       </c>
       <c r="I49" t="n">
-        <v>13946.5</v>
+        <v>11659.9</v>
       </c>
       <c r="J49" t="n">
-        <v>-546.9</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="15">
@@ -4076,29 +4084,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-478</v>
+        <v>-511</v>
       </c>
       <c r="E50" t="n">
-        <v>-42</v>
+        <v>132</v>
       </c>
       <c r="F50" t="n">
-        <v>-437</v>
+        <v>-643</v>
       </c>
       <c r="G50" t="n">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="H50" t="n">
-        <v>37.7</v>
+        <v>314.6</v>
       </c>
       <c r="I50" t="n">
-        <v>3421.8</v>
+        <v>13946.5</v>
       </c>
       <c r="J50" t="n">
-        <v>-191.7</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
@@ -4121,7 +4129,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>주간 순매수 상위 종목이며 대차잔고가 2,044.8억 감소하여 숏커버 여지가 있음.</t>
+          <t>주가 상승에도 대차잔고 감소로 숏커버 여지가 있으며, 외국인과 기관의 순매수가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4146,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>기관 순매수 2,220억이 집중되었으며 원전 모멘텀이 지속됨.</t>
+          <t>원전 수주 기대감과 함께 기관 순매수 2,220억이 유입됨.</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4158,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>주간 순매도 1,568억으로 수급 이탈이 뚜렷함.</t>
+          <t>주가 하락세 속 외국인 -2,520억, 기관 -550억의 순매도가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4180,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 순매도 968억으로 수급이 악화됨.</t>
+          <t>주가 하락세 속 기관 -833억의 순매도가 집중됨.</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4199,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 국면을 연출함.</t>
+          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 장세가 연출됨.</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4211,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>반도체 및 기계·장비 섹터가 지수 상승을 견인했으나, 주 후반 경기 둔화 우려와 금리 인상 경계감이 부각되며 상승분을 일부 반납함.</t>
+          <t>반도체 섹터로의 수급 쏠림이 극대화되며 삼성전자와 SK하이닉스가 지수 상승을 견인함.</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4223,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 급등이 시장의 밸류에이션 부담을 가중시킴.</t>
+          <t>주 후반 미국발 금리 인상 우려와 국내 2분기 GDP 성장률 0.6% 기록에 따른 경기 둔화 우려가 부각되며 상승분 일부를 반납함.</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4235,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>개인 투자자는 주간 내내 차익 실현 매물을 쏟아내며 외국인·기관의 매수 물량을 받아내는 양상을 보임.</t>
+          <t>개인 투자자의 대규모 차익 실현 매물이 출회되는 가운데, 원/달러 환율은 1,340원대에서 등락하며 변동성이 지속됨.</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4254,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>반도체 및 기계·장비 섹터는 AI 모멘텀과 원전 수주 기대감으로 주간 내내 강세를 유지하며 시장 주도력을 확보함.</t>
+          <t>반도체·AI: 삼성전자와 SK하이닉스 중심의 수급 쏠림이 지속되며 주도 섹터 지위 공고화.</t>
         </is>
       </c>
     </row>
@@ -4258,31 +4266,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>음식료·담배 및 부동산 섹터는 환율 하락에 따른 수출 우려와 고금리 부담으로 인해 약세 흐름이 지속됨.</t>
+          <t>건설·원전: 미국 내 대형 원전 8기 건설 협의 및 가덕도 신공항 이슈로 건설 및 기계·장비 섹터가 강한 순환매 흐름 형성.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>소비재·IT서비스: 환율 하락에 따른 수출 우려와 차익 실현 매물로 음식료 및 IT 서비스 섹터는 약세 전환.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>외국인과 기관의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
@@ -4294,23 +4297,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" t="n">
-        <v>40.59</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>KOSPI 4.61% 급등, 외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4314,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>네오오토</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4334,11 +4326,11 @@
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>37.21</v>
+        <v>40.59</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4342,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4362,11 +4354,11 @@
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>10.23</v>
+        <v>37.21</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -4378,23 +4370,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>12.31</v>
+        <v>10.23</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4398,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4415,14 +4407,14 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>15.02</v>
+        <v>12.31</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4426,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4446,11 +4438,11 @@
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>13.01</v>
+        <v>15.02</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4454,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4474,11 +4466,11 @@
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>8.859999999999999</v>
+        <v>13.01</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4482,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4502,28 +4494,39 @@
         <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>5.48</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="15">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>5.48</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2분기 GDP 성장률 0.6%로 둔화 및 국채 금리 급등에 따른 투자 심리 위축으로 KOSPI 0.58% 하락</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4535,23 +4538,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>빛과전자</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>34.07</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>KOSPI 0.58% 하락, 2분기 GDP 성장률 0.6% 발표에 따른 경기 둔화 우려 부각.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4555,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4575,11 +4567,11 @@
         <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>39.88</v>
+        <v>34.07</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4583,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4603,11 +4595,11 @@
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>37.07</v>
+        <v>39.88</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4619,23 +4611,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>32.53</v>
+        <v>37.07</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4639,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4656,14 +4648,14 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>31.32</v>
+        <v>32.53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4667,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4687,66 +4679,82 @@
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>18.52</v>
+        <v>31.32</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="15">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="15">
       <c r="A82" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>반도체 및 원전 관련주가 외국인 수급을 유지하면 지수 하방 경직성 확보 및 완만한 상승세 지속</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>미국 물가지표(PPI, CPI)가 예상치를 상회하여 금리 인상 우려가 심화되면 지수 조정 압력 확대</t>
+          <t>반도체 수급이 지속되고 미국 물가 지표가 안정적이면 지수 반등 시도</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9월 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과가 금리 경로에 미칠 영향</t>
+          <t>미국 물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 지수 조정</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>핵심 이벤트</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>9월 10일 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4766,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4778,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>국내 무역수지</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15"/>
+          <t>미국 소비자물가지수(CPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="15">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>한국 무역수지</t>
+        </is>
+      </c>
+    </row>
     <row r="89" ht="15" customHeight="1" s="15"/>
     <row r="90" ht="15" customHeight="1" s="15"/>
     <row r="91" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-08 21:43 KST</t>
+          <t>2026-09-08 21:56 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체 주도 수급 쏠림과 매크로 불확실성 사이의 줄타기</t>
+          <t>AI 반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 기대 후퇴로 지수 상단은 제한됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1" s="15">
+          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44.5" customHeight="1" s="15">
       <c r="A26" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 0.6% 발표와 맞물려 지수 하락을 견인함.</t>
+          <t>미국 국채금리 급등과 연준의 금리 인상 가능성 제기라는 매크로 악재가 국내 2분기 GDP 성장률 둔화와 맞물리며 지수 하락을 압박함.</t>
         </is>
       </c>
     </row>
@@ -1376,21 +1376,21 @@
     <row r="30" ht="31" customHeight="1" s="15">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경은 미국 고용지표가 16만 2천 명 증가하며 견조함을 보였으나, 국내 2분기 GDP 성장률이 0.6%로 이전치 1.8%를 하회하며 경기 둔화 우려가 상존함.</t>
+          <t>- 미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 상회하는 서프라이즈를 기록했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경의 불확실성을 높임.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="15">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도는 전기·전자 섹터에 외국인 32,305억, 기관 25,821억의 대규모 순매수가 집중되며 반도체 쏠림 현상이 뚜렷했음.</t>
+          <t>- 수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으며, 삼성전자(45,121억)와 SK하이닉스(29,092억)가 주간 순매수 상위를 독점함.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="15">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>- 종합적으로 반도체 중심의 수급 주도력은 강력하나, 매크로 지표의 엇박자와 개인의 차익 실현 매물이 지수 변동성을 키우는 국면임.</t>
+          <t>- 반도체 중심의 수급 쏠림이 지수를 방어하고 있으나, 매크로 지표의 엇갈린 신호와 경기 둔화 우려가 공존하며 시장의 변동성이 확대되는 국면임.</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>주가 상승에도 대차잔고 감소로 숏커버 여지가 있으며, 외국인과 기관의 순매수가 집중됨.</t>
+          <t>주간 순매수 45,121억으로 수급 집중도 최상위</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B60" s="30" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>원전 수주 기대감과 함께 기관 순매수 2,220억이 유입됨.</t>
+          <t>주간 순매수 29,092억 및 대차잔고 감소로 숏커버 여지</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>주가 하락세 속 외국인 -2,520억, 기관 -550억의 순매도가 집중됨.</t>
+          <t>주간 순매수 -3,070억으로 수급 이탈 뚜렷</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B62" s="30" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주가 하락세 속 기관 -833억의 순매도가 집중됨.</t>
+          <t>주간 순매수 -1,568억으로 수급 약세 지속</t>
         </is>
       </c>
     </row>
@@ -2333,28 +2333,28 @@
     <row r="66" ht="31" customHeight="1" s="15">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 장세가 연출됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="15">
+          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 'Risk-On' 국면을 연출함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 섹터로의 수급 쏠림이 극대화되며 삼성전자와 SK하이닉스가 지수 상승을 견인함.</t>
+          <t>- 미국 필라델피아 반도체 지수의 강세가 국내 반도체 대형주로 이어지며 지수 상승을 견인했으나, 주 후반 금리 인상 우려와 국채 금리 급등으로 상승폭을 일부 반납함.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="31" customHeight="1" s="15">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>- 주 후반 미국발 금리 인상 우려와 국내 2분기 GDP 성장률 0.6% 기록에 따른 경기 둔화 우려가 부각되며 상승분 일부를 반납함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="15">
+          <t>- 개인 투자자는 주간 내내 대규모 순매도를 기록하며 차익 실현에 집중한 반면, 외국인과 기관은 삼성전자와 SK하이닉스를 중심으로 수급을 집중함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- 개인 투자자의 대규모 차익 실현 매물이 출회되는 가운데, 원/달러 환율은 1,340원대에서 등락하며 변동성이 지속됨.</t>
+          <t>- 국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각된 점이 시장의 상단을 제한하는 요인으로 작용함.</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2382,21 @@
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 반도체·AI: 삼성전자와 SK하이닉스 중심의 수급 쏠림이 지속되며 주도 섹터 지위 공고화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="31" customHeight="1" s="15">
+          <t>- 전기·전자 및 기계·장비 섹터가 AI 반도체 및 원전 수주 기대감으로 주도주 지위를 공고히 함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>- 건설·원전: 미국 내 대형 원전 8기 건설 협의 및 가덕도 신공항 이슈로 건설 및 기계·장비 섹터가 강한 순환매 흐름 형성.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="15">
+          <t>- 건설 섹터는 미국 내 대형 원전 8기 건설 협의 소식에 힘입어 주간 7.86% 상승하며 강한 모멘텀을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="31" customHeight="1" s="15">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>- 소비재·IT서비스: 환율 하락에 따른 수출 우려와 차익 실현 매물로 음식료 및 IT 서비스 섹터는 약세 전환.</t>
+          <t>- 반면 음식료·담배 및 부동산 섹터는 환율 하락과 고금리 장기화 부담으로 인해 차익 실현 매물이 출회되며 약세를 면치 못함.</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       <c r="E77" s="29" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>KOSPI 4.61% 급등, 외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입.</t>
+          <t>미국 8월 비농업 고용지수 예상치 상회 및 필라델피아 반도체 지수 급등에 따른 국내 반도체 중심의 강세.</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       <c r="E86" s="29" t="inlineStr"/>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>KOSPI 0.58% 하락, 2분기 GDP 성장률 0.6% 발표에 따른 경기 둔화 우려 부각.</t>
+          <t>국내 2분기 GDP 성장률 0.6%로 둔화 및 미국 금리 인상 우려 부각에 따른 지수 조정.</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>반도체 수급이 지속되고 미국 물가 지표가 안정적이면 지수 반등 시도</t>
+          <t>반도체 대형주 수급 유지 시 지수 하단 지지</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>미국 물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 지수 조정</t>
+          <t>미국 물가 지표 충격 시 금리 인상 우려 재점화</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>9월 10일 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과</t>
+          <t>미국 CPI 및 PPI 발표 결과</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>한국 무역수지</t>
+          <t>국내 무역수지</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 21:43 KST</t>
+          <t>2026-09-08 21:56 KST</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반도체 주도 수급 쏠림과 매크로 불확실성 사이의 줄타기</t>
+          <t>AI 반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 기대 후퇴로 지수 상단은 제한됨.</t>
+          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담으로 작용하며, 2분기 GDP 성장률 0.6% 발표와 맞물려 지수 하락을 견인함.</t>
+          <t>미국 국채금리 급등과 연준의 금리 인상 가능성 제기라는 매크로 악재가 국내 2분기 GDP 성장률 둔화와 맞물리며 지수 하락을 압박함.</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>매크로 환경은 미국 고용지표가 16만 2천 명 증가하며 견조함을 보였으나, 국내 2분기 GDP 성장률이 0.6%로 이전치 1.8%를 하회하며 경기 둔화 우려가 상존함.</t>
+          <t>미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 상회하는 서프라이즈를 기록했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경의 불확실성을 높임.</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>수급 구도는 전기·전자 섹터에 외국인 32,305억, 기관 25,821억의 대규모 순매수가 집중되며 반도체 쏠림 현상이 뚜렷했음.</t>
+          <t>수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으며, 삼성전자(45,121억)와 SK하이닉스(29,092억)가 주간 순매수 상위를 독점함.</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>종합적으로 반도체 중심의 수급 주도력은 강력하나, 매크로 지표의 엇박자와 개인의 차익 실현 매물이 지수 변동성을 키우는 국면임.</t>
+          <t>반도체 중심의 수급 쏠림이 지수를 방어하고 있으나, 매크로 지표의 엇갈린 신호와 경기 둔화 우려가 공존하며 시장의 변동성이 확대되는 국면임.</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>주가 상승에도 대차잔고 감소로 숏커버 여지가 있으며, 외국인과 기관의 순매수가 집중됨.</t>
+          <t>주간 순매수 45,121억으로 수급 집중도 최상위</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>원전 수주 기대감과 함께 기관 순매수 2,220억이 유입됨.</t>
+          <t>주간 순매수 29,092억 및 대차잔고 감소로 숏커버 여지</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>주가 하락세 속 외국인 -2,520억, 기관 -550억의 순매도가 집중됨.</t>
+          <t>주간 순매수 -3,070억으로 수급 이탈 뚜렷</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주가 하락세 속 기관 -833억의 순매도가 집중됨.</t>
+          <t>주간 순매수 -1,568억으로 수급 약세 지속</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 강한 'Risk-On' 장세가 연출됨.</t>
+          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 'Risk-On' 국면을 연출함.</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>반도체 섹터로의 수급 쏠림이 극대화되며 삼성전자와 SK하이닉스가 지수 상승을 견인함.</t>
+          <t>미국 필라델피아 반도체 지수의 강세가 국내 반도체 대형주로 이어지며 지수 상승을 견인했으나, 주 후반 금리 인상 우려와 국채 금리 급등으로 상승폭을 일부 반납함.</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>주 후반 미국발 금리 인상 우려와 국내 2분기 GDP 성장률 0.6% 기록에 따른 경기 둔화 우려가 부각되며 상승분 일부를 반납함.</t>
+          <t>개인 투자자는 주간 내내 대규모 순매도를 기록하며 차익 실현에 집중한 반면, 외국인과 기관은 삼성전자와 SK하이닉스를 중심으로 수급을 집중함.</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>개인 투자자의 대규모 차익 실현 매물이 출회되는 가운데, 원/달러 환율은 1,340원대에서 등락하며 변동성이 지속됨.</t>
+          <t>국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각된 점이 시장의 상단을 제한하는 요인으로 작용함.</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>반도체·AI: 삼성전자와 SK하이닉스 중심의 수급 쏠림이 지속되며 주도 섹터 지위 공고화.</t>
+          <t>전기·전자 및 기계·장비 섹터가 AI 반도체 및 원전 수주 기대감으로 주도주 지위를 공고히 함.</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>건설·원전: 미국 내 대형 원전 8기 건설 협의 및 가덕도 신공항 이슈로 건설 및 기계·장비 섹터가 강한 순환매 흐름 형성.</t>
+          <t>건설 섹터는 미국 내 대형 원전 8기 건설 협의 소식에 힘입어 주간 7.86% 상승하며 강한 모멘텀을 보임.</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>소비재·IT서비스: 환율 하락에 따른 수출 우려와 차익 실현 매물로 음식료 및 IT 서비스 섹터는 약세 전환.</t>
+          <t>반면 음식료·담배 및 부동산 섹터는 환율 하락과 고금리 장기화 부담으로 인해 차익 실현 매물이 출회되며 약세를 면치 못함.</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KOSPI 4.61% 급등, 외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입.</t>
+          <t>미국 8월 비농업 고용지수 예상치 상회 및 필라델피아 반도체 지수 급등에 따른 국내 반도체 중심의 강세.</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KOSPI 0.58% 하락, 2분기 GDP 성장률 0.6% 발표에 따른 경기 둔화 우려 부각.</t>
+          <t>국내 2분기 GDP 성장률 0.6%로 둔화 및 미국 금리 인상 우려 부각에 따른 지수 조정.</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>반도체 수급이 지속되고 미국 물가 지표가 안정적이면 지수 반등 시도</t>
+          <t>반도체 대형주 수급 유지 시 지수 하단 지지</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>미국 물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 지수 조정</t>
+          <t>미국 물가 지표 충격 시 금리 인상 우려 재점화</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9월 10일 생산자물가지수(PPI)와 11일 소비자물가지수(CPI) 결과</t>
+          <t>미국 CPI 및 PPI 발표 결과</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한국 무역수지</t>
+          <t>국내 무역수지</t>
         </is>
       </c>
     </row>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-07 ~ 2026-09-08</t>
+          <t>2026-09-07 ~ 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-08 21:56 KST</t>
+          <t>2026-09-09 08:48 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>AI 반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
+          <t>반도체와 원전이 주도한 급등 랠리와 고금리 경계감의 공존</t>
         </is>
       </c>
     </row>
@@ -905,19 +905,19 @@
         <v>32918</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>-0.76</v>
+        <v>-1.34</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-1.02</v>
+        <v>-2.2</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>-0.58</v>
+        <v>-0.9</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>6.77</v>
+        <v>9.52</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>6.74</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -967,17 +967,17 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>반도체 +5.22%</t>
+          <t>반도체 +6.41%</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>기술 +1.4%</t>
+          <t>기술 +1.72%</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>산업재 +0.82%</t>
+          <t>산업재 +0.34%</t>
         </is>
       </c>
     </row>
@@ -987,19 +987,19 @@
           <t>US 하락 섹터</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>임의소비재 -2.66%</t>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>헬스케어 -4.6%</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>헬스케어 -2.08%</t>
+          <t>임의소비재 -3.46%</t>
         </is>
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>에너지 -1.74%</t>
+          <t>금융 -2.96%</t>
         </is>
       </c>
     </row>
@@ -1216,403 +1216,396 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="15">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>소비자신용</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="E22" s="30" t="inlineStr"/>
+      <c r="F22" s="30" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>BUSD</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>이전比 상회</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1" s="15">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>실업률(계절조정계열)</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E23" s="30" t="inlineStr"/>
+      <c r="F23" s="30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>이전比 하회</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>일별 요약</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>코스피(%)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>코스피 ▲/▼</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>코스닥(%)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>코스닥 ▲/▼</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>주도 섹터</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>전일 미국장 → 한국장 반응</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1" s="15">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="27" ht="44.5" customHeight="1" s="15">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B27" s="29" t="n">
         <v>4.61</v>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>데이터 없음</t>
         </is>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D27" s="29" t="n">
         <v>1.07</v>
       </c>
-      <c r="E25" s="30" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>데이터 없음</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>기계·장비, 전기·전자</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44.5" customHeight="1" s="15">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>미국 반도체 지수 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감이 상단을 제한함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44.5" customHeight="1" s="15">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B28" s="28" t="n">
         <v>-0.58</v>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>231▲/634▼</t>
         </is>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D28" s="28" t="n">
         <v>-1.25</v>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>506▲/1141▼ 상한6</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>전기·가스, 건설</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 가능성 제기라는 매크로 악재가 국내 2분기 GDP 성장률 둔화와 맞물리며 지수 하락을 압박함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44.5" customHeight="1" s="15">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려와 중동 지정학적 리스크가 겹치며 시장의 관망세가 짙어짐.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>주간 종합 코멘트 — 매크로·수급</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="31" customHeight="1" s="15">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 상회하는 서프라이즈를 기록했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경의 불확실성을 높임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="31" customHeight="1" s="15">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>- 수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으며, 삼성전자(45,121억)와 SK하이닉스(29,092억)가 주간 순매수 상위를 독점함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="31" customHeight="1" s="15">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>- 반도체 중심의 수급 쏠림이 지수를 방어하고 있으나, 매크로 지표의 엇갈린 신호와 경기 둔화 우려가 공존하며 시장의 변동성이 확대되는 국면임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33" ht="31" customHeight="1" s="15">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>- 매크로 환경: 미국 비농업고용지수(162K)가 예상치(55K)를 상회하며 고용 호조를 보였으나, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="31" customHeight="1" s="15">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>- 수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주도권을 형성했으나, 개인은 전 섹터에서 차익 실현 매물을 출회함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="15">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>- 종합 관점: 반도체와 원전 중심의 수급 쏠림이 뚜렷한 가운데, 매크로 불확실성 확대가 지수 변동성을 키우는 국면임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>투자자 합산 순매수 상위/하위</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="18" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>외인+기관계, 억원</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="39" ht="31" customHeight="1" s="15">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B39" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="30" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="n">
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="n">
         <v>45121</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E39" s="29" t="n">
         <v>21100</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F39" s="29" t="n">
         <v>24020</v>
       </c>
-      <c r="G36" s="28" t="n">
+      <c r="G39" s="28" t="n">
         <v>-55192</v>
       </c>
-      <c r="H36" s="30" t="n">
+      <c r="H39" s="30" t="n">
         <v>1816.7</v>
       </c>
-      <c r="I36" s="30" t="n">
+      <c r="I39" s="30" t="n">
         <v>240284.8</v>
       </c>
-      <c r="J36" s="30" t="n">
+      <c r="J39" s="30" t="n">
         <v>-7162.4</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="n">
-        <v>29092</v>
-      </c>
-      <c r="E37" s="29" t="n">
-        <v>19197</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>9895</v>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>-52130</v>
-      </c>
-      <c r="H37" s="30" t="n">
-        <v>3364.2</v>
-      </c>
-      <c r="I37" s="30" t="n">
-        <v>223759.5</v>
-      </c>
-      <c r="J37" s="30" t="n">
-        <v>-2044.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="30" t="inlineStr">
-        <is>
-          <t>SK스퀘어</t>
-        </is>
-      </c>
-      <c r="D38" s="29" t="n">
-        <v>5294</v>
-      </c>
-      <c r="E38" s="29" t="n">
-        <v>3070</v>
-      </c>
-      <c r="F38" s="29" t="n">
-        <v>2223</v>
-      </c>
-      <c r="G38" s="28" t="n">
-        <v>-5184</v>
-      </c>
-      <c r="H38" s="30" t="n">
-        <v>365.7</v>
-      </c>
-      <c r="I38" s="30" t="n">
-        <v>32891.8</v>
-      </c>
-      <c r="J38" s="30" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="D39" s="29" t="n">
-        <v>2338</v>
-      </c>
-      <c r="E39" s="29" t="n">
-        <v>740</v>
-      </c>
-      <c r="F39" s="29" t="n">
-        <v>1598</v>
-      </c>
-      <c r="G39" s="28" t="n">
-        <v>-2361</v>
-      </c>
-      <c r="H39" s="30" t="n">
-        <v>206.2</v>
-      </c>
-      <c r="I39" s="30" t="n">
-        <v>28477.7</v>
-      </c>
-      <c r="J39" s="30" t="n">
-        <v>-666.1</v>
       </c>
     </row>
     <row r="40" ht="31" customHeight="1" s="15">
@@ -1622,357 +1615,357 @@
         </is>
       </c>
       <c r="B40" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>29092</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>19197</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>9895</v>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>-52130</v>
+      </c>
+      <c r="H40" s="30" t="n">
+        <v>3364.2</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>223759.5</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <v>-2044.8</v>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1" s="15">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>5294</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>2223</v>
+      </c>
+      <c r="G41" s="28" t="n">
+        <v>-5184</v>
+      </c>
+      <c r="H41" s="30" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="I41" s="30" t="n">
+        <v>32891.8</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1" s="15">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자우 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>2338</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>740</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>1598</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>-2361</v>
+      </c>
+      <c r="H42" s="30" t="n">
+        <v>206.2</v>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>28477.7</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>-666.1</v>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1" s="15">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="n">
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n">
         <v>2138</v>
       </c>
-      <c r="E40" s="28" t="n">
+      <c r="E43" s="28" t="n">
         <v>-81</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F43" s="29" t="n">
         <v>2220</v>
       </c>
-      <c r="G40" s="28" t="n">
+      <c r="G43" s="28" t="n">
         <v>-2125</v>
       </c>
-      <c r="H40" s="30" t="n">
+      <c r="H43" s="30" t="n">
         <v>900.5</v>
       </c>
-      <c r="I40" s="30" t="n">
+      <c r="I43" s="30" t="n">
         <v>19469.6</v>
       </c>
-      <c r="J40" s="30" t="n">
+      <c r="J43" s="30" t="n">
         <v>-5.9</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="44" ht="31" customHeight="1" s="15">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
+      <c r="B44" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>한미반도체</t>
-        </is>
-      </c>
-      <c r="D41" s="29" t="n">
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="n">
         <v>1581</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E44" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F44" s="29" t="n">
         <v>581</v>
       </c>
-      <c r="G41" s="28" t="n">
+      <c r="G44" s="28" t="n">
         <v>-1560</v>
       </c>
-      <c r="H41" s="30" t="n">
+      <c r="H44" s="30" t="n">
         <v>485.3</v>
       </c>
-      <c r="I41" s="30" t="n">
+      <c r="I44" s="30" t="n">
         <v>43511.4</v>
       </c>
-      <c r="J41" s="30" t="n">
+      <c r="J44" s="30" t="n">
         <v>-835.3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="45" ht="31" customHeight="1" s="15">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B42" s="30" t="n">
+      <c r="B45" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C42" s="30" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D42" s="29" t="n">
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="n">
         <v>1182</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E45" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F45" s="29" t="n">
         <v>541</v>
       </c>
-      <c r="G42" s="28" t="n">
+      <c r="G45" s="28" t="n">
         <v>-1175</v>
       </c>
-      <c r="H42" s="30" t="n">
+      <c r="H45" s="30" t="n">
         <v>422.1</v>
       </c>
-      <c r="I42" s="30" t="n">
+      <c r="I45" s="30" t="n">
         <v>10178.7</v>
       </c>
-      <c r="J42" s="30" t="n">
+      <c r="J45" s="30" t="n">
         <v>-497.1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="46" ht="31" customHeight="1" s="15">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B43" s="30" t="n">
+      <c r="B46" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="30" t="inlineStr">
-        <is>
-          <t>효성중공업</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="n">
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>효성중공업 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="n">
         <v>852</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E46" s="29" t="n">
         <v>687</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F46" s="29" t="n">
         <v>166</v>
       </c>
-      <c r="G43" s="28" t="n">
+      <c r="G46" s="28" t="n">
         <v>-863</v>
       </c>
-      <c r="H43" s="30" t="n">
+      <c r="H46" s="30" t="n">
         <v>144</v>
       </c>
-      <c r="I43" s="30" t="n">
+      <c r="I46" s="30" t="n">
         <v>5502.2</v>
       </c>
-      <c r="J43" s="30" t="n">
+      <c r="J46" s="30" t="n">
         <v>-624.2</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="47" ht="31" customHeight="1" s="15">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
+      <c r="B47" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C44" s="30" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="D44" s="29" t="n">
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>대우건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="n">
         <v>813</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E47" s="29" t="n">
         <v>369</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F47" s="29" t="n">
         <v>444</v>
       </c>
-      <c r="G44" s="28" t="n">
+      <c r="G47" s="28" t="n">
         <v>-812</v>
       </c>
-      <c r="H44" s="30" t="n">
+      <c r="H47" s="30" t="n">
         <v>164.4</v>
       </c>
-      <c r="I44" s="30" t="n">
+      <c r="I47" s="30" t="n">
         <v>6222.6</v>
       </c>
-      <c r="J44" s="30" t="n">
+      <c r="J47" s="30" t="n">
         <v>482.9</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="48" ht="31" customHeight="1" s="15">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B45" s="30" t="n">
+      <c r="B48" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C45" s="30" t="inlineStr">
-        <is>
-          <t>현대건설</t>
-        </is>
-      </c>
-      <c r="D45" s="29" t="n">
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="n">
         <v>754</v>
       </c>
-      <c r="E45" s="28" t="n">
+      <c r="E48" s="28" t="n">
         <v>-258</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F48" s="29" t="n">
         <v>1011</v>
       </c>
-      <c r="G45" s="28" t="n">
+      <c r="G48" s="28" t="n">
         <v>-760</v>
       </c>
-      <c r="H45" s="30" t="n">
+      <c r="H48" s="30" t="n">
         <v>292.4</v>
       </c>
-      <c r="I45" s="30" t="n">
+      <c r="I48" s="30" t="n">
         <v>8765.6</v>
       </c>
-      <c r="J45" s="30" t="n">
+      <c r="J48" s="30" t="n">
         <v>297</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="49" ht="31" customHeight="1" s="15">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B46" s="30" t="n">
+      <c r="B49" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="30" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="n">
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="n">
         <v>-3070</v>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="E49" s="28" t="n">
         <v>-2520</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F49" s="28" t="n">
         <v>-550</v>
       </c>
-      <c r="G46" s="29" t="n">
+      <c r="G49" s="29" t="n">
         <v>3076</v>
       </c>
-      <c r="H46" s="30" t="n">
+      <c r="H49" s="30" t="n">
         <v>686.4</v>
       </c>
-      <c r="I46" s="30" t="n">
+      <c r="I49" s="30" t="n">
         <v>36009</v>
       </c>
-      <c r="J46" s="30" t="n">
+      <c r="J49" s="30" t="n">
         <v>-2801</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="30" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>-1568</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>-695</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>-873</v>
-      </c>
-      <c r="G47" s="29" t="n">
-        <v>1591</v>
-      </c>
-      <c r="H47" s="30" t="n">
-        <v>284</v>
-      </c>
-      <c r="I47" s="30" t="n">
-        <v>13231</v>
-      </c>
-      <c r="J47" s="30" t="n">
-        <v>-296.9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B48" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" s="30" t="inlineStr">
-        <is>
-          <t>삼양식품</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="n">
-        <v>-968</v>
-      </c>
-      <c r="E48" s="28" t="n">
-        <v>-135</v>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>-833</v>
-      </c>
-      <c r="G48" s="29" t="n">
-        <v>966</v>
-      </c>
-      <c r="H48" s="30" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="I48" s="30" t="n">
-        <v>8138.3</v>
-      </c>
-      <c r="J48" s="30" t="n">
-        <v>-220.9</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" s="30" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="n">
-        <v>-783</v>
-      </c>
-      <c r="E49" s="28" t="n">
-        <v>-551</v>
-      </c>
-      <c r="F49" s="28" t="n">
-        <v>-232</v>
-      </c>
-      <c r="G49" s="29" t="n">
-        <v>626</v>
-      </c>
-      <c r="H49" s="30" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="I49" s="30" t="n">
-        <v>12546.7</v>
-      </c>
-      <c r="J49" s="30" t="n">
-        <v>-283.6</v>
       </c>
     </row>
     <row r="50" ht="31" customHeight="1" s="15">
@@ -1982,69 +1975,69 @@
         </is>
       </c>
       <c r="B50" s="30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>삼성SDI (전기·전자)</t>
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>-679</v>
+        <v>-1568</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>-292</v>
+        <v>-695</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>-386</v>
+        <v>-873</v>
       </c>
       <c r="G50" s="29" t="n">
-        <v>764</v>
+        <v>1591</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>419.2</v>
+        <v>284</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>31440</v>
+        <v>13231</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>-1186.9</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>-296.9</v>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1" s="15">
       <c r="A51" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
       <c r="B51" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C51" s="30" t="inlineStr">
-        <is>
-          <t>에이피알</t>
+        <v>3</v>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>삼양식품 (음식료·담배)</t>
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>-629</v>
+        <v>-968</v>
       </c>
       <c r="E51" s="28" t="n">
-        <v>-46</v>
+        <v>-135</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>-583</v>
+        <v>-833</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>634</v>
+        <v>966</v>
       </c>
       <c r="H51" s="30" t="n">
-        <v>133.3</v>
+        <v>96.5</v>
       </c>
       <c r="I51" s="30" t="n">
-        <v>14504.2</v>
+        <v>8138.3</v>
       </c>
       <c r="J51" s="30" t="n">
-        <v>-390.7</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="52" ht="31" customHeight="1" s="15">
@@ -2054,69 +2047,69 @@
         </is>
       </c>
       <c r="B52" s="30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>셀트리온 (제약)</t>
         </is>
       </c>
       <c r="D52" s="28" t="n">
-        <v>-593</v>
+        <v>-783</v>
       </c>
       <c r="E52" s="28" t="n">
-        <v>-468</v>
+        <v>-551</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>-125</v>
+        <v>-232</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>588</v>
+        <v>626</v>
       </c>
       <c r="H52" s="30" t="n">
-        <v>222.6</v>
+        <v>125.5</v>
       </c>
       <c r="I52" s="30" t="n">
-        <v>6895.6</v>
+        <v>12546.7</v>
       </c>
       <c r="J52" s="30" t="n">
-        <v>-292.3</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>-283.6</v>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1" s="15">
       <c r="A53" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
       <c r="B53" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C53" s="30" t="inlineStr">
-        <is>
-          <t>LG이노텍</t>
+        <v>5</v>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
         </is>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-582</v>
+        <v>-679</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>-195</v>
+        <v>-292</v>
       </c>
       <c r="F53" s="28" t="n">
         <v>-386</v>
       </c>
       <c r="G53" s="29" t="n">
-        <v>571</v>
+        <v>764</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>563.7</v>
+        <v>419.2</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>9333.9</v>
+        <v>31440</v>
       </c>
       <c r="J53" s="30" t="n">
-        <v>-1092.4</v>
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="54" ht="31" customHeight="1" s="15">
@@ -2126,412 +2119,417 @@
         </is>
       </c>
       <c r="B54" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>에이피알 (화학)</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>-629</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>-46</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>-583</v>
+      </c>
+      <c r="G54" s="29" t="n">
+        <v>634</v>
+      </c>
+      <c r="H54" s="30" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="I54" s="30" t="n">
+        <v>14504.2</v>
+      </c>
+      <c r="J54" s="30" t="n">
+        <v>-390.7</v>
+      </c>
+    </row>
+    <row r="55" ht="44.5" customHeight="1" s="15">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>-593</v>
+      </c>
+      <c r="E55" s="28" t="n">
+        <v>-468</v>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G55" s="29" t="n">
+        <v>588</v>
+      </c>
+      <c r="H55" s="30" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="I55" s="30" t="n">
+        <v>6895.6</v>
+      </c>
+      <c r="J55" s="30" t="n">
+        <v>-292.3</v>
+      </c>
+    </row>
+    <row r="56" ht="31" customHeight="1" s="15">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="n">
+        <v>-582</v>
+      </c>
+      <c r="E56" s="28" t="n">
+        <v>-195</v>
+      </c>
+      <c r="F56" s="28" t="n">
+        <v>-386</v>
+      </c>
+      <c r="G56" s="29" t="n">
+        <v>571</v>
+      </c>
+      <c r="H56" s="30" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="I56" s="30" t="n">
+        <v>9333.9</v>
+      </c>
+      <c r="J56" s="30" t="n">
+        <v>-1092.4</v>
+      </c>
+    </row>
+    <row r="57" ht="44.5" customHeight="1" s="15">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
-        </is>
-      </c>
-      <c r="D54" s="28" t="n">
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="n">
         <v>-524</v>
       </c>
-      <c r="E54" s="28" t="n">
+      <c r="E57" s="28" t="n">
         <v>-559</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F57" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="G54" s="29" t="n">
+      <c r="G57" s="29" t="n">
         <v>528</v>
       </c>
-      <c r="H54" s="30" t="n">
+      <c r="H57" s="30" t="n">
         <v>146.9</v>
       </c>
-      <c r="I54" s="30" t="n">
+      <c r="I57" s="30" t="n">
         <v>11659.9</v>
       </c>
-      <c r="J54" s="30" t="n">
+      <c r="J57" s="30" t="n">
         <v>-434.4</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="58" ht="31" customHeight="1" s="15">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B55" s="30" t="n">
+      <c r="B58" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="30" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="D55" s="28" t="n">
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>알테오젠 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="D58" s="28" t="n">
         <v>-511</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E58" s="29" t="n">
         <v>132</v>
       </c>
-      <c r="F55" s="28" t="n">
+      <c r="F58" s="28" t="n">
         <v>-643</v>
       </c>
-      <c r="G55" s="29" t="n">
+      <c r="G58" s="29" t="n">
         <v>559</v>
       </c>
-      <c r="H55" s="30" t="n">
+      <c r="H58" s="30" t="n">
         <v>314.6</v>
       </c>
-      <c r="I55" s="30" t="n">
+      <c r="I58" s="30" t="n">
         <v>13946.5</v>
       </c>
-      <c r="J55" s="30" t="n">
+      <c r="J58" s="30" t="n">
         <v>-546.9</v>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>수급 관찰</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>관찰 사유</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="15">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="15">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>주간 순매수 45,121억으로 수급 집중도 최상위</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="15">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>주간 주가 상승률 7.86% 대비 기관 순매수 1,732억이 유입되며 수급 개선세 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="15">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>주간 순매수 29,092억 및 대차잔고 감소로 숏커버 여지</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>주간 주가 상승률 7.43%와 함께 외국인 528억, 기관 2,736억의 동반 매수세 유입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="15">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>주간 순매수 -3,070억으로 수급 이탈 뚜렷</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="15">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>주간 주가 하락률 -3.39%에도 불구하고 개인 순매수 1,233억이 집중되어 수급 부담 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="15">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>주간 순매수 -1,568억으로 수급 약세 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>주간 주가 하락률 -1.75%와 함께 기관 순매도 -233억이 지속되며 하방 압력 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>주간 시장 흐름</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="31" customHeight="1" s="15">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 'Risk-On' 국면을 연출함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="31" customHeight="1" s="15">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 필라델피아 반도체 지수의 강세가 국내 반도체 대형주로 이어지며 지수 상승을 견인했으나, 주 후반 금리 인상 우려와 국채 금리 급등으로 상승폭을 일부 반납함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="31" customHeight="1" s="15">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>- 개인 투자자는 주간 내내 대규모 순매도를 기록하며 차익 실현에 집중한 반면, 외국인과 기관은 삼성전자와 SK하이닉스를 중심으로 수급을 집중함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="31" customHeight="1" s="15">
+    <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- 국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각된 점이 시장의 상단을 제한하는 요인으로 작용함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>섹터·테마 흐름</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+          <t>- KOSPI는 외국인과 기관의 강력한 동반 매수세에 힘입어 주 초반 4.61% 급등하며 강한 상승세를 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한하며 주 후반 지수 하락 및 보합세로 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="15">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체와 원전·전력설비 관련주로 수급 쏠림 현상이 뚜렷하게 나타남.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 및 기계·장비 섹터가 AI 반도체 및 원전 수주 기대감으로 주도주 지위를 공고히 함.</t>
+          <t>- 개인은 주간 내내 차익 실현 매물을 쏟아내며 지수 하락 압박 요인으로 작용.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="15">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>- 건설 섹터는 미국 내 대형 원전 8기 건설 협의 소식에 힘입어 주간 7.86% 상승하며 강한 모멘텀을 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="31" customHeight="1" s="15">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t>- 반면 음식료·담배 및 부동산 섹터는 환율 하락과 고금리 장기화 부담으로 인해 차익 실현 매물이 출회되며 약세를 면치 못함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+          <t>- 중동 지정학적 리스크와 글로벌 경기 둔화 우려가 혼재되며 시장의 관망세가 짙어짐.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>섹터·테마 흐름</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="15">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체/AI: 삼성전자, SK하이닉스 중심의 외국인·기관 매수세가 지속되며 시장 주도.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="15">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>- 원전/전력설비: 대형 수주 기대감으로 기계·장비 및 건설 섹터가 급등하며 순환매 주도.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="15">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>- 음식료/소비재: 글로벌 소비 둔화 우려 및 환율 영향으로 약세 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="18" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr"/>
-      <c r="D77" s="14" t="inlineStr"/>
-      <c r="E77" s="29" t="inlineStr"/>
-      <c r="F77" s="17" t="inlineStr">
-        <is>
-          <t>미국 8월 비농업 고용지수 예상치 상회 및 필라델피아 반도체 지수 급등에 따른 국내 반도체 중심의 강세.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="31" customHeight="1" s="15">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="31" customHeight="1" s="15">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B79" s="30" t="inlineStr">
-        <is>
-          <t>필옵틱스</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E79" s="29" t="n">
-        <v>37.21</v>
-      </c>
-      <c r="F79" s="17" t="inlineStr">
-        <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="31" customHeight="1" s="15">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B80" s="30" t="inlineStr">
-        <is>
-          <t>나무가</t>
-        </is>
-      </c>
-      <c r="C80" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E80" s="29" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2543,25 +2541,15 @@
       </c>
       <c r="B81" s="30" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C81" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E81" s="29" t="n">
-        <v>12.31</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr"/>
+      <c r="D81" s="14" t="inlineStr"/>
+      <c r="E81" s="29" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
         </is>
       </c>
     </row>
@@ -2571,27 +2559,27 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B82" s="30" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>네오오토 (운송장비·부품)</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>15.02</v>
+        <v>40.59</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2601,27 +2589,27 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B83" s="30" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>필옵틱스 (기계·장비)</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>13.01</v>
+        <v>37.21</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2631,27 +2619,27 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B84" s="30" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>나무가 (전기·전자)</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2661,9 +2649,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B85" s="30" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀 (전기·전자)</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
@@ -2673,185 +2661,185 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>5.48</v>
+        <v>12.31</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="31" customHeight="1" s="15">
       <c r="A86" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B86" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C86" s="30" t="inlineStr"/>
-      <c r="D86" s="14" t="inlineStr"/>
-      <c r="E86" s="29" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>DB하이텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="n">
+        <v>15.02</v>
+      </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률 0.6%로 둔화 및 미국 금리 인상 우려 부각에 따른 지수 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="15">
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="31" customHeight="1" s="15">
       <c r="A87" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B87" s="30" t="inlineStr">
-        <is>
-          <t>빛과전자</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>34.07</v>
+        <v>13.01</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="31" customHeight="1" s="15">
       <c r="A88" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B88" s="30" t="inlineStr">
-        <is>
-          <t>오르비텍</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>39.88</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" s="15">
       <c r="A89" s="30" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E89" s="29" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="31" customHeight="1" s="15">
+      <c r="A90" s="30" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B89" s="30" t="inlineStr">
-        <is>
-          <t>서전기전</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="30" t="inlineStr"/>
+      <c r="D90" s="14" t="inlineStr"/>
+      <c r="E90" s="29" t="inlineStr"/>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>미국 국채금리 상승 및 국내 2분기 GDP 성장률(0.6%) 둔화로 지수 0.58% 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="31" customHeight="1" s="15">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>빛과전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="D91" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="E89" s="29" t="n">
-        <v>37.07</v>
-      </c>
-      <c r="F89" s="17" t="inlineStr">
-        <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B90" s="30" t="inlineStr">
-        <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="C90" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D90" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E90" s="29" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="F90" s="17" t="inlineStr">
-        <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B91" s="30" t="inlineStr">
-        <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="C91" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
       <c r="E91" s="29" t="n">
-        <v>31.32</v>
+        <v>34.07</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -2863,182 +2851,325 @@
       </c>
       <c r="B92" s="30" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E92" s="29" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="31" customHeight="1" s="15">
+      <c r="A93" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>서전기전 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C93" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E93" s="29" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="31" customHeight="1" s="15">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>한전기술 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="C94" s="30" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D92" s="14" t="inlineStr">
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E94" s="29" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="31" customHeight="1" s="15">
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>현대약품 (제약)</t>
+        </is>
+      </c>
+      <c r="C95" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
         <is>
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E92" s="29" t="n">
+      <c r="E95" s="29" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="31" customHeight="1" s="15">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>대우건설 (건설)</t>
+        </is>
+      </c>
+      <c r="C96" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E96" s="29" t="n">
         <v>18.52</v>
       </c>
-      <c r="F92" s="17" t="inlineStr">
+      <c r="F96" s="17" t="inlineStr">
         <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97" ht="31" customHeight="1" s="15">
+      <c r="A97" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B97" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="30" t="inlineStr"/>
+      <c r="D97" s="14" t="inlineStr"/>
+      <c r="E97" s="29" t="inlineStr"/>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>미국 고용지표 호조에 따른 금리 인상 우려와 중동 지정학적 리스크로 관망세 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr"/>
-      <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="31" customHeight="1" s="15">
-      <c r="A96" s="31" t="inlineStr">
+    <row r="101" ht="31" customHeight="1" s="15">
+      <c r="A101" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>반도체 대형주 수급 유지 시 지수 하단 지지</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="31" customHeight="1" s="15">
-      <c r="A97" s="32" t="inlineStr">
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>미국 CPI가 예상치를 하회하면 금리 인상 우려 완화로 반도체 중심 상승세 재개</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="31" customHeight="1" s="15">
+      <c r="A102" s="32" t="inlineStr">
         <is>
           <t>하방 시나리오</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>미국 물가 지표 충격 시 금리 인상 우려 재점화</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>미국 CPI가 예상치를 상회하면 고금리 장기화 우려로 외국인 수급 이탈 및 지수 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="15">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>판별 신호</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>미국 CPI 및 PPI 발표 결과</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="15">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="15">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr">
+      <c r="B104" s="17" t="inlineStr">
         <is>
           <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="15">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="105" ht="15" customHeight="1" s="15">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>미국 생산자물가지수(PPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>한국 무역수지</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="15">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>국내 무역수지</t>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>미국 소매판매</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="F78:J78"/>
-    <mergeCell ref="B98:J98"/>
+  <mergeCells count="51">
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="F87:J87"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="B101:J101"/>
     <mergeCell ref="C62:J62"/>
-    <mergeCell ref="C58:J58"/>
-    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="F84:J84"/>
     <mergeCell ref="F89:J89"/>
-    <mergeCell ref="A68:J68"/>
     <mergeCell ref="C4:J4"/>
-    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="C64:J64"/>
     <mergeCell ref="F83:J83"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="B103:J103"/>
+    <mergeCell ref="F95:J95"/>
+    <mergeCell ref="C63:J63"/>
+    <mergeCell ref="C65:J65"/>
     <mergeCell ref="F86:J86"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="F80:J80"/>
-    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="F94:J94"/>
     <mergeCell ref="A73:J73"/>
-    <mergeCell ref="F79:J79"/>
     <mergeCell ref="F85:J85"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="F97:J97"/>
+    <mergeCell ref="B104:J104"/>
     <mergeCell ref="F91:J91"/>
-    <mergeCell ref="C59:J59"/>
-    <mergeCell ref="B95:J95"/>
+    <mergeCell ref="A70:J70"/>
     <mergeCell ref="F81:J81"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="F90:J90"/>
-    <mergeCell ref="C60:J60"/>
     <mergeCell ref="A69:J69"/>
-    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="F93:J93"/>
     <mergeCell ref="C61:J61"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="F96:J96"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="B100:J100"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="F92:J92"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A71:J71"/>
     <mergeCell ref="F82:J82"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="B102:J102"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A33:J33"/>
     <mergeCell ref="F88:J88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3051,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -3071,7 +3202,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-09-07 ~ 2026-09-08</t>
+          <t>2026-09-07 ~ 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3214,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 21:56 KST</t>
+          <t>2026-09-09 08:48 KST</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3226,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI 반도체 주도 랠리와 매크로 불확실성 사이의 줄타기</t>
+          <t>반도체와 원전이 주도한 급등 랠리와 고금리 경계감의 공존</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3305,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.76</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="15">
@@ -3184,7 +3315,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.58</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="15">
@@ -3194,7 +3325,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.02</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="15">
@@ -3204,7 +3335,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.74</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="15">
@@ -3214,7 +3345,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.77</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="15"/>
@@ -3300,201 +3431,152 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15"/>
+    <row r="21" ht="15" customHeight="1" s="15">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>소비자신용</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
     <row r="22" ht="15" customHeight="1" s="15">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4. 일별 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>필라델피아 반도체 지수의 3.37% 급등과 마이크론 상승세가 국내 반도체 소부장 및 대형주로 이어지며 외국인·기관의 강력한 매수세를 유도함.</t>
-        </is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>실업률(계절조정계열)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="15">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 가능성 제기라는 매크로 악재가 국내 2분기 GDP 성장률 둔화와 맞물리며 지수 하락을 압박함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="15"/>
+          <t>4. 일별 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="15">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>미국 반도체 지수 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감이 상단을 제한함.</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="15" customHeight="1" s="15">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5. 주간 종합 코멘트</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="15">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 상회하는 서프라이즈를 기록했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경의 불확실성을 높임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>수급 측면에서는 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되었으며, 삼성전자(45,121억)와 SK하이닉스(29,092억)가 주간 순매수 상위를 독점함.</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려와 중동 지정학적 리스크가 겹치며 시장의 관망세가 짙어짐.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="15">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>반도체 중심의 수급 쏠림이 지수를 방어하고 있으나, 매크로 지표의 엇갈린 신호와 경기 둔화 우려가 공존하며 시장의 변동성이 확대되는 국면임.</t>
+          <t>5. 주간 종합 코멘트</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="15">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6. 투자자 합산 순매수 (억원)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>매크로 환경: 미국 비농업고용지수(162K)가 예상치(55K)를 상회하며 고용 호조를 보였으나, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="15">
       <c r="A31" t="inlineStr">
         <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>45121</v>
-      </c>
-      <c r="E31" t="n">
-        <v>21100</v>
-      </c>
-      <c r="F31" t="n">
-        <v>24020</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-55192</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1816.7</v>
-      </c>
-      <c r="I31" t="n">
-        <v>240284.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-7162.4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주도권을 형성했으나, 개인은 전 섹터에서 차익 실현 매물을 출회함.</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="15">
       <c r="A32" t="inlineStr">
         <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>29092</v>
-      </c>
-      <c r="E32" t="n">
-        <v>19197</v>
-      </c>
-      <c r="F32" t="n">
-        <v>9895</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-52130</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3364.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>223759.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-2044.8</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>종합 관점: 반도체와 원전 중심의 수급 쏠림이 뚜렷한 가운데, 매크로 불확실성 확대가 지수 변동성을 키우는 국면임.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SK스퀘어</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>5294</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3070</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2223</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-5184</v>
-      </c>
-      <c r="H33" t="n">
-        <v>365.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>32891.8</v>
-      </c>
-      <c r="J33" t="n">
-        <v>79.8</v>
+          <t>6. 투자자 합산 순매수 (억원)</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="15">
@@ -3504,33 +3586,33 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2338</v>
+        <v>45121</v>
       </c>
       <c r="E34" t="n">
-        <v>740</v>
+        <v>21100</v>
       </c>
       <c r="F34" t="n">
-        <v>1598</v>
+        <v>24020</v>
       </c>
       <c r="G34" t="n">
-        <v>-2361</v>
+        <v>-55192</v>
       </c>
       <c r="H34" t="n">
-        <v>206.2</v>
+        <v>1816.7</v>
       </c>
       <c r="I34" t="n">
-        <v>28477.7</v>
+        <v>240284.8</v>
       </c>
       <c r="J34" t="n">
-        <v>-666.1</v>
+        <v>-7162.4</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="15">
@@ -3540,33 +3622,33 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2138</v>
+        <v>29092</v>
       </c>
       <c r="E35" t="n">
-        <v>-81</v>
+        <v>19197</v>
       </c>
       <c r="F35" t="n">
-        <v>2220</v>
+        <v>9895</v>
       </c>
       <c r="G35" t="n">
-        <v>-2125</v>
+        <v>-52130</v>
       </c>
       <c r="H35" t="n">
-        <v>900.5</v>
+        <v>3364.2</v>
       </c>
       <c r="I35" t="n">
-        <v>19469.6</v>
+        <v>223759.5</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.9</v>
+        <v>-2044.8</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="15">
@@ -3576,33 +3658,33 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1581</v>
+        <v>5294</v>
       </c>
       <c r="E36" t="n">
-        <v>1000</v>
+        <v>3070</v>
       </c>
       <c r="F36" t="n">
-        <v>581</v>
+        <v>2223</v>
       </c>
       <c r="G36" t="n">
-        <v>-1560</v>
+        <v>-5184</v>
       </c>
       <c r="H36" t="n">
-        <v>485.3</v>
+        <v>365.7</v>
       </c>
       <c r="I36" t="n">
-        <v>43511.4</v>
+        <v>32891.8</v>
       </c>
       <c r="J36" t="n">
-        <v>-835.3</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="15">
@@ -3612,33 +3694,33 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1182</v>
+        <v>2338</v>
       </c>
       <c r="E37" t="n">
-        <v>640</v>
+        <v>740</v>
       </c>
       <c r="F37" t="n">
-        <v>541</v>
+        <v>1598</v>
       </c>
       <c r="G37" t="n">
-        <v>-1175</v>
+        <v>-2361</v>
       </c>
       <c r="H37" t="n">
-        <v>422.1</v>
+        <v>206.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10178.7</v>
+        <v>28477.7</v>
       </c>
       <c r="J37" t="n">
-        <v>-497.1</v>
+        <v>-666.1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="15">
@@ -3648,33 +3730,33 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>852</v>
+        <v>2138</v>
       </c>
       <c r="E38" t="n">
-        <v>687</v>
+        <v>-81</v>
       </c>
       <c r="F38" t="n">
-        <v>166</v>
+        <v>2220</v>
       </c>
       <c r="G38" t="n">
-        <v>-863</v>
+        <v>-2125</v>
       </c>
       <c r="H38" t="n">
-        <v>144</v>
+        <v>900.5</v>
       </c>
       <c r="I38" t="n">
-        <v>5502.2</v>
+        <v>19469.6</v>
       </c>
       <c r="J38" t="n">
-        <v>-624.2</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
@@ -3684,33 +3766,33 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>813</v>
+        <v>1581</v>
       </c>
       <c r="E39" t="n">
-        <v>369</v>
+        <v>1000</v>
       </c>
       <c r="F39" t="n">
-        <v>444</v>
+        <v>581</v>
       </c>
       <c r="G39" t="n">
-        <v>-812</v>
+        <v>-1560</v>
       </c>
       <c r="H39" t="n">
-        <v>164.4</v>
+        <v>485.3</v>
       </c>
       <c r="I39" t="n">
-        <v>6222.6</v>
+        <v>43511.4</v>
       </c>
       <c r="J39" t="n">
-        <v>482.9</v>
+        <v>-835.3</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="15">
@@ -3720,141 +3802,141 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>754</v>
+        <v>1182</v>
       </c>
       <c r="E40" t="n">
-        <v>-258</v>
+        <v>640</v>
       </c>
       <c r="F40" t="n">
-        <v>1011</v>
+        <v>541</v>
       </c>
       <c r="G40" t="n">
-        <v>-760</v>
+        <v>-1175</v>
       </c>
       <c r="H40" t="n">
-        <v>292.4</v>
+        <v>422.1</v>
       </c>
       <c r="I40" t="n">
-        <v>8765.6</v>
+        <v>10178.7</v>
       </c>
       <c r="J40" t="n">
-        <v>297</v>
+        <v>-497.1</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="15">
       <c r="A41" t="inlineStr">
         <is>
-          <t>순매도 상위</t>
+          <t>순매수 상위</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3070</v>
+        <v>852</v>
       </c>
       <c r="E41" t="n">
-        <v>-2520</v>
+        <v>687</v>
       </c>
       <c r="F41" t="n">
-        <v>-550</v>
+        <v>166</v>
       </c>
       <c r="G41" t="n">
-        <v>3076</v>
+        <v>-863</v>
       </c>
       <c r="H41" t="n">
-        <v>686.4</v>
+        <v>144</v>
       </c>
       <c r="I41" t="n">
-        <v>36009</v>
+        <v>5502.2</v>
       </c>
       <c r="J41" t="n">
-        <v>-2801</v>
+        <v>-624.2</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
       <c r="A42" t="inlineStr">
         <is>
-          <t>순매도 상위</t>
+          <t>순매수 상위</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1568</v>
+        <v>813</v>
       </c>
       <c r="E42" t="n">
-        <v>-695</v>
+        <v>369</v>
       </c>
       <c r="F42" t="n">
-        <v>-873</v>
+        <v>444</v>
       </c>
       <c r="G42" t="n">
-        <v>1591</v>
+        <v>-812</v>
       </c>
       <c r="H42" t="n">
-        <v>284</v>
+        <v>164.4</v>
       </c>
       <c r="I42" t="n">
-        <v>13231</v>
+        <v>6222.6</v>
       </c>
       <c r="J42" t="n">
-        <v>-296.9</v>
+        <v>482.9</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
       <c r="A43" t="inlineStr">
         <is>
-          <t>순매도 상위</t>
+          <t>순매수 상위</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-968</v>
+        <v>754</v>
       </c>
       <c r="E43" t="n">
-        <v>-135</v>
+        <v>-258</v>
       </c>
       <c r="F43" t="n">
-        <v>-833</v>
+        <v>1011</v>
       </c>
       <c r="G43" t="n">
-        <v>966</v>
+        <v>-760</v>
       </c>
       <c r="H43" t="n">
-        <v>96.5</v>
+        <v>292.4</v>
       </c>
       <c r="I43" t="n">
-        <v>8138.3</v>
+        <v>8765.6</v>
       </c>
       <c r="J43" t="n">
-        <v>-220.9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
@@ -3864,33 +3946,33 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-783</v>
+        <v>-3070</v>
       </c>
       <c r="E44" t="n">
-        <v>-551</v>
+        <v>-2520</v>
       </c>
       <c r="F44" t="n">
-        <v>-232</v>
+        <v>-550</v>
       </c>
       <c r="G44" t="n">
-        <v>626</v>
+        <v>3076</v>
       </c>
       <c r="H44" t="n">
-        <v>125.5</v>
+        <v>686.4</v>
       </c>
       <c r="I44" t="n">
-        <v>12546.7</v>
+        <v>36009</v>
       </c>
       <c r="J44" t="n">
-        <v>-283.6</v>
+        <v>-2801</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
@@ -3900,33 +3982,33 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-679</v>
+        <v>-1568</v>
       </c>
       <c r="E45" t="n">
-        <v>-292</v>
+        <v>-695</v>
       </c>
       <c r="F45" t="n">
-        <v>-386</v>
+        <v>-873</v>
       </c>
       <c r="G45" t="n">
-        <v>764</v>
+        <v>1591</v>
       </c>
       <c r="H45" t="n">
-        <v>419.2</v>
+        <v>284</v>
       </c>
       <c r="I45" t="n">
-        <v>31440</v>
+        <v>13231</v>
       </c>
       <c r="J45" t="n">
-        <v>-1186.9</v>
+        <v>-296.9</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
@@ -3936,33 +4018,33 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-629</v>
+        <v>-968</v>
       </c>
       <c r="E46" t="n">
-        <v>-46</v>
+        <v>-135</v>
       </c>
       <c r="F46" t="n">
-        <v>-583</v>
+        <v>-833</v>
       </c>
       <c r="G46" t="n">
-        <v>634</v>
+        <v>966</v>
       </c>
       <c r="H46" t="n">
-        <v>133.3</v>
+        <v>96.5</v>
       </c>
       <c r="I46" t="n">
-        <v>14504.2</v>
+        <v>8138.3</v>
       </c>
       <c r="J46" t="n">
-        <v>-390.7</v>
+        <v>-220.9</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
@@ -3972,33 +4054,33 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-593</v>
+        <v>-783</v>
       </c>
       <c r="E47" t="n">
-        <v>-468</v>
+        <v>-551</v>
       </c>
       <c r="F47" t="n">
-        <v>-125</v>
+        <v>-232</v>
       </c>
       <c r="G47" t="n">
-        <v>588</v>
+        <v>626</v>
       </c>
       <c r="H47" t="n">
-        <v>222.6</v>
+        <v>125.5</v>
       </c>
       <c r="I47" t="n">
-        <v>6895.6</v>
+        <v>12546.7</v>
       </c>
       <c r="J47" t="n">
-        <v>-292.3</v>
+        <v>-283.6</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
@@ -4008,33 +4090,33 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-582</v>
+        <v>-679</v>
       </c>
       <c r="E48" t="n">
-        <v>-195</v>
+        <v>-292</v>
       </c>
       <c r="F48" t="n">
         <v>-386</v>
       </c>
       <c r="G48" t="n">
-        <v>571</v>
+        <v>764</v>
       </c>
       <c r="H48" t="n">
-        <v>563.7</v>
+        <v>419.2</v>
       </c>
       <c r="I48" t="n">
-        <v>9333.9</v>
+        <v>31440</v>
       </c>
       <c r="J48" t="n">
-        <v>-1092.4</v>
+        <v>-1186.9</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="15">
@@ -4044,33 +4126,33 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-524</v>
+        <v>-629</v>
       </c>
       <c r="E49" t="n">
-        <v>-559</v>
+        <v>-46</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>-583</v>
       </c>
       <c r="G49" t="n">
-        <v>528</v>
+        <v>634</v>
       </c>
       <c r="H49" t="n">
-        <v>146.9</v>
+        <v>133.3</v>
       </c>
       <c r="I49" t="n">
-        <v>11659.9</v>
+        <v>14504.2</v>
       </c>
       <c r="J49" t="n">
-        <v>-434.4</v>
+        <v>-390.7</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="15">
@@ -4080,150 +4162,222 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-511</v>
+        <v>-593</v>
       </c>
       <c r="E50" t="n">
-        <v>132</v>
+        <v>-468</v>
       </c>
       <c r="F50" t="n">
-        <v>-643</v>
+        <v>-125</v>
       </c>
       <c r="G50" t="n">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="H50" t="n">
-        <v>314.6</v>
+        <v>222.6</v>
       </c>
       <c r="I50" t="n">
-        <v>13946.5</v>
+        <v>6895.6</v>
       </c>
       <c r="J50" t="n">
-        <v>-546.9</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7. 수급 관찰</t>
-        </is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-582</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-195</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-386</v>
+      </c>
+      <c r="G51" t="n">
+        <v>571</v>
+      </c>
+      <c r="H51" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9333.9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-1092.4</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="15">
       <c r="A52" t="inlineStr">
         <is>
-          <t>상방 관찰</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>9</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>주간 순매수 45,121억으로 수급 집중도 최상위</t>
-        </is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-524</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-559</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35</v>
+      </c>
+      <c r="G52" t="n">
+        <v>528</v>
+      </c>
+      <c r="H52" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>11659.9</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-434.4</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="15">
       <c r="A53" t="inlineStr">
         <is>
-          <t>상방 관찰</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>10</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>주간 순매수 29,092억 및 대차잔고 감소로 숏커버 여지</t>
-        </is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-511</v>
+      </c>
+      <c r="E53" t="n">
+        <v>132</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G53" t="n">
+        <v>559</v>
+      </c>
+      <c r="H53" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>13946.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-546.9</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="15">
       <c r="A54" t="inlineStr">
         <is>
-          <t>하방 관찰</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>주간 순매수 -3,070억으로 수급 이탈 뚜렷</t>
+          <t>7. 수급 관찰</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="15">
       <c r="A55" t="inlineStr">
         <is>
-          <t>하방 관찰</t>
+          <t>상방 관찰</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 순매수 -1,568억으로 수급 약세 지속</t>
+          <t>주간 주가 상승률 7.86% 대비 기관 순매수 1,732억이 유입되며 수급 개선세 확인.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8. 주간 시장 흐름</t>
+          <t>상방 관찰</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>주간 주가 상승률 7.43%와 함께 외국인 528억, 기관 2,736억의 동반 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="15">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>하방 관찰</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 'Risk-On' 국면을 연출함.</t>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>주간 주가 하락률 -3.39%에도 불구하고 개인 순매수 1,233억이 집중되어 수급 부담 존재.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="15">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>하방 관찰</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수의 강세가 국내 반도체 대형주로 이어지며 지수 상승을 견인했으나, 주 후반 금리 인상 우려와 국채 금리 급등으로 상승폭을 일부 반납함.</t>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>주간 주가 하락률 -1.75%와 함께 기관 순매도 -233억이 지속되며 하방 압력 확인.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>개인 투자자는 주간 내내 대규모 순매도를 기록하며 차익 실현에 집중한 반면, 외국인과 기관은 삼성전자와 SK하이닉스를 중심으로 수급을 집중함.</t>
+          <t>8. 주간 시장 흐름</t>
         </is>
       </c>
     </row>
@@ -4235,14 +4389,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각된 점이 시장의 상단을 제한하는 요인으로 작용함.</t>
+          <t>KOSPI는 외국인과 기관의 강력한 동반 매수세에 힘입어 주 초반 4.61% 급등하며 강한 상승세를 보임.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="15">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9. 섹터·테마 흐름</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한하며 주 후반 지수 하락 및 보합세로 전환.</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4413,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전기·전자 및 기계·장비 섹터가 AI 반도체 및 원전 수주 기대감으로 주도주 지위를 공고히 함.</t>
+          <t>반도체와 원전·전력설비 관련주로 수급 쏠림 현상이 뚜렷하게 나타남.</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4425,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>건설 섹터는 미국 내 대형 원전 8기 건설 협의 소식에 힘입어 주간 7.86% 상승하며 강한 모멘텀을 보임.</t>
+          <t>개인은 주간 내내 차익 실현 매물을 쏟아내며 지수 하락 압박 요인으로 작용.</t>
         </is>
       </c>
     </row>
@@ -4278,115 +4437,57 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>반면 음식료·담배 및 부동산 섹터는 환율 하락과 고금리 장기화 부담으로 인해 차익 실현 매물이 출회되며 약세를 면치 못함.</t>
+          <t>중동 지정학적 리스크와 글로벌 경기 둔화 우려가 혼재되며 시장의 관망세가 짙어짐.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>9. 섹터·테마 흐름</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="15">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>미국 8월 비농업 고용지수 예상치 상회 및 필라델피아 반도체 지수 급등에 따른 국내 반도체 중심의 강세.</t>
+          <t>반도체/AI: 삼성전자, SK하이닉스 중심의 외국인·기관 매수세가 지속되며 시장 주도.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="15">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>원전/전력설비: 대형 수주 기대감으로 기계·장비 및 건설 섹터가 급등하며 순환매 주도.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>5</v>
-      </c>
-      <c r="E68" t="n">
-        <v>37.21</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>음식료/소비재: 글로벌 소비 둔화 우려 및 환율 영향으로 약세 전환.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>나무가</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
@@ -4398,23 +4499,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>12.31</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
         </is>
       </c>
     </row>
@@ -4426,23 +4516,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>네오오토</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>15.02</v>
+        <v>40.59</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4454,23 +4544,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>13.01</v>
+        <v>37.21</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -4482,23 +4572,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>8.859999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4600,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4519,115 +4609,126 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>5.48</v>
+        <v>12.31</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="15">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15.02</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>국내 2분기 GDP 성장률 0.6%로 둔화 및 미국 금리 인상 우려 부각에 따른 지수 조정.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="15">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>34.07</v>
+        <v>13.01</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>39.88</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="15">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>37.07</v>
+        <v>5.48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4639,23 +4740,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>5</v>
-      </c>
-      <c r="E79" t="n">
-        <v>32.53</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>미국 국채금리 상승 및 국내 2분기 GDP 성장률(0.6%) 둔화로 지수 0.58% 하락.</t>
         </is>
       </c>
     </row>
@@ -4667,23 +4757,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>31.32</v>
+        <v>34.07</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -4695,109 +4785,234 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>18.52</v>
+        <v>39.88</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="15">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>서전기전</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>반도체 대형주 수급 유지 시 지수 하단 지지</t>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>미국 물가 지표 충격 시 금리 인상 우려 재점화</t>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>미국 CPI 및 PPI 발표 결과</t>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
-          <t>핵심 이벤트</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>미국 고용지표 호조에 따른 금리 인상 우려와 중동 지정학적 리스크로 관망세 지속.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" t="inlineStr">
         <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="15">
       <c r="A88" t="inlineStr">
         <is>
+          <t>상승 시나리오</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>미국 CPI가 예상치를 하회하면 금리 인상 우려 완화로 반도체 중심 상승세 재개</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="15">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>하방 시나리오</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>미국 CPI가 예상치를 상회하면 고금리 장기화 우려로 외국인 수급 이탈 및 지수 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="15">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>판별 신호</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="15">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>핵심 이벤트</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>국내 무역수지</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15"/>
-    <row r="90" ht="15" customHeight="1" s="15"/>
-    <row r="91" ht="15" customHeight="1" s="15"/>
-    <row r="93" ht="15" customHeight="1" s="15"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>미국 소비자물가지수(CPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>한국 무역수지</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="15">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>미국 소매판매</t>
+        </is>
+      </c>
+    </row>
     <row r="94" ht="15" customHeight="1" s="15"/>
     <row r="95" ht="15" customHeight="1" s="15"/>
     <row r="96" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 08:48 KST</t>
+          <t>2026-09-09 09:14 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체와 원전이 주도한 급등 랠리와 고금리 경계감의 공존</t>
+          <t>AI 반도체와 원전 모멘텀이 이끈 주간 상승세</t>
         </is>
       </c>
     </row>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-98706</v>
+        <v>-98067</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>31848</v>
+        <v>31154</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>32918</v>
+        <v>32584</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>-1.34</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>3387</v>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>-99</v>
+        <v>2870</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>542</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>-3471</v>
+        <v>-3583</v>
       </c>
     </row>
     <row r="10"/>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>건설 +7.86%</t>
+          <t>건설 +12.14%</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>기계·장비 +7.43%</t>
+          <t>기계·장비 +11.19%</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>전기·전자 +5.93%</t>
+          <t>전기·전자 +7.09%</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>음식료·담배 -3.39%</t>
+          <t>음식료·담배 -3.69%</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>IT 서비스 -1.75%</t>
+          <t>IT 서비스 -2.18%</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>화학 -1.32%</t>
+          <t>섬유·의류 -1.91%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="44.5" customHeight="1" s="15">
+    <row r="27" ht="58" customHeight="1" s="15">
       <c r="A27" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감이 상단을 제한함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44.5" customHeight="1" s="15">
+          <t>미국 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단이 제한됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1" s="15">
       <c r="A28" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1404,40 +1404,40 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44.5" customHeight="1" s="15">
+          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 8기 건설 협의 소식이 국내 건설 및 전기·가스 섹터의 강세를 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1" s="15">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
-        <v>0</v>
+      <c r="B29" s="29" t="n">
+        <v>0.79</v>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="30" t="inlineStr">
-        <is>
-          <t>데이터 없음</t>
+          <t>436▲/370▼</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>987▲/561▼ 상한3</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>건설, 기계·장비</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려와 중동 지정학적 리스크가 겹치며 시장의 관망세가 짙어짐.</t>
+          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려에도 불구하고, 해외 원전 및 AIDC 수주 기대감이 건설·기계 섹터의 상승을 주도함.</t>
         </is>
       </c>
     </row>
@@ -1477,21 +1477,21 @@
     <row r="33" ht="31" customHeight="1" s="15">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경: 미국 비농업고용지수(162K)가 예상치(55K)를 상회하며 고용 호조를 보였으나, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
+          <t>- 매크로 환경은 미국 비농업고용지수가 162K로 예상치를 상회하며 금리 인상 우려를 자극했고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 공존함.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="31" customHeight="1" s="15">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주도권을 형성했으나, 개인은 전 섹터에서 차익 실현 매물을 출회함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
+          <t>- 수급 구도는 전기·전자 섹터에 외국인 31,234억, 기관 25,529억이 집중되었고, 기계·장비 섹터에도 기관 2,795억이 유입되며 주도 섹터로 자리 잡음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1" s="15">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>- 종합 관점: 반도체와 원전 중심의 수급 쏠림이 뚜렷한 가운데, 매크로 불확실성 확대가 지수 변동성을 키우는 국면임.</t>
+          <t>- 종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 원전이라는 확실한 모멘텀이 수급을 견인하며 시장의 하방을 지지하는 국면임.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주간 주가 상승률 7.86% 대비 기관 순매수 1,732억이 유입되며 수급 개선세 확인.</t>
+          <t>주간 12.14% 상승하며 기관이 1,743억 순매수함.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>주간 주가 상승률 7.43%와 함께 외국인 528억, 기관 2,736억의 동반 매수세 유입.</t>
+          <t>주간 11.19% 상승하며 기관이 2,795억 순매수함.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>주간 주가 하락률 -3.39%에도 불구하고 개인 순매수 1,233억이 집중되어 수급 부담 존재.</t>
+          <t>주간 3.69% 하락하며 기관이 1,083억 순매도함.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>주간 주가 하락률 -1.75%와 함께 기관 순매도 -233억이 지속되며 하방 압력 확인.</t>
+          <t>주간 2.18% 하락하며 기관이 250억 순매도함.</t>
         </is>
       </c>
     </row>
@@ -2434,102 +2434,127 @@
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>- KOSPI는 외국인과 기관의 강력한 동반 매수세에 힘입어 주 초반 4.61% 급등하며 강한 상승세를 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" s="15">
+          <t>- 주 초반 미국 반도체 지수 급등에 힘입어 KOSPI가 4.61% 급등하며 7000선에 근접함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="15">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한하며 주 후반 지수 하락 및 보합세로 전환.</t>
+          <t>- 미국 고용지표 호조에 따른 금리 인상 우려가 부각되며 주 중반 지수 조정이 발생함.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="15">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>- 반도체와 원전·전력설비 관련주로 수급 쏠림 현상이 뚜렷하게 나타남.</t>
+          <t>- 원전 및 데이터센터 전력 수요 관련 수주 기대감이 건설·기계 섹터의 강세를 견인함.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 개인은 주간 내내 차익 실현 매물을 쏟아내며 지수 하락 압박 요인으로 작용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="15">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>- 중동 지정학적 리스크와 글로벌 경기 둔화 우려가 혼재되며 시장의 관망세가 짙어짐.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+          <t>- 외국인과 기관은 전기·전자 섹터에 각각 31,234억, 25,529억을 순매수하며 수급을 주도함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>섹터·테마 흐름</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="15">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>- 전기·전자: AI 반도체 수요 기대감으로 주간 7.09% 상승하며 수급 집중.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="15">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>- 반도체/AI: 삼성전자, SK하이닉스 중심의 외국인·기관 매수세가 지속되며 시장 주도.</t>
+          <t>- 건설/기계·장비: 원전 및 데이터센터 수주 기대감으로 각각 12.14%, 11.19% 상승하며 주도 섹터로 부상.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t>- 원전/전력설비: 대형 수주 기대감으로 기계·장비 및 건설 섹터가 급등하며 순환매 주도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>- 음식료/소비재: 글로벌 소비 둔화 우려 및 환율 영향으로 약세 전환.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
+          <t>- 음식료/보험: 규제 및 실적 우려로 각각 3.69%, 0.37% 하락하며 약세 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>주간 촉매 타임라인</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="18" t="inlineStr">
+        <is>
+          <t>등락률 = 주간 누적</t>
+        </is>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>주간 촉매 타임라인</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" s="3" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="18" t="inlineStr">
-        <is>
-          <t>등락률 = 주간 누적</t>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>등락률(%)</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>핵심 촉매</t>
         </is>
       </c>
     </row>
@@ -2539,17 +2564,27 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B81" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C81" s="30" t="inlineStr"/>
-      <c r="D81" s="14" t="inlineStr"/>
-      <c r="E81" s="29" t="inlineStr"/>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>네오오토 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E81" s="29" t="n">
+        <v>40.59</v>
+      </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2596,7 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>네오오토 (운송장비·부품)</t>
+          <t>필옵틱스 (기계·장비)</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
@@ -2575,11 +2610,11 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>40.59</v>
+        <v>37.21</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2626,7 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>필옵틱스 (기계·장비)</t>
+          <t>나무가 (전기·전자)</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
@@ -2605,11 +2640,11 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>37.21</v>
+        <v>10.23</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2656,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>나무가 (전기·전자)</t>
+          <t>두산퓨얼셀 (전기·전자)</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -2635,11 +2670,11 @@
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>10.23</v>
+        <v>12.31</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2686,7 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>두산퓨얼셀 (전기·전자)</t>
+          <t>DB하이텍 (전기·전자)</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
@@ -2661,15 +2696,15 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>12.31</v>
+        <v>15.02</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2716,7 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>DB하이텍 (전기·전자)</t>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
@@ -2695,11 +2730,11 @@
         </is>
       </c>
       <c r="E86" s="29" t="n">
-        <v>15.02</v>
+        <v>13.01</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2746,7 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>두산에너빌리티 (기계·장비)</t>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
@@ -2725,11 +2760,11 @@
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>13.01</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2776,7 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>SK하이닉스 (전기·전자)</t>
+          <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
@@ -2755,41 +2790,41 @@
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" s="15">
       <c r="A89" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>삼성전자 (전기·전자)</t>
+          <t>빛과전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E89" s="29" t="n">
-        <v>5.48</v>
+        <v>34.07</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -2799,17 +2834,27 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B90" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C90" s="30" t="inlineStr"/>
-      <c r="D90" s="14" t="inlineStr"/>
-      <c r="E90" s="29" t="inlineStr"/>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>오르비텍 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="C90" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E90" s="29" t="n">
+        <v>39.88</v>
+      </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 상승 및 국내 2분기 GDP 성장률(0.6%) 둔화로 지수 0.58% 하락.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2866,7 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>빛과전자 (전기·전자)</t>
+          <t>서전기전 (전기·전자)</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
@@ -2835,28 +2880,28 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>34.07</v>
+        <v>37.07</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="15">
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="31" customHeight="1" s="15">
       <c r="A92" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B92" s="30" t="inlineStr">
-        <is>
-          <t>오르비텍</t>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>한전기술 (일반서비스)</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -2865,11 +2910,11 @@
         </is>
       </c>
       <c r="E92" s="29" t="n">
-        <v>39.88</v>
+        <v>32.53</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2881,25 +2926,25 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>서전기전 (전기·전자)</t>
+          <t>현대약품 (제약)</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>37.07</v>
+        <v>31.32</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2956,7 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>한전기술 (일반서비스)</t>
+          <t>대우건설 (건설)</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
@@ -2921,205 +2966,126 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E94" s="29" t="n">
-        <v>32.53</v>
+        <v>18.52</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="31" customHeight="1" s="15">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>현대약품 (제약)</t>
-        </is>
-      </c>
-      <c r="C95" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E95" s="29" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="F95" s="17" t="inlineStr">
-        <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="31" customHeight="1" s="15">
-      <c r="A96" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>대우건설 (건설)</t>
-        </is>
-      </c>
-      <c r="C96" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E96" s="29" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="F96" s="17" t="inlineStr">
-        <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="31" customHeight="1" s="15">
-      <c r="A97" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B97" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C97" s="30" t="inlineStr"/>
-      <c r="D97" s="14" t="inlineStr"/>
-      <c r="E97" s="29" t="inlineStr"/>
-      <c r="F97" s="17" t="inlineStr">
-        <is>
-          <t>미국 고용지표 호조에 따른 금리 인상 우려와 중동 지정학적 리스크로 관망세 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr"/>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="3" t="inlineStr"/>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="31" customHeight="1" s="15">
-      <c r="A101" s="31" t="inlineStr">
+    <row r="98" ht="31" customHeight="1" s="15">
+      <c r="A98" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>미국 물가 지표가 안정적으로 확인되면 반도체 및 원전 주도 상승세 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="31" customHeight="1" s="15">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>하방 시나리오</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화될 경우 조정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="15">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>판별 신호</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI) 결과가 시장 방향성을 결정할 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="15">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>미국 CPI가 예상치를 하회하면 금리 인상 우려 완화로 반도체 중심 상승세 재개</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="31" customHeight="1" s="15">
-      <c r="A102" s="32" t="inlineStr">
-        <is>
-          <t>하방 시나리오</t>
+          <t>미국 소비자물가지수(CPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="15">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>미국 CPI가 예상치를 상회하면 고금리 장기화 우려로 외국인 수급 이탈 및 지수 조정</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="15">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="15">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="15">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>한국 무역수지</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="15">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>미국 소매판매</t>
+          <t>국내 무역수지</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="48">
+    <mergeCell ref="B98:J98"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="F87:J87"/>
@@ -3135,39 +3101,35 @@
     <mergeCell ref="C64:J64"/>
     <mergeCell ref="F83:J83"/>
     <mergeCell ref="B103:J103"/>
-    <mergeCell ref="F95:J95"/>
+    <mergeCell ref="B99:J99"/>
     <mergeCell ref="C63:J63"/>
     <mergeCell ref="C65:J65"/>
     <mergeCell ref="F86:J86"/>
     <mergeCell ref="A77:J77"/>
     <mergeCell ref="A34:J34"/>
+    <mergeCell ref="F80:J80"/>
     <mergeCell ref="F94:J94"/>
-    <mergeCell ref="A73:J73"/>
     <mergeCell ref="F85:J85"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="B68:J68"/>
-    <mergeCell ref="F97:J97"/>
-    <mergeCell ref="B104:J104"/>
     <mergeCell ref="F91:J91"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="F81:J81"/>
     <mergeCell ref="B32:J32"/>
-    <mergeCell ref="A78:J78"/>
     <mergeCell ref="F90:J90"/>
     <mergeCell ref="A69:J69"/>
-    <mergeCell ref="B106:J106"/>
     <mergeCell ref="F93:J93"/>
     <mergeCell ref="C61:J61"/>
+    <mergeCell ref="B97:J97"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="F96:J96"/>
+    <mergeCell ref="B100:J100"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B100:J100"/>
+    <mergeCell ref="A75:J75"/>
     <mergeCell ref="F92:J92"/>
     <mergeCell ref="A71:J71"/>
     <mergeCell ref="F82:J82"/>
     <mergeCell ref="B102:J102"/>
-    <mergeCell ref="B105:J105"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="F88:J88"/>
@@ -3182,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -3214,7 +3176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 08:48 KST</t>
+          <t>2026-09-09 09:14 KST</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반도체와 원전이 주도한 급등 랠리와 고금리 경계감의 공존</t>
+          <t>AI 반도체와 원전 모멘텀이 이끈 주간 상승세</t>
         </is>
       </c>
     </row>
@@ -3266,13 +3228,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-98706</v>
+        <v>-98067</v>
       </c>
       <c r="C7" t="n">
-        <v>31848</v>
+        <v>31154</v>
       </c>
       <c r="D7" t="n">
-        <v>32918</v>
+        <v>32584</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="15">
@@ -3282,13 +3244,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3387</v>
+        <v>2870</v>
       </c>
       <c r="C8" t="n">
-        <v>-99</v>
+        <v>542</v>
       </c>
       <c r="D8" t="n">
-        <v>-3471</v>
+        <v>-3583</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="15">
@@ -3495,7 +3457,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감이 상단을 제한함.</t>
+          <t>미국 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단이 제한됨.</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3472,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 국내 증시의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
+          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 8기 건설 협의 소식이 국내 건설 및 전기·가스 섹터의 강세를 견인함.</t>
         </is>
       </c>
     </row>
@@ -3521,11 +3483,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려와 중동 지정학적 리스크가 겹치며 시장의 관망세가 짙어짐.</t>
+          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려에도 불구하고, 해외 원전 및 AIDC 수주 기대감이 건설·기계 섹터의 상승을 주도함.</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3506,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>매크로 환경: 미국 비농업고용지수(162K)가 예상치(55K)를 상회하며 고용 호조를 보였으나, 국내 2분기 GDP 성장률(0.6%)은 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각됨.</t>
+          <t>매크로 환경은 미국 비농업고용지수가 162K로 예상치를 상회하며 금리 인상 우려를 자극했고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 공존함.</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3518,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>수급 구도: 전기·전자 섹터에 외국인(32,305억)과 기관(25,821억)의 매수세가 집중되며 주도권을 형성했으나, 개인은 전 섹터에서 차익 실현 매물을 출회함.</t>
+          <t>수급 구도는 전기·전자 섹터에 외국인 31,234억, 기관 25,529억이 집중되었고, 기계·장비 섹터에도 기관 2,795억이 유입되며 주도 섹터로 자리 잡음.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3530,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>종합 관점: 반도체와 원전 중심의 수급 쏠림이 뚜렷한 가운데, 매크로 불확실성 확대가 지수 변동성을 키우는 국면임.</t>
+          <t>종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 원전이라는 확실한 모멘텀이 수급을 견인하며 시장의 하방을 지지하는 국면임.</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4281,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 주가 상승률 7.86% 대비 기관 순매수 1,732억이 유입되며 수급 개선세 확인.</t>
+          <t>주간 12.14% 상승하며 기관이 1,743억 순매수함.</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4298,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>주간 주가 상승률 7.43%와 함께 외국인 528억, 기관 2,736억의 동반 매수세 유입.</t>
+          <t>주간 11.19% 상승하며 기관이 2,795억 순매수함.</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4315,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>주간 주가 하락률 -3.39%에도 불구하고 개인 순매수 1,233억이 집중되어 수급 부담 존재.</t>
+          <t>주간 3.69% 하락하며 기관이 1,083억 순매도함.</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4332,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>주간 주가 하락률 -1.75%와 함께 기관 순매도 -233억이 지속되며 하방 압력 확인.</t>
+          <t>주간 2.18% 하락하며 기관이 250억 순매도함.</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4351,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KOSPI는 외국인과 기관의 강력한 동반 매수세에 힘입어 주 초반 4.61% 급등하며 강한 상승세를 보임.</t>
+          <t>주 초반 미국 반도체 지수 급등에 힘입어 KOSPI가 4.61% 급등하며 7000선에 근접함.</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4363,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 국채 금리 상승이 시장 상단을 제한하며 주 후반 지수 하락 및 보합세로 전환.</t>
+          <t>미국 고용지표 호조에 따른 금리 인상 우려가 부각되며 주 중반 지수 조정이 발생함.</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4375,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>반도체와 원전·전력설비 관련주로 수급 쏠림 현상이 뚜렷하게 나타남.</t>
+          <t>원전 및 데이터센터 전력 수요 관련 수주 기대감이 건설·기계 섹터의 강세를 견인함.</t>
         </is>
       </c>
     </row>
@@ -4425,26 +4387,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>개인은 주간 내내 차익 실현 매물을 쏟아내며 지수 하락 압박 요인으로 작용.</t>
+          <t>외국인과 기관은 전기·전자 섹터에 각각 31,234억, 25,529억을 순매수하며 수급을 주도함.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>중동 지정학적 리스크와 글로벌 경기 둔화 우려가 혼재되며 시장의 관망세가 짙어짐.</t>
+          <t>9. 섹터·테마 흐름</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9. 섹터·테마 흐름</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>전기·전자: AI 반도체 수요 기대감으로 주간 7.09% 상승하며 수급 집중.</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4418,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>반도체/AI: 삼성전자, SK하이닉스 중심의 외국인·기관 매수세가 지속되며 시장 주도.</t>
+          <t>건설/기계·장비: 원전 및 데이터센터 수주 기대감으로 각각 12.14%, 11.19% 상승하며 주도 섹터로 부상.</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4430,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>원전/전력설비: 대형 수주 기대감으로 기계·장비 및 건설 섹터가 급등하며 순환매 주도.</t>
+          <t>음식료/보험: 규제 및 실적 우려로 각각 3.69%, 0.37% 하락하며 약세 지속.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>음식료/소비재: 글로벌 소비 둔화 우려 및 환율 영향으로 약세 전환.</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네오오토</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4477,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>필옵틱스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>37.21</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>외국인(+25,532억)과 기관(+26,491억)의 강력한 동반 매수세 유입으로 KOSPI 4.61% 급등.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4505,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네오오토</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4528,11 +4517,11 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>40.59</v>
+        <v>10.23</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4544,23 +4533,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>37.21</v>
+        <v>12.31</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4572,23 +4561,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>10.23</v>
+        <v>15.02</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4589,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4609,14 +4598,14 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>12.31</v>
+        <v>13.01</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4617,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4640,11 +4629,11 @@
         <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>15.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4645,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4668,67 +4657,67 @@
         <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>13.01</v>
+        <v>5.48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>8.859999999999999</v>
+        <v>34.07</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="15">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>5.48</v>
+        <v>39.88</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4729,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>서전기전</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>37.07</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>미국 국채금리 상승 및 국내 2분기 GDP 성장률(0.6%) 둔화로 지수 0.58% 하락.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -4757,23 +4757,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>34.07</v>
+        <v>32.53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4785,23 +4785,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>39.88</v>
+        <v>31.32</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -4813,206 +4813,108 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>37.07</v>
+        <v>18.52</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>5</v>
-      </c>
-      <c r="E83" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>4</v>
-      </c>
-      <c r="E84" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 물가 지표가 안정적으로 확인되면 반도체 및 원전 주도 상승세 지속.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>4</v>
-      </c>
-      <c r="E85" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화될 경우 조정.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>미국 고용지표 호조에 따른 금리 인상 우려와 중동 지정학적 리스크로 관망세 지속.</t>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI) 결과가 시장 방향성을 결정할 것.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="15">
       <c r="A88" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>미국 CPI가 예상치를 하회하면 금리 인상 우려 완화로 반도체 중심 상승세 재개</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="15">
       <c r="A89" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>미국 CPI가 예상치를 상회하면 고금리 장기화 우려로 외국인 수급 이탈 및 지수 조정</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>판별 신호</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>한국 무역수지</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="15">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>미국 소매판매</t>
-        </is>
-      </c>
-    </row>
+          <t>국내 무역수지</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="15"/>
+    <row r="91" ht="15" customHeight="1" s="15"/>
+    <row r="93" ht="15" customHeight="1" s="15"/>
     <row r="94" ht="15" customHeight="1" s="15"/>
     <row r="95" ht="15" customHeight="1" s="15"/>
     <row r="96" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 09:14 KST</t>
+          <t>2026-09-09 09:21 KST</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="E81" s="29" t="n">
-        <v>40.59</v>
+        <v>40.81</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>37.21</v>
+        <v>37.02</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>10.23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>12.31</v>
+        <v>19.5</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>15.02</v>
+        <v>24.36</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="E86" s="29" t="n">
-        <v>13.01</v>
+        <v>16.16</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>5.48</v>
+        <v>5.58</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="E89" s="29" t="n">
-        <v>34.07</v>
+        <v>42.17</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>39.88</v>
+        <v>43.82</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>37.07</v>
+        <v>35.64</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="E92" s="29" t="n">
-        <v>32.53</v>
+        <v>40.52</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>31.32</v>
+        <v>28.43</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E94" s="29" t="n">
-        <v>18.52</v>
+        <v>20.77</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:14 KST</t>
+          <t>2026-09-09 09:21 KST</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>40.59</v>
+        <v>40.81</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>37.21</v>
+        <v>37.02</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>10.23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>12.31</v>
+        <v>19.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>15.02</v>
+        <v>24.36</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>13.01</v>
+        <v>16.16</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>8.859999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>5.48</v>
+        <v>5.58</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>34.07</v>
+        <v>42.17</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>39.88</v>
+        <v>43.82</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>37.07</v>
+        <v>35.64</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>32.53</v>
+        <v>40.52</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>31.32</v>
+        <v>28.43</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>18.52</v>
+        <v>20.77</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -7,7 +7,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간 브리핑" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원본 데이터" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신고가 근접" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투자자별 순매수" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공매도·대차" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원본 데이터" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -251,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -343,6 +347,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -747,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -787,7 +794,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 09:21 KST</t>
+          <t>2026-09-09 09:39 KST</t>
         </is>
       </c>
     </row>
@@ -800,7 +807,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>AI 반도체와 원전 모멘텀이 이끈 주간 상승세</t>
+          <t>반도체와 원전·건설이 이끈 안도 랠리와 매크로 경계감의 혼조</t>
         </is>
       </c>
     </row>
@@ -1009,19 +1016,19 @@
           <t>KR 상승 섹터</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>건설 +12.14%</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>기계·장비 +11.19%</t>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>기계·장비 +11.08%</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>건설 +10.99%</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>전기·전자 +7.09%</t>
+          <t>전기·전자 +6.71%</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1040,17 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>음식료·담배 -3.69%</t>
+          <t>음식료·담배 -3.76%</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>IT 서비스 -2.18%</t>
+          <t>IT 서비스 -2.61%</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>섬유·의류 -1.91%</t>
+          <t>섬유·의류 -2.01%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1349,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1" s="15">
+    <row r="27" ht="71.5" customHeight="1" s="15">
       <c r="A27" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1371,11 +1378,11 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단이 제한됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1" s="15">
+          <t>미국 필라델피아 반도체 지수가 3.37% 급등하고 고용지표 호조로 금리 인하 기대감이 후퇴하는 중립 스탠스 속에서도, 국내 증시는 반도체 대형주 중심의 강력한 외국인·기관 매수세가 유입되며 코스피가 4.61% 급등했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="71.5" customHeight="1" s="15">
       <c r="A28" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1404,11 +1411,11 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 8기 건설 협의 소식이 국내 건설 및 전기·가스 섹터의 강세를 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1" s="15">
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 제기되는 중립 스탠스 하에서, 국내 증시는 미국 원전 건설 협의 기대감으로 원전·건설주는 급등했으나 경기 둔화 우려와 개인 매도세로 코스피가 0.58% 하락했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="71.5" customHeight="1" s="15">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -1419,7 +1426,7 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>436▲/370▼</t>
+          <t>470▲/372▼</t>
         </is>
       </c>
       <c r="D29" s="29" t="n">
@@ -1427,7 +1434,7 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>987▲/561▼ 상한3</t>
+          <t>949▲/661▼ 상한2</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -1437,7 +1444,7 @@
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려에도 불구하고, 해외 원전 및 AIDC 수주 기대감이 건설·기계 섹터의 상승을 주도함.</t>
+          <t>미국 고용지표의 블로우아웃 수준 발표로 금리 인상 우려가 재점화된 위험회피 스탠스 속에서도, 국내 증시는 해외 원전 및 AIDC 수주 기대감과 반도체 장비 투자 확대 기대감에 힘입어 코스피가 0.79% 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1481,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="31" customHeight="1" s="15">
+    <row r="33" ht="44.5" customHeight="1" s="15">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경은 미국 비농업고용지수가 162K로 예상치를 상회하며 금리 인상 우려를 자극했고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 공존함.</t>
+          <t>- 이번 주 매크로 환경은 미국의 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 크게 상회해 금리 인하 경로에 대한 불확실성을 키웠고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려를 자극했습니다.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="31" customHeight="1" s="15">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도는 전기·전자 섹터에 외국인 31,234억, 기관 25,529억이 집중되었고, 기계·장비 섹터에도 기관 2,795억이 유입되며 주도 섹터로 자리 잡음.</t>
+          <t>- 수급 측면에서는 전기·전자 업종에 외국인(+30,380억원)과 기관(+26,434억원)의 순매수가 집중되며 주간 6.71% 상승했고, 기계·장비 업종 역시 기관(+2,888억원)의 매수세로 11.08% 급등했습니다.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="31" customHeight="1" s="15">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>- 종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 원전이라는 확실한 모멘텀이 수급을 견인하며 시장의 하방을 지지하는 국면임.</t>
+          <t>- 반면 음식료·담배 업종은 기관(-1,100억원)과 외국인(-202억원)의 동반 순매도로 주간 3.76% 하락하며 밸류에이션 부담과 환율 하락에 따른 수출 우려를 반영했습니다.</t>
         </is>
       </c>
     </row>
@@ -1587,10 +1594,10 @@
         </is>
       </c>
       <c r="D39" s="29" t="n">
-        <v>45121</v>
+        <v>43264</v>
       </c>
       <c r="E39" s="29" t="n">
-        <v>21100</v>
+        <v>19244</v>
       </c>
       <c r="F39" s="29" t="n">
         <v>24020</v>
@@ -1623,10 +1630,10 @@
         </is>
       </c>
       <c r="D40" s="29" t="n">
-        <v>29092</v>
+        <v>28602</v>
       </c>
       <c r="E40" s="29" t="n">
-        <v>19197</v>
+        <v>18707</v>
       </c>
       <c r="F40" s="29" t="n">
         <v>9895</v>
@@ -1659,10 +1666,10 @@
         </is>
       </c>
       <c r="D41" s="29" t="n">
-        <v>5294</v>
+        <v>4949</v>
       </c>
       <c r="E41" s="29" t="n">
-        <v>3070</v>
+        <v>2725</v>
       </c>
       <c r="F41" s="29" t="n">
         <v>2223</v>
@@ -1691,29 +1698,29 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>삼성전자우 (전기·전자)</t>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="D42" s="29" t="n">
-        <v>2338</v>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>740</v>
+        <v>2172</v>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>-48</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>1598</v>
+        <v>2220</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>-2361</v>
+        <v>-2125</v>
       </c>
       <c r="H42" s="30" t="n">
-        <v>206.2</v>
+        <v>900.5</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>28477.7</v>
+        <v>19469.6</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>-666.1</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="43" ht="31" customHeight="1" s="15">
@@ -1727,29 +1734,29 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>두산에너빌리티 (기계·장비)</t>
+          <t>삼성전자우 (전기·전자)</t>
         </is>
       </c>
       <c r="D43" s="29" t="n">
-        <v>2138</v>
-      </c>
-      <c r="E43" s="28" t="n">
-        <v>-81</v>
+        <v>2097</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <v>499</v>
       </c>
       <c r="F43" s="29" t="n">
-        <v>2220</v>
+        <v>1598</v>
       </c>
       <c r="G43" s="28" t="n">
-        <v>-2125</v>
+        <v>-2361</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>900.5</v>
+        <v>206.2</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>19469.6</v>
+        <v>28477.7</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>-5.9</v>
+        <v>-666.1</v>
       </c>
     </row>
     <row r="44" ht="31" customHeight="1" s="15">
@@ -1767,10 +1774,10 @@
         </is>
       </c>
       <c r="D44" s="29" t="n">
-        <v>1581</v>
+        <v>1546</v>
       </c>
       <c r="E44" s="29" t="n">
-        <v>1000</v>
+        <v>965</v>
       </c>
       <c r="F44" s="29" t="n">
         <v>581</v>
@@ -1803,10 +1810,10 @@
         </is>
       </c>
       <c r="D45" s="29" t="n">
-        <v>1182</v>
+        <v>1141</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="F45" s="29" t="n">
         <v>541</v>
@@ -1839,10 +1846,10 @@
         </is>
       </c>
       <c r="D46" s="29" t="n">
-        <v>852</v>
+        <v>911</v>
       </c>
       <c r="E46" s="29" t="n">
-        <v>687</v>
+        <v>745</v>
       </c>
       <c r="F46" s="29" t="n">
         <v>166</v>
@@ -1871,29 +1878,29 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>대우건설 (건설)</t>
+          <t>현대건설 (건설)</t>
         </is>
       </c>
       <c r="D47" s="29" t="n">
-        <v>813</v>
-      </c>
-      <c r="E47" s="29" t="n">
-        <v>369</v>
+        <v>791</v>
+      </c>
+      <c r="E47" s="28" t="n">
+        <v>-221</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>444</v>
+        <v>1011</v>
       </c>
       <c r="G47" s="28" t="n">
-        <v>-812</v>
+        <v>-760</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>164.4</v>
+        <v>292.4</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>6222.6</v>
+        <v>8765.6</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>482.9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" ht="31" customHeight="1" s="15">
@@ -1907,29 +1914,29 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>현대건설 (건설)</t>
+          <t>LS ELECTRIC (전기·전자)</t>
         </is>
       </c>
       <c r="D48" s="29" t="n">
-        <v>754</v>
-      </c>
-      <c r="E48" s="28" t="n">
-        <v>-258</v>
+        <v>711</v>
+      </c>
+      <c r="E48" s="29" t="n">
+        <v>431</v>
       </c>
       <c r="F48" s="29" t="n">
-        <v>1011</v>
+        <v>280</v>
       </c>
       <c r="G48" s="28" t="n">
-        <v>-760</v>
+        <v>-649</v>
       </c>
       <c r="H48" s="30" t="n">
-        <v>292.4</v>
+        <v>37.7</v>
       </c>
       <c r="I48" s="30" t="n">
-        <v>8765.6</v>
+        <v>9403.4</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" ht="31" customHeight="1" s="15">
@@ -1947,10 +1954,10 @@
         </is>
       </c>
       <c r="D49" s="28" t="n">
-        <v>-3070</v>
+        <v>-2718</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>-2520</v>
+        <v>-2168</v>
       </c>
       <c r="F49" s="28" t="n">
         <v>-550</v>
@@ -1983,10 +1990,10 @@
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>-1568</v>
+        <v>-1521</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>-695</v>
+        <v>-648</v>
       </c>
       <c r="F50" s="28" t="n">
         <v>-873</v>
@@ -2091,10 +2098,10 @@
         </is>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-679</v>
+        <v>-700</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>-292</v>
+        <v>-313</v>
       </c>
       <c r="F53" s="28" t="n">
         <v>-386</v>
@@ -2148,7 +2155,7 @@
         <v>-390.7</v>
       </c>
     </row>
-    <row r="55" ht="44.5" customHeight="1" s="15">
+    <row r="55" ht="31" customHeight="1" s="15">
       <c r="A55" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2159,32 +2166,32 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>레인보우로보틱스 (기계·장비)</t>
+          <t>LG이노텍 (전기·전자)</t>
         </is>
       </c>
       <c r="D55" s="28" t="n">
-        <v>-593</v>
+        <v>-598</v>
       </c>
       <c r="E55" s="28" t="n">
-        <v>-468</v>
+        <v>-212</v>
       </c>
       <c r="F55" s="28" t="n">
-        <v>-125</v>
+        <v>-386</v>
       </c>
       <c r="G55" s="29" t="n">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="H55" s="30" t="n">
-        <v>222.6</v>
+        <v>563.7</v>
       </c>
       <c r="I55" s="30" t="n">
-        <v>6895.6</v>
+        <v>9333.9</v>
       </c>
       <c r="J55" s="30" t="n">
-        <v>-292.3</v>
-      </c>
-    </row>
-    <row r="56" ht="31" customHeight="1" s="15">
+        <v>-1092.4</v>
+      </c>
+    </row>
+    <row r="56" ht="44.5" customHeight="1" s="15">
       <c r="A56" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2195,29 +2202,29 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>LG이노텍 (전기·전자)</t>
+          <t>레인보우로보틱스 (기계·장비)</t>
         </is>
       </c>
       <c r="D56" s="28" t="n">
-        <v>-582</v>
+        <v>-593</v>
       </c>
       <c r="E56" s="28" t="n">
-        <v>-195</v>
+        <v>-468</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>-386</v>
+        <v>-125</v>
       </c>
       <c r="G56" s="29" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="H56" s="30" t="n">
-        <v>563.7</v>
+        <v>222.6</v>
       </c>
       <c r="I56" s="30" t="n">
-        <v>9333.9</v>
+        <v>6895.6</v>
       </c>
       <c r="J56" s="30" t="n">
-        <v>-1092.4</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="57" ht="44.5" customHeight="1" s="15">
@@ -2267,29 +2274,29 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>알테오젠 (일반서비스)</t>
+          <t>OCI홀딩스 (금융)</t>
         </is>
       </c>
       <c r="D58" s="28" t="n">
-        <v>-511</v>
-      </c>
-      <c r="E58" s="29" t="n">
-        <v>132</v>
+        <v>-478</v>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>-42</v>
       </c>
       <c r="F58" s="28" t="n">
-        <v>-643</v>
+        <v>-437</v>
       </c>
       <c r="G58" s="29" t="n">
-        <v>559</v>
+        <v>507</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>314.6</v>
+        <v>37.7</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>13946.5</v>
+        <v>3421.8</v>
       </c>
       <c r="J58" s="30" t="n">
-        <v>-546.9</v>
+        <v>-191.7</v>
       </c>
     </row>
     <row r="59"/>
@@ -2330,261 +2337,248 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="15">
+    <row r="62" ht="31" customHeight="1" s="15">
       <c r="A62" s="8" t="inlineStr">
         <is>
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>건설</t>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주간 12.14% 상승하며 기관이 1,743억 순매수함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="15">
+          <t>주간 수급 집중 1위 종목으로 외국인(+19,244억원)과 기관(+24,020억원)의 강력한 순매수가 유입되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="15">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>상방 관찰</t>
         </is>
       </c>
-      <c r="B63" s="30" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>주간 11.19% 상승하며 기관이 2,795억 순매수함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="15">
-      <c r="A64" s="10" t="inlineStr">
+          <t>주간 수급 집중 2위 종목으로 외국인(+18,707억원)과 기관(+9,895억원)의 순매수가 집중되었으며 대차잔고가 2,044.8억원 감소하여 숏커버 여지가 존재합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>상방 관찰</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>건설 업종 주간 10.99% 상승 속에서 기관이 1,011억원을 순매수하였고 대차잔고가 297.0% 증가하여 향후 숏커버링 가능성을 관찰할 필요가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>주간 3.69% 하락하며 기관이 1,083억 순매도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="15">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>주간 순매수 최하위 종목으로 외국인(-2,168억원)과 기관(-550억원)의 동반 순매도가 출회되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>하방 관찰</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>주간 2.18% 하락하며 기관이 250억 순매도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>삼양식품 (음식료·담배)</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>음식료·담배 업종의 주간 3.76% 하락 속에서 기관(-833억원)과 외국인(-135억원)의 순매도가 집중되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>주간 시장 흐름</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="15">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>- 주 초반 미국 반도체 지수 급등에 힘입어 KOSPI가 4.61% 급등하며 7000선에 근접함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="15">
+    <row r="70" ht="31" customHeight="1" s="15">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조에 따른 금리 인상 우려가 부각되며 주 중반 지수 조정이 발생함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="15">
+          <t>- 주 초반 미국 필라델피아 반도체 지수의 급등과 마이크론의 강세에 힘입어 코스피가 외국인과 기관의 강력한 동반 매수세로 4.61% 급등하며 출발했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="31" customHeight="1" s="15">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>- 원전 및 데이터센터 전력 수요 관련 수주 기대감이 건설·기계 섹터의 강세를 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="15">
+          <t>- 주 중반에는 미국 내 대형 원전 8기 건설 협의 기대감과 가덕도 신공항 설계 제출 등 대형 호재가 겹치며 건설 및 전기·가스 섹터가 강세를 주도했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="31" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 외국인과 기관은 전기·전자 섹터에 각각 31,234억, 25,529억을 순매수하며 수급을 주도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+          <t>- 다만 한국의 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되었고, 개인의 대규모 매도세가 출회되며 지수 상승 탄력이 일부 제한되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>- 주 후반에는 중동 지정학적 리스크로 인한 유가 상승과 미국의 고용지표 호조에 따른 금리 인상 우려가 재점화되며 시장 전반에 경계감이 유지되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>섹터·테마 흐름</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr"/>
-      <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="15">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>- 전기·전자: AI 반도체 수요 기대감으로 주간 7.09% 상승하며 수급 집중.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="15">
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="31" customHeight="1" s="15">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>- 건설/기계·장비: 원전 및 데이터센터 수주 기대감으로 각각 12.14%, 11.19% 상승하며 주도 섹터로 부상.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
+          <t>- 주 초반에는 삼성전자와 SK하이닉스를 필두로 한 전기·전자(+5.92%) 및 기계·장비(+6.47%) 섹터가 AI 반도체 수요 기대감으로 시장을 주도했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="31" customHeight="1" s="15">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t>- 음식료/보험: 규제 및 실적 우려로 각각 3.69%, 0.37% 하락하며 약세 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+          <t>- 주 중반 이후에는 미국 원전 건설 협의 소식과 가덕도 신공항 모멘텀이 부각되며 건설(+2.99%) 및 전기·가스(+3.11%) 섹터로 매기 이전이 일어났습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="31" customHeight="1" s="15">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>- 반면 음식료·담배(-3.76%)와 IT 서비스(-2.61%) 섹터는 환율 하락에 따른 수출 우려 및 차익 실현 매물 출회로 주간 내내 약세를 보였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="18" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="31" customHeight="1" s="15">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>네오오토 (운송장비·부품)</t>
-        </is>
-      </c>
-      <c r="C81" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="E81" s="29" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2590,7 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>필옵틱스 (기계·장비)</t>
+          <t>네오오토 (운송장비·부품)</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
@@ -2610,11 +2604,11 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>37.02</v>
+        <v>39.17</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2620,7 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>나무가 (전기·전자)</t>
+          <t>필옵틱스 (기계·장비)</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
@@ -2640,11 +2634,11 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>37.98</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2650,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>두산퓨얼셀 (전기·전자)</t>
+          <t>나무가 (전기·전자)</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -2670,11 +2664,11 @@
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>19.5</v>
+        <v>10.09</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2680,7 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>DB하이텍 (전기·전자)</t>
+          <t>두산퓨얼셀 (전기·전자)</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
@@ -2696,15 +2690,15 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>24.36</v>
+        <v>22.92</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2710,7 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>두산에너빌리티 (기계·장비)</t>
+          <t>DB하이텍 (전기·전자)</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
@@ -2730,11 +2724,11 @@
         </is>
       </c>
       <c r="E86" s="29" t="n">
-        <v>16.16</v>
+        <v>27.47</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2740,7 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>SK하이닉스 (전기·전자)</t>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
@@ -2760,11 +2754,11 @@
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>10.14</v>
+        <v>17.55</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2770,7 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>삼성전자 (전기·전자)</t>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
@@ -2790,41 +2784,41 @@
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>5.58</v>
+        <v>11.48</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" s="15">
       <c r="A89" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>빛과전자 (전기·전자)</t>
+          <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E89" s="29" t="n">
-        <v>42.17</v>
+        <v>6.26</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2830,7 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>오르비텍 (일반서비스)</t>
+          <t>빛과전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
@@ -2850,11 +2844,11 @@
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>43.82</v>
+        <v>53.96</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2860,7 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>서전기전 (전기·전자)</t>
+          <t>오르비텍 (일반서비스)</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
@@ -2880,11 +2874,11 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>35.64</v>
+        <v>42.66</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2890,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>한전기술 (일반서비스)</t>
+          <t>서전기전 (전기·전자)</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -2910,11 +2904,11 @@
         </is>
       </c>
       <c r="E92" s="29" t="n">
-        <v>40.52</v>
+        <v>33.97</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2920,7 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>현대약품 (제약)</t>
+          <t>한전기술 (일반서비스)</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
@@ -2936,15 +2930,15 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>28.43</v>
+        <v>35.04</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2956,106 +2950,124 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
+          <t>현대약품 (제약)</t>
+        </is>
+      </c>
+      <c r="C94" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="E94" s="29" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="31" customHeight="1" s="15">
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
           <t>대우건설 (건설)</t>
         </is>
       </c>
-      <c r="C94" s="30" t="inlineStr">
+      <c r="C95" s="30" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D94" s="14" t="inlineStr">
+      <c r="D95" s="14" t="inlineStr">
         <is>
           <t>★★★★</t>
         </is>
       </c>
-      <c r="E94" s="29" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F94" s="17" t="inlineStr">
+      <c r="E95" s="29" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
         <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr"/>
-      <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr"/>
+      <c r="D97" s="3" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr"/>
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="31" customHeight="1" s="15">
-      <c r="A98" s="31" t="inlineStr">
+    <row r="99" ht="31" customHeight="1" s="15">
+      <c r="A99" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>미국 물가 지표가 안정적으로 확인되면 반도체 및 원전 주도 상승세 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="31" customHeight="1" s="15">
-      <c r="A99" s="32" t="inlineStr">
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>미국 CPI 및 PPI 지표가 안정세를 보이며 금리 인하 경로가 명확해지면 반도체 및 기술주 중심의 외국인 수급 유입과 함께 상승 랠리가 전개될 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="31" customHeight="1" s="15">
+      <c r="A100" s="32" t="inlineStr">
         <is>
           <t>하방 시나리오</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화될 경우 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="15">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>미국 물가 지표가 예상치를 상회하여 인플레이션 우려가 재점화되고 국채 금리가 급등하면 기술주 및 성장주 중심의 차익 실현 매물이 출회되며 하방 압력이 커질 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="31" customHeight="1" s="15">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>판별 신호</t>
         </is>
       </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>9월 11일 발표되는 미국 소비자물가지수(CPI) 결과가 시장 방향성을 결정할 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 8월 소비자물가지수(CPI)의 전월대비 및 전년대비 실제치와 이에 따른 미국 국채 금리의 변동성 여부입니다.</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3079,7 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>미국 생산자물가지수(PPI) 전월대비 (9월 10일 21:30)</t>
         </is>
       </c>
     </row>
@@ -3079,12 +3091,24 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>국내 무역수지</t>
+          <t>미국 소비자물가지수(CPI) 전년대비 (9월 11일 21:30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="15">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>미국 소매판매 전월대비 (9월 16일 21:30)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="49">
     <mergeCell ref="B98:J98"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="G26:J26"/>
@@ -3096,40 +3120,41 @@
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="F84:J84"/>
+    <mergeCell ref="B69:J69"/>
     <mergeCell ref="F89:J89"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C64:J64"/>
     <mergeCell ref="F83:J83"/>
     <mergeCell ref="B103:J103"/>
-    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="F95:J95"/>
     <mergeCell ref="C63:J63"/>
     <mergeCell ref="C65:J65"/>
     <mergeCell ref="F86:J86"/>
+    <mergeCell ref="B99:J99"/>
     <mergeCell ref="A77:J77"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="F80:J80"/>
     <mergeCell ref="F94:J94"/>
+    <mergeCell ref="A73:J73"/>
     <mergeCell ref="F85:J85"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B104:J104"/>
     <mergeCell ref="F91:J91"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="F81:J81"/>
     <mergeCell ref="B32:J32"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="F90:J90"/>
-    <mergeCell ref="A69:J69"/>
     <mergeCell ref="F93:J93"/>
     <mergeCell ref="C61:J61"/>
-    <mergeCell ref="B97:J97"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A75:J75"/>
     <mergeCell ref="F92:J92"/>
     <mergeCell ref="A71:J71"/>
     <mergeCell ref="F82:J82"/>
     <mergeCell ref="B102:J102"/>
+    <mergeCell ref="C66:J66"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="F88:J88"/>
@@ -3144,7 +3169,3258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
+    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
+    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
+    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
+    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
+    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
+    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
+    <col width="13" customWidth="1" style="15" min="9" max="9"/>
+    <col width="13" customWidth="1" style="15" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1" s="15">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>신고가 근접</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>52주 신고가 근접</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>수급=주간 누적(억)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="31" customHeight="1" s="15">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>합산</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>외인</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>공매도(억)</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>대차잔고(증감,억)</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t>등락률(주간,%)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>신고가 대비(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1" s="15">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>하나금융지주 (금융)</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>-130</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>219</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>6,946 (-721)</t>
+        </is>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J5" s="30" t="n">
+        <v>-5.09</v>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1" s="15">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>대한항공 (운송·창고)</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>417</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>277</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>141</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>-395</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>1,717 (-1)</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>-4.17</v>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1" s="15">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>신한지주 (금융)</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>160</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>-133</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>293</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>7,226 (-535)</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=주간 누적 확정(억원)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
+    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
+    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
+    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
+    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
+    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
+    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
+    <col width="13" customWidth="1" style="15" min="9" max="9"/>
+    <col width="13" customWidth="1" style="15" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1" s="15">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>투자자별 순매수</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>외국인 누적 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>금액(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1" s="15">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>19244</v>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1" s="15">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>18707</v>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1" s="15">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1" s="15">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1" s="15">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>효성중공업 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1" s="15">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="11" ht="31" customHeight="1" s="15">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>HPSP (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="12" ht="31" customHeight="1" s="15">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자우 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1" s="15">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>LS ELECTRIC (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1" s="15">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>심텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" ht="31" customHeight="1" s="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>-2168</v>
+      </c>
+    </row>
+    <row r="16" ht="31" customHeight="1" s="15">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>삼성SDI (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>-648</v>
+      </c>
+    </row>
+    <row r="17" ht="44.5" customHeight="1" s="15">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>-559</v>
+      </c>
+    </row>
+    <row r="18" ht="31" customHeight="1" s="15">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>셀트리온 (제약)</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>-551</v>
+      </c>
+    </row>
+    <row r="19" ht="44.5" customHeight="1" s="15">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>-468</v>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1" s="15">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스 (금속)</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>-444</v>
+      </c>
+    </row>
+    <row r="21" ht="31" customHeight="1" s="15">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>현대차 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>-387</v>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1" s="15">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>-313</v>
+      </c>
+    </row>
+    <row r="23" ht="44.5" customHeight="1" s="15">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>HD현대중공업 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>-306</v>
+      </c>
+    </row>
+    <row r="24" ht="31" customHeight="1" s="15">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>DB하이텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="n">
+        <v>-265</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>기관계 누적 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>금액(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="31" customHeight="1" s="15">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>24020</v>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1" s="15">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>9895</v>
+      </c>
+    </row>
+    <row r="30" ht="31" customHeight="1" s="15">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="31" ht="31" customHeight="1" s="15">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="32" ht="31" customHeight="1" s="15">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자우 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="33" ht="31" customHeight="1" s="15">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="34" ht="31" customHeight="1" s="15">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>삼성물산 (유통)</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1" s="15">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="36" ht="31" customHeight="1" s="15">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="37" ht="31" customHeight="1" s="15">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>대우건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="38" ht="31" customHeight="1" s="15">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>삼성SDI (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>-873</v>
+      </c>
+    </row>
+    <row r="39" ht="31" customHeight="1" s="15">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>삼양식품 (음식료·담배)</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="n">
+        <v>-833</v>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1" s="15">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>알테오젠 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="n">
+        <v>-643</v>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1" s="15">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>에이피알 (화학)</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="n">
+        <v>-583</v>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1" s="15">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>-550</v>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1" s="15">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>현대모비스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1" s="15">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>OCI홀딩스 (금융)</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="n">
+        <v>-437</v>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1" s="15">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D45" s="28" t="n">
+        <v>-386</v>
+      </c>
+    </row>
+    <row r="46" ht="31" customHeight="1" s="15">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>-386</v>
+      </c>
+    </row>
+    <row r="47" ht="31" customHeight="1" s="15">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>실리콘투 (유통)</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="n">
+        <v>-357</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>연기금 누적 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>금액(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1" s="15">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1" s="15">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1" s="15">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1" s="15">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>두산 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" ht="31" customHeight="1" s="15">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자우 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" ht="31" customHeight="1" s="15">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" ht="31" customHeight="1" s="15">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" ht="31" customHeight="1" s="15">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>이수페타시스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="59" ht="31" customHeight="1" s="15">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>SK이노베이션 (화학)</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" ht="31" customHeight="1" s="15">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>삼성생명 (보험)</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" ht="31" customHeight="1" s="15">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="n">
+        <v>-1339</v>
+      </c>
+    </row>
+    <row r="62" ht="31" customHeight="1" s="15">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="n">
+        <v>-832</v>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="15">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>현대차 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="n">
+        <v>-383</v>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>현대모비스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="n">
+        <v>-366</v>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>삼성SDI (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="n">
+        <v>-325</v>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>셀트리온 (제약)</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="n">
+        <v>-244</v>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>대덕전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="n">
+        <v>-188</v>
+      </c>
+    </row>
+    <row r="68" ht="31" customHeight="1" s="15">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>알테오젠 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="D68" s="28" t="n">
+        <v>-184</v>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="n">
+        <v>-164</v>
+      </c>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>엘앤에프 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D70" s="28" t="n">
+        <v>-155</v>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>개인 누적 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>금액(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="31" customHeight="1" s="15">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="n">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="75" ht="31" customHeight="1" s="15">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>삼성SDI (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="76" ht="31" customHeight="1" s="15">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>삼양식품 (음식료·담배)</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="n">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="77" ht="31" customHeight="1" s="15">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="n">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="78" ht="31" customHeight="1" s="15">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B78" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>에이피알 (화학)</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="79" ht="31" customHeight="1" s="15">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B79" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>셀트리온 (제약)</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="80" ht="44.5" customHeight="1" s="15">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B80" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="81" ht="31" customHeight="1" s="15">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B81" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="82" ht="31" customHeight="1" s="15">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B82" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>알테오젠 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="83" ht="44.5" customHeight="1" s="15">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B83" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="84" ht="31" customHeight="1" s="15">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B84" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D84" s="28" t="n">
+        <v>-55192</v>
+      </c>
+    </row>
+    <row r="85" ht="31" customHeight="1" s="15">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B85" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D85" s="28" t="n">
+        <v>-52130</v>
+      </c>
+    </row>
+    <row r="86" ht="31" customHeight="1" s="15">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B86" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="n">
+        <v>-5184</v>
+      </c>
+    </row>
+    <row r="87" ht="31" customHeight="1" s="15">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B87" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자우 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D87" s="28" t="n">
+        <v>-2361</v>
+      </c>
+    </row>
+    <row r="88" ht="31" customHeight="1" s="15">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D88" s="28" t="n">
+        <v>-2125</v>
+      </c>
+    </row>
+    <row r="89" ht="31" customHeight="1" s="15">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B89" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="D89" s="28" t="n">
+        <v>-1560</v>
+      </c>
+    </row>
+    <row r="90" ht="31" customHeight="1" s="15">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B90" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D90" s="28" t="n">
+        <v>-1175</v>
+      </c>
+    </row>
+    <row r="91" ht="31" customHeight="1" s="15">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B91" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>효성중공업 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="n">
+        <v>-863</v>
+      </c>
+    </row>
+    <row r="92" ht="31" customHeight="1" s="15">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>대우건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="n">
+        <v>-812</v>
+      </c>
+    </row>
+    <row r="93" ht="31" customHeight="1" s="15">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B93" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="n">
+        <v>-760</v>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D50:J50"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
+    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
+    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
+    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
+    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
+    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
+    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
+    <col width="13" customWidth="1" style="15" min="9" max="9"/>
+    <col width="13" customWidth="1" style="15" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1" s="15">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>공매도·대차</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>공매도 누적 상위</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>공매도 누적(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1" s="15">
+      <c r="A5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1" s="15">
+      <c r="A6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1" s="15">
+      <c r="A7" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1" s="15">
+      <c r="A8" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1" s="15">
+      <c r="A10" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="11" ht="31" customHeight="1" s="15">
+      <c r="A11" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="12" ht="31" customHeight="1" s="15">
+      <c r="A12" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>LG전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1" s="15">
+      <c r="A13" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1" s="15">
+      <c r="A14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>대차잔고 증가 상위</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>증감(억)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>잔고(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="31" customHeight="1" s="15">
+      <c r="A18" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>대우건설 (건설)</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>482.9</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>6222.6</v>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1" s="15">
+      <c r="A19" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>한전기술 (일반서비스)</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>428.8</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>3588.6</v>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1" s="15">
+      <c r="A20" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>현대건설 (건설)</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>297</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>8765.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>2580.7</v>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1" s="15">
+      <c r="A22" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>하이브 (오락·문화)</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>4141.5</v>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1" s="15">
+      <c r="A23" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>한미사이언스 (금융)</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>1555.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>한진칼 (금융)</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>3084.3</v>
+      </c>
+    </row>
+    <row r="25" ht="31" customHeight="1" s="15">
+      <c r="A25" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>미래에셋증권 (증권)</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>8085.4</v>
+      </c>
+    </row>
+    <row r="26" ht="31" customHeight="1" s="15">
+      <c r="A26" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>SK스퀘어 (금융)</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>32891.8</v>
+      </c>
+    </row>
+    <row r="27" ht="31" customHeight="1" s="15">
+      <c r="A27" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>산일전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>4014.7</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>대차잔고 감소 상위 (숏커버 추정)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>주간 누적, 억원</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>증감(억)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>잔고(억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="31" customHeight="1" s="15">
+      <c r="A31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>삼성전자 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>-7162.4</v>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>240284.8</v>
+      </c>
+    </row>
+    <row r="32" ht="31" customHeight="1" s="15">
+      <c r="A32" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>삼성전기 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>-2801</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>36009</v>
+      </c>
+    </row>
+    <row r="33" ht="31" customHeight="1" s="15">
+      <c r="A33" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>-2044.8</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>223759.5</v>
+      </c>
+    </row>
+    <row r="34" ht="31" customHeight="1" s="15">
+      <c r="A34" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>-1186.9</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>31440</v>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1" s="15">
+      <c r="A35" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n">
+        <v>-1092.4</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>9333.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>-870.4</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>32571.3</v>
+      </c>
+    </row>
+    <row r="37" ht="31" customHeight="1" s="15">
+      <c r="A37" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>한미반도체 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>-835.3</v>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>43511.4</v>
+      </c>
+    </row>
+    <row r="38" ht="31" customHeight="1" s="15">
+      <c r="A38" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>심텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>-770</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>7482.8</v>
+      </c>
+    </row>
+    <row r="39" ht="31" customHeight="1" s="15">
+      <c r="A39" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>하나금융지주 (금융)</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>-720.6</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1" s="15">
+      <c r="A40" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NAVER (IT 서비스)</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>-685.7</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>11396.4</v>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=주초 대비 최신 잔고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
+    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
+    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
+    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
+    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
+    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
+    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
+    <col width="13" customWidth="1" style="15" min="9" max="9"/>
+    <col width="13" customWidth="1" style="15" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1" s="15">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>섹터x수급</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>섹터 x 수급 매트릭스</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>주간 등락 vs 투자자 순매수(억)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>주간등락(%)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>외인</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>연기금</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>신호</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>886</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>2888</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>908</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>-3784</v>
+      </c>
+      <c r="G5" s="30" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>-67</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>1773</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>407</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-1936</v>
+      </c>
+      <c r="G6" s="30" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>30380</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>26434</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>-1482</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-91575</v>
+      </c>
+      <c r="G7" s="30" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>전기·가스</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-352</v>
+      </c>
+      <c r="G8" s="30" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>28795</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>26164</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>-2649</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>-90066</v>
+      </c>
+      <c r="G9" s="30" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>-24</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>703</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>106</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-654</v>
+      </c>
+      <c r="G10" s="30" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>-191</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>602</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>-713</v>
+      </c>
+      <c r="G11" s="30" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>1082</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>4076</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>917</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>-5257</v>
+      </c>
+      <c r="G12" s="30" t="inlineStr"/>
+    </row>
+    <row r="13" ht="31" customHeight="1" s="15">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>-106</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="30" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>증권</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>260</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>-252</v>
+      </c>
+      <c r="G14" s="30" t="inlineStr"/>
+    </row>
+    <row r="15" ht="31" customHeight="1" s="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>-868</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>-416</v>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>-1077</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G15" s="30" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>-742</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>194</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>489</v>
+      </c>
+      <c r="G16" s="30" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>오락·문화</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G17" s="30" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>363</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>191</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-532</v>
+      </c>
+      <c r="G18" s="30" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>통신</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>199</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G19" s="30" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>비금속</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="30" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>-71</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>-1231</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>-298</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G21" s="30" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>-252</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>445</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>216</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>-204</v>
+      </c>
+      <c r="G22" s="30" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G23" s="30" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>-471</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>-651</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>-530</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>916</v>
+      </c>
+      <c r="G25" s="30" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>섬유·의류</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="30" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>-301</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>-269</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>-367</v>
+      </c>
+      <c r="F27" s="29" t="n">
+        <v>580</v>
+      </c>
+      <c r="G27" s="30" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>-202</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>-182</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>1278</v>
+      </c>
+      <c r="G28" s="30" t="inlineStr"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>KIS 업종(KRX 산업분류) 일별 확정 합산 · 과열주의=주가 상승+수급 이탈 · 수급유입=주가 하락+수급 유입</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A30:J30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -3176,7 +6452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:21 KST</t>
+          <t>2026-09-09 09:39 KST</t>
         </is>
       </c>
     </row>
@@ -3188,7 +6464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI 반도체와 원전 모멘텀이 이끈 주간 상승세</t>
+          <t>반도체와 원전·건설이 이끈 안도 랠리와 매크로 경계감의 혼조</t>
         </is>
       </c>
     </row>
@@ -3457,7 +6733,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단이 제한됨.</t>
+          <t>미국 필라델피아 반도체 지수가 3.37% 급등하고 고용지표 호조로 금리 인하 기대감이 후퇴하는 중립 스탠스 속에서도, 국내 증시는 반도체 대형주 중심의 강력한 외국인·기관 매수세가 유입되며 코스피가 4.61% 급등했습니다.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +6748,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 8기 건설 협의 소식이 국내 건설 및 전기·가스 섹터의 강세를 견인함.</t>
+          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 제기되는 중립 스탠스 하에서, 국내 증시는 미국 원전 건설 협의 기대감으로 원전·건설주는 급등했으나 경기 둔화 우려와 개인 매도세로 코스피가 0.58% 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -3487,7 +6763,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>미국 고용지표 '블로우아웃'에 따른 금리 인상 우려에도 불구하고, 해외 원전 및 AIDC 수주 기대감이 건설·기계 섹터의 상승을 주도함.</t>
+          <t>미국 고용지표의 블로우아웃 수준 발표로 금리 인상 우려가 재점화된 위험회피 스탠스 속에서도, 국내 증시는 해외 원전 및 AIDC 수주 기대감과 반도체 장비 투자 확대 기대감에 힘입어 코스피가 0.79% 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +6782,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>매크로 환경은 미국 비농업고용지수가 162K로 예상치를 상회하며 금리 인상 우려를 자극했고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 공존함.</t>
+          <t>이번 주 매크로 환경은 미국의 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 크게 상회해 금리 인하 경로에 대한 불확실성을 키웠고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려를 자극했습니다.</t>
         </is>
       </c>
     </row>
@@ -3518,7 +6794,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>수급 구도는 전기·전자 섹터에 외국인 31,234억, 기관 25,529억이 집중되었고, 기계·장비 섹터에도 기관 2,795억이 유입되며 주도 섹터로 자리 잡음.</t>
+          <t>수급 측면에서는 전기·전자 업종에 외국인(+30,380억원)과 기관(+26,434억원)의 순매수가 집중되며 주간 6.71% 상승했고, 기계·장비 업종 역시 기관(+2,888억원)의 매수세로 11.08% 급등했습니다.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +6806,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 원전이라는 확실한 모멘텀이 수급을 견인하며 시장의 하방을 지지하는 국면임.</t>
+          <t>반면 음식료·담배 업종은 기관(-1,100억원)과 외국인(-202억원)의 동반 순매도로 주간 3.76% 하락하며 밸류에이션 부담과 환율 하락에 따른 수출 우려를 반영했습니다.</t>
         </is>
       </c>
     </row>
@@ -3556,10 +6832,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45121</v>
+        <v>43264</v>
       </c>
       <c r="E34" t="n">
-        <v>21100</v>
+        <v>19244</v>
       </c>
       <c r="F34" t="n">
         <v>24020</v>
@@ -3592,10 +6868,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29092</v>
+        <v>28602</v>
       </c>
       <c r="E35" t="n">
-        <v>19197</v>
+        <v>18707</v>
       </c>
       <c r="F35" t="n">
         <v>9895</v>
@@ -3628,10 +6904,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5294</v>
+        <v>4949</v>
       </c>
       <c r="E36" t="n">
-        <v>3070</v>
+        <v>2725</v>
       </c>
       <c r="F36" t="n">
         <v>2223</v>
@@ -3660,29 +6936,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2338</v>
+        <v>2172</v>
       </c>
       <c r="E37" t="n">
-        <v>740</v>
+        <v>-48</v>
       </c>
       <c r="F37" t="n">
-        <v>1598</v>
+        <v>2220</v>
       </c>
       <c r="G37" t="n">
-        <v>-2361</v>
+        <v>-2125</v>
       </c>
       <c r="H37" t="n">
-        <v>206.2</v>
+        <v>900.5</v>
       </c>
       <c r="I37" t="n">
-        <v>28477.7</v>
+        <v>19469.6</v>
       </c>
       <c r="J37" t="n">
-        <v>-666.1</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="15">
@@ -3696,29 +6972,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2138</v>
+        <v>2097</v>
       </c>
       <c r="E38" t="n">
-        <v>-81</v>
+        <v>499</v>
       </c>
       <c r="F38" t="n">
-        <v>2220</v>
+        <v>1598</v>
       </c>
       <c r="G38" t="n">
-        <v>-2125</v>
+        <v>-2361</v>
       </c>
       <c r="H38" t="n">
-        <v>900.5</v>
+        <v>206.2</v>
       </c>
       <c r="I38" t="n">
-        <v>19469.6</v>
+        <v>28477.7</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.9</v>
+        <v>-666.1</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
@@ -3736,10 +7012,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1581</v>
+        <v>1546</v>
       </c>
       <c r="E39" t="n">
-        <v>1000</v>
+        <v>965</v>
       </c>
       <c r="F39" t="n">
         <v>581</v>
@@ -3772,10 +7048,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1182</v>
+        <v>1141</v>
       </c>
       <c r="E40" t="n">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="F40" t="n">
         <v>541</v>
@@ -3808,10 +7084,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>852</v>
+        <v>911</v>
       </c>
       <c r="E41" t="n">
-        <v>687</v>
+        <v>745</v>
       </c>
       <c r="F41" t="n">
         <v>166</v>
@@ -3840,29 +7116,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="E42" t="n">
-        <v>369</v>
+        <v>-221</v>
       </c>
       <c r="F42" t="n">
-        <v>444</v>
+        <v>1011</v>
       </c>
       <c r="G42" t="n">
-        <v>-812</v>
+        <v>-760</v>
       </c>
       <c r="H42" t="n">
-        <v>164.4</v>
+        <v>292.4</v>
       </c>
       <c r="I42" t="n">
-        <v>6222.6</v>
+        <v>8765.6</v>
       </c>
       <c r="J42" t="n">
-        <v>482.9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
@@ -3876,29 +7152,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>754</v>
+        <v>711</v>
       </c>
       <c r="E43" t="n">
-        <v>-258</v>
+        <v>431</v>
       </c>
       <c r="F43" t="n">
-        <v>1011</v>
+        <v>280</v>
       </c>
       <c r="G43" t="n">
-        <v>-760</v>
+        <v>-649</v>
       </c>
       <c r="H43" t="n">
-        <v>292.4</v>
+        <v>37.7</v>
       </c>
       <c r="I43" t="n">
-        <v>8765.6</v>
+        <v>9403.4</v>
       </c>
       <c r="J43" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
@@ -3916,10 +7192,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-3070</v>
+        <v>-2718</v>
       </c>
       <c r="E44" t="n">
-        <v>-2520</v>
+        <v>-2168</v>
       </c>
       <c r="F44" t="n">
         <v>-550</v>
@@ -3952,10 +7228,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-1568</v>
+        <v>-1521</v>
       </c>
       <c r="E45" t="n">
-        <v>-695</v>
+        <v>-648</v>
       </c>
       <c r="F45" t="n">
         <v>-873</v>
@@ -4060,10 +7336,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-679</v>
+        <v>-700</v>
       </c>
       <c r="E48" t="n">
-        <v>-292</v>
+        <v>-313</v>
       </c>
       <c r="F48" t="n">
         <v>-386</v>
@@ -4128,29 +7404,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-593</v>
+        <v>-598</v>
       </c>
       <c r="E50" t="n">
-        <v>-468</v>
+        <v>-212</v>
       </c>
       <c r="F50" t="n">
-        <v>-125</v>
+        <v>-386</v>
       </c>
       <c r="G50" t="n">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="H50" t="n">
-        <v>222.6</v>
+        <v>563.7</v>
       </c>
       <c r="I50" t="n">
-        <v>6895.6</v>
+        <v>9333.9</v>
       </c>
       <c r="J50" t="n">
-        <v>-292.3</v>
+        <v>-1092.4</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
@@ -4164,29 +7440,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-582</v>
+        <v>-593</v>
       </c>
       <c r="E51" t="n">
-        <v>-195</v>
+        <v>-468</v>
       </c>
       <c r="F51" t="n">
-        <v>-386</v>
+        <v>-125</v>
       </c>
       <c r="G51" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="H51" t="n">
-        <v>563.7</v>
+        <v>222.6</v>
       </c>
       <c r="I51" t="n">
-        <v>9333.9</v>
+        <v>6895.6</v>
       </c>
       <c r="J51" t="n">
-        <v>-1092.4</v>
+        <v>-292.3</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="15">
@@ -4236,29 +7512,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-511</v>
+        <v>-478</v>
       </c>
       <c r="E53" t="n">
-        <v>132</v>
+        <v>-42</v>
       </c>
       <c r="F53" t="n">
-        <v>-643</v>
+        <v>-437</v>
       </c>
       <c r="G53" t="n">
-        <v>559</v>
+        <v>507</v>
       </c>
       <c r="H53" t="n">
-        <v>314.6</v>
+        <v>37.7</v>
       </c>
       <c r="I53" t="n">
-        <v>13946.5</v>
+        <v>3421.8</v>
       </c>
       <c r="J53" t="n">
-        <v>-546.9</v>
+        <v>-191.7</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="15">
@@ -4276,12 +7552,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 12.14% 상승하며 기관이 1,743억 순매수함.</t>
+          <t>주간 수급 집중 1위 종목으로 외국인(+19,244억원)과 기관(+24,020억원)의 강력한 순매수가 유입되었습니다.</t>
         </is>
       </c>
     </row>
@@ -4293,29 +7569,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>주간 11.19% 상승하며 기관이 2,795억 순매수함.</t>
+          <t>주간 수급 집중 2위 종목으로 외국인(+18,707억원)과 기관(+9,895억원)의 순매수가 집중되었으며 대차잔고가 2,044.8억원 감소하여 숏커버 여지가 존재합니다.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="15">
       <c r="A57" t="inlineStr">
         <is>
-          <t>하방 관찰</t>
+          <t>상방 관찰</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>주간 3.69% 하락하며 기관이 1,083억 순매도함.</t>
+          <t>건설 업종 주간 10.99% 상승 속에서 기관이 1,011억원을 순매수하였고 대차잔고가 297.0% 증가하여 향후 숏커버링 가능성을 관찰할 필요가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -4327,31 +7603,36 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>주간 2.18% 하락하며 기관이 250억 순매도함.</t>
+          <t>주간 순매수 최하위 종목으로 외국인(-2,168억원)과 기관(-550억원)의 동반 순매도가 출회되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8. 주간 시장 흐름</t>
+          <t>하방 관찰</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>음식료·담배 업종의 주간 3.76% 하락 속에서 기관(-833억원)과 외국인(-135억원)의 순매도가 집중되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="15">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>주 초반 미국 반도체 지수 급등에 힘입어 KOSPI가 4.61% 급등하며 7000선에 근접함.</t>
+          <t>8. 주간 시장 흐름</t>
         </is>
       </c>
     </row>
@@ -4363,7 +7644,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>미국 고용지표 호조에 따른 금리 인상 우려가 부각되며 주 중반 지수 조정이 발생함.</t>
+          <t>주 초반 미국 필라델피아 반도체 지수의 급등과 마이크론의 강세에 힘입어 코스피가 외국인과 기관의 강력한 동반 매수세로 4.61% 급등하며 출발했습니다.</t>
         </is>
       </c>
     </row>
@@ -4375,7 +7656,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>원전 및 데이터센터 전력 수요 관련 수주 기대감이 건설·기계 섹터의 강세를 견인함.</t>
+          <t>주 중반에는 미국 내 대형 원전 8기 건설 협의 기대감과 가덕도 신공항 설계 제출 등 대형 호재가 겹치며 건설 및 전기·가스 섹터가 강세를 주도했습니다.</t>
         </is>
       </c>
     </row>
@@ -4387,26 +7668,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>외국인과 기관은 전기·전자 섹터에 각각 31,234억, 25,529억을 순매수하며 수급을 주도함.</t>
+          <t>다만 한국의 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되었고, 개인의 대규모 매도세가 출회되며 지수 상승 탄력이 일부 제한되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9. 섹터·테마 흐름</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>주 후반에는 중동 지정학적 리스크로 인한 유가 상승과 미국의 고용지표 호조에 따른 금리 인상 우려가 재점화되며 시장 전반에 경계감이 유지되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>전기·전자: AI 반도체 수요 기대감으로 주간 7.09% 상승하며 수급 집중.</t>
+          <t>9. 섹터·테마 흐름</t>
         </is>
       </c>
     </row>
@@ -4418,7 +7699,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>건설/기계·장비: 원전 및 데이터센터 수주 기대감으로 각각 12.14%, 11.19% 상승하며 주도 섹터로 부상.</t>
+          <t>주 초반에는 삼성전자와 SK하이닉스를 필두로 한 전기·전자(+5.92%) 및 기계·장비(+6.47%) 섹터가 AI 반도체 수요 기대감으로 시장을 주도했습니다.</t>
         </is>
       </c>
     </row>
@@ -4430,42 +7711,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>음식료/보험: 규제 및 실적 우려로 각각 3.69%, 0.37% 하락하며 약세 지속.</t>
+          <t>주 중반 이후에는 미국 원전 건설 협의 소식과 가덕도 신공항 모멘텀이 부각되며 건설(+2.99%) 및 전기·가스(+3.11%) 섹터로 매기 이전이 일어났습니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>반면 음식료·담배(-3.76%)와 IT 서비스(-2.61%) 섹터는 환율 하락에 따른 수출 우려 및 차익 실현 매물 출회로 주간 내내 약세를 보였습니다.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
@@ -4477,7 +7742,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>네오오토</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4489,11 +7754,11 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>37.02</v>
+        <v>39.17</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -4505,7 +7770,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4517,11 +7782,11 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>9.800000000000001</v>
+        <v>37.98</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -4533,23 +7798,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>19.5</v>
+        <v>10.09</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4561,7 +7826,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4570,14 +7835,14 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>24.36</v>
+        <v>22.92</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -4589,7 +7854,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4601,11 +7866,11 @@
         <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>16.16</v>
+        <v>27.47</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -4617,7 +7882,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4629,11 +7894,11 @@
         <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>10.14</v>
+        <v>17.55</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -4645,7 +7910,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4657,39 +7922,39 @@
         <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>5.58</v>
+        <v>11.48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>42.17</v>
+        <v>6.26</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -4701,7 +7966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4713,11 +7978,11 @@
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>43.82</v>
+        <v>53.96</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
@@ -4729,7 +7994,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4741,11 +8006,11 @@
         <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>35.64</v>
+        <v>42.66</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4757,23 +8022,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>40.52</v>
+        <v>33.97</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -4785,7 +8050,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4794,14 +8059,14 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>28.43</v>
+        <v>35.04</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -4813,7 +8078,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4825,66 +8090,82 @@
         <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>20.77</v>
+        <v>33.21</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>미국 물가 지표가 안정적으로 확인되면 반도체 및 원전 주도 상승세 지속.</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화될 경우 조정.</t>
+          <t>미국 CPI 및 PPI 지표가 안정세를 보이며 금리 인하 경로가 명확해지면 반도체 및 기술주 중심의 외국인 수급 유입과 함께 상승 랠리가 전개될 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>하방 시나리오</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9월 11일 발표되는 미국 소비자물가지수(CPI) 결과가 시장 방향성을 결정할 것.</t>
+          <t>미국 물가 지표가 예상치를 상회하여 인플레이션 우려가 재점화되고 국채 금리가 급등하면 기술주 및 성장주 중심의 차익 실현 매물이 출회되며 하방 압력이 커질 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" t="inlineStr">
         <is>
-          <t>핵심 이벤트</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>미국 소비자물가지수(CPI)</t>
+          <t>미국 8월 소비자물가지수(CPI)의 전월대비 및 전년대비 실제치와 이에 따른 미국 국채 금리의 변동성 여부입니다.</t>
         </is>
       </c>
     </row>
@@ -4896,7 +8177,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI)</t>
+          <t>미국 생산자물가지수(PPI) 전월대비 (9월 10일 21:30)</t>
         </is>
       </c>
     </row>
@@ -4908,11 +8189,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>국내 무역수지</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="15"/>
+          <t>미국 소비자물가지수(CPI) 전년대비 (9월 11일 21:30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="15">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>미국 소매판매 전월대비 (9월 16일 21:30)</t>
+        </is>
+      </c>
+    </row>
     <row r="91" ht="15" customHeight="1" s="15"/>
     <row r="93" ht="15" customHeight="1" s="15"/>
     <row r="94" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -13,14 +13,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원본 데이터" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$G$28</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="+#,##0.0;-#,##0.0;0.0"/>
+    <numFmt numFmtId="166" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="23">
     <font>
       <name val="Calibri"/>
@@ -255,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -350,7 +358,52 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -794,7 +847,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 09:39 KST</t>
+          <t>2026-09-09 10:24 KST</t>
         </is>
       </c>
     </row>
@@ -807,7 +860,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체와 원전·건설이 이끈 안도 랠리와 매크로 경계감의 혼조</t>
+          <t>AI 반도체와 전력 인프라가 주도한 주간 강세장</t>
         </is>
       </c>
     </row>
@@ -903,13 +956,13 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-98067</v>
+        <v>-101949</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>31154</v>
+        <v>30104</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>32584</v>
+        <v>34875</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>-1.34</v>
@@ -934,13 +987,13 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>2870</v>
+        <v>1830</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>542</v>
+        <v>1369</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>-3583</v>
+        <v>-3368</v>
       </c>
     </row>
     <row r="10"/>
@@ -1018,17 +1071,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>기계·장비 +11.08%</t>
+          <t>기계·장비 +10.61%</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>건설 +10.99%</t>
+          <t>건설 +10.22%</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>전기·전자 +6.71%</t>
+          <t>전기·전자 +8.16%</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1093,17 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>음식료·담배 -3.76%</t>
+          <t>음식료·담배 -4.75%</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>IT 서비스 -2.61%</t>
+          <t>IT 서비스 -2.46%</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>섬유·의류 -2.01%</t>
+          <t>섬유·의류 -2.07%</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="71.5" customHeight="1" s="15">
+    <row r="27" ht="44.5" customHeight="1" s="15">
       <c r="A27" s="30" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1378,11 +1431,11 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수가 3.37% 급등하고 고용지표 호조로 금리 인하 기대감이 후퇴하는 중립 스탠스 속에서도, 국내 증시는 반도체 대형주 중심의 강력한 외국인·기관 매수세가 유입되며 코스피가 4.61% 급등했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="71.5" customHeight="1" s="15">
+          <t>미국 필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 중심의 강세로 이어지며 지수 상승을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44.5" customHeight="1" s="15">
       <c r="A28" s="30" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1411,40 +1464,40 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 제기되는 중립 스탠스 하에서, 국내 증시는 미국 원전 건설 협의 기대감으로 원전·건설주는 급등했으나 경기 둔화 우려와 개인 매도세로 코스피가 0.58% 하락했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="71.5" customHeight="1" s="15">
+          <t>미국 국채금리 급등과 금리 인상 우려가 시장의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44.5" customHeight="1" s="15">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>470▲/372▼</t>
+          <t>411▲/441▼</t>
         </is>
       </c>
       <c r="D29" s="29" t="n">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>949▲/661▼ 상한2</t>
+          <t>991▲/647▼ 상한4</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>건설, 기계·장비</t>
+          <t>기계·장비, 의료·정밀기기</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>미국 고용지표의 블로우아웃 수준 발표로 금리 인상 우려가 재점화된 위험회피 스탠스 속에서도, 국내 증시는 해외 원전 및 AIDC 수주 기대감과 반도체 장비 투자 확대 기대감에 힘입어 코스피가 0.79% 상승했습니다.</t>
+          <t>미국 기술주의 차별화된 흐름과 지정학적 리스크에도 불구하고 AI 전력 수요 모멘텀이 부각되며 국내 증시가 반등함.</t>
         </is>
       </c>
     </row>
@@ -1481,24 +1534,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="44.5" customHeight="1" s="15">
+    <row r="33" ht="31" customHeight="1" s="15">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>- 이번 주 매크로 환경은 미국의 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 크게 상회해 금리 인하 경로에 대한 불확실성을 키웠고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려를 자극했습니다.</t>
+          <t>- 미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 상존함.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="31" customHeight="1" s="15">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서는 전기·전자 업종에 외국인(+30,380억원)과 기관(+26,434억원)의 순매수가 집중되며 주간 6.71% 상승했고, 기계·장비 업종 역시 기관(+2,888억원)의 매수세로 11.08% 급등했습니다.</t>
+          <t>- 수급 측면에서 전기·전자 섹터에 외국인(31,244억)과 기관(28,343억)의 매수세가 집중되었으며, 기계·장비 섹터 역시 기관(2,841억)의 순매수가 유입되며 주도 섹터로 부상함.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="31" customHeight="1" s="15">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>- 반면 음식료·담배 업종은 기관(-1,100억원)과 외국인(-202억원)의 동반 순매도로 주간 3.76% 하락하며 밸류에이션 부담과 환율 하락에 따른 수출 우려를 반영했습니다.</t>
+          <t>- 매크로 지표의 둔화에도 불구하고 AI 반도체와 전력 인프라라는 확실한 모멘텀을 가진 섹터로 수급이 쏠리는 양극화 장세가 지속됨.</t>
         </is>
       </c>
     </row>
@@ -1594,13 +1647,13 @@
         </is>
       </c>
       <c r="D39" s="29" t="n">
-        <v>43264</v>
+        <v>43827</v>
       </c>
       <c r="E39" s="29" t="n">
-        <v>19244</v>
+        <v>19774</v>
       </c>
       <c r="F39" s="29" t="n">
-        <v>24020</v>
+        <v>24053</v>
       </c>
       <c r="G39" s="28" t="n">
         <v>-55192</v>
@@ -1630,13 +1683,13 @@
         </is>
       </c>
       <c r="D40" s="29" t="n">
-        <v>28602</v>
+        <v>29241</v>
       </c>
       <c r="E40" s="29" t="n">
-        <v>18707</v>
+        <v>19401</v>
       </c>
       <c r="F40" s="29" t="n">
-        <v>9895</v>
+        <v>9839</v>
       </c>
       <c r="G40" s="28" t="n">
         <v>-52130</v>
@@ -1666,13 +1719,13 @@
         </is>
       </c>
       <c r="D41" s="29" t="n">
-        <v>4949</v>
+        <v>4815</v>
       </c>
       <c r="E41" s="29" t="n">
-        <v>2725</v>
+        <v>2558</v>
       </c>
       <c r="F41" s="29" t="n">
-        <v>2223</v>
+        <v>2258</v>
       </c>
       <c r="G41" s="28" t="n">
         <v>-5184</v>
@@ -1702,13 +1755,13 @@
         </is>
       </c>
       <c r="D42" s="29" t="n">
-        <v>2172</v>
-      </c>
-      <c r="E42" s="28" t="n">
-        <v>-48</v>
+        <v>2257</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>23</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>2220</v>
+        <v>2234</v>
       </c>
       <c r="G42" s="28" t="n">
         <v>-2125</v>
@@ -1738,13 +1791,13 @@
         </is>
       </c>
       <c r="D43" s="29" t="n">
-        <v>2097</v>
+        <v>2009</v>
       </c>
       <c r="E43" s="29" t="n">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="F43" s="29" t="n">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G43" s="28" t="n">
         <v>-2361</v>
@@ -1774,13 +1827,13 @@
         </is>
       </c>
       <c r="D44" s="29" t="n">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="E44" s="29" t="n">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G44" s="28" t="n">
         <v>-1560</v>
@@ -1810,13 +1863,13 @@
         </is>
       </c>
       <c r="D45" s="29" t="n">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G45" s="28" t="n">
         <v>-1175</v>
@@ -1882,13 +1935,13 @@
         </is>
       </c>
       <c r="D47" s="29" t="n">
-        <v>791</v>
+        <v>865</v>
       </c>
       <c r="E47" s="28" t="n">
-        <v>-221</v>
+        <v>-181</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>1011</v>
+        <v>1047</v>
       </c>
       <c r="G47" s="28" t="n">
         <v>-760</v>
@@ -1918,10 +1971,10 @@
         </is>
       </c>
       <c r="D48" s="29" t="n">
-        <v>711</v>
+        <v>756</v>
       </c>
       <c r="E48" s="29" t="n">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="F48" s="29" t="n">
         <v>280</v>
@@ -1954,13 +2007,13 @@
         </is>
       </c>
       <c r="D49" s="28" t="n">
-        <v>-2718</v>
+        <v>-2265</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>-2168</v>
+        <v>-1786</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>-550</v>
+        <v>-479</v>
       </c>
       <c r="G49" s="29" t="n">
         <v>3076</v>
@@ -1990,13 +2043,13 @@
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>-1521</v>
+        <v>-1520</v>
       </c>
       <c r="E50" s="28" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>-873</v>
+        <v>-878</v>
       </c>
       <c r="G50" s="29" t="n">
         <v>1591</v>
@@ -2062,13 +2115,13 @@
         </is>
       </c>
       <c r="D52" s="28" t="n">
-        <v>-783</v>
+        <v>-805</v>
       </c>
       <c r="E52" s="28" t="n">
-        <v>-551</v>
+        <v>-575</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>-232</v>
+        <v>-230</v>
       </c>
       <c r="G52" s="29" t="n">
         <v>626</v>
@@ -2098,13 +2151,13 @@
         </is>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-700</v>
+        <v>-717</v>
       </c>
       <c r="E53" s="28" t="n">
-        <v>-313</v>
+        <v>-327</v>
       </c>
       <c r="F53" s="28" t="n">
-        <v>-386</v>
+        <v>-390</v>
       </c>
       <c r="G53" s="29" t="n">
         <v>764</v>
@@ -2134,13 +2187,13 @@
         </is>
       </c>
       <c r="D54" s="28" t="n">
-        <v>-629</v>
+        <v>-644</v>
       </c>
       <c r="E54" s="28" t="n">
-        <v>-46</v>
+        <v>-57</v>
       </c>
       <c r="F54" s="28" t="n">
-        <v>-583</v>
+        <v>-587</v>
       </c>
       <c r="G54" s="29" t="n">
         <v>634</v>
@@ -2170,13 +2223,13 @@
         </is>
       </c>
       <c r="D55" s="28" t="n">
-        <v>-598</v>
+        <v>-609</v>
       </c>
       <c r="E55" s="28" t="n">
-        <v>-212</v>
+        <v>-228</v>
       </c>
       <c r="F55" s="28" t="n">
-        <v>-386</v>
+        <v>-381</v>
       </c>
       <c r="G55" s="29" t="n">
         <v>571</v>
@@ -2206,13 +2259,13 @@
         </is>
       </c>
       <c r="D56" s="28" t="n">
-        <v>-593</v>
+        <v>-534</v>
       </c>
       <c r="E56" s="28" t="n">
-        <v>-468</v>
+        <v>-405</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>-125</v>
+        <v>-129</v>
       </c>
       <c r="G56" s="29" t="n">
         <v>588</v>
@@ -2227,7 +2280,7 @@
         <v>-292.3</v>
       </c>
     </row>
-    <row r="57" ht="44.5" customHeight="1" s="15">
+    <row r="57" ht="31" customHeight="1" s="15">
       <c r="A57" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2238,32 +2291,32 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>한화에어로스페이스 (운송장비·부품)</t>
+          <t>OCI홀딩스 (금융)</t>
         </is>
       </c>
       <c r="D57" s="28" t="n">
-        <v>-524</v>
+        <v>-478</v>
       </c>
       <c r="E57" s="28" t="n">
-        <v>-559</v>
-      </c>
-      <c r="F57" s="29" t="n">
-        <v>35</v>
+        <v>-42</v>
+      </c>
+      <c r="F57" s="28" t="n">
+        <v>-437</v>
       </c>
       <c r="G57" s="29" t="n">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>146.9</v>
+        <v>37.7</v>
       </c>
       <c r="I57" s="30" t="n">
-        <v>11659.9</v>
+        <v>3421.8</v>
       </c>
       <c r="J57" s="30" t="n">
-        <v>-434.4</v>
-      </c>
-    </row>
-    <row r="58" ht="31" customHeight="1" s="15">
+        <v>-191.7</v>
+      </c>
+    </row>
+    <row r="58" ht="44.5" customHeight="1" s="15">
       <c r="A58" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
@@ -2274,29 +2327,29 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>OCI홀딩스 (금융)</t>
+          <t>한화에어로스페이스 (운송장비·부품)</t>
         </is>
       </c>
       <c r="D58" s="28" t="n">
-        <v>-478</v>
+        <v>-472</v>
       </c>
       <c r="E58" s="28" t="n">
-        <v>-42</v>
-      </c>
-      <c r="F58" s="28" t="n">
-        <v>-437</v>
+        <v>-517</v>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>45</v>
       </c>
       <c r="G58" s="29" t="n">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>37.7</v>
+        <v>146.9</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>3421.8</v>
+        <v>11659.9</v>
       </c>
       <c r="J58" s="30" t="n">
-        <v>-191.7</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="59"/>
@@ -2345,12 +2398,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>삼성전자 (전기·전자)</t>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>주간 수급 집중 1위 종목으로 외국인(+19,244억원)과 기관(+24,020억원)의 강력한 순매수가 유입되었습니다.</t>
+          <t>주간 순매수 29,241억으로 수급 집중도가 높고 AI 메모리 모멘텀 지속.</t>
         </is>
       </c>
     </row>
@@ -2362,29 +2415,29 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>SK하이닉스 (전기·전자)</t>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>주간 수급 집중 2위 종목으로 외국인(+18,707억원)과 기관(+9,895억원)의 순매수가 집중되었으며 대차잔고가 2,044.8억원 감소하여 숏커버 여지가 존재합니다.</t>
+          <t>주간 순매수 2,257억 및 원전 수주 기대감으로 기계·장비 섹터 상승 주도.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="31" customHeight="1" s="15">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>상방 관찰</t>
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>하방 관찰</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>현대건설 (건설)</t>
+          <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>건설 업종 주간 10.99% 상승 속에서 기관이 1,011억원을 순매수하였고 대차잔고가 297.0% 증가하여 향후 숏커버링 가능성을 관찰할 필요가 있습니다.</t>
+          <t>주간 순매수 -2,265억으로 수급 이탈이 뚜렷함.</t>
         </is>
       </c>
     </row>
@@ -2396,189 +2449,225 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>삼성전기 (전기·전자)</t>
+          <t>셀트리온 (제약)</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>주간 순매수 최하위 종목으로 외국인(-2,168억원)과 기관(-550억원)의 동반 순매도가 출회되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="31" customHeight="1" s="15">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>하방 관찰</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>삼양식품 (음식료·담배)</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>음식료·담배 업종의 주간 3.76% 하락 속에서 기관(-833억원)과 외국인(-135억원)의 순매도가 집중되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
+          <t>주간 순매수 -805억으로 수급 약세 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>주간 시장 흐름</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+    </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>주간 시장 흐름</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="15">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 상승 출발.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="31" customHeight="1" s="15">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>- 주 초반 미국 필라델피아 반도체 지수의 급등과 마이크론의 강세에 힘입어 코스피가 외국인과 기관의 강력한 동반 매수세로 4.61% 급등하며 출발했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="31" customHeight="1" s="15">
+          <t>- 2분기 국내 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되어 주 중반 지수 조정 발생.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="15">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>- 주 중반에는 미국 내 대형 원전 8기 건설 협의 기대감과 가덕도 신공항 설계 제출 등 대형 호재가 겹치며 건설 및 전기·가스 섹터가 강세를 주도했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="31" customHeight="1" s="15">
+          <t>- 주 후반 AI 데이터센터 전력 수요 급증과 원전 협력 기대감이 시장을 견인하며 다시 반등세로 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>- 다만 한국의 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되었고, 개인의 대규모 매도세가 출회되며 지수 상승 탄력이 일부 제한되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>- 주 후반에는 중동 지정학적 리스크로 인한 유가 상승과 미국의 고용지표 호조에 따른 금리 인상 우려가 재점화되며 시장 전반에 경계감이 유지되었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+          <t>- 주간 내내 반도체와 전력 설비 섹터로 수급이 집중되는 쏠림 현상이 지속됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>섹터·테마 흐름</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="31" customHeight="1" s="15">
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="15">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체 섹터는 주간 내내 외국인과 기관의 순매수가 집중되며 시장의 핵심 주도주로 자리매김.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="15">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>- 주 초반에는 삼성전자와 SK하이닉스를 필두로 한 전기·전자(+5.92%) 및 기계·장비(+6.47%) 섹터가 AI 반도체 수요 기대감으로 시장을 주도했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>- 주 중반 이후에는 미국 원전 건설 협의 소식과 가덕도 신공항 모멘텀이 부각되며 건설(+2.99%) 및 전기·가스(+3.11%) 섹터로 매기 이전이 일어났습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="31" customHeight="1" s="15">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>- 반면 음식료·담배(-3.76%)와 IT 서비스(-2.61%) 섹터는 환율 하락에 따른 수출 우려 및 차익 실현 매물 출회로 주간 내내 약세를 보였습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+          <t>- 기계·장비 및 건설 섹터는 원전 및 전력 설비 수주 기대감이 확산되며 주 후반으로 갈수록 상승 탄력 강화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" s="3" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="18" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="31" customHeight="1" s="15">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>네오오토 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="C80" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E80" s="29" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="31" customHeight="1" s="15">
+      <c r="A81" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>필옵틱스 (기계·장비)</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="E81" s="29" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2679,7 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>네오오토 (운송장비·부품)</t>
+          <t>나무가 (전기·전자)</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
@@ -2604,11 +2693,11 @@
         </is>
       </c>
       <c r="E82" s="29" t="n">
-        <v>39.17</v>
+        <v>10.45</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2709,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>필옵틱스 (기계·장비)</t>
+          <t>두산퓨얼셀 (전기·전자)</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -2634,11 +2723,11 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>37.98</v>
+        <v>34.32</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -2650,25 +2739,25 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>나무가 (전기·전자)</t>
+          <t>DB하이텍 (전기·전자)</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>10.09</v>
+        <v>27.59</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2769,7 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>두산퓨얼셀 (전기·전자)</t>
+          <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
@@ -2690,15 +2779,15 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>22.92</v>
+        <v>17.3</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2799,7 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>DB하이텍 (전기·전자)</t>
+          <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
@@ -2724,11 +2813,11 @@
         </is>
       </c>
       <c r="E86" s="29" t="n">
-        <v>27.47</v>
+        <v>12.2</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2829,7 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>두산에너빌리티 (기계·장비)</t>
+          <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
@@ -2754,71 +2843,71 @@
         </is>
       </c>
       <c r="E87" s="29" t="n">
-        <v>17.55</v>
+        <v>6.65</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="31" customHeight="1" s="15">
       <c r="A88" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>SK하이닉스 (전기·전자)</t>
+          <t>빛과전자 (전기·전자)</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E88" s="29" t="n">
-        <v>11.48</v>
+        <v>42.54</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" s="15">
       <c r="A89" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>삼성전자 (전기·전자)</t>
+          <t>오르비텍 (일반서비스)</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="E89" s="29" t="n">
-        <v>6.26</v>
+        <v>42.43</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2919,7 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>빛과전자 (전기·전자)</t>
+          <t>서전기전 (전기·전자)</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
@@ -2844,11 +2933,11 @@
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>53.96</v>
+        <v>34.68</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2949,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>오르비텍 (일반서비스)</t>
+          <t>한전기술 (일반서비스)</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -2874,11 +2963,11 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>42.66</v>
+        <v>34.48</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -2890,25 +2979,25 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>서전기전 (전기·전자)</t>
+          <t>현대약품 (제약)</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E92" s="29" t="n">
-        <v>33.97</v>
+        <v>30.44</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -2920,7 +3009,7 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>한전기술 (일반서비스)</t>
+          <t>대우건설 (건설)</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
@@ -2930,144 +3019,108 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>35.04</v>
+        <v>20.18</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="31" customHeight="1" s="15">
-      <c r="A94" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>현대약품 (제약)</t>
-        </is>
-      </c>
-      <c r="C94" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E94" s="29" t="n">
-        <v>33.21</v>
-      </c>
-      <c r="F94" s="17" t="inlineStr">
-        <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="31" customHeight="1" s="15">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>대우건설 (건설)</t>
-        </is>
-      </c>
-      <c r="C95" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="E95" s="29" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="F95" s="17" t="inlineStr">
-        <is>
           <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr"/>
-      <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" s="3" t="inlineStr"/>
-      <c r="F97" s="3" t="inlineStr"/>
-      <c r="G97" s="3" t="inlineStr"/>
-      <c r="H97" s="3" t="inlineStr"/>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="31" customHeight="1" s="15">
-      <c r="A99" s="31" t="inlineStr">
+    <row r="97" ht="31" customHeight="1" s="15">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>상승 시나리오</t>
         </is>
       </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>미국 물가 지표가 예상치를 하회하면 금리 인하 기대감 회복으로 기술주 중심의 상승세 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="31" customHeight="1" s="15">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>하방 시나리오</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 경기 민감주 및 전력 설비주로의 방어적 로테이션 전개</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="15">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>판별 신호</t>
+        </is>
+      </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>미국 CPI 및 PPI 지표가 안정세를 보이며 금리 인하 경로가 명확해지면 반도체 및 기술주 중심의 외국인 수급 유입과 함께 상승 랠리가 전개될 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="31" customHeight="1" s="15">
-      <c r="A100" s="32" t="inlineStr">
-        <is>
-          <t>하방 시나리오</t>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 등락폭</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="15">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>미국 물가 지표가 예상치를 상회하여 인플레이션 우려가 재점화되고 국채 금리가 급등하면 기술주 및 성장주 중심의 차익 실현 매물이 출회되며 하방 압력이 커질 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="31" customHeight="1" s="15">
+          <t>미국 생산자물가지수(PPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="15">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>미국 8월 소비자물가지수(CPI)의 전월대비 및 전년대비 실제치와 이에 따른 미국 국채 금리의 변동성 여부입니다.</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -3079,36 +3132,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI) 전월대비 (9월 10일 21:30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="15">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI) 전년대비 (9월 11일 21:30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="15">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>미국 소매판매 전월대비 (9월 16일 21:30)</t>
+          <t>미국 소매판매</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="47">
     <mergeCell ref="B98:J98"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="G26:J26"/>
@@ -3120,41 +3149,39 @@
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="F84:J84"/>
-    <mergeCell ref="B69:J69"/>
     <mergeCell ref="F89:J89"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C64:J64"/>
     <mergeCell ref="F83:J83"/>
-    <mergeCell ref="B103:J103"/>
-    <mergeCell ref="F95:J95"/>
+    <mergeCell ref="B99:J99"/>
     <mergeCell ref="C63:J63"/>
     <mergeCell ref="C65:J65"/>
     <mergeCell ref="F86:J86"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="A77:J77"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="F94:J94"/>
-    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="F80:J80"/>
+    <mergeCell ref="F79:J79"/>
     <mergeCell ref="F85:J85"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B68:J68"/>
     <mergeCell ref="F91:J91"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="F81:J81"/>
     <mergeCell ref="B32:J32"/>
-    <mergeCell ref="A78:J78"/>
     <mergeCell ref="F90:J90"/>
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="F93:J93"/>
     <mergeCell ref="C61:J61"/>
+    <mergeCell ref="B97:J97"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A75:J75"/>
     <mergeCell ref="F92:J92"/>
     <mergeCell ref="A71:J71"/>
     <mergeCell ref="F82:J82"/>
     <mergeCell ref="B102:J102"/>
-    <mergeCell ref="C66:J66"/>
+    <mergeCell ref="B96:J96"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="F88:J88"/>
@@ -3169,19 +3196,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
-    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
-    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
-    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
-    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
-    <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
-    <col width="13" customWidth="1" style="15" min="9" max="9"/>
+    <col width="30" customWidth="1" style="15" min="1" max="1"/>
+    <col width="9" customWidth="1" style="15" min="2" max="2"/>
+    <col width="10.5" customWidth="1" style="15" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10.5" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="15" min="6" max="6"/>
+    <col width="10.5" customWidth="1" style="15" min="7" max="7"/>
+    <col width="11.5" customWidth="1" style="15" min="8" max="8"/>
+    <col width="11.5" customWidth="1" style="15" min="9" max="9"/>
     <col width="13" customWidth="1" style="15" min="10" max="10"/>
+    <col width="13.5" customWidth="1" style="15" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -3190,12 +3218,12 @@
           <t>신고가 근접</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>기간</t>
         </is>
       </c>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>2026-09-07 ~ 2026-09-09</t>
         </is>
@@ -3221,190 +3249,231 @@
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="18" t="inlineStr">
         <is>
-          <t>수급=주간 누적(억)</t>
+          <t>단위: 억원, %</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="31" customHeight="1" s="15">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>종목 정보</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>수급 (주간 누적, 억원)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>신고가 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>공매도(억)</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>대차잔고(증감,억)</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>등락률(주간,%)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>신고가 대비(%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1" s="15">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>하나금융지주 (금융)</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>공매도</t>
+        </is>
+      </c>
+      <c r="H5" s="33" t="inlineStr">
+        <is>
+          <t>대차잔고</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>대차증감</t>
+        </is>
+      </c>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>주간등락(%)</t>
+        </is>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t>신고가대비(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>대한항공 (운송·창고)</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
-        <v>89</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>-130</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>219</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G5" s="30" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>6,946 (-721)</t>
-        </is>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="J5" s="30" t="n">
-        <v>-5.09</v>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1" s="15">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>대한항공 (운송·창고)</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="C6" s="35" t="n">
+        <v>417</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>277</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>141</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>-395</v>
+      </c>
+      <c r="G6" s="37" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="H6" s="37" t="n">
+        <v>1717.2</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="39" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="K6" s="40" t="n">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>신한지주 (금융)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>417</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>277</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>141</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>-395</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="H6" s="30" t="inlineStr">
-        <is>
-          <t>1,717 (-1)</t>
-        </is>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="J6" s="30" t="n">
-        <v>-4.17</v>
-      </c>
-    </row>
-    <row r="7" ht="31" customHeight="1" s="15">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>신한지주 (금융)</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="35" t="n">
         <v>160</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="36" t="n">
         <v>-133</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="35" t="n">
         <v>293</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="36" t="n">
         <v>-144</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="37" t="n">
         <v>253.3</v>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>7,226 (-535)</t>
-        </is>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J7" s="30" t="n">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="H7" s="37" t="n">
+        <v>7226.2</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>-535.3</v>
+      </c>
+      <c r="J7" s="39" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="K7" s="41" t="n">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>티에스이 (의료·정밀기기)</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr"/>
+      <c r="D8" s="42" t="inlineStr"/>
+      <c r="E8" s="42" t="inlineStr"/>
+      <c r="F8" s="42" t="inlineStr"/>
+      <c r="G8" s="37" t="inlineStr"/>
+      <c r="H8" s="37" t="inlineStr"/>
+      <c r="I8" s="43" t="inlineStr"/>
+      <c r="J8" s="44" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="K8" s="41" t="n">
+        <v>-6.14</v>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=주간 누적 확정(억원)</t>
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>엠젠솔루션 (유통)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr"/>
+      <c r="D9" s="42" t="inlineStr"/>
+      <c r="E9" s="42" t="inlineStr"/>
+      <c r="F9" s="42" t="inlineStr"/>
+      <c r="G9" s="37" t="inlineStr"/>
+      <c r="H9" s="37" t="inlineStr"/>
+      <c r="I9" s="43" t="inlineStr"/>
+      <c r="J9" s="44" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>-2.87</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=주간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A1:G1"/>
+  <autoFilter ref="A5:K9"/>
+  <mergeCells count="6">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3420,12 +3489,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
-    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
-    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
-    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
-    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="6.5" customWidth="1" style="15" min="2" max="2"/>
+    <col width="30" customWidth="1" style="15" min="3" max="3"/>
+    <col width="13" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10" customWidth="1" style="15" min="6" max="6"/>
+    <col width="10" customWidth="1" style="15" min="7" max="7"/>
     <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
     <col width="13" customWidth="1" style="15" min="9" max="9"/>
     <col width="13" customWidth="1" style="15" min="10" max="10"/>
@@ -3474,259 +3543,259 @@
       <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31" customHeight="1" s="15">
+    <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
-        <v>19244</v>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1" s="15">
+      <c r="D5" s="35" t="n">
+        <v>19774</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
-        <v>18707</v>
-      </c>
-    </row>
-    <row r="7" ht="31" customHeight="1" s="15">
+      <c r="D6" s="35" t="n">
+        <v>19401</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
-        <v>2725</v>
-      </c>
-    </row>
-    <row r="8" ht="31" customHeight="1" s="15">
+      <c r="D7" s="35" t="n">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="9" ht="31" customHeight="1" s="15">
+      <c r="D8" s="35" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>효성중공업 (전기·전자)</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="35" t="n">
         <v>745</v>
       </c>
     </row>
-    <row r="10" ht="31" customHeight="1" s="15">
+    <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>LG전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="11" ht="31" customHeight="1" s="15">
+      <c r="D10" s="35" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>HPSP (기계·장비)</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="12" ht="31" customHeight="1" s="15">
+      <c r="D11" s="35" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>LS ELECTRIC (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>심텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>삼성전자우 (전기·전자)</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="13" ht="31" customHeight="1" s="15">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>LS ELECTRIC (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="15">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>심텍 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="15" ht="31" customHeight="1" s="15">
+      <c r="D14" s="35" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n">
-        <v>-2168</v>
-      </c>
-    </row>
-    <row r="16" ht="31" customHeight="1" s="15">
+      <c r="D15" s="36" t="n">
+        <v>-1786</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>삼성SDI (전기·전자)</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n">
-        <v>-648</v>
-      </c>
-    </row>
-    <row r="17" ht="44.5" customHeight="1" s="15">
+      <c r="D16" s="36" t="n">
+        <v>-642</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스 (운송장비·부품)</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="n">
-        <v>-559</v>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>셀트리온 (제약)</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="n">
+        <v>-575</v>
       </c>
     </row>
     <row r="18" ht="31" customHeight="1" s="15">
@@ -3735,124 +3804,124 @@
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="34" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>셀트리온 (제약)</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="n">
-        <v>-551</v>
-      </c>
-    </row>
-    <row r="19" ht="44.5" customHeight="1" s="15">
+          <t>한화에어로스페이스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="n">
+        <v>-517</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스 (금속)</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>-444</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>레인보우로보틱스 (기계·장비)</t>
         </is>
       </c>
-      <c r="D19" s="28" t="n">
-        <v>-468</v>
-      </c>
-    </row>
-    <row r="20" ht="31" customHeight="1" s="15">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="D20" s="36" t="n">
+        <v>-405</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>POSCO홀딩스 (금속)</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>-444</v>
-      </c>
-    </row>
-    <row r="21" ht="31" customHeight="1" s="15">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B21" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>현대차 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>-368</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>현대차 (운송장비·부품)</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>-387</v>
-      </c>
-    </row>
-    <row r="22" ht="31" customHeight="1" s="15">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="B22" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>-327</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>-313</v>
-      </c>
-    </row>
-    <row r="23" ht="44.5" customHeight="1" s="15">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="B23" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>HD현대중공업 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>-319</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>HD현대중공업 (운송장비·부품)</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="n">
-        <v>-306</v>
-      </c>
-    </row>
-    <row r="24" ht="31" customHeight="1" s="15">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>DB하이텍 (전기·전자)</t>
         </is>
       </c>
-      <c r="D24" s="28" t="n">
-        <v>-265</v>
+      <c r="D24" s="36" t="n">
+        <v>-282</v>
       </c>
     </row>
     <row r="25"/>
@@ -3881,385 +3950,385 @@
       <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="31" customHeight="1" s="15">
+    <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n">
-        <v>24020</v>
-      </c>
-    </row>
-    <row r="29" ht="31" customHeight="1" s="15">
+      <c r="D28" s="35" t="n">
+        <v>24053</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n">
-        <v>9895</v>
-      </c>
-    </row>
-    <row r="30" ht="31" customHeight="1" s="15">
+      <c r="D29" s="35" t="n">
+        <v>9839</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="D30" s="29" t="n">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="31" ht="31" customHeight="1" s="15">
+      <c r="D30" s="35" t="n">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
-      <c r="D31" s="29" t="n">
-        <v>2220</v>
-      </c>
-    </row>
-    <row r="32" ht="31" customHeight="1" s="15">
+      <c r="D31" s="35" t="n">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>삼성전자우 (전기·전자)</t>
         </is>
       </c>
-      <c r="D32" s="29" t="n">
-        <v>1598</v>
-      </c>
-    </row>
-    <row r="33" ht="31" customHeight="1" s="15">
+      <c r="D32" s="35" t="n">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>현대건설 (건설)</t>
         </is>
       </c>
-      <c r="D33" s="29" t="n">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="34" ht="31" customHeight="1" s="15">
+      <c r="D33" s="35" t="n">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>삼성물산 (유통)</t>
         </is>
       </c>
-      <c r="D34" s="29" t="n">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="35" ht="31" customHeight="1" s="15">
+      <c r="D34" s="35" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="D35" s="29" t="n">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="36" ht="31" customHeight="1" s="15">
+      <c r="D35" s="35" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>LG전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D36" s="29" t="n">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="37" ht="31" customHeight="1" s="15">
+      <c r="D36" s="35" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>대우건설 (건설)</t>
         </is>
       </c>
-      <c r="D37" s="29" t="n">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="38" ht="31" customHeight="1" s="15">
+      <c r="D37" s="35" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B38" s="30" t="n">
+      <c r="B38" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>삼성SDI (전기·전자)</t>
         </is>
       </c>
-      <c r="D38" s="28" t="n">
-        <v>-873</v>
-      </c>
-    </row>
-    <row r="39" ht="31" customHeight="1" s="15">
+      <c r="D38" s="36" t="n">
+        <v>-878</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n">
+      <c r="B39" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>삼양식품 (음식료·담배)</t>
         </is>
       </c>
-      <c r="D39" s="28" t="n">
+      <c r="D39" s="36" t="n">
         <v>-833</v>
       </c>
     </row>
-    <row r="40" ht="31" customHeight="1" s="15">
+    <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B40" s="30" t="n">
+      <c r="B40" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>알테오젠 (일반서비스)</t>
         </is>
       </c>
-      <c r="D40" s="28" t="n">
-        <v>-643</v>
-      </c>
-    </row>
-    <row r="41" ht="31" customHeight="1" s="15">
+      <c r="D40" s="36" t="n">
+        <v>-685</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
+      <c r="B41" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>에이피알 (화학)</t>
         </is>
       </c>
-      <c r="D41" s="28" t="n">
-        <v>-583</v>
-      </c>
-    </row>
-    <row r="42" ht="31" customHeight="1" s="15">
+      <c r="D41" s="36" t="n">
+        <v>-587</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B42" s="30" t="n">
+      <c r="B42" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>현대모비스 (운송장비·부품)</t>
+        </is>
+      </c>
+      <c r="D42" s="36" t="n">
+        <v>-508</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="D42" s="28" t="n">
-        <v>-550</v>
-      </c>
-    </row>
-    <row r="43" ht="31" customHeight="1" s="15">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="D43" s="36" t="n">
+        <v>-479</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B43" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>현대모비스 (운송장비·부품)</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="44" ht="31" customHeight="1" s="15">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="B44" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>OCI홀딩스 (금융)</t>
+        </is>
+      </c>
+      <c r="D44" s="36" t="n">
+        <v>-437</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>OCI홀딩스 (금융)</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="n">
-        <v>-437</v>
-      </c>
-    </row>
-    <row r="45" ht="31" customHeight="1" s="15">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="B45" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="n">
+        <v>-390</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B45" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="n">
-        <v>-386</v>
-      </c>
-    </row>
-    <row r="46" ht="31" customHeight="1" s="15">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="B46" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>LG이노텍 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D46" s="36" t="n">
+        <v>-381</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B46" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>LG이노텍 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="n">
-        <v>-386</v>
-      </c>
-    </row>
-    <row r="47" ht="31" customHeight="1" s="15">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="n">
+      <c r="B47" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>실리콘투 (유통)</t>
         </is>
       </c>
-      <c r="D47" s="28" t="n">
-        <v>-357</v>
+      <c r="D47" s="36" t="n">
+        <v>-364</v>
       </c>
     </row>
     <row r="48"/>
@@ -4288,385 +4357,385 @@
       <c r="J49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="33" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="31" customHeight="1" s="15">
+    <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B51" s="30" t="n">
+      <c r="B51" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="C51" s="30" t="inlineStr">
         <is>
           <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
-      <c r="D51" s="29" t="n">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="52" ht="31" customHeight="1" s="15">
+      <c r="D51" s="35" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B52" s="30" t="n">
+      <c r="B52" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="D52" s="29" t="n">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="53" ht="31" customHeight="1" s="15">
+      <c r="D52" s="35" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B53" s="30" t="n">
+      <c r="B53" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="30" t="inlineStr">
         <is>
           <t>현대건설 (건설)</t>
         </is>
       </c>
-      <c r="D53" s="29" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="54" ht="31" customHeight="1" s="15">
+      <c r="D53" s="35" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B54" s="30" t="n">
+      <c r="B54" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>두산 (전기·전자)</t>
         </is>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="35" t="n">
         <v>265</v>
       </c>
     </row>
-    <row r="55" ht="31" customHeight="1" s="15">
+    <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B55" s="30" t="n">
+      <c r="B55" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>삼성전자우 (전기·전자)</t>
         </is>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="35" t="n">
         <v>247</v>
       </c>
     </row>
-    <row r="56" ht="31" customHeight="1" s="15">
+    <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B56" s="30" t="n">
+      <c r="B56" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>LG전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D56" s="29" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" ht="31" customHeight="1" s="15">
+      <c r="D56" s="35" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B57" s="30" t="n">
+      <c r="B57" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C57" s="30" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="D57" s="29" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" ht="31" customHeight="1" s="15">
+      <c r="D57" s="35" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B58" s="30" t="n">
+      <c r="B58" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>이수페타시스 (전기·전자)</t>
         </is>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="35" t="n">
         <v>172</v>
       </c>
     </row>
-    <row r="59" ht="31" customHeight="1" s="15">
+    <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B59" s="30" t="n">
+      <c r="B59" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>SK이노베이션 (화학)</t>
         </is>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="35" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="60" ht="31" customHeight="1" s="15">
+    <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B60" s="30" t="n">
+      <c r="B60" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>삼성생명 (보험)</t>
         </is>
       </c>
-      <c r="D60" s="29" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="61" ht="31" customHeight="1" s="15">
+      <c r="D60" s="35" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B61" s="30" t="n">
+      <c r="B61" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D61" s="28" t="n">
-        <v>-1339</v>
-      </c>
-    </row>
-    <row r="62" ht="31" customHeight="1" s="15">
+      <c r="D61" s="36" t="n">
+        <v>-1309</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B62" s="30" t="n">
+      <c r="B62" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="D62" s="28" t="n">
-        <v>-832</v>
-      </c>
-    </row>
-    <row r="63" ht="31" customHeight="1" s="15">
+      <c r="D62" s="36" t="n">
+        <v>-739</v>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B63" s="30" t="n">
+      <c r="B63" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>현대차 (운송장비·부품)</t>
         </is>
       </c>
-      <c r="D63" s="28" t="n">
+      <c r="D63" s="36" t="n">
         <v>-383</v>
       </c>
     </row>
-    <row r="64" ht="31" customHeight="1" s="15">
+    <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B64" s="30" t="n">
+      <c r="B64" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>현대모비스 (운송장비·부품)</t>
         </is>
       </c>
-      <c r="D64" s="28" t="n">
-        <v>-366</v>
-      </c>
-    </row>
-    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="D64" s="36" t="n">
+        <v>-378</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B65" s="30" t="n">
+      <c r="B65" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>삼성SDI (전기·전자)</t>
         </is>
       </c>
-      <c r="D65" s="28" t="n">
-        <v>-325</v>
-      </c>
-    </row>
-    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="D65" s="36" t="n">
+        <v>-331</v>
+      </c>
+    </row>
+    <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B66" s="30" t="n">
+      <c r="B66" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>셀트리온 (제약)</t>
         </is>
       </c>
-      <c r="D66" s="28" t="n">
-        <v>-244</v>
-      </c>
-    </row>
-    <row r="67" ht="31" customHeight="1" s="15">
+      <c r="D66" s="36" t="n">
+        <v>-242</v>
+      </c>
+    </row>
+    <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B67" s="30" t="n">
+      <c r="B67" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>대덕전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D67" s="28" t="n">
+      <c r="D67" s="36" t="n">
         <v>-188</v>
       </c>
     </row>
-    <row r="68" ht="31" customHeight="1" s="15">
+    <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B68" s="30" t="n">
+      <c r="B68" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>알테오젠 (일반서비스)</t>
         </is>
       </c>
-      <c r="D68" s="28" t="n">
-        <v>-184</v>
-      </c>
-    </row>
-    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="D68" s="36" t="n">
+        <v>-186</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B69" s="30" t="n">
+      <c r="B69" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>삼성전기 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="n">
-        <v>-164</v>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>엘앤에프 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D69" s="36" t="n">
+        <v>-159</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B70" s="30" t="n">
+      <c r="B70" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C70" s="17" t="inlineStr">
-        <is>
-          <t>엘앤에프 (전기·전자)</t>
-        </is>
-      </c>
-      <c r="D70" s="28" t="n">
-        <v>-155</v>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 (전기·전자)</t>
+        </is>
+      </c>
+      <c r="D70" s="36" t="n">
+        <v>-154</v>
       </c>
     </row>
     <row r="71"/>
@@ -4695,196 +4764,196 @@
       <c r="J72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="33" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="33" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="31" customHeight="1" s="15">
+    <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B74" s="30" t="n">
+      <c r="B74" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="35" t="n">
         <v>3076</v>
       </c>
     </row>
-    <row r="75" ht="31" customHeight="1" s="15">
+    <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B75" s="30" t="n">
+      <c r="B75" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>삼성SDI (전기·전자)</t>
         </is>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="35" t="n">
         <v>1591</v>
       </c>
     </row>
-    <row r="76" ht="31" customHeight="1" s="15">
+    <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B76" s="30" t="n">
+      <c r="B76" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>삼양식품 (음식료·담배)</t>
         </is>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="35" t="n">
         <v>966</v>
       </c>
     </row>
-    <row r="77" ht="31" customHeight="1" s="15">
+    <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B77" s="30" t="n">
+      <c r="B77" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>LG에너지솔루션 (전기·전자)</t>
         </is>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="35" t="n">
         <v>764</v>
       </c>
     </row>
-    <row r="78" ht="31" customHeight="1" s="15">
+    <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B78" s="30" t="n">
+      <c r="B78" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>에이피알 (화학)</t>
         </is>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="35" t="n">
         <v>634</v>
       </c>
     </row>
-    <row r="79" ht="31" customHeight="1" s="15">
+    <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B79" s="30" t="n">
+      <c r="B79" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="C79" s="30" t="inlineStr">
         <is>
           <t>셀트리온 (제약)</t>
         </is>
       </c>
-      <c r="D79" s="29" t="n">
+      <c r="D79" s="35" t="n">
         <v>626</v>
       </c>
     </row>
-    <row r="80" ht="44.5" customHeight="1" s="15">
+    <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B80" s="30" t="n">
+      <c r="B80" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C80" s="17" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>레인보우로보틱스 (기계·장비)</t>
         </is>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="35" t="n">
         <v>588</v>
       </c>
     </row>
-    <row r="81" ht="31" customHeight="1" s="15">
+    <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B81" s="30" t="n">
+      <c r="B81" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C81" s="17" t="inlineStr">
+      <c r="C81" s="30" t="inlineStr">
         <is>
           <t>LG이노텍 (전기·전자)</t>
         </is>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="35" t="n">
         <v>571</v>
       </c>
     </row>
-    <row r="82" ht="31" customHeight="1" s="15">
+    <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B82" s="30" t="n">
+      <c r="B82" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C82" s="17" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <t>알테오젠 (일반서비스)</t>
         </is>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="35" t="n">
         <v>559</v>
       </c>
     </row>
-    <row r="83" ht="44.5" customHeight="1" s="15">
+    <row r="83" ht="31" customHeight="1" s="15">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B83" s="30" t="n">
+      <c r="B83" s="34" t="n">
         <v>10</v>
       </c>
       <c r="C83" s="17" t="inlineStr">
@@ -4892,187 +4961,187 @@
           <t>한화에어로스페이스 (운송장비·부품)</t>
         </is>
       </c>
-      <c r="D83" s="29" t="n">
+      <c r="D83" s="35" t="n">
         <v>528</v>
       </c>
     </row>
-    <row r="84" ht="31" customHeight="1" s="15">
+    <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B84" s="30" t="n">
+      <c r="B84" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C84" s="30" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D84" s="28" t="n">
+      <c r="D84" s="36" t="n">
         <v>-55192</v>
       </c>
     </row>
-    <row r="85" ht="31" customHeight="1" s="15">
+    <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B85" s="30" t="n">
+      <c r="B85" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="C85" s="17" t="inlineStr">
+      <c r="C85" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="D85" s="28" t="n">
+      <c r="D85" s="36" t="n">
         <v>-52130</v>
       </c>
     </row>
-    <row r="86" ht="31" customHeight="1" s="15">
+    <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B86" s="30" t="n">
+      <c r="B86" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C86" s="17" t="inlineStr">
+      <c r="C86" s="30" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="D86" s="28" t="n">
+      <c r="D86" s="36" t="n">
         <v>-5184</v>
       </c>
     </row>
-    <row r="87" ht="31" customHeight="1" s="15">
+    <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B87" s="30" t="n">
+      <c r="B87" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C87" s="17" t="inlineStr">
+      <c r="C87" s="30" t="inlineStr">
         <is>
           <t>삼성전자우 (전기·전자)</t>
         </is>
       </c>
-      <c r="D87" s="28" t="n">
+      <c r="D87" s="36" t="n">
         <v>-2361</v>
       </c>
     </row>
-    <row r="88" ht="31" customHeight="1" s="15">
+    <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B88" s="30" t="n">
+      <c r="B88" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
-      <c r="D88" s="28" t="n">
+      <c r="D88" s="36" t="n">
         <v>-2125</v>
       </c>
     </row>
-    <row r="89" ht="31" customHeight="1" s="15">
+    <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B89" s="30" t="n">
+      <c r="B89" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C89" s="17" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="D89" s="28" t="n">
+      <c r="D89" s="36" t="n">
         <v>-1560</v>
       </c>
     </row>
-    <row r="90" ht="31" customHeight="1" s="15">
+    <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B90" s="30" t="n">
+      <c r="B90" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C90" s="17" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>LG전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="D90" s="28" t="n">
+      <c r="D90" s="36" t="n">
         <v>-1175</v>
       </c>
     </row>
-    <row r="91" ht="31" customHeight="1" s="15">
+    <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B91" s="30" t="n">
+      <c r="B91" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C91" s="17" t="inlineStr">
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>효성중공업 (전기·전자)</t>
         </is>
       </c>
-      <c r="D91" s="28" t="n">
+      <c r="D91" s="36" t="n">
         <v>-863</v>
       </c>
     </row>
-    <row r="92" ht="31" customHeight="1" s="15">
+    <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B92" s="30" t="n">
+      <c r="B92" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C92" s="17" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>대우건설 (건설)</t>
         </is>
       </c>
-      <c r="D92" s="28" t="n">
+      <c r="D92" s="36" t="n">
         <v>-812</v>
       </c>
     </row>
-    <row r="93" ht="31" customHeight="1" s="15">
+    <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B93" s="30" t="n">
+      <c r="B93" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C93" s="17" t="inlineStr">
+      <c r="C93" s="30" t="inlineStr">
         <is>
           <t>현대건설 (건설)</t>
         </is>
       </c>
-      <c r="D93" s="28" t="n">
+      <c r="D93" s="36" t="n">
         <v>-760</v>
       </c>
     </row>
@@ -5080,19 +5149,15 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치</t>
+          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D4:J4"/>
+  <mergeCells count="3">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A95:J95"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D50:J50"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="A95:J95"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5107,13 +5172,13 @@
   <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
-    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
-    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
-    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
-    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="6.5" customWidth="1" style="15" min="1" max="1"/>
+    <col width="30" customWidth="1" style="15" min="2" max="2"/>
+    <col width="14" customWidth="1" style="15" min="3" max="3"/>
+    <col width="13" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10" customWidth="1" style="15" min="6" max="6"/>
+    <col width="10" customWidth="1" style="15" min="7" max="7"/>
     <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
     <col width="13" customWidth="1" style="15" min="9" max="9"/>
     <col width="13" customWidth="1" style="15" min="10" max="10"/>
@@ -5162,76 +5227,76 @@
       <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>공매도 누적(억)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31" customHeight="1" s="15">
-      <c r="A5" s="30" t="n">
+    <row r="5">
+      <c r="A5" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="45" t="n">
         <v>3364</v>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1" s="15">
-      <c r="A6" s="30" t="n">
+    <row r="6">
+      <c r="A6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="45" t="n">
         <v>1817</v>
       </c>
     </row>
-    <row r="7" ht="31" customHeight="1" s="15">
-      <c r="A7" s="30" t="n">
+    <row r="7">
+      <c r="A7" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>두산에너빌리티 (기계·장비)</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="45" t="n">
         <v>900</v>
       </c>
     </row>
-    <row r="8" ht="31" customHeight="1" s="15">
-      <c r="A8" s="30" t="n">
+    <row r="8">
+      <c r="A8" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="45" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="34" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -5239,72 +5304,72 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="45" t="n">
         <v>682</v>
       </c>
     </row>
-    <row r="10" ht="31" customHeight="1" s="15">
-      <c r="A10" s="30" t="n">
+    <row r="10">
+      <c r="A10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>LG이노텍 (전기·전자)</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="45" t="n">
         <v>564</v>
       </c>
     </row>
-    <row r="11" ht="31" customHeight="1" s="15">
-      <c r="A11" s="30" t="n">
+    <row r="11">
+      <c r="A11" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="45" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="12" ht="31" customHeight="1" s="15">
-      <c r="A12" s="30" t="n">
+    <row r="12">
+      <c r="A12" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>LG전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="45" t="n">
         <v>422</v>
       </c>
     </row>
-    <row r="13" ht="31" customHeight="1" s="15">
-      <c r="A13" s="30" t="n">
+    <row r="13">
+      <c r="A13" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>LG에너지솔루션 (전기·전자)</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="45" t="n">
         <v>419</v>
       </c>
     </row>
-    <row r="14" ht="31" customHeight="1" s="15">
-      <c r="A14" s="30" t="n">
+    <row r="14">
+      <c r="A14" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="45" t="n">
         <v>366</v>
       </c>
     </row>
@@ -5334,77 +5399,77 @@
       <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>잔고(억)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="31" customHeight="1" s="15">
-      <c r="A18" s="30" t="n">
+    <row r="18">
+      <c r="A18" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>대우건설 (건설)</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="46" t="n">
         <v>482.9</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="45" t="n">
         <v>6222.6</v>
       </c>
     </row>
-    <row r="19" ht="31" customHeight="1" s="15">
-      <c r="A19" s="30" t="n">
+    <row r="19">
+      <c r="A19" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>한전기술 (일반서비스)</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="46" t="n">
         <v>428.8</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="45" t="n">
         <v>3588.6</v>
       </c>
     </row>
-    <row r="20" ht="31" customHeight="1" s="15">
-      <c r="A20" s="30" t="n">
+    <row r="20">
+      <c r="A20" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>현대건설 (건설)</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="46" t="n">
         <v>297</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="45" t="n">
         <v>8765.6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="34" t="n">
         <v>4</v>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -5412,47 +5477,47 @@
           <t>한국전력</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="46" t="n">
         <v>232.6</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="45" t="n">
         <v>2580.7</v>
       </c>
     </row>
-    <row r="22" ht="31" customHeight="1" s="15">
-      <c r="A22" s="30" t="n">
+    <row r="22">
+      <c r="A22" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>하이브 (오락·문화)</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="46" t="n">
         <v>208.2</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="45" t="n">
         <v>4141.5</v>
       </c>
     </row>
-    <row r="23" ht="31" customHeight="1" s="15">
-      <c r="A23" s="30" t="n">
+    <row r="23">
+      <c r="A23" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>한미사이언스 (금융)</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="46" t="n">
         <v>118.5</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="45" t="n">
         <v>1555.4</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="34" t="n">
         <v>7</v>
       </c>
       <c r="B24" s="30" t="inlineStr">
@@ -5460,58 +5525,58 @@
           <t>한진칼 (금융)</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="46" t="n">
         <v>105.4</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="45" t="n">
         <v>3084.3</v>
       </c>
     </row>
-    <row r="25" ht="31" customHeight="1" s="15">
-      <c r="A25" s="30" t="n">
+    <row r="25">
+      <c r="A25" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>미래에셋증권 (증권)</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="46" t="n">
         <v>81.8</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="45" t="n">
         <v>8085.4</v>
       </c>
     </row>
-    <row r="26" ht="31" customHeight="1" s="15">
-      <c r="A26" s="30" t="n">
+    <row r="26">
+      <c r="A26" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>SK스퀘어 (금융)</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="46" t="n">
         <v>79.8</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="45" t="n">
         <v>32891.8</v>
       </c>
     </row>
-    <row r="27" ht="31" customHeight="1" s="15">
-      <c r="A27" s="30" t="n">
+    <row r="27">
+      <c r="A27" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>산일전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="46" t="n">
         <v>63.6</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="45" t="n">
         <v>4014.7</v>
       </c>
     </row>
@@ -5541,109 +5606,109 @@
       <c r="J29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>종목</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>잔고(억)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="31" customHeight="1" s="15">
-      <c r="A31" s="30" t="n">
+    <row r="31">
+      <c r="A31" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>삼성전자 (전기·전자)</t>
         </is>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C31" s="38" t="n">
         <v>-7162.4</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="45" t="n">
         <v>240284.8</v>
       </c>
     </row>
-    <row r="32" ht="31" customHeight="1" s="15">
-      <c r="A32" s="30" t="n">
+    <row r="32">
+      <c r="A32" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>삼성전기 (전기·전자)</t>
         </is>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="38" t="n">
         <v>-2801</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="45" t="n">
         <v>36009</v>
       </c>
     </row>
-    <row r="33" ht="31" customHeight="1" s="15">
-      <c r="A33" s="30" t="n">
+    <row r="33">
+      <c r="A33" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스 (전기·전자)</t>
         </is>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C33" s="38" t="n">
         <v>-2044.8</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="45" t="n">
         <v>223759.5</v>
       </c>
     </row>
-    <row r="34" ht="31" customHeight="1" s="15">
-      <c r="A34" s="30" t="n">
+    <row r="34">
+      <c r="A34" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>LG에너지솔루션 (전기·전자)</t>
         </is>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C34" s="38" t="n">
         <v>-1186.9</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="45" t="n">
         <v>31440</v>
       </c>
     </row>
-    <row r="35" ht="31" customHeight="1" s="15">
-      <c r="A35" s="30" t="n">
+    <row r="35">
+      <c r="A35" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>LG이노텍 (전기·전자)</t>
         </is>
       </c>
-      <c r="C35" s="28" t="n">
+      <c r="C35" s="38" t="n">
         <v>-1092.4</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="45" t="n">
         <v>9333.9</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="34" t="n">
         <v>6</v>
       </c>
       <c r="B36" s="30" t="inlineStr">
@@ -5651,74 +5716,74 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C36" s="38" t="n">
         <v>-870.4</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="45" t="n">
         <v>32571.3</v>
       </c>
     </row>
-    <row r="37" ht="31" customHeight="1" s="15">
-      <c r="A37" s="30" t="n">
+    <row r="37">
+      <c r="A37" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>한미반도체 (기계·장비)</t>
         </is>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="38" t="n">
         <v>-835.3</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="45" t="n">
         <v>43511.4</v>
       </c>
     </row>
-    <row r="38" ht="31" customHeight="1" s="15">
-      <c r="A38" s="30" t="n">
+    <row r="38">
+      <c r="A38" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>심텍 (전기·전자)</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C38" s="38" t="n">
         <v>-770</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="45" t="n">
         <v>7482.8</v>
       </c>
     </row>
-    <row r="39" ht="31" customHeight="1" s="15">
-      <c r="A39" s="30" t="n">
+    <row r="39">
+      <c r="A39" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>하나금융지주 (금융)</t>
         </is>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C39" s="38" t="n">
         <v>-720.6</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="45" t="n">
         <v>6946</v>
       </c>
     </row>
-    <row r="40" ht="31" customHeight="1" s="15">
-      <c r="A40" s="30" t="n">
+    <row r="40">
+      <c r="A40" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>NAVER (IT 서비스)</t>
         </is>
       </c>
-      <c r="C40" s="28" t="n">
+      <c r="C40" s="38" t="n">
         <v>-685.7</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="45" t="n">
         <v>11396.4</v>
       </c>
     </row>
@@ -5731,13 +5796,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C4:J4"/>
+  <mergeCells count="3">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D30:J30"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5752,13 +5814,13 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
-    <col width="13.9" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12.9" customWidth="1" style="15" min="4" max="4"/>
-    <col width="13.9" customWidth="1" style="15" min="5" max="5"/>
-    <col width="20.9" customWidth="1" style="15" min="6" max="6"/>
-    <col width="14.9" customWidth="1" style="15" min="7" max="7"/>
+    <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
+    <col width="12" customWidth="1" style="15" min="2" max="2"/>
+    <col width="10.5" customWidth="1" style="15" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10.5" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="15" min="6" max="6"/>
+    <col width="12" customWidth="1" style="15" min="7" max="7"/>
     <col width="12.9" customWidth="1" style="15" min="8" max="8"/>
     <col width="13" customWidth="1" style="15" min="9" max="9"/>
     <col width="13" customWidth="1" style="15" min="10" max="10"/>
@@ -5798,46 +5860,46 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>주간 등락 vs 투자자 순매수(억)</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>주간등락(%)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -5849,22 +5911,22 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="C5" s="29" t="n">
-        <v>886</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <v>2888</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>908</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-3784</v>
-      </c>
-      <c r="G5" s="30" t="inlineStr"/>
+      <c r="B5" s="44" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>837</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>2841</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>868</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>-3685</v>
+      </c>
+      <c r="G5" s="34" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
@@ -5872,22 +5934,22 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>-67</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>1773</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>407</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-1936</v>
-      </c>
-      <c r="G6" s="30" t="inlineStr"/>
+      <c r="B6" s="44" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>1835</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>439</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>-2114</v>
+      </c>
+      <c r="G6" s="34" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="30" t="inlineStr">
@@ -5895,68 +5957,68 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="C7" s="29" t="n">
-        <v>30380</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>26434</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>-1482</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-91575</v>
-      </c>
-      <c r="G7" s="30" t="inlineStr"/>
+      <c r="B7" s="44" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>31244</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>28343</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>-810</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>-96473</v>
+      </c>
+      <c r="G7" s="34" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-352</v>
-      </c>
-      <c r="G8" s="30" t="inlineStr"/>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>29396</v>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>27891</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>-2060</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>-94525</v>
+      </c>
+      <c r="G8" s="34" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>28795</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>26164</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-2649</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-90066</v>
-      </c>
-      <c r="G9" s="30" t="inlineStr"/>
+          <t>전기·가스</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>331</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>-345</v>
+      </c>
+      <c r="G9" s="34" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -5964,22 +6026,22 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="C10" s="28" t="n">
-        <v>-24</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>703</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>106</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-654</v>
-      </c>
-      <c r="G10" s="30" t="inlineStr"/>
+      <c r="B10" s="44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>744</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>115</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>-683</v>
+      </c>
+      <c r="G10" s="34" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
@@ -5987,68 +6049,72 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>-191</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>602</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-713</v>
-      </c>
-      <c r="G11" s="30" t="inlineStr"/>
+      <c r="B11" s="44" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>-247</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>587</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>-668</v>
+      </c>
+      <c r="G11" s="34" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
         <is>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>-94</v>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>54</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="47" t="inlineStr">
+        <is>
+          <t>과열주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>1082</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>4076</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>917</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>-5257</v>
-      </c>
-      <c r="G12" s="30" t="inlineStr"/>
-    </row>
-    <row r="13" ht="31" customHeight="1" s="15">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>-106</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="30" t="inlineStr"/>
+      <c r="B13" s="44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>871</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>960</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G13" s="34" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -6056,45 +6122,45 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>260</v>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>-17</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>-252</v>
-      </c>
-      <c r="G14" s="30" t="inlineStr"/>
-    </row>
-    <row r="15" ht="31" customHeight="1" s="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="B14" s="44" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>254</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F14" s="36" t="n">
+        <v>-242</v>
+      </c>
+      <c r="G14" s="34" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C15" s="28" t="n">
-        <v>-868</v>
-      </c>
-      <c r="D15" s="28" t="n">
-        <v>-416</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>-1077</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>1260</v>
-      </c>
-      <c r="G15" s="30" t="inlineStr"/>
+      <c r="B15" s="44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>-910</v>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>-443</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>-1089</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>1335</v>
+      </c>
+      <c r="G15" s="34" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
@@ -6102,229 +6168,237 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>-742</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>194</v>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>489</v>
-      </c>
-      <c r="G16" s="30" t="inlineStr"/>
+      <c r="B16" s="39" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>-760</v>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>153</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>-85</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>544</v>
+      </c>
+      <c r="G16" s="34" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>오락·문화</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G17" s="30" t="inlineStr"/>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>-232</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>432</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>199</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>-206</v>
+      </c>
+      <c r="G17" s="34" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>363</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>191</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>27</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-532</v>
-      </c>
-      <c r="G18" s="30" t="inlineStr"/>
+          <t>통신</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="C18" s="35" t="n">
+        <v>52</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>152</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>-202</v>
+      </c>
+      <c r="G18" s="34" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>통신</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>199</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>-231</v>
-      </c>
-      <c r="G19" s="30" t="inlineStr"/>
+          <t>비금속</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="34" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>비금속</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="30" t="inlineStr"/>
+          <t>오락·문화</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>-12</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="34" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="C21" s="28" t="n">
-        <v>-71</v>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>-1231</v>
-      </c>
-      <c r="E21" s="28" t="n">
-        <v>-298</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>1287</v>
-      </c>
-      <c r="G21" s="30" t="inlineStr"/>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>-8</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G21" s="34" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>-252</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>445</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>216</v>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>-204</v>
-      </c>
-      <c r="G22" s="30" t="inlineStr"/>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>-86</v>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>-1240</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>-268</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G22" s="34" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="C23" s="28" t="n">
-        <v>-10</v>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="E23" s="29" t="n">
-        <v>21</v>
-      </c>
-      <c r="F23" s="28" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G23" s="30" t="inlineStr"/>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>-533</v>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>-663</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>-532</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>982</v>
+      </c>
+      <c r="G23" s="34" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>종이·목재</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="C24" s="28" t="n">
-        <v>-5</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G24" s="30" t="inlineStr"/>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>419</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>180</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="F24" s="36" t="n">
+        <v>-577</v>
+      </c>
+      <c r="G24" s="48" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C25" s="28" t="n">
-        <v>-471</v>
-      </c>
-      <c r="D25" s="28" t="n">
-        <v>-651</v>
-      </c>
-      <c r="E25" s="28" t="n">
-        <v>-530</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>916</v>
-      </c>
-      <c r="G25" s="30" t="inlineStr"/>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G25" s="48" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
@@ -6332,22 +6406,22 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="C26" s="28" t="n">
-        <v>-15</v>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E26" s="29" t="n">
+      <c r="B26" s="39" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>-16</v>
+      </c>
+      <c r="D26" s="36" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E26" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="F26" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="G26" s="30" t="inlineStr"/>
+      <c r="F26" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="G26" s="34" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
@@ -6355,22 +6429,22 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
-        <v>-2.61</v>
-      </c>
-      <c r="C27" s="28" t="n">
-        <v>-301</v>
-      </c>
-      <c r="D27" s="28" t="n">
-        <v>-269</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>-367</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>580</v>
-      </c>
-      <c r="G27" s="30" t="inlineStr"/>
+      <c r="B27" s="39" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>-387</v>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>-342</v>
+      </c>
+      <c r="E27" s="36" t="n">
+        <v>-388</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>746</v>
+      </c>
+      <c r="G27" s="34" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
@@ -6378,22 +6452,22 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
-        <v>-3.76</v>
-      </c>
-      <c r="C28" s="28" t="n">
-        <v>-202</v>
-      </c>
-      <c r="D28" s="28" t="n">
-        <v>-1100</v>
-      </c>
-      <c r="E28" s="28" t="n">
-        <v>-182</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>1278</v>
-      </c>
-      <c r="G28" s="30" t="inlineStr"/>
+      <c r="B28" s="39" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>-273</v>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <v>-192</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G28" s="34" t="inlineStr"/>
     </row>
     <row r="29"/>
     <row r="30">
@@ -6404,12 +6478,21 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <autoFilter ref="A4:G28"/>
+  <mergeCells count="3">
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="G4:J4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A30:J30"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:B28">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="0019B6C9"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6420,7 +6503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
@@ -6452,7 +6535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:39 KST</t>
+          <t>2026-09-09 10:24 KST</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반도체와 원전·건설이 이끈 안도 랠리와 매크로 경계감의 혼조</t>
+          <t>AI 반도체와 전력 인프라가 주도한 주간 강세장</t>
         </is>
       </c>
     </row>
@@ -6504,13 +6587,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-98067</v>
+        <v>-101949</v>
       </c>
       <c r="C7" t="n">
-        <v>31154</v>
+        <v>30104</v>
       </c>
       <c r="D7" t="n">
-        <v>32584</v>
+        <v>34875</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="15">
@@ -6520,13 +6603,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2870</v>
+        <v>1830</v>
       </c>
       <c r="C8" t="n">
-        <v>542</v>
+        <v>1369</v>
       </c>
       <c r="D8" t="n">
-        <v>-3583</v>
+        <v>-3368</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="15">
@@ -6733,7 +6816,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수가 3.37% 급등하고 고용지표 호조로 금리 인하 기대감이 후퇴하는 중립 스탠스 속에서도, 국내 증시는 반도체 대형주 중심의 강력한 외국인·기관 매수세가 유입되며 코스피가 4.61% 급등했습니다.</t>
+          <t>미국 필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 중심의 강세로 이어지며 지수 상승을 견인함.</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6831,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 연준의 금리 인상 우려가 제기되는 중립 스탠스 하에서, 국내 증시는 미국 원전 건설 협의 기대감으로 원전·건설주는 급등했으나 경기 둔화 우려와 개인 매도세로 코스피가 0.58% 하락했습니다.</t>
+          <t>미국 국채금리 급등과 금리 인상 우려가 시장의 밸류에이션 부담을 가중시키며 지수 하락을 유발함.</t>
         </is>
       </c>
     </row>
@@ -6759,11 +6842,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>미국 고용지표의 블로우아웃 수준 발표로 금리 인상 우려가 재점화된 위험회피 스탠스 속에서도, 국내 증시는 해외 원전 및 AIDC 수주 기대감과 반도체 장비 투자 확대 기대감에 힘입어 코스피가 0.79% 상승했습니다.</t>
+          <t>미국 기술주의 차별화된 흐름과 지정학적 리스크에도 불구하고 AI 전력 수요 모멘텀이 부각되며 국내 증시가 반등함.</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6865,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>이번 주 매크로 환경은 미국의 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치(55.0K)를 크게 상회해 금리 인하 경로에 대한 불확실성을 키웠고, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려를 자극했습니다.</t>
+          <t>미국 비농업 고용지표가 16만 2천 명 증가하며 예상치를 상회했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 매크로 환경의 불확실성이 상존함.</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6877,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>수급 측면에서는 전기·전자 업종에 외국인(+30,380억원)과 기관(+26,434억원)의 순매수가 집중되며 주간 6.71% 상승했고, 기계·장비 업종 역시 기관(+2,888억원)의 매수세로 11.08% 급등했습니다.</t>
+          <t>수급 측면에서 전기·전자 섹터에 외국인(31,244억)과 기관(28,343억)의 매수세가 집중되었으며, 기계·장비 섹터 역시 기관(2,841억)의 순매수가 유입되며 주도 섹터로 부상함.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6889,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>반면 음식료·담배 업종은 기관(-1,100억원)과 외국인(-202억원)의 동반 순매도로 주간 3.76% 하락하며 밸류에이션 부담과 환율 하락에 따른 수출 우려를 반영했습니다.</t>
+          <t>매크로 지표의 둔화에도 불구하고 AI 반도체와 전력 인프라라는 확실한 모멘텀을 가진 섹터로 수급이 쏠리는 양극화 장세가 지속됨.</t>
         </is>
       </c>
     </row>
@@ -6832,13 +6915,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>43264</v>
+        <v>43827</v>
       </c>
       <c r="E34" t="n">
-        <v>19244</v>
+        <v>19774</v>
       </c>
       <c r="F34" t="n">
-        <v>24020</v>
+        <v>24053</v>
       </c>
       <c r="G34" t="n">
         <v>-55192</v>
@@ -6868,13 +6951,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28602</v>
+        <v>29241</v>
       </c>
       <c r="E35" t="n">
-        <v>18707</v>
+        <v>19401</v>
       </c>
       <c r="F35" t="n">
-        <v>9895</v>
+        <v>9839</v>
       </c>
       <c r="G35" t="n">
         <v>-52130</v>
@@ -6904,13 +6987,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4949</v>
+        <v>4815</v>
       </c>
       <c r="E36" t="n">
-        <v>2725</v>
+        <v>2558</v>
       </c>
       <c r="F36" t="n">
-        <v>2223</v>
+        <v>2258</v>
       </c>
       <c r="G36" t="n">
         <v>-5184</v>
@@ -6940,13 +7023,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2172</v>
+        <v>2257</v>
       </c>
       <c r="E37" t="n">
-        <v>-48</v>
+        <v>23</v>
       </c>
       <c r="F37" t="n">
-        <v>2220</v>
+        <v>2234</v>
       </c>
       <c r="G37" t="n">
         <v>-2125</v>
@@ -6976,13 +7059,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2097</v>
+        <v>2009</v>
       </c>
       <c r="E38" t="n">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="F38" t="n">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G38" t="n">
         <v>-2361</v>
@@ -7012,13 +7095,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="E39" t="n">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="F39" t="n">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G39" t="n">
         <v>-1560</v>
@@ -7048,13 +7131,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="E40" t="n">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="F40" t="n">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G40" t="n">
         <v>-1175</v>
@@ -7120,13 +7203,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>791</v>
+        <v>865</v>
       </c>
       <c r="E42" t="n">
-        <v>-221</v>
+        <v>-181</v>
       </c>
       <c r="F42" t="n">
-        <v>1011</v>
+        <v>1047</v>
       </c>
       <c r="G42" t="n">
         <v>-760</v>
@@ -7156,10 +7239,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>711</v>
+        <v>756</v>
       </c>
       <c r="E43" t="n">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="F43" t="n">
         <v>280</v>
@@ -7192,13 +7275,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-2718</v>
+        <v>-2265</v>
       </c>
       <c r="E44" t="n">
-        <v>-2168</v>
+        <v>-1786</v>
       </c>
       <c r="F44" t="n">
-        <v>-550</v>
+        <v>-479</v>
       </c>
       <c r="G44" t="n">
         <v>3076</v>
@@ -7228,13 +7311,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-1521</v>
+        <v>-1520</v>
       </c>
       <c r="E45" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="F45" t="n">
-        <v>-873</v>
+        <v>-878</v>
       </c>
       <c r="G45" t="n">
         <v>1591</v>
@@ -7300,13 +7383,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-783</v>
+        <v>-805</v>
       </c>
       <c r="E47" t="n">
-        <v>-551</v>
+        <v>-575</v>
       </c>
       <c r="F47" t="n">
-        <v>-232</v>
+        <v>-230</v>
       </c>
       <c r="G47" t="n">
         <v>626</v>
@@ -7336,13 +7419,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-700</v>
+        <v>-717</v>
       </c>
       <c r="E48" t="n">
-        <v>-313</v>
+        <v>-327</v>
       </c>
       <c r="F48" t="n">
-        <v>-386</v>
+        <v>-390</v>
       </c>
       <c r="G48" t="n">
         <v>764</v>
@@ -7372,13 +7455,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-629</v>
+        <v>-644</v>
       </c>
       <c r="E49" t="n">
-        <v>-46</v>
+        <v>-57</v>
       </c>
       <c r="F49" t="n">
-        <v>-583</v>
+        <v>-587</v>
       </c>
       <c r="G49" t="n">
         <v>634</v>
@@ -7408,13 +7491,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-598</v>
+        <v>-609</v>
       </c>
       <c r="E50" t="n">
-        <v>-212</v>
+        <v>-228</v>
       </c>
       <c r="F50" t="n">
-        <v>-386</v>
+        <v>-381</v>
       </c>
       <c r="G50" t="n">
         <v>571</v>
@@ -7444,13 +7527,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-593</v>
+        <v>-534</v>
       </c>
       <c r="E51" t="n">
-        <v>-468</v>
+        <v>-405</v>
       </c>
       <c r="F51" t="n">
-        <v>-125</v>
+        <v>-129</v>
       </c>
       <c r="G51" t="n">
         <v>588</v>
@@ -7476,29 +7559,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-524</v>
+        <v>-478</v>
       </c>
       <c r="E52" t="n">
-        <v>-559</v>
+        <v>-42</v>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>-437</v>
       </c>
       <c r="G52" t="n">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="H52" t="n">
-        <v>146.9</v>
+        <v>37.7</v>
       </c>
       <c r="I52" t="n">
-        <v>11659.9</v>
+        <v>3421.8</v>
       </c>
       <c r="J52" t="n">
-        <v>-434.4</v>
+        <v>-191.7</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="15">
@@ -7512,29 +7595,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-478</v>
+        <v>-472</v>
       </c>
       <c r="E53" t="n">
-        <v>-42</v>
+        <v>-517</v>
       </c>
       <c r="F53" t="n">
-        <v>-437</v>
+        <v>45</v>
       </c>
       <c r="G53" t="n">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="H53" t="n">
-        <v>37.7</v>
+        <v>146.9</v>
       </c>
       <c r="I53" t="n">
-        <v>3421.8</v>
+        <v>11659.9</v>
       </c>
       <c r="J53" t="n">
-        <v>-191.7</v>
+        <v>-434.4</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="15">
@@ -7552,12 +7635,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>주간 수급 집중 1위 종목으로 외국인(+19,244억원)과 기관(+24,020억원)의 강력한 순매수가 유입되었습니다.</t>
+          <t>주간 순매수 29,241억으로 수급 집중도가 높고 AI 메모리 모멘텀 지속.</t>
         </is>
       </c>
     </row>
@@ -7569,29 +7652,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>주간 수급 집중 2위 종목으로 외국인(+18,707억원)과 기관(+9,895억원)의 순매수가 집중되었으며 대차잔고가 2,044.8억원 감소하여 숏커버 여지가 존재합니다.</t>
+          <t>주간 순매수 2,257억 및 원전 수주 기대감으로 기계·장비 섹터 상승 주도.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="15">
       <c r="A57" t="inlineStr">
         <is>
-          <t>상방 관찰</t>
+          <t>하방 관찰</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>건설 업종 주간 10.99% 상승 속에서 기관이 1,011억원을 순매수하였고 대차잔고가 297.0% 증가하여 향후 숏커버링 가능성을 관찰할 필요가 있습니다.</t>
+          <t>주간 순매수 -2,265억으로 수급 이탈이 뚜렷함.</t>
         </is>
       </c>
     </row>
@@ -7603,36 +7686,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>주간 순매수 최하위 종목으로 외국인(-2,168억원)과 기관(-550억원)의 동반 순매도가 출회되었습니다.</t>
+          <t>주간 순매수 -805억으로 수급 약세 지속.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="A59" t="inlineStr">
         <is>
-          <t>하방 관찰</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>삼양식품</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>음식료·담배 업종의 주간 3.76% 하락 속에서 기관(-833억원)과 외국인(-135억원)의 순매도가 집중되었습니다.</t>
+          <t>8. 주간 시장 흐름</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="15">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8. 주간 시장 흐름</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등하는 등 강한 상승 출발.</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7722,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>주 초반 미국 필라델피아 반도체 지수의 급등과 마이크론의 강세에 힘입어 코스피가 외국인과 기관의 강력한 동반 매수세로 4.61% 급등하며 출발했습니다.</t>
+          <t>2분기 국내 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되어 주 중반 지수 조정 발생.</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7734,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>주 중반에는 미국 내 대형 원전 8기 건설 협의 기대감과 가덕도 신공항 설계 제출 등 대형 호재가 겹치며 건설 및 전기·가스 섹터가 강세를 주도했습니다.</t>
+          <t>주 후반 AI 데이터센터 전력 수요 급증과 원전 협력 기대감이 시장을 견인하며 다시 반등세로 전환.</t>
         </is>
       </c>
     </row>
@@ -7668,26 +7746,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>다만 한국의 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되었고, 개인의 대규모 매도세가 출회되며 지수 상승 탄력이 일부 제한되었습니다.</t>
+          <t>주간 내내 반도체와 전력 설비 섹터로 수급이 집중되는 쏠림 현상이 지속됨.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>주 후반에는 중동 지정학적 리스크로 인한 유가 상승과 미국의 고용지표 호조에 따른 금리 인상 우려가 재점화되며 시장 전반에 경계감이 유지되었습니다.</t>
+          <t>9. 섹터·테마 흐름</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9. 섹터·테마 흐름</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>반도체 섹터는 주간 내내 외국인과 기관의 순매수가 집중되며 시장의 핵심 주도주로 자리매김.</t>
         </is>
       </c>
     </row>
@@ -7699,38 +7777,70 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>주 초반에는 삼성전자와 SK하이닉스를 필두로 한 전기·전자(+5.92%) 및 기계·장비(+6.47%) 섹터가 AI 반도체 수요 기대감으로 시장을 주도했습니다.</t>
+          <t>기계·장비 및 건설 섹터는 원전 및 전력 설비 수주 기대감이 확산되며 주 후반으로 갈수록 상승 탄력 강화.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="15">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>주 중반 이후에는 미국 원전 건설 협의 소식과 가덕도 신공항 모멘텀이 부각되며 건설(+2.99%) 및 전기·가스(+3.11%) 섹터로 매기 이전이 일어났습니다.</t>
+          <t>10. 촉매 타임라인</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>반면 음식료·담배(-3.76%)와 IT 서비스(-2.61%) 섹터는 환율 하락에 따른 수출 우려 및 차익 실현 매물 출회로 주간 내내 약세를 보였습니다.</t>
+          <t>네오오토</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="15">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10. 촉매 타임라인</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>필옵틱스</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7852,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네오오토</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7754,11 +7864,11 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>39.17</v>
+        <v>10.45</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -7770,23 +7880,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>37.98</v>
+        <v>34.32</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -7798,23 +7908,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>10.09</v>
+        <v>27.59</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7936,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7835,14 +7945,14 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>22.92</v>
+        <v>17.3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7964,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7866,11 +7976,11 @@
         <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>27.47</v>
+        <v>12.2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7992,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7894,67 +8004,67 @@
         <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>17.55</v>
+        <v>6.65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="15">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>11.48</v>
+        <v>42.54</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>6.26</v>
+        <v>42.43</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -7966,7 +8076,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7978,11 +8088,11 @@
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>53.96</v>
+        <v>34.68</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
@@ -7994,23 +8104,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>42.66</v>
+        <v>34.48</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -8022,23 +8132,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>33.97</v>
+        <v>30.44</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8160,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8059,113 +8169,81 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>35.04</v>
+        <v>20.18</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="15">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>4</v>
-      </c>
-      <c r="E82" t="n">
-        <v>33.21</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>11. 다음 주 프리뷰</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="15">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>상승 시나리오</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>4</v>
-      </c>
-      <c r="E83" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>미국 물가 지표가 예상치를 하회하면 금리 인하 기대감 회복으로 기술주 중심의 상승세 지속</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11. 다음 주 프리뷰</t>
+          <t>하방 시나리오</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>물가 지표가 예상치를 상회하여 금리 인상 우려가 재점화되면 경기 민감주 및 전력 설비주로의 방어적 로테이션 전개</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="15">
       <c r="A85" t="inlineStr">
         <is>
-          <t>상승 시나리오</t>
+          <t>판별 신호</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>미국 CPI 및 PPI 지표가 안정세를 보이며 금리 인하 경로가 명확해지면 반도체 및 기술주 중심의 외국인 수급 유입과 함께 상승 랠리가 전개될 수 있습니다.</t>
+          <t>9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 등락폭</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" t="inlineStr">
         <is>
-          <t>하방 시나리오</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미국 물가 지표가 예상치를 상회하여 인플레이션 우려가 재점화되고 국채 금리가 급등하면 기술주 및 성장주 중심의 차익 실현 매물이 출회되며 하방 압력이 커질 수 있습니다.</t>
+          <t>미국 생산자물가지수(PPI)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" t="inlineStr">
         <is>
-          <t>판별 신호</t>
+          <t>핵심 이벤트</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>미국 8월 소비자물가지수(CPI)의 전월대비 및 전년대비 실제치와 이에 따른 미국 국채 금리의 변동성 여부입니다.</t>
+          <t>미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
@@ -8177,34 +8255,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>미국 생산자물가지수(PPI) 전월대비 (9월 10일 21:30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI) 전년대비 (9월 11일 21:30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>핵심 이벤트</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>미국 소매판매 전월대비 (9월 16일 21:30)</t>
-        </is>
-      </c>
-    </row>
+          <t>미국 소매판매</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="15"/>
+    <row r="90" ht="15" customHeight="1" s="15"/>
     <row r="91" ht="15" customHeight="1" s="15"/>
     <row r="93" ht="15" customHeight="1" s="15"/>
     <row r="94" ht="15" customHeight="1" s="15"/>

--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -10,12 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신고가 근접" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투자자별 순매수" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공매도·대차" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원본 데이터" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$N$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -255,14 +252,6 @@
       <color rgb="FF6B7280"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -329,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -426,6 +415,9 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -462,10 +454,10 @@
     <xf numFmtId="167" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -505,24 +497,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -968,7 +942,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 16:16 KST</t>
+          <t>2026-09-09 16:34 KST</t>
         </is>
       </c>
     </row>
@@ -981,7 +955,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>AI 반도체와 전력 인프라가 주도한 수급 쏠림과 지수 상승</t>
+          <t>AI 반도체와 전력 인프라가 주도한 수급 쏠림과 지수 반등</t>
         </is>
       </c>
     </row>
@@ -1273,11 +1247,13 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="n">
-        <v>10.16</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1293,11 +1269,13 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>8.48</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1313,11 +1291,13 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="n">
-        <v>7.94</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1333,11 +1313,13 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>-4.38</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1353,11 +1335,13 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="n">
-        <v>-3.11</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1373,11 +1357,13 @@
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="n">
-        <v>-2.07</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="24"/>
@@ -1706,11 +1692,11 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 급등(3.37%)이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 상단이 제한됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="31" customHeight="1" s="15">
+          <t>미국 필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단은 제한됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44.5" customHeight="1" s="15">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1775,7 +1761,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 금리 인상 우려가 국내 증시 밸류에이션 부담으로 작용하며 지수가 하락함.</t>
+          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 건설 협의 소식이 전해지며 국내 건설 및 전기·가스 섹터가 강세를 보임.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1830,7 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>미국 기술주 내 차별화 흐름과 고용지표 호조에 따른 금리 인상 우려에도 불구하고, 기관의 강한 매수세가 유입되며 지수가 반등함.</t>
+          <t>미국 증시의 기술주 차별화 흐름과 지정학적 리스크에도 불구하고, 기관의 강한 매수세가 유입되며 KOSPI 7,000선 안착에 성공함.</t>
         </is>
       </c>
     </row>
@@ -1882,24 +1868,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="15">
+    <row r="41" ht="31" customHeight="1" s="15">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>- 미국 고용지표 호조와 국내 2분기 GDP 성장률 0.6%(이전 1.8%) 둔화가 맞물리며 매크로 불확실성이 확대됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
+          <t>- 매크로 환경은 미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치를 상회하고, 국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하는 등 경기 둔화와 금리 인상 우려가 혼재된 상황임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1" s="15">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>- 수급 측면에서는 전기·전자(순매수 625억)와 기계·장비(순매수 398억) 섹터로 외국인과 기관의 매수세가 집중되며 시장을 주도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="15">
+          <t>- 수급 구도는 삼성전자(42,067억)와 SK하이닉스(31,296억) 등 반도체 대형주에 외국인과 기관의 매수세가 집중되었으며, 반면 삼성전기(-1,354억)와 삼양식품(-1,254억) 등은 순매도 상위에 위치함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1" s="15">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경의 불확실성에도 불구하고 AI 인프라 관련 핵심 섹터로의 수급 쏠림이 지수 하단을 방어하는 모습.</t>
+          <t>- 종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 전력 인프라라는 확실한 성장 모멘텀을 가진 섹터로 수급이 쏠리는 'Risk-On' 국면이 지속되고 있음.</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1986,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D47" s="34" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2041,7 +2027,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2082,7 +2068,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2123,7 +2109,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2164,7 +2150,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2205,7 +2191,7 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2246,7 +2232,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D53" s="34" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2287,7 +2273,7 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2328,7 +2314,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D55" s="34" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2369,7 +2355,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2410,7 +2396,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D57" s="34" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2451,7 +2437,7 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
@@ -2492,7 +2478,7 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2533,7 +2519,7 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -2574,7 +2560,7 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2615,7 +2601,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2656,7 +2642,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D63" s="34" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2697,7 +2683,7 @@
           <t>레인보우로보틱스</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2738,7 +2724,7 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="D65" s="34" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2779,7 +2765,7 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="D66" s="34" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
@@ -2833,7 +2819,7 @@
       <c r="K68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="35" t="inlineStr">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -2859,12 +2845,12 @@
     <row r="71"/>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="36" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G73" s="37" t="inlineStr">
+      <c r="G73" s="38" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -2885,7 +2871,7 @@
     <row r="75"/>
     <row r="76"/>
     <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="38" t="inlineStr">
+      <c r="A77" s="39" t="inlineStr">
         <is>
           <t>현재 확보된 주간 브리핑 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 주간 촉매) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -2925,31 +2911,31 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="15">
+    <row r="81" ht="31" customHeight="1" s="15">
       <c r="A81" s="17" t="inlineStr">
         <is>
-          <t>- AI 반도체 및 HBM 수요 기대감으로 외국인과 기관의 강력한 매수세가 유입되며 지수 상승을 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="15">
+          <t>- 주 초반 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 기술주 약세로 변동성이 확대되었으나, 주 후반 반도체 및 전력 인프라 관련주로 외국인과 기관의 매수세가 집중되며 지수 반등을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="31" customHeight="1" s="15">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>- 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되어 일시적 조정 발생.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="15">
+          <t>- KOSPI는 주중 7,000선 안착을 시도하며 1.4% 상승 마감했고, KOSDAQ은 외국인 매수세 유입에 힘입어 2.28% 급등함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="31" customHeight="1" s="15">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t>- 원/달러 환율 하락세가 지속되며 외국인 투자자의 환차손 부담이 완화됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="15">
+          <t>- 원/달러 환율은 1,336.6원까지 하락하며 원화 강세 흐름을 보였고, 이는 외국인 투자자의 환차손 부담을 완화하며 대형주 중심의 수급 유입을 뒷받침함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="31" customHeight="1" s="15">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>- 전력 설비 및 원전 관련주로 수급이 확산되며 섹터별 차별화 장세가 심화됨.</t>
+          <t>- 개인은 주간 내내 대규모 순매도를 지속하며 차익 실현에 집중한 반면, 기관과 외국인은 반도체와 전력 설비 등 주도 섹터에 수급을 집중하는 양극화된 흐름을 보임.</t>
         </is>
       </c>
     </row>
@@ -2978,21 +2964,21 @@
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>- 전기·전자 및 기계·장비 섹터는 AI 반도체와 데이터센터 인프라 수요를 바탕으로 주간 내내 강세 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
+          <t>- 반도체 섹터는 AI 메모리 및 HBM 수요 기대감으로 주간 내내 외국인과 기관의 강력한 매수세가 유입되며 시장 주도력을 유지함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="31" customHeight="1" s="15">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>- 원전 및 전력 설비 관련주는 대형 수주 기대감과 함께 신규 주도 테마로 부상.</t>
+          <t>- 전력 설비 및 원전 관련주는 미국 내 데이터센터 전력 수요와 원전 건설 협의 이슈가 부각되며 기계·장비 섹터의 강세를 지속적으로 견인함.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="15">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t>- 음식료·담배 및 IT 서비스 섹터는 차익 실현 매물과 실적 우려로 약세 전환.</t>
+          <t>- 음식료 및 소비재 섹터는 글로벌 실적 우려와 환율 하락에 따른 수출 실적 부담으로 차익 실현 매물이 출회되며 약세 흐름을 보임.</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3061,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D93" s="34" t="inlineStr">
+      <c r="D93" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -3110,7 +3096,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D94" s="34" t="inlineStr">
+      <c r="D94" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3121,7 +3107,7 @@
         </is>
       </c>
       <c r="F94" s="29" t="n">
-        <v>33.4</v>
+        <v>33.59</v>
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
@@ -3145,7 +3131,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D95" s="34" t="inlineStr">
+      <c r="D95" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3156,7 +3142,7 @@
         </is>
       </c>
       <c r="F95" s="29" t="n">
-        <v>11.91</v>
+        <v>12.2</v>
       </c>
       <c r="G95" s="17" t="inlineStr">
         <is>
@@ -3180,7 +3166,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D96" s="34" t="inlineStr">
+      <c r="D96" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3191,7 +3177,7 @@
         </is>
       </c>
       <c r="F96" s="29" t="n">
-        <v>24.23</v>
+        <v>24.45</v>
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
@@ -3215,7 +3201,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D97" s="34" t="inlineStr">
+      <c r="D97" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3226,7 +3212,7 @@
         </is>
       </c>
       <c r="F97" s="29" t="n">
-        <v>23.59</v>
+        <v>23.37</v>
       </c>
       <c r="G97" s="17" t="inlineStr">
         <is>
@@ -3250,7 +3236,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D98" s="34" t="inlineStr">
+      <c r="D98" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3261,7 +3247,7 @@
         </is>
       </c>
       <c r="F98" s="29" t="n">
-        <v>15.04</v>
+        <v>15.16</v>
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
@@ -3285,7 +3271,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D99" s="34" t="inlineStr">
+      <c r="D99" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3296,7 +3282,7 @@
         </is>
       </c>
       <c r="F99" s="29" t="n">
-        <v>11.73</v>
+        <v>11.55</v>
       </c>
       <c r="G99" s="17" t="inlineStr">
         <is>
@@ -3320,7 +3306,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D100" s="34" t="inlineStr">
+      <c r="D100" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3331,7 +3317,7 @@
         </is>
       </c>
       <c r="F100" s="29" t="n">
-        <v>5.06</v>
+        <v>4.86</v>
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
@@ -3355,7 +3341,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D101" s="34" t="inlineStr">
+      <c r="D101" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3390,7 +3376,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D102" s="34" t="inlineStr">
+      <c r="D102" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3425,7 +3411,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D103" s="34" t="inlineStr">
+      <c r="D103" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3460,7 +3446,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D104" s="34" t="inlineStr">
+      <c r="D104" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3471,7 +3457,7 @@
         </is>
       </c>
       <c r="F104" s="29" t="n">
-        <v>32.1</v>
+        <v>32.65</v>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
@@ -3495,7 +3481,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D105" s="34" t="inlineStr">
+      <c r="D105" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -3506,7 +3492,7 @@
         </is>
       </c>
       <c r="F105" s="29" t="n">
-        <v>29.56</v>
+        <v>23.99</v>
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
@@ -3530,7 +3516,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D106" s="34" t="inlineStr">
+      <c r="D106" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
@@ -3565,7 +3551,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D107" s="34" t="inlineStr">
+      <c r="D107" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3600,7 +3586,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D108" s="34" t="inlineStr">
+      <c r="D108" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3635,7 +3621,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D109" s="34" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3670,7 +3656,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
+      <c r="D110" s="35" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -3705,7 +3691,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D111" s="34" t="inlineStr">
+      <c r="D111" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3740,7 +3726,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D112" s="34" t="inlineStr">
+      <c r="D112" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3775,7 +3761,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D113" s="34" t="inlineStr">
+      <c r="D113" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -3810,7 +3796,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D114" s="34" t="inlineStr">
+      <c r="D114" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3845,7 +3831,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D115" s="34" t="inlineStr">
+      <c r="D115" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -3856,7 +3842,7 @@
         </is>
       </c>
       <c r="F115" s="29" t="n">
-        <v>10.35</v>
+        <v>10.06</v>
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
@@ -3880,7 +3866,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D116" s="34" t="inlineStr">
+      <c r="D116" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3891,7 +3877,7 @@
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>24.23</v>
+        <v>24.45</v>
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
@@ -3915,7 +3901,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D117" s="34" t="inlineStr">
+      <c r="D117" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3926,7 +3912,7 @@
         </is>
       </c>
       <c r="F117" s="29" t="n">
-        <v>23.59</v>
+        <v>23.37</v>
       </c>
       <c r="G117" s="17" t="inlineStr">
         <is>
@@ -3950,7 +3936,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D118" s="34" t="inlineStr">
+      <c r="D118" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3961,7 +3947,7 @@
         </is>
       </c>
       <c r="F118" s="29" t="n">
-        <v>11.73</v>
+        <v>11.55</v>
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
@@ -3985,7 +3971,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D119" s="34" t="inlineStr">
+      <c r="D119" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3996,7 +3982,7 @@
         </is>
       </c>
       <c r="F119" s="29" t="n">
-        <v>15.04</v>
+        <v>15.16</v>
       </c>
       <c r="G119" s="17" t="inlineStr">
         <is>
@@ -4020,7 +4006,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D120" s="34" t="inlineStr">
+      <c r="D120" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -4031,7 +4017,7 @@
         </is>
       </c>
       <c r="F120" s="29" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
@@ -4064,35 +4050,35 @@
     <row r="123" ht="15" customHeight="1" s="15">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 및 전력 인프라 섹터의 수급이 유지되면 지수 상승세 지속</t>
+          <t>- 미국 CPI가 예상치를 하회하면 금리 인하 기대감에 힘입어 반도체 및 성장주 중심의 상승세 지속</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="15">
       <c r="A124" s="17" t="inlineStr">
         <is>
-          <t>- 미국 CPI 발표 후 금리 인상 우려가 재점화되면 단기 조정 가능</t>
+          <t>- 미국 CPI가 예상치를 상회하면 금리 인상 우려 재점화로 외국인 수급 이탈 및 지수 조정</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="15">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>- 미국 소비자물가지수(CPI) 발표 결과에 따른 시장의 금리 경로 해석</t>
+          <t>- 9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률과 국채 금리의 변동성</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="15">
       <c r="A126" s="17" t="inlineStr">
         <is>
-          <t>- 미국 소비자물가지수(CPI)</t>
+          <t>- 미국 소비자물가지수(CPI) 발표</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="15">
       <c r="A127" s="17" t="inlineStr">
         <is>
-          <t>- 한국 무역수지</t>
+          <t>- 국내 무역수지 및 수출입 데이터 발표</t>
         </is>
       </c>
     </row>
@@ -4252,62 +4238,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="39" t="inlineStr">
+      <c r="E5" s="40" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="39" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="39" t="inlineStr">
+      <c r="H5" s="40" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="39" t="inlineStr">
+      <c r="I5" s="40" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="39" t="inlineStr">
+      <c r="K5" s="40" t="inlineStr">
         <is>
           <t>주간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="39" t="inlineStr">
+      <c r="L5" s="40" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -4319,7 +4305,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -4329,31 +4315,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="41" t="n">
         <v>1393</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="41" t="n">
         <v>740</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="41" t="n">
         <v>653</v>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="42" t="n">
         <v>-1398</v>
       </c>
-      <c r="H6" s="42" t="n">
+      <c r="H6" s="43" t="n">
         <v>129.7</v>
       </c>
-      <c r="I6" s="42" t="n">
+      <c r="I6" s="43" t="n">
         <v>3293.5</v>
       </c>
-      <c r="J6" s="43" t="n">
+      <c r="J6" s="44" t="n">
         <v>-298.3</v>
       </c>
-      <c r="K6" s="44" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="L6" s="45" t="n">
+      <c r="K6" s="45" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="L6" s="46" t="n">
         <v>-1.24</v>
       </c>
     </row>
@@ -4363,7 +4349,7 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -4373,31 +4359,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="41" t="n">
         <v>119</v>
       </c>
-      <c r="E7" s="41" t="n">
+      <c r="E7" s="42" t="n">
         <v>-368</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="41" t="n">
         <v>487</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="42" t="n">
         <v>-102</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="43" t="n">
         <v>310.1</v>
       </c>
-      <c r="I7" s="42" t="n">
+      <c r="I7" s="43" t="n">
         <v>7226.2</v>
       </c>
-      <c r="J7" s="43" t="n">
+      <c r="J7" s="44" t="n">
         <v>-230.6</v>
       </c>
-      <c r="K7" s="44" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L7" s="46" t="n">
+      <c r="K7" s="47" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L7" s="48" t="n">
         <v>-5.33</v>
       </c>
     </row>
@@ -4407,7 +4393,7 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -4417,31 +4403,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="41" t="n">
         <v>56</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="42" t="n">
         <v>-193</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="41" t="n">
         <v>248</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="42" t="n">
         <v>-42</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="43" t="n">
         <v>127.6</v>
       </c>
-      <c r="I8" s="42" t="n">
+      <c r="I8" s="43" t="n">
         <v>6946</v>
       </c>
-      <c r="J8" s="43" t="n">
+      <c r="J8" s="44" t="n">
         <v>-552.7</v>
       </c>
       <c r="K8" s="47" t="n">
         <v>-0.52</v>
       </c>
-      <c r="L8" s="46" t="n">
+      <c r="L8" s="48" t="n">
         <v>-6.34</v>
       </c>
     </row>
@@ -4451,7 +4437,7 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4461,31 +4447,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="41" t="n">
         <v>573</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="41" t="n">
         <v>632</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="42" t="n">
         <v>-59</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="42" t="n">
         <v>-548</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="43" t="n">
         <v>50.9</v>
       </c>
-      <c r="I9" s="42" t="n">
+      <c r="I9" s="43" t="n">
         <v>1717.2</v>
       </c>
-      <c r="J9" s="48" t="n">
+      <c r="J9" s="49" t="n">
         <v>5.5</v>
       </c>
       <c r="K9" s="47" t="n">
         <v>-6.14</v>
       </c>
-      <c r="L9" s="49" t="n">
+      <c r="L9" s="50" t="n">
         <v>-4.7</v>
       </c>
     </row>
@@ -4495,7 +4481,7 @@
           <t>IPARK현대산업개발</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
@@ -4505,31 +4491,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="41" t="n">
         <v>16</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="42" t="n">
         <v>-37</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="43" t="n">
         <v>8.1</v>
       </c>
-      <c r="I10" s="42" t="n">
+      <c r="I10" s="43" t="n">
         <v>444.4</v>
       </c>
-      <c r="J10" s="43" t="n">
+      <c r="J10" s="44" t="n">
         <v>-3.4</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="45" t="n">
         <v>1.08</v>
       </c>
-      <c r="L10" s="46" t="n">
+      <c r="L10" s="48" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4539,35 +4525,35 @@
           <t>S-Oil우</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr"/>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="41" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="41" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="42" t="n">
         <v>-30</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="43" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="42" t="n">
+      <c r="I11" s="43" t="n">
         <v>180.7</v>
       </c>
-      <c r="J11" s="48" t="n">
+      <c r="J11" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="50" t="inlineStr"/>
-      <c r="L11" s="45" t="n">
+      <c r="K11" s="51" t="inlineStr"/>
+      <c r="L11" s="46" t="n">
         <v>-1.68</v>
       </c>
     </row>
@@ -4577,7 +4563,7 @@
           <t>코메론</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
@@ -4587,31 +4573,31 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="51" t="n">
+      <c r="E12" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="42" t="n">
         <v>-1</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="I12" s="42" t="n">
+      <c r="I12" s="43" t="n">
         <v>41.2</v>
       </c>
-      <c r="J12" s="43" t="n">
+      <c r="J12" s="44" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="45" t="n">
         <v>0.89</v>
       </c>
-      <c r="L12" s="49" t="n">
+      <c r="L12" s="50" t="n">
         <v>-4.42</v>
       </c>
     </row>
@@ -4621,7 +4607,7 @@
           <t>아이앤씨</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4631,29 +4617,29 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="42" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="42" t="n">
         <v>-6</v>
       </c>
-      <c r="H13" s="42" t="inlineStr"/>
-      <c r="I13" s="42" t="n">
+      <c r="H13" s="43" t="inlineStr"/>
+      <c r="I13" s="43" t="n">
         <v>16.2</v>
       </c>
-      <c r="J13" s="48" t="n">
+      <c r="J13" s="49" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="45" t="n">
         <v>14.63</v>
       </c>
-      <c r="L13" s="45" t="n">
+      <c r="L13" s="46" t="n">
         <v>-1.94</v>
       </c>
     </row>
@@ -4731,7 +4717,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -4741,111 +4727,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="52" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="54" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="53" t="inlineStr">
+      <c r="J4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="54" t="inlineStr">
+      <c r="N4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="39" t="inlineStr">
+      <c r="E5" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="39" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="39" t="inlineStr">
+      <c r="H5" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="39" t="inlineStr">
+      <c r="K5" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="39" t="inlineStr">
+      <c r="L5" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="39" t="inlineStr">
+      <c r="M5" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="39" t="inlineStr">
+      <c r="N5" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="39" t="inlineStr">
+      <c r="O5" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="39" t="inlineStr">
+      <c r="P5" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="39" t="inlineStr">
+      <c r="Q5" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -4860,12 +4846,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>20011</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -4876,12 +4862,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="56" t="n">
         <v>-1162</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -4892,12 +4878,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L6" s="34" t="inlineStr">
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="41" t="n">
+      <c r="M6" s="42" t="n">
         <v>28767</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -4908,12 +4894,12 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="Q6" s="55" t="n">
+      <c r="Q6" s="56" t="n">
         <v>-1230</v>
       </c>
     </row>
@@ -4926,12 +4912,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="42" t="n">
         <v>13300</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -4942,12 +4928,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="56" t="n">
         <v>-577</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -4958,12 +4944,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L7" s="34" t="inlineStr">
+      <c r="L7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="41" t="n">
+      <c r="M7" s="42" t="n">
         <v>11284</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -4974,12 +4960,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q7" s="55" t="n">
+      <c r="Q7" s="56" t="n">
         <v>-929</v>
       </c>
     </row>
@@ -4992,12 +4978,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="42" t="n">
         <v>2759</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -5008,12 +4994,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="56" t="n">
         <v>-555</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -5024,12 +5010,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L8" s="34" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M8" s="41" t="n">
+      <c r="M8" s="42" t="n">
         <v>2370</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -5040,12 +5026,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="P8" s="34" t="inlineStr">
+      <c r="P8" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q8" s="55" t="n">
+      <c r="Q8" s="56" t="n">
         <v>-678</v>
       </c>
     </row>
@@ -5058,12 +5044,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="42" t="n">
         <v>857</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -5074,12 +5060,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="56" t="n">
         <v>-506</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -5090,12 +5076,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L9" s="34" t="inlineStr">
+      <c r="L9" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="M9" s="41" t="n">
+      <c r="M9" s="42" t="n">
         <v>2370</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -5106,12 +5092,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="P9" s="56" t="inlineStr">
+      <c r="P9" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="55" t="n">
+      <c r="Q9" s="56" t="n">
         <v>-631</v>
       </c>
     </row>
@@ -5124,12 +5110,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="42" t="n">
         <v>835</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -5140,12 +5126,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G10" s="56" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="56" t="n">
         <v>-451</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -5156,12 +5142,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L10" s="34" t="inlineStr">
+      <c r="L10" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M10" s="41" t="n">
+      <c r="M10" s="42" t="n">
         <v>1800</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -5172,12 +5158,12 @@
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="Q10" s="55" t="n">
+      <c r="Q10" s="56" t="n">
         <v>-568</v>
       </c>
     </row>
@@ -5190,12 +5176,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="42" t="n">
         <v>816</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -5206,12 +5192,12 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="56" t="n">
         <v>-444</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -5222,12 +5208,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="L11" s="34" t="inlineStr">
+      <c r="L11" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="M11" s="41" t="n">
+      <c r="M11" s="42" t="n">
         <v>1141</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -5238,12 +5224,12 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q11" s="55" t="n">
+      <c r="Q11" s="56" t="n">
         <v>-437</v>
       </c>
     </row>
@@ -5256,12 +5242,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="42" t="n">
         <v>740</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -5272,12 +5258,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G12" s="56" t="inlineStr">
+      <c r="G12" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H12" s="55" t="n">
+      <c r="H12" s="56" t="n">
         <v>-418</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -5288,12 +5274,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="L12" s="34" t="inlineStr">
+      <c r="L12" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M12" s="41" t="n">
+      <c r="M12" s="42" t="n">
         <v>655</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -5304,12 +5290,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P12" s="34" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q12" s="55" t="n">
+      <c r="Q12" s="56" t="n">
         <v>-386</v>
       </c>
     </row>
@@ -5322,12 +5308,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D13" s="42" t="n">
         <v>673</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -5338,12 +5324,12 @@
           <t>LG</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="H13" s="55" t="n">
+      <c r="H13" s="56" t="n">
         <v>-415</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -5354,12 +5340,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="41" t="n">
+      <c r="M13" s="42" t="n">
         <v>653</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -5370,12 +5356,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="P13" s="34" t="inlineStr">
+      <c r="P13" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q13" s="55" t="n">
+      <c r="Q13" s="56" t="n">
         <v>-374</v>
       </c>
     </row>
@@ -5388,12 +5374,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D14" s="42" t="n">
         <v>632</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -5404,12 +5390,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="56" t="n">
         <v>-368</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -5420,12 +5406,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="L14" s="56" t="inlineStr">
+      <c r="L14" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M14" s="41" t="n">
+      <c r="M14" s="42" t="n">
         <v>623</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -5436,12 +5422,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="P14" s="34" t="inlineStr">
+      <c r="P14" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q14" s="55" t="n">
+      <c r="Q14" s="56" t="n">
         <v>-343</v>
       </c>
     </row>
@@ -5454,12 +5440,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="42" t="n">
         <v>583</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -5470,12 +5456,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H15" s="55" t="n">
+      <c r="H15" s="56" t="n">
         <v>-338</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -5486,12 +5472,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="L15" s="34" t="inlineStr">
+      <c r="L15" s="35" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="M15" s="41" t="n">
+      <c r="M15" s="42" t="n">
         <v>567</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -5502,12 +5488,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="P15" s="34" t="inlineStr">
+      <c r="P15" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q15" s="55" t="n">
+      <c r="Q15" s="56" t="n">
         <v>-342</v>
       </c>
     </row>
@@ -5518,7 +5504,7 @@
           <t>F3 연기금</t>
         </is>
       </c>
-      <c r="E17" s="52" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -5528,111 +5514,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="52" t="inlineStr">
+      <c r="N17" s="53" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="54" t="inlineStr">
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="53" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="54" t="inlineStr">
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="39" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="39" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="39" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="39" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="39" t="inlineStr">
+      <c r="H19" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="39" t="inlineStr">
+      <c r="J19" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="39" t="inlineStr">
+      <c r="K19" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="39" t="inlineStr">
+      <c r="L19" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="39" t="inlineStr">
+      <c r="M19" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="39" t="inlineStr">
+      <c r="N19" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="39" t="inlineStr">
+      <c r="O19" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="39" t="inlineStr">
+      <c r="P19" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="39" t="inlineStr">
+      <c r="Q19" s="40" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5647,12 +5633,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="42" t="n">
         <v>817</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -5663,12 +5649,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="55" t="n">
+      <c r="H20" s="56" t="n">
         <v>-1831</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -5679,12 +5665,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L20" s="34" t="inlineStr">
+      <c r="L20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="41" t="n">
+      <c r="M20" s="42" t="n">
         <v>1376</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -5695,12 +5681,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P20" s="34" t="inlineStr">
+      <c r="P20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="55" t="n">
+      <c r="Q20" s="56" t="n">
         <v>-66116</v>
       </c>
     </row>
@@ -5713,12 +5699,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D21" s="41" t="n">
+      <c r="D21" s="42" t="n">
         <v>598</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -5729,12 +5715,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="55" t="n">
+      <c r="H21" s="56" t="n">
         <v>-924</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -5745,12 +5731,12 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="L21" s="34" t="inlineStr">
+      <c r="L21" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="M21" s="41" t="n">
+      <c r="M21" s="42" t="n">
         <v>1250</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -5761,12 +5747,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P21" s="34" t="inlineStr">
+      <c r="P21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="55" t="n">
+      <c r="Q21" s="56" t="n">
         <v>-57740</v>
       </c>
     </row>
@@ -5779,12 +5765,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D22" s="42" t="n">
         <v>435</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -5795,12 +5781,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G22" s="56" t="inlineStr">
+      <c r="G22" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H22" s="55" t="n">
+      <c r="H22" s="56" t="n">
         <v>-442</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -5811,12 +5797,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="L22" s="34" t="inlineStr">
+      <c r="L22" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M22" s="41" t="n">
+      <c r="M22" s="42" t="n">
         <v>965</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -5827,12 +5813,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="P22" s="34" t="inlineStr">
+      <c r="P22" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q22" s="55" t="n">
+      <c r="Q22" s="56" t="n">
         <v>-5018</v>
       </c>
     </row>
@@ -5845,12 +5831,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="42" t="n">
         <v>374</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -5861,12 +5847,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G23" s="56" t="inlineStr">
+      <c r="G23" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H23" s="55" t="n">
+      <c r="H23" s="56" t="n">
         <v>-393</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -5877,12 +5863,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L23" s="34" t="inlineStr">
+      <c r="L23" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M23" s="41" t="n">
+      <c r="M23" s="42" t="n">
         <v>764</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -5893,12 +5879,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P23" s="34" t="inlineStr">
+      <c r="P23" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q23" s="55" t="n">
+      <c r="Q23" s="56" t="n">
         <v>-2464</v>
       </c>
     </row>
@@ -5911,12 +5897,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="42" t="n">
         <v>267</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -5927,12 +5913,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="G24" s="34" t="inlineStr">
+      <c r="G24" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="H24" s="55" t="n">
+      <c r="H24" s="56" t="n">
         <v>-218</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -5943,12 +5929,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L24" s="34" t="inlineStr">
+      <c r="L24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="41" t="n">
+      <c r="M24" s="42" t="n">
         <v>668</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -5959,12 +5945,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P24" s="34" t="inlineStr">
+      <c r="P24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q24" s="55" t="n">
+      <c r="Q24" s="56" t="n">
         <v>-1769</v>
       </c>
     </row>
@@ -5977,12 +5963,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="42" t="n">
         <v>216</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -5993,12 +5979,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H25" s="55" t="n">
+      <c r="H25" s="56" t="n">
         <v>-203</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -6009,12 +5995,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L25" s="34" t="inlineStr">
+      <c r="L25" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M25" s="41" t="n">
+      <c r="M25" s="42" t="n">
         <v>590</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -6025,12 +6011,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P25" s="34" t="inlineStr">
+      <c r="P25" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q25" s="55" t="n">
+      <c r="Q25" s="56" t="n">
         <v>-1495</v>
       </c>
     </row>
@@ -6043,12 +6029,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <v>186</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -6059,12 +6045,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H26" s="55" t="n">
+      <c r="H26" s="56" t="n">
         <v>-195</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -6075,12 +6061,12 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="L26" s="34" t="inlineStr">
+      <c r="L26" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="M26" s="41" t="n">
+      <c r="M26" s="42" t="n">
         <v>507</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -6091,12 +6077,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P26" s="34" t="inlineStr">
+      <c r="P26" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q26" s="55" t="n">
+      <c r="Q26" s="56" t="n">
         <v>-1398</v>
       </c>
     </row>
@@ -6109,12 +6095,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="41" t="n">
+      <c r="D27" s="42" t="n">
         <v>172</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -6125,12 +6111,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H27" s="55" t="n">
+      <c r="H27" s="56" t="n">
         <v>-188</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -6141,12 +6127,12 @@
           <t>레인보우로보틱스</t>
         </is>
       </c>
-      <c r="L27" s="34" t="inlineStr">
+      <c r="L27" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M27" s="41" t="n">
+      <c r="M27" s="42" t="n">
         <v>479</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -6157,12 +6143,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="P27" s="34" t="inlineStr">
+      <c r="P27" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="55" t="n">
+      <c r="Q27" s="56" t="n">
         <v>-1222</v>
       </c>
     </row>
@@ -6175,12 +6161,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D28" s="42" t="n">
         <v>157</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -6191,12 +6177,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="55" t="n">
+      <c r="H28" s="56" t="n">
         <v>-184</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -6207,12 +6193,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L28" s="34" t="inlineStr">
+      <c r="L28" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M28" s="41" t="n">
+      <c r="M28" s="42" t="n">
         <v>464</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -6223,12 +6209,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P28" s="34" t="inlineStr">
+      <c r="P28" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q28" s="55" t="n">
+      <c r="Q28" s="56" t="n">
         <v>-1048</v>
       </c>
     </row>
@@ -6241,12 +6227,12 @@
           <t>가온전선</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="42" t="n">
         <v>142</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -6257,12 +6243,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H29" s="55" t="n">
+      <c r="H29" s="56" t="n">
         <v>-174</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -6273,12 +6259,12 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="L29" s="34" t="inlineStr">
+      <c r="L29" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="M29" s="41" t="n">
+      <c r="M29" s="42" t="n">
         <v>441</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -6289,18 +6275,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P29" s="34" t="inlineStr">
+      <c r="P29" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q29" s="55" t="n">
+      <c r="Q29" s="56" t="n">
         <v>-951</v>
       </c>
     </row>
     <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="57" t="inlineStr">
+      <c r="A31" s="58" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치</t>
         </is>
@@ -6395,72 +6381,72 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>공매도 누적</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="40" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="40" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
       </c>
-      <c r="L4" s="39" t="inlineStr">
+      <c r="L4" s="40" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="M4" s="39" t="inlineStr">
+      <c r="M4" s="40" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="N4" s="39" t="inlineStr">
+      <c r="N4" s="40" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="O4" s="39" t="inlineStr">
+      <c r="O4" s="40" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="P4" s="39" t="inlineStr">
+      <c r="P4" s="40" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
@@ -6475,12 +6461,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="58" t="n">
+      <c r="D5" s="59" t="n">
         <v>8112</v>
       </c>
       <c r="F5" s="30" t="n">
@@ -6491,15 +6477,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="H5" s="34" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I5" s="43" t="n">
+      <c r="I5" s="44" t="n">
         <v>12055.8</v>
       </c>
-      <c r="J5" s="59" t="n">
+      <c r="J5" s="60" t="n">
         <v>223759.5</v>
       </c>
       <c r="L5" s="30" t="n">
@@ -6510,15 +6496,15 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="N5" s="34" t="inlineStr">
+      <c r="N5" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="O5" s="60" t="n">
+      <c r="O5" s="61" t="n">
         <v>-4249.4</v>
       </c>
-      <c r="P5" s="59" t="n">
+      <c r="P5" s="60" t="n">
         <v>11541.9</v>
       </c>
     </row>
@@ -6531,12 +6517,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="58" t="n">
+      <c r="D6" s="59" t="n">
         <v>3338</v>
       </c>
       <c r="F6" s="30" t="n">
@@ -6547,15 +6533,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="44" t="n">
         <v>4301.7</v>
       </c>
-      <c r="J6" s="59" t="n">
+      <c r="J6" s="60" t="n">
         <v>240284.8</v>
       </c>
       <c r="L6" s="30" t="n">
@@ -6566,15 +6552,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="N6" s="34" t="inlineStr">
+      <c r="N6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O6" s="60" t="n">
+      <c r="O6" s="61" t="n">
         <v>-1010.4</v>
       </c>
-      <c r="P6" s="59" t="n">
+      <c r="P6" s="60" t="n">
         <v>36009</v>
       </c>
     </row>
@@ -6587,12 +6573,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="58" t="n">
+      <c r="D7" s="59" t="n">
         <v>1216</v>
       </c>
       <c r="F7" s="30" t="n">
@@ -6603,15 +6589,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="H7" s="34" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="44" t="n">
         <v>2502.6</v>
       </c>
-      <c r="J7" s="59" t="n">
+      <c r="J7" s="60" t="n">
         <v>32891.8</v>
       </c>
       <c r="L7" s="30" t="n">
@@ -6622,15 +6608,15 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="N7" s="34" t="inlineStr">
+      <c r="N7" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="O7" s="60" t="n">
+      <c r="O7" s="61" t="n">
         <v>-1003</v>
       </c>
-      <c r="P7" s="59" t="n">
+      <c r="P7" s="60" t="n">
         <v>14504.2</v>
       </c>
     </row>
@@ -6643,12 +6629,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="58" t="n">
+      <c r="D8" s="59" t="n">
         <v>872</v>
       </c>
       <c r="F8" s="30" t="n">
@@ -6659,15 +6645,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="44" t="n">
         <v>2019.9</v>
       </c>
-      <c r="J8" s="59" t="n">
+      <c r="J8" s="60" t="n">
         <v>19469.6</v>
       </c>
       <c r="L8" s="30" t="n">
@@ -6678,15 +6664,15 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="N8" s="56" t="inlineStr">
+      <c r="N8" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="O8" s="60" t="n">
+      <c r="O8" s="61" t="n">
         <v>-783.9</v>
       </c>
-      <c r="P8" s="59" t="n">
+      <c r="P8" s="60" t="n">
         <v>11659.9</v>
       </c>
     </row>
@@ -6699,12 +6685,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="58" t="n">
+      <c r="D9" s="59" t="n">
         <v>868</v>
       </c>
       <c r="F9" s="30" t="n">
@@ -6715,15 +6701,15 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="H9" s="56" t="inlineStr">
+      <c r="H9" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="44" t="n">
         <v>1308.3</v>
       </c>
-      <c r="J9" s="59" t="n">
+      <c r="J9" s="60" t="n">
         <v>29404.2</v>
       </c>
       <c r="L9" s="30" t="n">
@@ -6734,15 +6720,15 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="N9" s="34" t="inlineStr">
+      <c r="N9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O9" s="60" t="n">
+      <c r="O9" s="61" t="n">
         <v>-750.2</v>
       </c>
-      <c r="P9" s="59" t="n">
+      <c r="P9" s="60" t="n">
         <v>9333.9</v>
       </c>
     </row>
@@ -6755,8 +6741,8 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr"/>
-      <c r="D10" s="58" t="n">
+      <c r="C10" s="35" t="inlineStr"/>
+      <c r="D10" s="59" t="n">
         <v>868</v>
       </c>
       <c r="F10" s="30" t="n">
@@ -6767,15 +6753,15 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr">
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="44" t="n">
         <v>972</v>
       </c>
-      <c r="J10" s="59" t="n">
+      <c r="J10" s="60" t="n">
         <v>6222.6</v>
       </c>
       <c r="L10" s="30" t="n">
@@ -6786,15 +6772,15 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="N10" s="34" t="inlineStr">
+      <c r="N10" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="O10" s="60" t="n">
+      <c r="O10" s="61" t="n">
         <v>-706.3</v>
       </c>
-      <c r="P10" s="59" t="n">
+      <c r="P10" s="60" t="n">
         <v>13946.5</v>
       </c>
     </row>
@@ -6807,12 +6793,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="58" t="n">
+      <c r="D11" s="59" t="n">
         <v>709</v>
       </c>
       <c r="F11" s="30" t="n">
@@ -6823,15 +6809,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="H11" s="34" t="inlineStr">
+      <c r="H11" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="44" t="n">
         <v>963.8</v>
       </c>
-      <c r="J11" s="59" t="n">
+      <c r="J11" s="60" t="n">
         <v>43511.4</v>
       </c>
       <c r="L11" s="30" t="n">
@@ -6842,15 +6828,15 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="N11" s="34" t="inlineStr">
+      <c r="N11" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="O11" s="60" t="n">
+      <c r="O11" s="61" t="n">
         <v>-667.1</v>
       </c>
-      <c r="P11" s="59" t="n">
+      <c r="P11" s="60" t="n">
         <v>8138.3</v>
       </c>
     </row>
@@ -6863,12 +6849,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="58" t="n">
+      <c r="D12" s="59" t="n">
         <v>635</v>
       </c>
       <c r="F12" s="30" t="n">
@@ -6879,15 +6865,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I12" s="43" t="n">
+      <c r="I12" s="44" t="n">
         <v>819.1</v>
       </c>
-      <c r="J12" s="59" t="n">
+      <c r="J12" s="60" t="n">
         <v>15407.3</v>
       </c>
       <c r="L12" s="30" t="n">
@@ -6898,15 +6884,15 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="N12" s="34" t="inlineStr">
+      <c r="N12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O12" s="60" t="n">
+      <c r="O12" s="61" t="n">
         <v>-608.6</v>
       </c>
-      <c r="P12" s="59" t="n">
+      <c r="P12" s="60" t="n">
         <v>7482.8</v>
       </c>
     </row>
@@ -6919,12 +6905,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="58" t="n">
+      <c r="D13" s="59" t="n">
         <v>569</v>
       </c>
       <c r="F13" s="30" t="n">
@@ -6935,15 +6921,15 @@
           <t>한전기술</t>
         </is>
       </c>
-      <c r="H13" s="34" t="inlineStr">
+      <c r="H13" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="44" t="n">
         <v>787</v>
       </c>
-      <c r="J13" s="59" t="n">
+      <c r="J13" s="60" t="n">
         <v>3588.6</v>
       </c>
       <c r="L13" s="30" t="n">
@@ -6954,15 +6940,15 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="N13" s="34" t="inlineStr">
+      <c r="N13" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="O13" s="60" t="n">
+      <c r="O13" s="61" t="n">
         <v>-575.6</v>
       </c>
-      <c r="P13" s="59" t="n">
+      <c r="P13" s="60" t="n">
         <v>4333.9</v>
       </c>
     </row>
@@ -6975,12 +6961,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D14" s="58" t="n">
+      <c r="D14" s="59" t="n">
         <v>558</v>
       </c>
       <c r="F14" s="30" t="n">
@@ -6991,15 +6977,15 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="44" t="n">
         <v>707.2</v>
       </c>
-      <c r="J14" s="59" t="n">
+      <c r="J14" s="60" t="n">
         <v>8765.6</v>
       </c>
       <c r="L14" s="30" t="n">
@@ -7010,21 +6996,21 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr">
+      <c r="N14" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="O14" s="60" t="n">
+      <c r="O14" s="61" t="n">
         <v>-552.7</v>
       </c>
-      <c r="P14" s="59" t="n">
+      <c r="P14" s="60" t="n">
         <v>6946</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=주초 대비 최신 잔고</t>
         </is>
@@ -7041,3518 +7027,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
-    <col width="8.199999999999999" customWidth="1" style="15" min="2" max="2"/>
-    <col width="8.199999999999999" customWidth="1" style="15" min="3" max="3"/>
-    <col width="8.199999999999999" customWidth="1" style="15" min="4" max="4"/>
-    <col width="8.199999999999999" customWidth="1" style="15" min="5" max="5"/>
-    <col width="9.5" customWidth="1" style="15" min="6" max="6"/>
-    <col width="9.5" customWidth="1" style="15" min="7" max="7"/>
-    <col width="10" customWidth="1" style="15" min="8" max="8"/>
-    <col width="9.5" customWidth="1" style="15" min="9" max="9"/>
-    <col width="9.5" customWidth="1" style="15" min="10" max="10"/>
-    <col width="9.5" customWidth="1" style="15" min="11" max="11"/>
-    <col width="10.5" customWidth="1" style="15" min="12" max="12"/>
-    <col width="9.5" customWidth="1" style="15" min="13" max="13"/>
-    <col width="11.5" customWidth="1" style="15" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20.25" customHeight="1" s="15">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>섹터x수급</t>
-        </is>
-      </c>
-      <c r="K1" s="25" t="inlineStr">
-        <is>
-          <t>기간</t>
-        </is>
-      </c>
-      <c r="L1" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-07 ~ 2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>섹터 x 수급 매트릭스</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="18" t="inlineStr">
-        <is>
-          <t>가격 %, 수급 억원</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>YTD</t>
-        </is>
-      </c>
-      <c r="C4" s="39" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="D4" s="39" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="inlineStr">
-        <is>
-          <t>1W</t>
-        </is>
-      </c>
-      <c r="F4" s="39" t="inlineStr">
-        <is>
-          <t>외인</t>
-        </is>
-      </c>
-      <c r="G4" s="39" t="inlineStr">
-        <is>
-          <t>기관(합)</t>
-        </is>
-      </c>
-      <c r="H4" s="39" t="inlineStr">
-        <is>
-          <t>외인+기관</t>
-        </is>
-      </c>
-      <c r="I4" s="39" t="inlineStr">
-        <is>
-          <t>연기금</t>
-        </is>
-      </c>
-      <c r="J4" s="39" t="inlineStr">
-        <is>
-          <t>금융투자</t>
-        </is>
-      </c>
-      <c r="K4" s="39" t="inlineStr">
-        <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="L4" s="39" t="inlineStr">
-        <is>
-          <t>투신(사모)</t>
-        </is>
-      </c>
-      <c r="M4" s="39" t="inlineStr">
-        <is>
-          <t>개인</t>
-        </is>
-      </c>
-      <c r="N4" s="39" t="inlineStr">
-        <is>
-          <t>신호</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="B5" s="61" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="C5" s="46" t="inlineStr"/>
-      <c r="D5" s="61" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="E5" s="61" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="F5" s="62" t="n">
-        <v>808</v>
-      </c>
-      <c r="G5" s="62" t="n">
-        <v>3180</v>
-      </c>
-      <c r="H5" s="62" t="n">
-        <v>3988</v>
-      </c>
-      <c r="I5" s="62" t="n">
-        <v>977</v>
-      </c>
-      <c r="J5" s="62" t="n">
-        <v>1003</v>
-      </c>
-      <c r="K5" s="62" t="n">
-        <v>138</v>
-      </c>
-      <c r="L5" s="62" t="n">
-        <v>1052</v>
-      </c>
-      <c r="M5" s="63" t="n">
-        <v>-3977</v>
-      </c>
-      <c r="N5" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="B6" s="61" t="n">
-        <v>82.94</v>
-      </c>
-      <c r="C6" s="46" t="inlineStr"/>
-      <c r="D6" s="61" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="E6" s="61" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="F6" s="63" t="n">
-        <v>-97</v>
-      </c>
-      <c r="G6" s="62" t="n">
-        <v>1911</v>
-      </c>
-      <c r="H6" s="62" t="n">
-        <v>1814</v>
-      </c>
-      <c r="I6" s="62" t="n">
-        <v>499</v>
-      </c>
-      <c r="J6" s="62" t="n">
-        <v>367</v>
-      </c>
-      <c r="K6" s="62" t="n">
-        <v>65</v>
-      </c>
-      <c r="L6" s="62" t="n">
-        <v>977</v>
-      </c>
-      <c r="M6" s="63" t="n">
-        <v>-2131</v>
-      </c>
-      <c r="N6" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="n">
-        <v>120.04</v>
-      </c>
-      <c r="C7" s="46" t="inlineStr"/>
-      <c r="D7" s="61" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="E7" s="61" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="F7" s="62" t="n">
-        <v>27507</v>
-      </c>
-      <c r="G7" s="62" t="n">
-        <v>35068</v>
-      </c>
-      <c r="H7" s="62" t="n">
-        <v>62575</v>
-      </c>
-      <c r="I7" s="63" t="n">
-        <v>-2425</v>
-      </c>
-      <c r="J7" s="62" t="n">
-        <v>26878</v>
-      </c>
-      <c r="K7" s="63" t="n">
-        <v>-281</v>
-      </c>
-      <c r="L7" s="62" t="n">
-        <v>10927</v>
-      </c>
-      <c r="M7" s="63" t="n">
-        <v>-113041</v>
-      </c>
-      <c r="N7" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="n">
-        <v>77.61</v>
-      </c>
-      <c r="C8" s="46" t="inlineStr"/>
-      <c r="D8" s="61" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="E8" s="61" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="F8" s="62" t="n">
-        <v>27339</v>
-      </c>
-      <c r="G8" s="62" t="n">
-        <v>35171</v>
-      </c>
-      <c r="H8" s="62" t="n">
-        <v>62510</v>
-      </c>
-      <c r="I8" s="63" t="n">
-        <v>-3535</v>
-      </c>
-      <c r="J8" s="62" t="n">
-        <v>31614</v>
-      </c>
-      <c r="K8" s="63" t="n">
-        <v>-435</v>
-      </c>
-      <c r="L8" s="62" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M8" s="63" t="n">
-        <v>-113470</v>
-      </c>
-      <c r="N8" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="B9" s="65" t="n">
-        <v>-22.38</v>
-      </c>
-      <c r="C9" s="46" t="inlineStr"/>
-      <c r="D9" s="65" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="E9" s="61" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="F9" s="63" t="n">
-        <v>-84</v>
-      </c>
-      <c r="G9" s="62" t="n">
-        <v>406</v>
-      </c>
-      <c r="H9" s="62" t="n">
-        <v>322</v>
-      </c>
-      <c r="I9" s="62" t="n">
-        <v>127</v>
-      </c>
-      <c r="J9" s="62" t="n">
-        <v>276</v>
-      </c>
-      <c r="K9" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" s="63" t="n">
-        <v>-19</v>
-      </c>
-      <c r="M9" s="63" t="n">
-        <v>-326</v>
-      </c>
-      <c r="N9" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="C10" s="46" t="inlineStr"/>
-      <c r="D10" s="61" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="E10" s="61" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F10" s="62" t="n">
-        <v>37</v>
-      </c>
-      <c r="G10" s="62" t="n">
-        <v>767</v>
-      </c>
-      <c r="H10" s="62" t="n">
-        <v>804</v>
-      </c>
-      <c r="I10" s="62" t="n">
-        <v>107</v>
-      </c>
-      <c r="J10" s="62" t="n">
-        <v>344</v>
-      </c>
-      <c r="K10" s="63" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L10" s="62" t="n">
-        <v>324</v>
-      </c>
-      <c r="M10" s="63" t="n">
-        <v>-775</v>
-      </c>
-      <c r="N10" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="B11" s="61" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="C11" s="46" t="inlineStr"/>
-      <c r="D11" s="61" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="E11" s="61" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="F11" s="62" t="n">
-        <v>1017</v>
-      </c>
-      <c r="G11" s="63" t="n">
-        <v>-599</v>
-      </c>
-      <c r="H11" s="62" t="n">
-        <v>418</v>
-      </c>
-      <c r="I11" s="62" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" s="62" t="n">
-        <v>225</v>
-      </c>
-      <c r="K11" s="63" t="n">
-        <v>-36</v>
-      </c>
-      <c r="L11" s="63" t="n">
-        <v>-806</v>
-      </c>
-      <c r="M11" s="63" t="n">
-        <v>-427</v>
-      </c>
-      <c r="N11" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="B12" s="61" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="C12" s="46" t="inlineStr"/>
-      <c r="D12" s="61" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="E12" s="61" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="F12" s="62" t="n">
-        <v>754</v>
-      </c>
-      <c r="G12" s="62" t="n">
-        <v>4602</v>
-      </c>
-      <c r="H12" s="62" t="n">
-        <v>5357</v>
-      </c>
-      <c r="I12" s="62" t="n">
-        <v>855</v>
-      </c>
-      <c r="J12" s="62" t="n">
-        <v>3254</v>
-      </c>
-      <c r="K12" s="62" t="n">
-        <v>89</v>
-      </c>
-      <c r="L12" s="63" t="n">
-        <v>-205</v>
-      </c>
-      <c r="M12" s="63" t="n">
-        <v>-5523</v>
-      </c>
-      <c r="N12" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="C13" s="46" t="inlineStr"/>
-      <c r="D13" s="61" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E13" s="61" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F13" s="63" t="n">
-        <v>-394</v>
-      </c>
-      <c r="G13" s="62" t="n">
-        <v>605</v>
-      </c>
-      <c r="H13" s="62" t="n">
-        <v>211</v>
-      </c>
-      <c r="I13" s="63" t="n">
-        <v>-15</v>
-      </c>
-      <c r="J13" s="62" t="n">
-        <v>533</v>
-      </c>
-      <c r="K13" s="62" t="n">
-        <v>32</v>
-      </c>
-      <c r="L13" s="62" t="n">
-        <v>53</v>
-      </c>
-      <c r="M13" s="63" t="n">
-        <v>-606</v>
-      </c>
-      <c r="N13" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="C14" s="46" t="inlineStr"/>
-      <c r="D14" s="65" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="E14" s="61" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F14" s="63" t="n">
-        <v>-650</v>
-      </c>
-      <c r="G14" s="63" t="n">
-        <v>-441</v>
-      </c>
-      <c r="H14" s="63" t="n">
-        <v>-1091</v>
-      </c>
-      <c r="I14" s="63" t="n">
-        <v>-1204</v>
-      </c>
-      <c r="J14" s="62" t="n">
-        <v>2489</v>
-      </c>
-      <c r="K14" s="63" t="n">
-        <v>-106</v>
-      </c>
-      <c r="L14" s="63" t="n">
-        <v>-1588</v>
-      </c>
-      <c r="M14" s="62" t="n">
-        <v>1058</v>
-      </c>
-      <c r="N14" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="C15" s="46" t="inlineStr"/>
-      <c r="D15" s="61" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E15" s="61" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F15" s="63" t="n">
-        <v>-649</v>
-      </c>
-      <c r="G15" s="62" t="n">
-        <v>167</v>
-      </c>
-      <c r="H15" s="63" t="n">
-        <v>-482</v>
-      </c>
-      <c r="I15" s="63" t="n">
-        <v>-165</v>
-      </c>
-      <c r="J15" s="62" t="n">
-        <v>433</v>
-      </c>
-      <c r="K15" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="63" t="n">
-        <v>-101</v>
-      </c>
-      <c r="M15" s="62" t="n">
-        <v>373</v>
-      </c>
-      <c r="N15" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>증권</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="C16" s="46" t="inlineStr"/>
-      <c r="D16" s="65" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="E16" s="61" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F16" s="63" t="n">
-        <v>-21</v>
-      </c>
-      <c r="G16" s="62" t="n">
-        <v>212</v>
-      </c>
-      <c r="H16" s="62" t="n">
-        <v>191</v>
-      </c>
-      <c r="I16" s="63" t="n">
-        <v>-42</v>
-      </c>
-      <c r="J16" s="62" t="n">
-        <v>240</v>
-      </c>
-      <c r="K16" s="63" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L16" s="62" t="n">
-        <v>22</v>
-      </c>
-      <c r="M16" s="63" t="n">
-        <v>-184</v>
-      </c>
-      <c r="N16" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="C17" s="46" t="inlineStr"/>
-      <c r="D17" s="61" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="E17" s="61" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F17" s="63" t="n">
-        <v>-88</v>
-      </c>
-      <c r="G17" s="62" t="n">
-        <v>41</v>
-      </c>
-      <c r="H17" s="63" t="n">
-        <v>-47</v>
-      </c>
-      <c r="I17" s="62" t="n">
-        <v>63</v>
-      </c>
-      <c r="J17" s="63" t="n">
-        <v>-5</v>
-      </c>
-      <c r="K17" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" s="63" t="n">
-        <v>-25</v>
-      </c>
-      <c r="M17" s="62" t="n">
-        <v>42</v>
-      </c>
-      <c r="N17" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B18" s="65" t="n">
-        <v>-11.74</v>
-      </c>
-      <c r="C18" s="46" t="inlineStr"/>
-      <c r="D18" s="65" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="E18" s="65" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="F18" s="63" t="n">
-        <v>-440</v>
-      </c>
-      <c r="G18" s="63" t="n">
-        <v>-697</v>
-      </c>
-      <c r="H18" s="63" t="n">
-        <v>-1137</v>
-      </c>
-      <c r="I18" s="63" t="n">
-        <v>-576</v>
-      </c>
-      <c r="J18" s="62" t="n">
-        <v>334</v>
-      </c>
-      <c r="K18" s="63" t="n">
-        <v>-90</v>
-      </c>
-      <c r="L18" s="63" t="n">
-        <v>-359</v>
-      </c>
-      <c r="M18" s="62" t="n">
-        <v>826</v>
-      </c>
-      <c r="N18" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="n">
-        <v>59.53</v>
-      </c>
-      <c r="C19" s="46" t="inlineStr"/>
-      <c r="D19" s="61" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="E19" s="65" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="F19" s="63" t="n">
-        <v>-264</v>
-      </c>
-      <c r="G19" s="62" t="n">
-        <v>365</v>
-      </c>
-      <c r="H19" s="62" t="n">
-        <v>101</v>
-      </c>
-      <c r="I19" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="J19" s="62" t="n">
-        <v>339</v>
-      </c>
-      <c r="K19" s="63" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L19" s="63" t="n">
-        <v>-115</v>
-      </c>
-      <c r="M19" s="63" t="n">
-        <v>-115</v>
-      </c>
-      <c r="N19" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="B20" s="61" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="C20" s="46" t="inlineStr"/>
-      <c r="D20" s="65" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="E20" s="65" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="F20" s="62" t="n">
-        <v>628</v>
-      </c>
-      <c r="G20" s="63" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H20" s="62" t="n">
-        <v>585</v>
-      </c>
-      <c r="I20" s="63" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J20" s="62" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" s="63" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L20" s="63" t="n">
-        <v>-58</v>
-      </c>
-      <c r="M20" s="63" t="n">
-        <v>-565</v>
-      </c>
-      <c r="N20" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>통신</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="C21" s="46" t="inlineStr"/>
-      <c r="D21" s="61" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E21" s="65" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="F21" s="62" t="n">
-        <v>68</v>
-      </c>
-      <c r="G21" s="62" t="n">
-        <v>25</v>
-      </c>
-      <c r="H21" s="62" t="n">
-        <v>93</v>
-      </c>
-      <c r="I21" s="62" t="n">
-        <v>29</v>
-      </c>
-      <c r="J21" s="62" t="n">
-        <v>309</v>
-      </c>
-      <c r="K21" s="63" t="n">
-        <v>-26</v>
-      </c>
-      <c r="L21" s="63" t="n">
-        <v>-282</v>
-      </c>
-      <c r="M21" s="63" t="n">
-        <v>-77</v>
-      </c>
-      <c r="N21" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="B22" s="65" t="n">
-        <v>-10.97</v>
-      </c>
-      <c r="C22" s="46" t="inlineStr"/>
-      <c r="D22" s="61" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E22" s="65" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="F22" s="62" t="n">
-        <v>40</v>
-      </c>
-      <c r="G22" s="63" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H22" s="62" t="n">
-        <v>37</v>
-      </c>
-      <c r="I22" s="62" t="n">
-        <v>37</v>
-      </c>
-      <c r="J22" s="62" t="n">
-        <v>33</v>
-      </c>
-      <c r="K22" s="63" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L22" s="63" t="n">
-        <v>-64</v>
-      </c>
-      <c r="M22" s="63" t="n">
-        <v>-36</v>
-      </c>
-      <c r="N22" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>비금속</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="n">
-        <v>-12.46</v>
-      </c>
-      <c r="C23" s="46" t="inlineStr"/>
-      <c r="D23" s="61" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E23" s="65" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="F23" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="63" t="n">
-        <v>-17</v>
-      </c>
-      <c r="H23" s="63" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I23" s="63" t="n">
-        <v>-12</v>
-      </c>
-      <c r="J23" s="62" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L23" s="63" t="n">
-        <v>-12</v>
-      </c>
-      <c r="M23" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="N23" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>종이·목재</t>
-        </is>
-      </c>
-      <c r="B24" s="65" t="n">
-        <v>-18.72</v>
-      </c>
-      <c r="C24" s="46" t="inlineStr"/>
-      <c r="D24" s="61" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E24" s="65" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="F24" s="63" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G24" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="63" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N24" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>오락·문화</t>
-        </is>
-      </c>
-      <c r="B25" s="65" t="n">
-        <v>-41.39</v>
-      </c>
-      <c r="C25" s="46" t="inlineStr"/>
-      <c r="D25" s="65" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="E25" s="65" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="F25" s="63" t="n">
-        <v>-142</v>
-      </c>
-      <c r="G25" s="63" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H25" s="63" t="n">
-        <v>-175</v>
-      </c>
-      <c r="I25" s="63" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="62" t="n">
-        <v>25</v>
-      </c>
-      <c r="K25" s="63" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L25" s="63" t="n">
-        <v>-31</v>
-      </c>
-      <c r="M25" s="62" t="n">
-        <v>181</v>
-      </c>
-      <c r="N25" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="B26" s="65" t="n">
-        <v>-8.539999999999999</v>
-      </c>
-      <c r="C26" s="46" t="inlineStr"/>
-      <c r="D26" s="65" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="E26" s="65" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="F26" s="63" t="n">
-        <v>-26</v>
-      </c>
-      <c r="G26" s="63" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H26" s="63" t="n">
-        <v>-32</v>
-      </c>
-      <c r="I26" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="J26" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="K26" s="63" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L26" s="63" t="n">
-        <v>-20</v>
-      </c>
-      <c r="M26" s="62" t="n">
-        <v>27</v>
-      </c>
-      <c r="N26" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="C27" s="46" t="inlineStr"/>
-      <c r="D27" s="65" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="E27" s="65" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="F27" s="63" t="n">
-        <v>-667</v>
-      </c>
-      <c r="G27" s="63" t="n">
-        <v>-1073</v>
-      </c>
-      <c r="H27" s="63" t="n">
-        <v>-1740</v>
-      </c>
-      <c r="I27" s="63" t="n">
-        <v>-770</v>
-      </c>
-      <c r="J27" s="62" t="n">
-        <v>400</v>
-      </c>
-      <c r="K27" s="63" t="n">
-        <v>-94</v>
-      </c>
-      <c r="L27" s="63" t="n">
-        <v>-597</v>
-      </c>
-      <c r="M27" s="62" t="n">
-        <v>1754</v>
-      </c>
-      <c r="N27" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="C28" s="46" t="inlineStr"/>
-      <c r="D28" s="65" t="n">
-        <v>-6.27</v>
-      </c>
-      <c r="E28" s="65" t="n">
-        <v>-4.38</v>
-      </c>
-      <c r="F28" s="63" t="n">
-        <v>-136</v>
-      </c>
-      <c r="G28" s="63" t="n">
-        <v>-1533</v>
-      </c>
-      <c r="H28" s="63" t="n">
-        <v>-1668</v>
-      </c>
-      <c r="I28" s="63" t="n">
-        <v>-229</v>
-      </c>
-      <c r="J28" s="62" t="n">
-        <v>235</v>
-      </c>
-      <c r="K28" s="63" t="n">
-        <v>-65</v>
-      </c>
-      <c r="L28" s="63" t="n">
-        <v>-1441</v>
-      </c>
-      <c r="M28" s="62" t="n">
-        <v>1636</v>
-      </c>
-      <c r="N28" s="64" t="inlineStr">
-        <is>
-          <t>데이터부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>가격추세=YTD·3M·1M·1W(%) 중 3개 이상 동일 방향 · 핵심수급(외인+기관)=주간 누적 · KIS 업종(KRX 산업분류)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>동반강세=가격강세+수급유입 · 수급이탈=가격강세+수급이탈 · 수급유입=가격약세+수급유입 · 동반약세=가격약세+수급이탈 · 공란=혼조(가격방향 불명확) · 데이터부족=일부 기간 결측</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:N28"/>
-  <mergeCells count="4">
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A30:N30"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E5:E28">
-    <cfRule type="dataBar" priority="1">
-      <dataBar showValue="1">
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="0019B6C9"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="30.85546875" customWidth="1" style="15" min="1" max="1"/>
-    <col width="90.85546875" customWidth="1" style="15" min="2" max="2"/>
-    <col width="40.85546875" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12.85546875" customWidth="1" style="15" min="4" max="5"/>
-    <col width="40.85546875" customWidth="1" style="15" min="6" max="6"/>
-    <col width="80.85546875" customWidth="1" style="15" min="7" max="7"/>
-    <col width="10.85546875" customWidth="1" style="15" min="8" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>QUANT ANTIGRAVITY 주간 브리핑</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2026-09-07 ~ 2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>생성 기준</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-09 16:16 KST</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>헤드라인</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AI 반도체와 전력 인프라가 주도한 수급 쏠림과 지수 상승</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1. 주간 누적 수급 (억원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>개인</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>외국인</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>기관</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-121583</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27497</v>
-      </c>
-      <c r="D7" t="n">
-        <v>42339</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1240</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2153</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-3668</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2. US 미국 주간 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S&amp;P500</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>나스닥</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>다우</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>필라델피아 반도체</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8.039999999999999</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>VIX 변동성</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9.52</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="15"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3. 경제지표</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>실업률</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>비농업고용지수</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>162</v>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>국내총생산(GDP) 전분기 대비</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>소비자신용</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="F21" t="n">
-        <v>14.17</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>실업률(계절조정계열)</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>4. 일별 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>미국 반도체 지수 급등(3.37%)이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 상단이 제한됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>미국 국채금리 급등과 금리 인상 우려가 국내 증시 밸류에이션 부담으로 작용하며 지수가 하락함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="15">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>미국 기술주 내 차별화 흐름과 고용지표 호조에 따른 금리 인상 우려에도 불구하고, 기관의 강한 매수세가 유입되며 지수가 반등함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>5. 주간 종합 코멘트</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>미국 고용지표 호조와 국내 2분기 GDP 성장률 0.6%(이전 1.8%) 둔화가 맞물리며 매크로 불확실성이 확대됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>수급 측면에서는 전기·전자(순매수 625억)와 기계·장비(순매수 398억) 섹터로 외국인과 기관의 매수세가 집중되며 시장을 주도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>매크로 환경의 불확실성에도 불구하고 AI 인프라 관련 핵심 섹터로의 수급 쏠림이 지수 하단을 방어하는 모습.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>6. 투자자 합산 순매수 (억원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>42067</v>
-      </c>
-      <c r="E34" t="n">
-        <v>13300</v>
-      </c>
-      <c r="F34" t="n">
-        <v>28767</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-57740</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3338.3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>240284.8</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-7162.4</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>31296</v>
-      </c>
-      <c r="E35" t="n">
-        <v>20011</v>
-      </c>
-      <c r="F35" t="n">
-        <v>11284</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-66116</v>
-      </c>
-      <c r="H35" t="n">
-        <v>8112</v>
-      </c>
-      <c r="I35" t="n">
-        <v>223759.5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>-2044.8</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SK스퀘어</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>5129</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2759</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2370</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-5018</v>
-      </c>
-      <c r="H36" t="n">
-        <v>558.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>32891.8</v>
-      </c>
-      <c r="J36" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="15">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2483</v>
-      </c>
-      <c r="E37" t="n">
-        <v>112</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2370</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-2464</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1216</v>
-      </c>
-      <c r="I37" t="n">
-        <v>19469.6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-5.9</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1727</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-73</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-1769</v>
-      </c>
-      <c r="H38" t="n">
-        <v>232.6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>28477.7</v>
-      </c>
-      <c r="J38" t="n">
-        <v>-666.1</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한미반도체</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1512</v>
-      </c>
-      <c r="E39" t="n">
-        <v>857</v>
-      </c>
-      <c r="F39" t="n">
-        <v>655</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-1495</v>
-      </c>
-      <c r="H39" t="n">
-        <v>868.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>43511.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-835.3</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1393</v>
-      </c>
-      <c r="E40" t="n">
-        <v>740</v>
-      </c>
-      <c r="F40" t="n">
-        <v>653</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-1398</v>
-      </c>
-      <c r="H40" t="n">
-        <v>129.7</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3293.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-232.3</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LS ELECTRIC</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1232</v>
-      </c>
-      <c r="E41" t="n">
-        <v>835</v>
-      </c>
-      <c r="F41" t="n">
-        <v>397</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-1222</v>
-      </c>
-      <c r="H41" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9403.4</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>효성중공업</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1038</v>
-      </c>
-      <c r="E42" t="n">
-        <v>816</v>
-      </c>
-      <c r="F42" t="n">
-        <v>222</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-1048</v>
-      </c>
-      <c r="H42" t="n">
-        <v>291</v>
-      </c>
-      <c r="I42" t="n">
-        <v>5502.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-624.2</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="15">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>957</v>
-      </c>
-      <c r="E43" t="n">
-        <v>427</v>
-      </c>
-      <c r="F43" t="n">
-        <v>529</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-951</v>
-      </c>
-      <c r="H43" t="n">
-        <v>569.3</v>
-      </c>
-      <c r="I43" t="n">
-        <v>10178.7</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-497.1</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="15">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>-1354</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-1162</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-192</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1376</v>
-      </c>
-      <c r="H44" t="n">
-        <v>871.6</v>
-      </c>
-      <c r="I44" t="n">
-        <v>36009</v>
-      </c>
-      <c r="J44" t="n">
-        <v>-2801</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="15">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>삼양식품</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>-1254</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-24</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-1230</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="H45" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="I45" t="n">
-        <v>8138.3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-220.9</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="15">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>-964</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-929</v>
-      </c>
-      <c r="G46" t="n">
-        <v>965</v>
-      </c>
-      <c r="H46" t="n">
-        <v>151.3</v>
-      </c>
-      <c r="I46" t="n">
-        <v>14504.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>-390.7</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="15">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>-860</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-555</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-306</v>
-      </c>
-      <c r="G47" t="n">
-        <v>590</v>
-      </c>
-      <c r="H47" t="n">
-        <v>215.2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>12546.7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-283.6</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="15">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LG이노텍</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>-680</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-338</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-342</v>
-      </c>
-      <c r="G48" t="n">
-        <v>668</v>
-      </c>
-      <c r="H48" t="n">
-        <v>708.7</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9333.9</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-1092.4</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-679</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-292</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-386</v>
-      </c>
-      <c r="G49" t="n">
-        <v>764</v>
-      </c>
-      <c r="H49" t="n">
-        <v>419.2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31440</v>
-      </c>
-      <c r="J49" t="n">
-        <v>-1186.9</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="15">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>7</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>-514</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-506</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>464</v>
-      </c>
-      <c r="H50" t="n">
-        <v>486.8</v>
-      </c>
-      <c r="I50" t="n">
-        <v>13231</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-296.9</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>레인보우로보틱스</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-484</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-277</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-206</v>
-      </c>
-      <c r="G51" t="n">
-        <v>479</v>
-      </c>
-      <c r="H51" t="n">
-        <v>318.4</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6895.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-292.3</v>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="15">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>OCI홀딩스</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-478</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-42</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-437</v>
-      </c>
-      <c r="G52" t="n">
-        <v>507</v>
-      </c>
-      <c r="H52" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3421.8</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-191.7</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="15">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>10</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>POSCO홀딩스</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-429</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-444</v>
-      </c>
-      <c r="F53" t="n">
-        <v>15</v>
-      </c>
-      <c r="G53" t="n">
-        <v>441</v>
-      </c>
-      <c r="H53" t="n">
-        <v>211.7</v>
-      </c>
-      <c r="I53" t="n">
-        <v>7655.8</v>
-      </c>
-      <c r="J53" t="n">
-        <v>-621.3</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="15">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>7. 섹터 시그널 종목 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="15">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>8. 주간 시장 흐름</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>AI 반도체 및 HBM 수요 기대감으로 외국인과 기관의 강력한 매수세가 유입되며 지수 상승을 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="15">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되어 일시적 조정 발생.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="15">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>원/달러 환율 하락세가 지속되며 외국인 투자자의 환차손 부담이 완화됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="15">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>전력 설비 및 원전 관련주로 수급이 확산되며 섹터별 차별화 장세가 심화됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="15">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>9. 섹터·테마 흐름</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>전기·전자 및 기계·장비 섹터는 AI 반도체와 데이터센터 인프라 수요를 바탕으로 주간 내내 강세 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>원전 및 전력 설비 관련주는 대형 수주 기대감과 함께 신규 주도 테마로 부상.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="15">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>음식료·담배 및 IT 서비스 섹터는 차익 실현 매물과 실적 우려로 약세 전환.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="15">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>10. 촉매 타임라인</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="15">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="15">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>필옵틱스</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="15">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>나무가</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>5</v>
-      </c>
-      <c r="F67" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>두산퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5</v>
-      </c>
-      <c r="F68" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="15">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="15">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="15">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="15">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>빛과전자</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>5</v>
-      </c>
-      <c r="F73" t="n">
-        <v>40.33</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="15">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>오르비텍</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="15">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>서전기전</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>5</v>
-      </c>
-      <c r="F75" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="15">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>5</v>
-      </c>
-      <c r="F76" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F78" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="15">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>머큐리</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="15">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>페니트리움바이오</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>5</v>
-      </c>
-      <c r="F80" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>항암 후보물질 비교 평가 1차 연구 결과 발표에 따른 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="15">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>더코디</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>5</v>
-      </c>
-      <c r="F81" t="n">
-        <v>119.31</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>범LG가 구본호 회장 측의 최대주주 등극 소식에 따른 경영권 변화 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="15">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>우리로</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>5</v>
-      </c>
-      <c r="F82" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="15">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>범한퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>5</v>
-      </c>
-      <c r="F83" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="15">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>미국 광통신 시장 대규모 공급 계약에 따른 동반 수혜 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="15">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>에스엠벡셀</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>5</v>
-      </c>
-      <c r="F85" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="15">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>가온전선</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>5</v>
-      </c>
-      <c r="F86" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="15">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>4</v>
-      </c>
-      <c r="F87" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>자회사 흡수합병을 통한 사업 경쟁력 강화 및 기후테크 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>두산퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>4</v>
-      </c>
-      <c r="F88" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>미국 AI 데이터센터용 연료전지 대규모 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>파운드리 가격 상승 전망에 따른 실적 개선 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>4</v>
-      </c>
-      <c r="F90" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>AI 반도체 및 HBM 수요 확대에 따른 외국인·기관 매수세 집중.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>4</v>
-      </c>
-      <c r="F91" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>미국 AI 전력난에 따른 원전 및 가스터빈 수주 기대감 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>한화오션</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>4</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>태국 왕립해군 차세대 호위함 사업 우선협상대상자 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="15">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>11. 다음 주 프리뷰</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="15">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>반도체 및 전력 인프라 섹터의 수급이 유지되면 지수 상승세 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="15">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>미국 CPI 발표 후 금리 인상 우려가 재점화되면 단기 조정 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="15">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI) 발표 결과에 따른 시장의 금리 경로 해석</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="15">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>미국 소비자물가지수(CPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>한국 무역수지</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -10,9 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신고가 근접" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투자자별 순매수" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공매도·대차" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$N$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;;0.0&quot;%&quot;"/>
-    <numFmt numFmtId="165" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="166" formatCode="+#,##0.0;-#,##0.0;0.0"/>
-    <numFmt numFmtId="167" formatCode="+0.0;-0.0;0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="+0;-0;0"/>
+    <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -253,7 +256,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -305,6 +308,11 @@
         <fgColor rgb="FFEAF1FD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -318,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -415,14 +423,14 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -430,46 +438,49 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,7 +492,7 @@
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,11 +504,32 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -901,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -942,7 +974,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-09 16:34 KST</t>
+          <t>2026-09-09 16:54 KST</t>
         </is>
       </c>
     </row>
@@ -1247,13 +1279,11 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>10.16</v>
       </c>
     </row>
     <row r="19">
@@ -1269,13 +1299,11 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>8.48</v>
       </c>
     </row>
     <row r="20">
@@ -1291,13 +1319,11 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>7.94</v>
       </c>
     </row>
     <row r="21">
@@ -1313,13 +1339,11 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>-4.38</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1359,11 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="23">
@@ -1357,13 +1379,11 @@
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D23" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>섬유·의류</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="24"/>
@@ -1692,7 +1712,7 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 강세로 이어졌으나, 고용지표 호조에 따른 금리 인하 경계감으로 지수 상단은 제한됨.</t>
+          <t>필라델피아 반도체 지수의 3.37% 급등이 국내 반도체 소부장 강세를 이끌었으나, 미국 고용지표 호조에 따른 금리 인하 경계감이 상단을 제한함.</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>미국 국채금리 급등과 금리 인상 우려에도 불구하고, 미국 내 대형 원전 건설 협의 소식이 전해지며 국내 건설 및 전기·가스 섹터가 강세를 보임.</t>
+          <t>미국 국채금리 급등과 금리 인상 우려가 시장 밸류에이션 부담으로 작용하며, 반도체 강세에도 불구하고 지수 하락을 유발함.</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1850,7 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>미국 증시의 기술주 차별화 흐름과 지정학적 리스크에도 불구하고, 기관의 강한 매수세가 유입되며 KOSPI 7,000선 안착에 성공함.</t>
+          <t>미국 기술주 내 차별화 흐름과 지정학적 리스크에도 불구하고, 국내 기관의 강한 매수세가 유입되며 지수 반등을 견인함.</t>
         </is>
       </c>
     </row>
@@ -1871,21 +1891,21 @@
     <row r="41" ht="31" customHeight="1" s="15">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경은 미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치를 상회하고, 국내 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하는 등 경기 둔화와 금리 인상 우려가 혼재된 상황임.</t>
+          <t>- 미국 8월 비농업 고용지수가 16만 2천 명 증가하며 예상치를 상회했으나, 국내 2분기 GDP 성장률은 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 매크로 환경의 변수로 작용함.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" s="15">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도는 삼성전자(42,067억)와 SK하이닉스(31,296억) 등 반도체 대형주에 외국인과 기관의 매수세가 집중되었으며, 반면 삼성전기(-1,354억)와 삼양식품(-1,254억) 등은 순매도 상위에 위치함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="31" customHeight="1" s="15">
+          <t>- 수급 측면에서 전기·전자 섹터에 62,575억 원의 코어 플로우가 유입되며 주간 7.94% 상승했고, 기계·장비 섹터에도 3,988억 원이 유입되며 10.16% 상승함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="15">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>- 종합적으로 매크로 불확실성에도 불구하고 AI 반도체와 전력 인프라라는 확실한 성장 모멘텀을 가진 섹터로 수급이 쏠리는 'Risk-On' 국면이 지속되고 있음.</t>
+          <t>- 반면 음식료·담배 섹터는 1,668억 원의 수급 이탈과 함께 4.38% 하락하며 수급 쏠림 현상이 뚜렷한 한 주였음.</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2006,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="D47" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2027,7 +2047,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D48" s="35" t="inlineStr">
+      <c r="D48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2068,7 +2088,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="D49" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2109,7 +2129,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
+      <c r="D50" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2150,7 +2170,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D51" s="35" t="inlineStr">
+      <c r="D51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2191,7 +2211,7 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="D52" s="35" t="inlineStr">
+      <c r="D52" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2232,7 +2252,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2273,7 +2293,7 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2314,7 +2334,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2355,7 +2375,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2396,7 +2416,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2437,7 +2457,7 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D58" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
@@ -2478,7 +2498,7 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2519,7 +2539,7 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D60" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -2560,7 +2580,7 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2601,7 +2621,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2642,7 +2662,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2683,7 +2703,7 @@
           <t>레인보우로보틱스</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2724,7 +2744,7 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2765,7 +2785,7 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D66" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
@@ -2819,7 +2839,7 @@
       <c r="K68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="36" t="inlineStr">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -2831,427 +2851,321 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="B70" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr"/>
+      <c r="E70" s="31" t="inlineStr"/>
+      <c r="G70" s="31" t="inlineStr">
         <is>
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-      <c r="G70" s="31" t="inlineStr">
+    </row>
+    <row r="71" ht="44.5" customHeight="1" s="15">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +740억 순매수, 기관 +653억 순매수, 대차잔고 -232억 감소 — 화학(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>효성중공업</t>
+        </is>
+      </c>
+      <c r="B72" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr"/>
+      <c r="E72" s="31" t="inlineStr"/>
+    </row>
+    <row r="73" ht="44.5" customHeight="1" s="15">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +816억 순매수, 기관 +222억 순매수, 대차잔고 -624억 감소 — 전기·전자(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B74" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="C74" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr"/>
+      <c r="E74" s="31" t="inlineStr"/>
+    </row>
+    <row r="75" ht="44.5" customHeight="1" s="15">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +13,300억 순매수, 기관 +28,767억 순매수, 대차잔고 -7,162억 감소 — 전기·전자(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="37" t="inlineStr">
+        <is>
+          <t>● 수급이탈 — 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G77" s="38" t="inlineStr">
+        <is>
+          <t>● 동반약세 — 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
         <is>
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="37" t="inlineStr">
-        <is>
-          <t>● 수급이탈 — 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G73" s="38" t="inlineStr">
-        <is>
-          <t>● 동반약세 — 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>해당 섹터·조건 충족 종목 없음</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>해당 섹터·조건 충족 종목 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="39" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="I78" s="39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J78" s="31" t="inlineStr"/>
+      <c r="K78" s="31" t="inlineStr"/>
+    </row>
+    <row r="79" ht="31" customHeight="1" s="15">
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -24억 순매도, 기관 -1,230억 순매도 — 음식료·담배(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="I80" s="39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J80" s="31" t="inlineStr"/>
+      <c r="K80" s="31" t="inlineStr"/>
+    </row>
+    <row r="81" ht="31" customHeight="1" s="15">
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -555억 순매도, 기관 -306억 순매도 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="31" customHeight="1" s="15">
+      <c r="A83" s="40" t="inlineStr">
         <is>
           <t>현재 확보된 주간 브리핑 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 주간 촉매) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>주간 시장 흐름</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="31" customHeight="1" s="15">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t>- 주 초반 미국 고용지표 호조에 따른 금리 인하 기대감 후퇴와 기술주 약세로 변동성이 확대되었으나, 주 후반 반도체 및 전력 인프라 관련주로 외국인과 기관의 매수세가 집중되며 지수 반등을 견인함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="31" customHeight="1" s="15">
-      <c r="A82" s="17" t="inlineStr">
-        <is>
-          <t>- KOSPI는 주중 7,000선 안착을 시도하며 1.4% 상승 마감했고, KOSDAQ은 외국인 매수세 유입에 힘입어 2.28% 급등함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="31" customHeight="1" s="15">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>- 원/달러 환율은 1,336.6원까지 하락하며 원화 강세 흐름을 보였고, 이는 외국인 투자자의 환차손 부담을 완화하며 대형주 중심의 수급 유입을 뒷받침함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="31" customHeight="1" s="15">
-      <c r="A84" s="17" t="inlineStr">
-        <is>
-          <t>- 개인은 주간 내내 대규모 순매도를 지속하며 차익 실현에 집중한 반면, 기관과 외국인은 반도체와 전력 설비 등 주도 섹터에 수급을 집중하는 양극화된 흐름을 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>섹터·테마 흐름</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr"/>
-      <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" s="3" t="inlineStr"/>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr"/>
-      <c r="J86" s="3" t="inlineStr"/>
-      <c r="K86" s="3" t="inlineStr"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 섹터는 AI 메모리 및 HBM 수요 기대감으로 주간 내내 외국인과 기관의 강력한 매수세가 유입되며 시장 주도력을 유지함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="31" customHeight="1" s="15">
+          <t>- 주 초반 외국인과 기관의 강력한 동반 매수세가 유입되며 KOSPI가 4.61% 급등, 7,000선 안착을 시도함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="15">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>- 전력 설비 및 원전 관련주는 미국 내 데이터센터 전력 수요와 원전 건설 협의 이슈가 부각되며 기계·장비 섹터의 강세를 지속적으로 견인함.</t>
+          <t>- 8일 발표된 2분기 GDP 성장률이 0.6%로 이전치(1.8%)를 하회하며 경기 둔화 우려가 부각되어 지수가 0.58% 하락함.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="15">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t>- 음식료 및 소비재 섹터는 글로벌 실적 우려와 환율 하락에 따른 수출 실적 부담으로 차익 실현 매물이 출회되며 약세 흐름을 보임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+          <t>- 9일에는 기관의 매수세가 재차 유입되며 KOSPI가 1.4% 상승, 7,000선을 회복하며 마감함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="15">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>- 주간 내내 AI 반도체 및 HBM 수요 기대감과 미국 AI 데이터센터 관련 전력 인프라 수주 모멘텀이 시장을 주도함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>섹터·테마 흐름</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="15">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>- 전기·전자 섹터는 AI 반도체 및 HBM 수요 기대감으로 주간 내내 강력한 수급이 집중되며 시장 상승을 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="31" customHeight="1" s="15">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>- 기계·장비 및 건설 섹터는 미국 내 대형 원전 8기 건설 협의 및 AI 데이터센터 전력 인프라 수주 기대감으로 지속적인 강세를 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="15">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>- 음식료·담배 및 IT 서비스 섹터는 환율 하락 및 차익 실현 매물 출회로 주간 내내 약세 흐름을 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>주간 촉매 타임라인</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr"/>
-      <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="18" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr"/>
+      <c r="D97" s="3" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr"/>
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="18" t="inlineStr">
         <is>
           <t>등락률 = 주간 누적</t>
         </is>
       </c>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="31" customHeight="1" s="15">
-      <c r="A93" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B93" s="31" t="inlineStr">
-        <is>
-          <t>네오오토</t>
-        </is>
-      </c>
-      <c r="C93" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D93" s="35" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E93" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F93" s="29" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="31" customHeight="1" s="15">
-      <c r="A94" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B94" s="31" t="inlineStr">
-        <is>
-          <t>필옵틱스</t>
-        </is>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D94" s="35" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F94" s="29" t="n">
-        <v>33.59</v>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="31" customHeight="1" s="15">
-      <c r="A95" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B95" s="31" t="inlineStr">
-        <is>
-          <t>나무가</t>
-        </is>
-      </c>
-      <c r="C95" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D95" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F95" s="29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="31" customHeight="1" s="15">
-      <c r="A96" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B96" s="31" t="inlineStr">
-        <is>
-          <t>두산퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C96" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D96" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F96" s="29" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="31" customHeight="1" s="15">
-      <c r="A97" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B97" s="31" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
-        </is>
-      </c>
-      <c r="C97" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D97" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E97" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F97" s="29" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="G97" s="17" t="inlineStr">
-        <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="31" customHeight="1" s="15">
-      <c r="A98" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B98" s="31" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="C98" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D98" s="35" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F98" s="29" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3177,30 @@
       </c>
       <c r="B99" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>네오오토</t>
         </is>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D99" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D99" s="34" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F99" s="29" t="n">
-        <v>11.55</v>
+        <v>35.12</v>
       </c>
       <c r="G99" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>계열사 오토인더스트리를 완전 자회사로 편입한다는 결정에 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -3298,87 +3212,87 @@
       </c>
       <c r="B100" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="C100" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D100" s="35" t="inlineStr">
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F100" s="29" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>차세대 반도체 패키지용 유리기판 실물 공개 및 해외 고객사 수주 가시화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="31" customHeight="1" s="15">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>나무가</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F100" s="29" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="G100" s="17" t="inlineStr">
-        <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B101" s="31" t="inlineStr">
-        <is>
-          <t>빛과전자</t>
-        </is>
-      </c>
-      <c r="C101" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D101" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
       <c r="F101" s="29" t="n">
-        <v>40.33</v>
+        <v>12.06</v>
       </c>
       <c r="G101" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>북미 휴머노이드 로봇 기업에 3D 카메라 모듈 단독 공급 계약 체결.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="31" customHeight="1" s="15">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B102" s="31" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C102" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D102" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -3387,58 +3301,58 @@
         </is>
       </c>
       <c r="F102" s="29" t="n">
-        <v>42.89</v>
+        <v>24.45</v>
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="31" customHeight="1" s="15">
       <c r="A103" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B103" s="31" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D103" s="35" t="inlineStr">
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D103" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F103" s="29" t="n">
-        <v>35.16</v>
+        <v>23.48</v>
       </c>
       <c r="G103" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="31" customHeight="1" s="15">
       <c r="A104" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B104" s="31" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C104" s="31" t="inlineStr">
@@ -3446,34 +3360,34 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F104" s="29" t="n">
-        <v>32.65</v>
+        <v>15.16</v>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="31" customHeight="1" s="15">
       <c r="A105" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B105" s="31" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
@@ -3481,9 +3395,9 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
+      <c r="D105" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -3492,23 +3406,23 @@
         </is>
       </c>
       <c r="F105" s="29" t="n">
-        <v>23.99</v>
+        <v>11.43</v>
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="15">
+          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="31" customHeight="1" s="15">
       <c r="A106" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B106" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C106" s="31" t="inlineStr">
@@ -3516,9 +3430,9 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
-        <is>
-          <t>건설</t>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3527,23 +3441,23 @@
         </is>
       </c>
       <c r="F106" s="29" t="n">
-        <v>33.15</v>
+        <v>4.86</v>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="15">
       <c r="A107" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B107" s="31" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
@@ -3551,7 +3465,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D107" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3562,23 +3476,23 @@
         </is>
       </c>
       <c r="F107" s="29" t="n">
-        <v>28.09</v>
+        <v>40.33</v>
       </c>
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="31" customHeight="1" s="15">
       <c r="A108" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B108" s="17" t="inlineStr">
-        <is>
-          <t>페니트리움바이오</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B108" s="31" t="inlineStr">
+        <is>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C108" s="31" t="inlineStr">
@@ -3586,7 +3500,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D108" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3597,23 +3511,23 @@
         </is>
       </c>
       <c r="F108" s="29" t="n">
-        <v>26.84</v>
+        <v>42.89</v>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>항암 후보물질 비교 평가 1차 연구 결과 발표에 따른 기대감.</t>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="31" customHeight="1" s="15">
       <c r="A109" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B109" s="31" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
@@ -3621,7 +3535,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
+      <c r="D109" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3632,33 +3546,33 @@
         </is>
       </c>
       <c r="F109" s="29" t="n">
-        <v>119.31</v>
+        <v>35.16</v>
       </c>
       <c r="G109" s="17" t="inlineStr">
         <is>
-          <t>범LG가 구본호 회장 측의 최대주주 등극 소식에 따른 경영권 변화 기대.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="31" customHeight="1" s="15">
       <c r="A110" s="31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B110" s="31" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D110" s="35" t="inlineStr">
-        <is>
-          <t>유통</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -3667,116 +3581,116 @@
         </is>
       </c>
       <c r="F110" s="29" t="n">
-        <v>35.74</v>
+        <v>32.47</v>
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="31" customHeight="1" s="15">
       <c r="A111" s="31" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="31" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="C111" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F111" s="29" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="15">
+      <c r="A112" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B112" s="31" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F112" s="29" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="15">
+      <c r="A113" s="31" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B111" s="31" t="inlineStr">
-        <is>
-          <t>범한퓨얼셀</t>
-        </is>
-      </c>
-      <c r="C111" s="31" t="inlineStr">
+      <c r="B113" s="31" t="inlineStr">
+        <is>
+          <t>머큐리</t>
+        </is>
+      </c>
+      <c r="C113" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D111" s="35" t="inlineStr">
+      <c r="D113" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E111" s="14" t="inlineStr">
+      <c r="E113" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F111" s="29" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="G111" s="17" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="31" customHeight="1" s="15">
-      <c r="A112" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B112" s="31" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="C112" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D112" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F112" s="29" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>미국 광통신 시장 대규모 공급 계약에 따른 동반 수혜 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="31" customHeight="1" s="15">
-      <c r="A113" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B113" s="31" t="inlineStr">
-        <is>
-          <t>에스엠벡셀</t>
-        </is>
-      </c>
-      <c r="C113" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D113" s="35" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E113" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
       <c r="F113" s="29" t="n">
-        <v>23.31</v>
+        <v>28.09</v>
       </c>
       <c r="G113" s="17" t="inlineStr">
         <is>
-          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
+          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
         </is>
       </c>
     </row>
@@ -3786,19 +3700,19 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B114" s="31" t="inlineStr">
-        <is>
-          <t>가온전선</t>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="C114" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D114" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D114" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -3807,11 +3721,11 @@
         </is>
       </c>
       <c r="F114" s="29" t="n">
-        <v>24.65</v>
+        <v>26.84</v>
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
+          <t>항암 후보물질 비교 평가 1차 연구 결과 발표에 따른 기대감.</t>
         </is>
       </c>
     </row>
@@ -3823,34 +3737,34 @@
       </c>
       <c r="B115" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D115" s="35" t="inlineStr">
-        <is>
-          <t>화학</t>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D115" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F115" s="29" t="n">
-        <v>10.06</v>
+        <v>119.31</v>
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>자회사 흡수합병을 통한 사업 경쟁력 강화 및 기후테크 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="15">
+          <t>범LG가 구본호 회장 측의 최대주주 등극 소식에 따른 경영권 변화 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="31" customHeight="1" s="15">
       <c r="A116" s="31" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3858,65 +3772,65 @@
       </c>
       <c r="B116" s="31" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="C116" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D116" s="35" t="inlineStr">
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F116" s="29" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="31" customHeight="1" s="15">
+      <c r="A117" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B117" s="31" t="inlineStr">
+        <is>
+          <t>범한퓨얼셀</t>
+        </is>
+      </c>
+      <c r="C117" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D117" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F116" s="29" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>미국 AI 데이터센터용 연료전지 대규모 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="15" customHeight="1" s="15">
-      <c r="A117" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B117" s="31" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
-        </is>
-      </c>
-      <c r="C117" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D117" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F117" s="29" t="n">
-        <v>23.37</v>
+        <v>37.43</v>
       </c>
       <c r="G117" s="17" t="inlineStr">
         <is>
-          <t>파운드리 가격 상승 전망에 따른 실적 개선 기대감.</t>
+          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
         </is>
       </c>
     </row>
@@ -3928,30 +3842,30 @@
       </c>
       <c r="B118" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C118" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D118" s="35" t="inlineStr">
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F118" s="29" t="n">
-        <v>11.55</v>
+        <v>24.23</v>
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>AI 반도체 및 HBM 수요 확대에 따른 외국인·기관 매수세 집중.</t>
+          <t>미국 광통신 시장 대규모 공급 계약에 따른 동반 수혜 기대.</t>
         </is>
       </c>
     </row>
@@ -3963,186 +3877,407 @@
       </c>
       <c r="B119" s="31" t="inlineStr">
         <is>
+          <t>에스엠벡셀</t>
+        </is>
+      </c>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D119" s="34" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F119" s="29" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="G119" s="17" t="inlineStr">
+        <is>
+          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="31" customHeight="1" s="15">
+      <c r="A120" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B120" s="31" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="C120" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F120" s="29" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="31" customHeight="1" s="15">
+      <c r="A121" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C121" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D121" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F121" s="29" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="G121" s="17" t="inlineStr">
+        <is>
+          <t>자회사 흡수합병을 통한 사업 경쟁력 강화 및 기후테크 협력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="15">
+      <c r="A122" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B122" s="31" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="C122" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D122" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F122" s="29" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>미국 AI 데이터센터용 연료전지 대규모 공급 계약 체결.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="15">
+      <c r="A123" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B123" s="31" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="C123" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D123" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F123" s="29" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>파운드리 가격 상승 전망에 따른 실적 개선 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="31" customHeight="1" s="15">
+      <c r="A124" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B124" s="31" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C124" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D124" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F124" s="29" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>AI 반도체 및 HBM 수요 확대에 따른 외국인·기관 매수세 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="31" customHeight="1" s="15">
+      <c r="A125" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" s="31" t="inlineStr">
+        <is>
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C119" s="31" t="inlineStr">
+      <c r="C125" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D119" s="35" t="inlineStr">
+      <c r="D125" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="E119" s="14" t="inlineStr">
+      <c r="E125" s="14" t="inlineStr">
         <is>
           <t>★★★★</t>
         </is>
       </c>
-      <c r="F119" s="29" t="n">
+      <c r="F125" s="29" t="n">
         <v>15.16</v>
       </c>
-      <c r="G119" s="17" t="inlineStr">
+      <c r="G125" s="17" t="inlineStr">
         <is>
           <t>미국 AI 전력난에 따른 원전 및 가스터빈 수주 기대감 지속.</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="15">
-      <c r="A120" s="31" t="inlineStr">
+    <row r="126" ht="15" customHeight="1" s="15">
+      <c r="A126" s="31" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B120" s="31" t="inlineStr">
+      <c r="B126" s="31" t="inlineStr">
         <is>
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C120" s="31" t="inlineStr">
+      <c r="C126" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D120" s="35" t="inlineStr">
+      <c r="D126" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E120" s="14" t="inlineStr">
+      <c r="E126" s="14" t="inlineStr">
         <is>
           <t>★★★★</t>
         </is>
       </c>
-      <c r="F120" s="29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G120" s="17" t="inlineStr">
+      <c r="F126" s="29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
         <is>
           <t>태국 왕립해군 차세대 호위함 사업 우선협상대상자 선정.</t>
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr"/>
-      <c r="D122" s="3" t="inlineStr"/>
-      <c r="E122" s="3" t="inlineStr"/>
-      <c r="F122" s="3" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr"/>
-      <c r="H122" s="3" t="inlineStr"/>
-      <c r="I122" s="3" t="inlineStr"/>
-      <c r="J122" s="3" t="inlineStr"/>
-      <c r="K122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="15">
-      <c r="A123" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 CPI가 예상치를 하회하면 금리 인하 기대감에 힘입어 반도체 및 성장주 중심의 상승세 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15" customHeight="1" s="15">
-      <c r="A124" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 CPI가 예상치를 상회하면 금리 인상 우려 재점화로 외국인 수급 이탈 및 지수 조정</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="15">
-      <c r="A125" s="17" t="inlineStr">
-        <is>
-          <t>- 9월 11일 발표되는 미국 소비자물가지수(CPI)의 전월 대비 상승률과 국채 금리의 변동성</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1" s="15">
-      <c r="A126" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 소비자물가지수(CPI) 발표</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="15">
-      <c r="A127" s="17" t="inlineStr">
-        <is>
-          <t>- 국내 무역수지 및 수출입 데이터 발표</t>
+      <c r="C128" s="3" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr"/>
+      <c r="E128" s="3" t="inlineStr"/>
+      <c r="F128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="15">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 물가 지표가 예상치를 하회하면 금리 인하 기대감으로 기술주 중심의 상승세 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="15">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 물가 지표가 예상치를 상회하면 금리 인상 우려 재점화로 인한 외국인 수급 이탈 및 지수 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="15">
+      <c r="A131" s="17" t="inlineStr">
+        <is>
+          <t>- 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI)의 전월 대비 등락폭</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="15">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 생산자물가지수(PPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="15">
+      <c r="A133" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 소비자물가지수(CPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="15">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>- 한국 무역수지</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="G96:K96"/>
+  <mergeCells count="68">
+    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A83:K83"/>
-    <mergeCell ref="A127:K127"/>
     <mergeCell ref="G105:K105"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="G77:K77"/>
     <mergeCell ref="B40:K40"/>
-    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="G81:K81"/>
+    <mergeCell ref="A130:K130"/>
     <mergeCell ref="G115:K115"/>
     <mergeCell ref="G117:K117"/>
     <mergeCell ref="G36:K36"/>
     <mergeCell ref="G120:K120"/>
     <mergeCell ref="G98:K98"/>
-    <mergeCell ref="A123:K123"/>
     <mergeCell ref="G107:K107"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="G126:K126"/>
+    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A132:K132"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="B80:K80"/>
-    <mergeCell ref="G97:K97"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A88:K88"/>
+    <mergeCell ref="G122:K122"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="G116:K116"/>
-    <mergeCell ref="A124:K124"/>
     <mergeCell ref="A87:K87"/>
+    <mergeCell ref="G125:K125"/>
     <mergeCell ref="G101:K101"/>
     <mergeCell ref="G103:K103"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="G112:K112"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="G93:K93"/>
-    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A133:K133"/>
     <mergeCell ref="G118:K118"/>
     <mergeCell ref="G69:K69"/>
     <mergeCell ref="A89:K89"/>
-    <mergeCell ref="G74:K74"/>
-    <mergeCell ref="G92:K92"/>
+    <mergeCell ref="G121:K121"/>
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="G108:K108"/>
-    <mergeCell ref="G95:K95"/>
+    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:K129"/>
+    <mergeCell ref="G124:K124"/>
     <mergeCell ref="G104:K104"/>
     <mergeCell ref="A42:K42"/>
     <mergeCell ref="G114:K114"/>
+    <mergeCell ref="B86:K86"/>
     <mergeCell ref="G110:K110"/>
-    <mergeCell ref="G73:K73"/>
-    <mergeCell ref="A126:K126"/>
+    <mergeCell ref="G79:K79"/>
+    <mergeCell ref="G123:K123"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G35:K35"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="G100:K100"/>
     <mergeCell ref="G113:K113"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="G109:K109"/>
+    <mergeCell ref="A134:K134"/>
     <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="G94:K94"/>
     <mergeCell ref="G119:K119"/>
-    <mergeCell ref="A125:K125"/>
+    <mergeCell ref="A93:K93"/>
     <mergeCell ref="G99:K99"/>
     <mergeCell ref="G106:K106"/>
     <mergeCell ref="C4:K4"/>
@@ -4238,62 +4373,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="40" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="40" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="40" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="40" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="40" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="40" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>주간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="40" t="inlineStr">
+      <c r="L5" s="41" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -4305,7 +4440,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -4315,31 +4450,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>1393</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="42" t="n">
         <v>740</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="42" t="n">
         <v>653</v>
       </c>
-      <c r="G6" s="42" t="n">
+      <c r="G6" s="43" t="n">
         <v>-1398</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="44" t="n">
         <v>129.7</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="44" t="n">
         <v>3293.5</v>
       </c>
-      <c r="J6" s="44" t="n">
+      <c r="J6" s="45" t="n">
         <v>-298.3</v>
       </c>
-      <c r="K6" s="45" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="L6" s="46" t="n">
+      <c r="K6" s="46" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="L6" s="47" t="n">
         <v>-1.24</v>
       </c>
     </row>
@@ -4349,7 +4484,7 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -4359,31 +4494,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="42" t="n">
         <v>119</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="43" t="n">
         <v>-368</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="42" t="n">
         <v>487</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="43" t="n">
         <v>-102</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="44" t="n">
         <v>310.1</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="44" t="n">
         <v>7226.2</v>
       </c>
-      <c r="J7" s="44" t="n">
+      <c r="J7" s="45" t="n">
         <v>-230.6</v>
       </c>
-      <c r="K7" s="47" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="L7" s="48" t="n">
+      <c r="K7" s="48" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L7" s="49" t="n">
         <v>-5.33</v>
       </c>
     </row>
@@ -4393,7 +4528,7 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -4403,31 +4538,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="42" t="n">
         <v>56</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="43" t="n">
         <v>-193</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="42" t="n">
         <v>248</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="43" t="n">
         <v>-42</v>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="44" t="n">
         <v>127.6</v>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="44" t="n">
         <v>6946</v>
       </c>
-      <c r="J8" s="44" t="n">
+      <c r="J8" s="45" t="n">
         <v>-552.7</v>
       </c>
-      <c r="K8" s="47" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="L8" s="48" t="n">
+      <c r="K8" s="48" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="L8" s="49" t="n">
         <v>-6.34</v>
       </c>
     </row>
@@ -4437,7 +4572,7 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4447,31 +4582,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="42" t="n">
         <v>573</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E9" s="42" t="n">
         <v>632</v>
       </c>
-      <c r="F9" s="42" t="n">
+      <c r="F9" s="43" t="n">
         <v>-59</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="43" t="n">
         <v>-548</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="44" t="n">
         <v>50.9</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="44" t="n">
         <v>1717.2</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="50" t="n">
         <v>5.5</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="48" t="n">
         <v>-6.14</v>
       </c>
-      <c r="L9" s="50" t="n">
+      <c r="L9" s="51" t="n">
         <v>-4.7</v>
       </c>
     </row>
@@ -4481,7 +4616,7 @@
           <t>IPARK현대산업개발</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
@@ -4491,31 +4626,31 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="43" t="n">
         <v>-37</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H10" s="44" t="n">
         <v>8.1</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="44" t="n">
         <v>444.4</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="45" t="n">
         <v>-3.4</v>
       </c>
-      <c r="K10" s="45" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L10" s="48" t="n">
+      <c r="K10" s="46" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L10" s="49" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4525,35 +4660,35 @@
           <t>S-Oil우</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr"/>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="41" t="n">
+      <c r="E11" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="43" t="n">
         <v>-30</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="44" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="44" t="n">
         <v>180.7</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="51" t="inlineStr"/>
-      <c r="L11" s="46" t="n">
+      <c r="K11" s="52" t="inlineStr"/>
+      <c r="L11" s="47" t="n">
         <v>-1.68</v>
       </c>
     </row>
@@ -4563,7 +4698,7 @@
           <t>코메론</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
@@ -4573,31 +4708,31 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="43" t="n">
         <v>-1</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="I12" s="43" t="n">
+      <c r="I12" s="44" t="n">
         <v>41.2</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J12" s="45" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K12" s="45" t="n">
+      <c r="K12" s="46" t="n">
         <v>0.89</v>
       </c>
-      <c r="L12" s="50" t="n">
+      <c r="L12" s="51" t="n">
         <v>-4.42</v>
       </c>
     </row>
@@ -4607,7 +4742,7 @@
           <t>아이앤씨</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4617,29 +4752,29 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D13" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="41" t="n">
+      <c r="E13" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="42" t="n">
+      <c r="F13" s="43" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="43" t="n">
         <v>-6</v>
       </c>
-      <c r="H13" s="43" t="inlineStr"/>
-      <c r="I13" s="43" t="n">
+      <c r="H13" s="44" t="inlineStr"/>
+      <c r="I13" s="44" t="n">
         <v>16.2</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="J13" s="50" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="45" t="n">
+      <c r="K13" s="46" t="n">
         <v>14.63</v>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="47" t="n">
         <v>-1.94</v>
       </c>
     </row>
@@ -4717,7 +4852,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="54" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -4727,111 +4862,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="53" t="inlineStr">
+      <c r="N3" s="54" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="55" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="54" t="inlineStr">
+      <c r="J4" s="55" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="55" t="inlineStr">
+      <c r="N4" s="56" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="40" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="40" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="40" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="40" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="40" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="40" t="inlineStr">
+      <c r="L5" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="40" t="inlineStr">
+      <c r="M5" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="40" t="inlineStr">
+      <c r="N5" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="40" t="inlineStr">
+      <c r="O5" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="40" t="inlineStr">
+      <c r="P5" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="40" t="inlineStr">
+      <c r="Q5" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -4846,12 +4981,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="43" t="n">
         <v>20011</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -4862,12 +4997,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="56" t="n">
+      <c r="H6" s="57" t="n">
         <v>-1162</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -4878,12 +5013,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="42" t="n">
+      <c r="M6" s="43" t="n">
         <v>28767</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -4894,12 +5029,12 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="Q6" s="56" t="n">
+      <c r="Q6" s="57" t="n">
         <v>-1230</v>
       </c>
     </row>
@@ -4912,12 +5047,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D7" s="43" t="n">
         <v>13300</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -4928,12 +5063,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="57" t="n">
         <v>-577</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -4944,12 +5079,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="42" t="n">
+      <c r="M7" s="43" t="n">
         <v>11284</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -4960,12 +5095,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q7" s="56" t="n">
+      <c r="Q7" s="57" t="n">
         <v>-929</v>
       </c>
     </row>
@@ -4978,12 +5113,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D8" s="43" t="n">
         <v>2759</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -4994,12 +5129,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="57" t="n">
         <v>-555</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -5010,12 +5145,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M8" s="42" t="n">
+      <c r="M8" s="43" t="n">
         <v>2370</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -5026,12 +5161,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q8" s="56" t="n">
+      <c r="Q8" s="57" t="n">
         <v>-678</v>
       </c>
     </row>
@@ -5044,12 +5179,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D9" s="43" t="n">
         <v>857</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -5060,12 +5195,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="57" t="n">
         <v>-506</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -5076,12 +5211,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="M9" s="42" t="n">
+      <c r="M9" s="43" t="n">
         <v>2370</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -5092,12 +5227,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="P9" s="57" t="inlineStr">
+      <c r="P9" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="56" t="n">
+      <c r="Q9" s="57" t="n">
         <v>-631</v>
       </c>
     </row>
@@ -5110,12 +5245,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="43" t="n">
         <v>835</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -5126,12 +5261,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G10" s="57" t="inlineStr">
+      <c r="G10" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="57" t="n">
         <v>-451</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -5142,12 +5277,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M10" s="42" t="n">
+      <c r="M10" s="43" t="n">
         <v>1800</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -5158,12 +5293,12 @@
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="Q10" s="56" t="n">
+      <c r="Q10" s="57" t="n">
         <v>-568</v>
       </c>
     </row>
@@ -5176,12 +5311,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="42" t="n">
+      <c r="D11" s="43" t="n">
         <v>816</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -5192,12 +5327,12 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="57" t="n">
         <v>-444</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -5208,12 +5343,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="M11" s="42" t="n">
+      <c r="M11" s="43" t="n">
         <v>1141</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -5224,12 +5359,12 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q11" s="56" t="n">
+      <c r="Q11" s="57" t="n">
         <v>-437</v>
       </c>
     </row>
@@ -5242,12 +5377,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D12" s="43" t="n">
         <v>740</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -5258,12 +5393,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G12" s="57" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="57" t="n">
         <v>-418</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -5274,12 +5409,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M12" s="42" t="n">
+      <c r="M12" s="43" t="n">
         <v>655</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -5290,12 +5425,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q12" s="56" t="n">
+      <c r="Q12" s="57" t="n">
         <v>-386</v>
       </c>
     </row>
@@ -5308,12 +5443,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D13" s="43" t="n">
         <v>673</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -5324,12 +5459,12 @@
           <t>LG</t>
         </is>
       </c>
-      <c r="G13" s="35" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="57" t="n">
         <v>-415</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -5340,12 +5475,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="42" t="n">
+      <c r="M13" s="43" t="n">
         <v>653</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -5356,12 +5491,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q13" s="56" t="n">
+      <c r="Q13" s="57" t="n">
         <v>-374</v>
       </c>
     </row>
@@ -5374,12 +5509,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D14" s="42" t="n">
+      <c r="D14" s="43" t="n">
         <v>632</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -5390,12 +5525,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="H14" s="56" t="n">
+      <c r="H14" s="57" t="n">
         <v>-368</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -5406,12 +5541,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="L14" s="57" t="inlineStr">
+      <c r="L14" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M14" s="42" t="n">
+      <c r="M14" s="43" t="n">
         <v>623</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -5422,12 +5557,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q14" s="56" t="n">
+      <c r="Q14" s="57" t="n">
         <v>-343</v>
       </c>
     </row>
@@ -5440,12 +5575,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="42" t="n">
+      <c r="D15" s="43" t="n">
         <v>583</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -5456,12 +5591,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H15" s="56" t="n">
+      <c r="H15" s="57" t="n">
         <v>-338</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -5472,12 +5607,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="M15" s="42" t="n">
+      <c r="M15" s="43" t="n">
         <v>567</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -5488,12 +5623,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="P15" s="35" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q15" s="56" t="n">
+      <c r="Q15" s="57" t="n">
         <v>-342</v>
       </c>
     </row>
@@ -5504,7 +5639,7 @@
           <t>F3 연기금</t>
         </is>
       </c>
-      <c r="E17" s="53" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
@@ -5514,111 +5649,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="53" t="inlineStr">
+      <c r="N17" s="54" t="inlineStr">
         <is>
           <t>주간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="56" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="54" t="inlineStr">
+      <c r="J18" s="55" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="N18" s="56" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="G19" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="40" t="inlineStr">
+      <c r="H19" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="40" t="inlineStr">
+      <c r="J19" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="40" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="40" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="40" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="40" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="40" t="inlineStr">
+      <c r="O19" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="40" t="inlineStr">
+      <c r="P19" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="40" t="inlineStr">
+      <c r="Q19" s="41" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5633,12 +5768,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D20" s="42" t="n">
+      <c r="D20" s="43" t="n">
         <v>817</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -5649,12 +5784,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="56" t="n">
+      <c r="H20" s="57" t="n">
         <v>-1831</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -5665,12 +5800,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="42" t="n">
+      <c r="M20" s="43" t="n">
         <v>1376</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -5681,12 +5816,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="56" t="n">
+      <c r="Q20" s="57" t="n">
         <v>-66116</v>
       </c>
     </row>
@@ -5699,12 +5834,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D21" s="43" t="n">
         <v>598</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -5715,12 +5850,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="56" t="n">
+      <c r="H21" s="57" t="n">
         <v>-924</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -5731,12 +5866,12 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="M21" s="42" t="n">
+      <c r="M21" s="43" t="n">
         <v>1250</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -5747,12 +5882,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="56" t="n">
+      <c r="Q21" s="57" t="n">
         <v>-57740</v>
       </c>
     </row>
@@ -5765,12 +5900,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="43" t="n">
         <v>435</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -5781,12 +5916,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G22" s="57" t="inlineStr">
+      <c r="G22" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H22" s="56" t="n">
+      <c r="H22" s="57" t="n">
         <v>-442</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -5797,12 +5932,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M22" s="42" t="n">
+      <c r="M22" s="43" t="n">
         <v>965</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -5813,12 +5948,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q22" s="56" t="n">
+      <c r="Q22" s="57" t="n">
         <v>-5018</v>
       </c>
     </row>
@@ -5831,12 +5966,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D23" s="42" t="n">
+      <c r="D23" s="43" t="n">
         <v>374</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -5847,12 +5982,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G23" s="57" t="inlineStr">
+      <c r="G23" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H23" s="56" t="n">
+      <c r="H23" s="57" t="n">
         <v>-393</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -5863,12 +5998,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L23" s="35" t="inlineStr">
+      <c r="L23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M23" s="42" t="n">
+      <c r="M23" s="43" t="n">
         <v>764</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -5879,12 +6014,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q23" s="56" t="n">
+      <c r="Q23" s="57" t="n">
         <v>-2464</v>
       </c>
     </row>
@@ -5897,12 +6032,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="42" t="n">
+      <c r="D24" s="43" t="n">
         <v>267</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -5913,12 +6048,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="H24" s="56" t="n">
+      <c r="H24" s="57" t="n">
         <v>-218</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -5929,12 +6064,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="42" t="n">
+      <c r="M24" s="43" t="n">
         <v>668</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -5945,12 +6080,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q24" s="56" t="n">
+      <c r="Q24" s="57" t="n">
         <v>-1769</v>
       </c>
     </row>
@@ -5963,12 +6098,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D25" s="42" t="n">
+      <c r="D25" s="43" t="n">
         <v>216</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -5979,12 +6114,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H25" s="56" t="n">
+      <c r="H25" s="57" t="n">
         <v>-203</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -5995,12 +6130,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M25" s="42" t="n">
+      <c r="M25" s="43" t="n">
         <v>590</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -6011,12 +6146,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q25" s="56" t="n">
+      <c r="Q25" s="57" t="n">
         <v>-1495</v>
       </c>
     </row>
@@ -6029,12 +6164,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D26" s="42" t="n">
+      <c r="D26" s="43" t="n">
         <v>186</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -6045,12 +6180,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H26" s="56" t="n">
+      <c r="H26" s="57" t="n">
         <v>-195</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -6061,12 +6196,12 @@
           <t>OCI홀딩스</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="M26" s="42" t="n">
+      <c r="M26" s="43" t="n">
         <v>507</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -6077,12 +6212,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q26" s="56" t="n">
+      <c r="Q26" s="57" t="n">
         <v>-1398</v>
       </c>
     </row>
@@ -6095,12 +6230,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="42" t="n">
+      <c r="D27" s="43" t="n">
         <v>172</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -6111,12 +6246,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G27" s="35" t="inlineStr">
+      <c r="G27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H27" s="56" t="n">
+      <c r="H27" s="57" t="n">
         <v>-188</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -6127,12 +6262,12 @@
           <t>레인보우로보틱스</t>
         </is>
       </c>
-      <c r="L27" s="35" t="inlineStr">
+      <c r="L27" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M27" s="42" t="n">
+      <c r="M27" s="43" t="n">
         <v>479</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -6143,12 +6278,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="P27" s="35" t="inlineStr">
+      <c r="P27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="56" t="n">
+      <c r="Q27" s="57" t="n">
         <v>-1222</v>
       </c>
     </row>
@@ -6161,12 +6296,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="42" t="n">
+      <c r="D28" s="43" t="n">
         <v>157</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -6177,12 +6312,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="56" t="n">
+      <c r="H28" s="57" t="n">
         <v>-184</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -6193,12 +6328,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L28" s="35" t="inlineStr">
+      <c r="L28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M28" s="42" t="n">
+      <c r="M28" s="43" t="n">
         <v>464</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -6209,12 +6344,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q28" s="56" t="n">
+      <c r="Q28" s="57" t="n">
         <v>-1048</v>
       </c>
     </row>
@@ -6227,12 +6362,12 @@
           <t>가온전선</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="42" t="n">
+      <c r="D29" s="43" t="n">
         <v>142</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -6243,12 +6378,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="G29" s="35" t="inlineStr">
+      <c r="G29" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H29" s="56" t="n">
+      <c r="H29" s="57" t="n">
         <v>-174</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -6259,12 +6394,12 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="M29" s="42" t="n">
+      <c r="M29" s="43" t="n">
         <v>441</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -6275,18 +6410,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
+      <c r="P29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q29" s="56" t="n">
+      <c r="Q29" s="57" t="n">
         <v>-951</v>
       </c>
     </row>
     <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="58" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치</t>
         </is>
@@ -6381,72 +6516,72 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>공매도 누적</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="G4" s="40" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H4" s="40" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="I4" s="40" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="J4" s="40" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
       </c>
-      <c r="L4" s="40" t="inlineStr">
+      <c r="L4" s="41" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="M4" s="40" t="inlineStr">
+      <c r="M4" s="41" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="N4" s="40" t="inlineStr">
+      <c r="N4" s="41" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="O4" s="40" t="inlineStr">
+      <c r="O4" s="41" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
       </c>
-      <c r="P4" s="40" t="inlineStr">
+      <c r="P4" s="41" t="inlineStr">
         <is>
           <t>잔고</t>
         </is>
@@ -6461,12 +6596,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="59" t="n">
+      <c r="D5" s="60" t="n">
         <v>8112</v>
       </c>
       <c r="F5" s="30" t="n">
@@ -6477,15 +6612,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="45" t="n">
         <v>12055.8</v>
       </c>
-      <c r="J5" s="60" t="n">
+      <c r="J5" s="61" t="n">
         <v>223759.5</v>
       </c>
       <c r="L5" s="30" t="n">
@@ -6496,15 +6631,15 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="N5" s="35" t="inlineStr">
+      <c r="N5" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="O5" s="61" t="n">
+      <c r="O5" s="62" t="n">
         <v>-4249.4</v>
       </c>
-      <c r="P5" s="60" t="n">
+      <c r="P5" s="61" t="n">
         <v>11541.9</v>
       </c>
     </row>
@@ -6517,12 +6652,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="60" t="n">
         <v>3338</v>
       </c>
       <c r="F6" s="30" t="n">
@@ -6533,15 +6668,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I6" s="44" t="n">
+      <c r="I6" s="45" t="n">
         <v>4301.7</v>
       </c>
-      <c r="J6" s="60" t="n">
+      <c r="J6" s="61" t="n">
         <v>240284.8</v>
       </c>
       <c r="L6" s="30" t="n">
@@ -6552,15 +6687,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="N6" s="35" t="inlineStr">
+      <c r="N6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O6" s="61" t="n">
+      <c r="O6" s="62" t="n">
         <v>-1010.4</v>
       </c>
-      <c r="P6" s="60" t="n">
+      <c r="P6" s="61" t="n">
         <v>36009</v>
       </c>
     </row>
@@ -6573,12 +6708,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="59" t="n">
+      <c r="D7" s="60" t="n">
         <v>1216</v>
       </c>
       <c r="F7" s="30" t="n">
@@ -6589,15 +6724,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="45" t="n">
         <v>2502.6</v>
       </c>
-      <c r="J7" s="60" t="n">
+      <c r="J7" s="61" t="n">
         <v>32891.8</v>
       </c>
       <c r="L7" s="30" t="n">
@@ -6608,15 +6743,15 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="N7" s="35" t="inlineStr">
+      <c r="N7" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="O7" s="61" t="n">
+      <c r="O7" s="62" t="n">
         <v>-1003</v>
       </c>
-      <c r="P7" s="60" t="n">
+      <c r="P7" s="61" t="n">
         <v>14504.2</v>
       </c>
     </row>
@@ -6629,12 +6764,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="59" t="n">
+      <c r="D8" s="60" t="n">
         <v>872</v>
       </c>
       <c r="F8" s="30" t="n">
@@ -6645,15 +6780,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I8" s="44" t="n">
+      <c r="I8" s="45" t="n">
         <v>2019.9</v>
       </c>
-      <c r="J8" s="60" t="n">
+      <c r="J8" s="61" t="n">
         <v>19469.6</v>
       </c>
       <c r="L8" s="30" t="n">
@@ -6664,15 +6799,15 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="N8" s="57" t="inlineStr">
+      <c r="N8" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="O8" s="61" t="n">
+      <c r="O8" s="62" t="n">
         <v>-783.9</v>
       </c>
-      <c r="P8" s="60" t="n">
+      <c r="P8" s="61" t="n">
         <v>11659.9</v>
       </c>
     </row>
@@ -6685,12 +6820,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="59" t="n">
+      <c r="D9" s="60" t="n">
         <v>868</v>
       </c>
       <c r="F9" s="30" t="n">
@@ -6701,15 +6836,15 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="H9" s="57" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I9" s="44" t="n">
+      <c r="I9" s="45" t="n">
         <v>1308.3</v>
       </c>
-      <c r="J9" s="60" t="n">
+      <c r="J9" s="61" t="n">
         <v>29404.2</v>
       </c>
       <c r="L9" s="30" t="n">
@@ -6720,15 +6855,15 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="N9" s="35" t="inlineStr">
+      <c r="N9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O9" s="61" t="n">
+      <c r="O9" s="62" t="n">
         <v>-750.2</v>
       </c>
-      <c r="P9" s="60" t="n">
+      <c r="P9" s="61" t="n">
         <v>9333.9</v>
       </c>
     </row>
@@ -6741,8 +6876,8 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr"/>
-      <c r="D10" s="59" t="n">
+      <c r="C10" s="34" t="inlineStr"/>
+      <c r="D10" s="60" t="n">
         <v>868</v>
       </c>
       <c r="F10" s="30" t="n">
@@ -6753,15 +6888,15 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="H10" s="35" t="inlineStr">
+      <c r="H10" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I10" s="44" t="n">
+      <c r="I10" s="45" t="n">
         <v>972</v>
       </c>
-      <c r="J10" s="60" t="n">
+      <c r="J10" s="61" t="n">
         <v>6222.6</v>
       </c>
       <c r="L10" s="30" t="n">
@@ -6772,15 +6907,15 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="N10" s="35" t="inlineStr">
+      <c r="N10" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="O10" s="61" t="n">
+      <c r="O10" s="62" t="n">
         <v>-706.3</v>
       </c>
-      <c r="P10" s="60" t="n">
+      <c r="P10" s="61" t="n">
         <v>13946.5</v>
       </c>
     </row>
@@ -6793,12 +6928,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="59" t="n">
+      <c r="D11" s="60" t="n">
         <v>709</v>
       </c>
       <c r="F11" s="30" t="n">
@@ -6809,15 +6944,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="H11" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I11" s="44" t="n">
+      <c r="I11" s="45" t="n">
         <v>963.8</v>
       </c>
-      <c r="J11" s="60" t="n">
+      <c r="J11" s="61" t="n">
         <v>43511.4</v>
       </c>
       <c r="L11" s="30" t="n">
@@ -6828,15 +6963,15 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="N11" s="35" t="inlineStr">
+      <c r="N11" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="O11" s="61" t="n">
+      <c r="O11" s="62" t="n">
         <v>-667.1</v>
       </c>
-      <c r="P11" s="60" t="n">
+      <c r="P11" s="61" t="n">
         <v>8138.3</v>
       </c>
     </row>
@@ -6849,12 +6984,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="59" t="n">
+      <c r="D12" s="60" t="n">
         <v>635</v>
       </c>
       <c r="F12" s="30" t="n">
@@ -6865,15 +7000,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I12" s="44" t="n">
+      <c r="I12" s="45" t="n">
         <v>819.1</v>
       </c>
-      <c r="J12" s="60" t="n">
+      <c r="J12" s="61" t="n">
         <v>15407.3</v>
       </c>
       <c r="L12" s="30" t="n">
@@ -6884,15 +7019,15 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="N12" s="35" t="inlineStr">
+      <c r="N12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="O12" s="61" t="n">
+      <c r="O12" s="62" t="n">
         <v>-608.6</v>
       </c>
-      <c r="P12" s="60" t="n">
+      <c r="P12" s="61" t="n">
         <v>7482.8</v>
       </c>
     </row>
@@ -6905,12 +7040,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="59" t="n">
+      <c r="D13" s="60" t="n">
         <v>569</v>
       </c>
       <c r="F13" s="30" t="n">
@@ -6921,15 +7056,15 @@
           <t>한전기술</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="I13" s="44" t="n">
+      <c r="I13" s="45" t="n">
         <v>787</v>
       </c>
-      <c r="J13" s="60" t="n">
+      <c r="J13" s="61" t="n">
         <v>3588.6</v>
       </c>
       <c r="L13" s="30" t="n">
@@ -6940,15 +7075,15 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="N13" s="35" t="inlineStr">
+      <c r="N13" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="O13" s="61" t="n">
+      <c r="O13" s="62" t="n">
         <v>-575.6</v>
       </c>
-      <c r="P13" s="60" t="n">
+      <c r="P13" s="61" t="n">
         <v>4333.9</v>
       </c>
     </row>
@@ -6961,12 +7096,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D14" s="59" t="n">
+      <c r="D14" s="60" t="n">
         <v>558</v>
       </c>
       <c r="F14" s="30" t="n">
@@ -6977,15 +7112,15 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I14" s="44" t="n">
+      <c r="I14" s="45" t="n">
         <v>707.2</v>
       </c>
-      <c r="J14" s="60" t="n">
+      <c r="J14" s="61" t="n">
         <v>8765.6</v>
       </c>
       <c r="L14" s="30" t="n">
@@ -6996,21 +7131,21 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="N14" s="35" t="inlineStr">
+      <c r="N14" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="O14" s="61" t="n">
+      <c r="O14" s="62" t="n">
         <v>-552.7</v>
       </c>
-      <c r="P14" s="60" t="n">
+      <c r="P14" s="61" t="n">
         <v>6946</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=주초 대비 최신 잔고</t>
         </is>
@@ -7027,4 +7162,1303 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
+    <col width="8.199999999999999" customWidth="1" style="15" min="2" max="2"/>
+    <col width="8.199999999999999" customWidth="1" style="15" min="3" max="3"/>
+    <col width="8.199999999999999" customWidth="1" style="15" min="4" max="4"/>
+    <col width="8.199999999999999" customWidth="1" style="15" min="5" max="5"/>
+    <col width="9.5" customWidth="1" style="15" min="6" max="6"/>
+    <col width="9.5" customWidth="1" style="15" min="7" max="7"/>
+    <col width="10" customWidth="1" style="15" min="8" max="8"/>
+    <col width="9.5" customWidth="1" style="15" min="9" max="9"/>
+    <col width="9.5" customWidth="1" style="15" min="10" max="10"/>
+    <col width="9.5" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.5" customWidth="1" style="15" min="12" max="12"/>
+    <col width="9.5" customWidth="1" style="15" min="13" max="13"/>
+    <col width="11.5" customWidth="1" style="15" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1" s="15">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>섹터x수급</t>
+        </is>
+      </c>
+      <c r="K1" s="25" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="L1" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>섹터 x 수급 매트릭스</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>가격 %, 수급 억원</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>외인</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>기관(합)</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>외인+기관</t>
+        </is>
+      </c>
+      <c r="I4" s="41" t="inlineStr">
+        <is>
+          <t>연기금</t>
+        </is>
+      </c>
+      <c r="J4" s="41" t="inlineStr">
+        <is>
+          <t>금융투자</t>
+        </is>
+      </c>
+      <c r="K4" s="41" t="inlineStr">
+        <is>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="L4" s="41" t="inlineStr">
+        <is>
+          <t>투신(사모)</t>
+        </is>
+      </c>
+      <c r="M4" s="41" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+      <c r="N4" s="41" t="inlineStr">
+        <is>
+          <t>신호</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="C5" s="64" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="D5" s="63" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="E5" s="63" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="F5" s="65" t="n">
+        <v>808</v>
+      </c>
+      <c r="G5" s="65" t="n">
+        <v>3180</v>
+      </c>
+      <c r="H5" s="65" t="n">
+        <v>3988</v>
+      </c>
+      <c r="I5" s="65" t="n">
+        <v>977</v>
+      </c>
+      <c r="J5" s="65" t="n">
+        <v>1003</v>
+      </c>
+      <c r="K5" s="65" t="n">
+        <v>138</v>
+      </c>
+      <c r="L5" s="65" t="n">
+        <v>1052</v>
+      </c>
+      <c r="M5" s="66" t="n">
+        <v>-3977</v>
+      </c>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="C6" s="63" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="D6" s="63" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="E6" s="63" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="F6" s="66" t="n">
+        <v>-97</v>
+      </c>
+      <c r="G6" s="65" t="n">
+        <v>1911</v>
+      </c>
+      <c r="H6" s="65" t="n">
+        <v>1814</v>
+      </c>
+      <c r="I6" s="65" t="n">
+        <v>499</v>
+      </c>
+      <c r="J6" s="65" t="n">
+        <v>367</v>
+      </c>
+      <c r="K6" s="65" t="n">
+        <v>65</v>
+      </c>
+      <c r="L6" s="65" t="n">
+        <v>977</v>
+      </c>
+      <c r="M6" s="66" t="n">
+        <v>-2131</v>
+      </c>
+      <c r="N6" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="B7" s="63" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="C7" s="64" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="D7" s="63" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="E7" s="63" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F7" s="65" t="n">
+        <v>27507</v>
+      </c>
+      <c r="G7" s="65" t="n">
+        <v>35068</v>
+      </c>
+      <c r="H7" s="65" t="n">
+        <v>62575</v>
+      </c>
+      <c r="I7" s="66" t="n">
+        <v>-2425</v>
+      </c>
+      <c r="J7" s="65" t="n">
+        <v>26878</v>
+      </c>
+      <c r="K7" s="66" t="n">
+        <v>-281</v>
+      </c>
+      <c r="L7" s="65" t="n">
+        <v>10927</v>
+      </c>
+      <c r="M7" s="66" t="n">
+        <v>-113041</v>
+      </c>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="B8" s="63" t="n">
+        <v>77.61</v>
+      </c>
+      <c r="C8" s="64" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="D8" s="63" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="E8" s="63" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F8" s="65" t="n">
+        <v>27339</v>
+      </c>
+      <c r="G8" s="65" t="n">
+        <v>35171</v>
+      </c>
+      <c r="H8" s="65" t="n">
+        <v>62510</v>
+      </c>
+      <c r="I8" s="66" t="n">
+        <v>-3535</v>
+      </c>
+      <c r="J8" s="65" t="n">
+        <v>31614</v>
+      </c>
+      <c r="K8" s="66" t="n">
+        <v>-435</v>
+      </c>
+      <c r="L8" s="65" t="n">
+        <v>7630</v>
+      </c>
+      <c r="M8" s="66" t="n">
+        <v>-113470</v>
+      </c>
+      <c r="N8" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>전기·가스</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>-22.38</v>
+      </c>
+      <c r="C9" s="64" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="D9" s="64" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="E9" s="63" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="F9" s="66" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G9" s="65" t="n">
+        <v>406</v>
+      </c>
+      <c r="H9" s="65" t="n">
+        <v>322</v>
+      </c>
+      <c r="I9" s="65" t="n">
+        <v>127</v>
+      </c>
+      <c r="J9" s="65" t="n">
+        <v>276</v>
+      </c>
+      <c r="K9" s="65" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" s="66" t="n">
+        <v>-19</v>
+      </c>
+      <c r="M9" s="66" t="n">
+        <v>-326</v>
+      </c>
+      <c r="N9" s="67" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="B10" s="63" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="C10" s="63" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D10" s="63" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="E10" s="63" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F10" s="65" t="n">
+        <v>37</v>
+      </c>
+      <c r="G10" s="65" t="n">
+        <v>767</v>
+      </c>
+      <c r="H10" s="65" t="n">
+        <v>804</v>
+      </c>
+      <c r="I10" s="65" t="n">
+        <v>107</v>
+      </c>
+      <c r="J10" s="65" t="n">
+        <v>344</v>
+      </c>
+      <c r="K10" s="66" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L10" s="65" t="n">
+        <v>324</v>
+      </c>
+      <c r="M10" s="66" t="n">
+        <v>-775</v>
+      </c>
+      <c r="N10" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="C11" s="63" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="D11" s="63" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E11" s="63" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F11" s="65" t="n">
+        <v>1017</v>
+      </c>
+      <c r="G11" s="66" t="n">
+        <v>-599</v>
+      </c>
+      <c r="H11" s="65" t="n">
+        <v>418</v>
+      </c>
+      <c r="I11" s="65" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="65" t="n">
+        <v>225</v>
+      </c>
+      <c r="K11" s="66" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L11" s="66" t="n">
+        <v>-806</v>
+      </c>
+      <c r="M11" s="66" t="n">
+        <v>-427</v>
+      </c>
+      <c r="N11" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="C12" s="64" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="D12" s="63" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E12" s="63" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F12" s="65" t="n">
+        <v>754</v>
+      </c>
+      <c r="G12" s="65" t="n">
+        <v>4602</v>
+      </c>
+      <c r="H12" s="65" t="n">
+        <v>5357</v>
+      </c>
+      <c r="I12" s="65" t="n">
+        <v>855</v>
+      </c>
+      <c r="J12" s="65" t="n">
+        <v>3254</v>
+      </c>
+      <c r="K12" s="65" t="n">
+        <v>89</v>
+      </c>
+      <c r="L12" s="66" t="n">
+        <v>-205</v>
+      </c>
+      <c r="M12" s="66" t="n">
+        <v>-5523</v>
+      </c>
+      <c r="N12" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="C13" s="64" t="n">
+        <v>-12.45</v>
+      </c>
+      <c r="D13" s="63" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E13" s="63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F13" s="66" t="n">
+        <v>-394</v>
+      </c>
+      <c r="G13" s="65" t="n">
+        <v>605</v>
+      </c>
+      <c r="H13" s="65" t="n">
+        <v>211</v>
+      </c>
+      <c r="I13" s="66" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J13" s="65" t="n">
+        <v>533</v>
+      </c>
+      <c r="K13" s="65" t="n">
+        <v>32</v>
+      </c>
+      <c r="L13" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="M13" s="66" t="n">
+        <v>-606</v>
+      </c>
+      <c r="N13" s="55" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C14" s="64" t="n">
+        <v>-23.98</v>
+      </c>
+      <c r="D14" s="64" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="E14" s="63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F14" s="66" t="n">
+        <v>-650</v>
+      </c>
+      <c r="G14" s="66" t="n">
+        <v>-441</v>
+      </c>
+      <c r="H14" s="66" t="n">
+        <v>-1091</v>
+      </c>
+      <c r="I14" s="66" t="n">
+        <v>-1204</v>
+      </c>
+      <c r="J14" s="65" t="n">
+        <v>2489</v>
+      </c>
+      <c r="K14" s="66" t="n">
+        <v>-106</v>
+      </c>
+      <c r="L14" s="66" t="n">
+        <v>-1588</v>
+      </c>
+      <c r="M14" s="65" t="n">
+        <v>1058</v>
+      </c>
+      <c r="N14" s="30" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="C15" s="64" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="D15" s="63" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E15" s="63" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F15" s="66" t="n">
+        <v>-649</v>
+      </c>
+      <c r="G15" s="65" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" s="66" t="n">
+        <v>-482</v>
+      </c>
+      <c r="I15" s="66" t="n">
+        <v>-165</v>
+      </c>
+      <c r="J15" s="65" t="n">
+        <v>433</v>
+      </c>
+      <c r="K15" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="66" t="n">
+        <v>-101</v>
+      </c>
+      <c r="M15" s="65" t="n">
+        <v>373</v>
+      </c>
+      <c r="N15" s="69" t="inlineStr">
+        <is>
+          <t>수급이탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>증권</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="C16" s="64" t="n">
+        <v>-23.89</v>
+      </c>
+      <c r="D16" s="64" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E16" s="63" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F16" s="66" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G16" s="65" t="n">
+        <v>212</v>
+      </c>
+      <c r="H16" s="65" t="n">
+        <v>191</v>
+      </c>
+      <c r="I16" s="66" t="n">
+        <v>-42</v>
+      </c>
+      <c r="J16" s="65" t="n">
+        <v>240</v>
+      </c>
+      <c r="K16" s="66" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L16" s="65" t="n">
+        <v>22</v>
+      </c>
+      <c r="M16" s="66" t="n">
+        <v>-184</v>
+      </c>
+      <c r="N16" s="30" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="C17" s="64" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="D17" s="63" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E17" s="63" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F17" s="66" t="n">
+        <v>-88</v>
+      </c>
+      <c r="G17" s="65" t="n">
+        <v>41</v>
+      </c>
+      <c r="H17" s="66" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I17" s="65" t="n">
+        <v>63</v>
+      </c>
+      <c r="J17" s="66" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K17" s="65" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="66" t="n">
+        <v>-25</v>
+      </c>
+      <c r="M17" s="65" t="n">
+        <v>42</v>
+      </c>
+      <c r="N17" s="69" t="inlineStr">
+        <is>
+          <t>수급이탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="n">
+        <v>-11.74</v>
+      </c>
+      <c r="C18" s="63" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="D18" s="64" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="E18" s="64" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F18" s="66" t="n">
+        <v>-440</v>
+      </c>
+      <c r="G18" s="66" t="n">
+        <v>-697</v>
+      </c>
+      <c r="H18" s="66" t="n">
+        <v>-1137</v>
+      </c>
+      <c r="I18" s="66" t="n">
+        <v>-576</v>
+      </c>
+      <c r="J18" s="65" t="n">
+        <v>334</v>
+      </c>
+      <c r="K18" s="66" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L18" s="66" t="n">
+        <v>-359</v>
+      </c>
+      <c r="M18" s="65" t="n">
+        <v>826</v>
+      </c>
+      <c r="N18" s="56" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="B19" s="63" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="C19" s="64" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="D19" s="63" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="E19" s="64" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="F19" s="66" t="n">
+        <v>-264</v>
+      </c>
+      <c r="G19" s="65" t="n">
+        <v>365</v>
+      </c>
+      <c r="H19" s="65" t="n">
+        <v>101</v>
+      </c>
+      <c r="I19" s="65" t="n">
+        <v>150</v>
+      </c>
+      <c r="J19" s="65" t="n">
+        <v>339</v>
+      </c>
+      <c r="K19" s="66" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L19" s="66" t="n">
+        <v>-115</v>
+      </c>
+      <c r="M19" s="66" t="n">
+        <v>-115</v>
+      </c>
+      <c r="N19" s="30" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="C20" s="63" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="D20" s="64" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E20" s="64" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F20" s="65" t="n">
+        <v>628</v>
+      </c>
+      <c r="G20" s="66" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H20" s="65" t="n">
+        <v>585</v>
+      </c>
+      <c r="I20" s="66" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J20" s="65" t="n">
+        <v>17</v>
+      </c>
+      <c r="K20" s="66" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L20" s="66" t="n">
+        <v>-58</v>
+      </c>
+      <c r="M20" s="66" t="n">
+        <v>-565</v>
+      </c>
+      <c r="N20" s="30" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>통신</t>
+        </is>
+      </c>
+      <c r="B21" s="63" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="C21" s="64" t="n">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="D21" s="63" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E21" s="64" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="F21" s="65" t="n">
+        <v>68</v>
+      </c>
+      <c r="G21" s="65" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" s="65" t="n">
+        <v>93</v>
+      </c>
+      <c r="I21" s="65" t="n">
+        <v>29</v>
+      </c>
+      <c r="J21" s="65" t="n">
+        <v>309</v>
+      </c>
+      <c r="K21" s="66" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L21" s="66" t="n">
+        <v>-282</v>
+      </c>
+      <c r="M21" s="66" t="n">
+        <v>-77</v>
+      </c>
+      <c r="N21" s="30" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="C22" s="63" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="D22" s="63" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E22" s="64" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="F22" s="65" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" s="66" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H22" s="65" t="n">
+        <v>37</v>
+      </c>
+      <c r="I22" s="65" t="n">
+        <v>37</v>
+      </c>
+      <c r="J22" s="65" t="n">
+        <v>33</v>
+      </c>
+      <c r="K22" s="66" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L22" s="66" t="n">
+        <v>-64</v>
+      </c>
+      <c r="M22" s="66" t="n">
+        <v>-36</v>
+      </c>
+      <c r="N22" s="30" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>비금속</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="C23" s="63" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D23" s="63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E23" s="64" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="F23" s="65" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="66" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H23" s="66" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I23" s="66" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J23" s="65" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" s="66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L23" s="66" t="n">
+        <v>-12</v>
+      </c>
+      <c r="M23" s="65" t="n">
+        <v>14</v>
+      </c>
+      <c r="N23" s="30" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>-18.72</v>
+      </c>
+      <c r="C24" s="63" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="D24" s="63" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E24" s="64" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="F24" s="66" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G24" s="65" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="66" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>오락·문화</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>-41.39</v>
+      </c>
+      <c r="C25" s="64" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="D25" s="64" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="E25" s="64" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="F25" s="66" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G25" s="66" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H25" s="66" t="n">
+        <v>-175</v>
+      </c>
+      <c r="I25" s="66" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="65" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="66" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L25" s="66" t="n">
+        <v>-31</v>
+      </c>
+      <c r="M25" s="65" t="n">
+        <v>181</v>
+      </c>
+      <c r="N25" s="56" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>섬유·의류</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="C26" s="64" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="D26" s="64" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="E26" s="64" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="F26" s="66" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G26" s="66" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H26" s="66" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I26" s="65" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="66" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L26" s="66" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M26" s="65" t="n">
+        <v>27</v>
+      </c>
+      <c r="N26" s="56" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="C27" s="64" t="n">
+        <v>-17.99</v>
+      </c>
+      <c r="D27" s="64" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="E27" s="64" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="F27" s="66" t="n">
+        <v>-667</v>
+      </c>
+      <c r="G27" s="66" t="n">
+        <v>-1073</v>
+      </c>
+      <c r="H27" s="66" t="n">
+        <v>-1740</v>
+      </c>
+      <c r="I27" s="66" t="n">
+        <v>-770</v>
+      </c>
+      <c r="J27" s="65" t="n">
+        <v>400</v>
+      </c>
+      <c r="K27" s="66" t="n">
+        <v>-94</v>
+      </c>
+      <c r="L27" s="66" t="n">
+        <v>-597</v>
+      </c>
+      <c r="M27" s="65" t="n">
+        <v>1755</v>
+      </c>
+      <c r="N27" s="56" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="C28" s="64" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="D28" s="64" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="E28" s="64" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="F28" s="66" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G28" s="66" t="n">
+        <v>-1533</v>
+      </c>
+      <c r="H28" s="66" t="n">
+        <v>-1668</v>
+      </c>
+      <c r="I28" s="66" t="n">
+        <v>-229</v>
+      </c>
+      <c r="J28" s="65" t="n">
+        <v>235</v>
+      </c>
+      <c r="K28" s="66" t="n">
+        <v>-65</v>
+      </c>
+      <c r="L28" s="66" t="n">
+        <v>-1441</v>
+      </c>
+      <c r="M28" s="65" t="n">
+        <v>1636</v>
+      </c>
+      <c r="N28" s="56" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>가격추세=YTD·3M·1M·1W(%) 중 3개 이상 동일 방향 · 핵심수급(외인+기관)=주간 누적 · KIS 업종(KRX 산업분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>동반강세=가격강세+수급유입 · 수급이탈=가격강세+수급이탈 · 수급유입=가격약세+수급유입 · 동반약세=가격약세+수급이탈 · 공란=혼조(가격방향 불명확) · 데이터부족=일부 기간 결측</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:N28"/>
+  <mergeCells count="4">
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A30:N30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E28">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="0019B6C9"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/weekly_briefing.xlsx
+++ b/public/weekly_briefing.xlsx
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B102" s="31" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C102" s="31" t="inlineStr">
@@ -3297,102 +3297,102 @@
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F102" s="29" t="n">
-        <v>24.45</v>
+        <v>4.86</v>
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
+          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="31" customHeight="1" s="15">
       <c r="A103" s="31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B103" s="31" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D103" s="34" t="inlineStr">
         <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F103" s="29" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="15">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B104" s="31" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F103" s="29" t="n">
-        <v>23.48</v>
-      </c>
-      <c r="G103" s="17" t="inlineStr">
-        <is>
-          <t>차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="31" customHeight="1" s="15">
-      <c r="A104" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B104" s="31" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="C104" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D104" s="34" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F104" s="29" t="n">
-        <v>15.16</v>
+        <v>40.33</v>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="31" customHeight="1" s="15">
       <c r="A105" s="31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B105" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D105" s="34" t="inlineStr">
@@ -3402,27 +3402,27 @@
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F105" s="29" t="n">
-        <v>11.43</v>
+        <v>35.16</v>
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
+          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="31" customHeight="1" s="15">
       <c r="A106" s="31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B106" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C106" s="31" t="inlineStr">
@@ -3432,20 +3432,20 @@
       </c>
       <c r="D106" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F106" s="29" t="n">
-        <v>4.86</v>
+        <v>32.47</v>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>AI 메모리 수요 확대 기대감과 외국인·기관의 대규모 순매수세 유입.</t>
+          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
         </is>
       </c>
     </row>
@@ -3457,30 +3457,30 @@
       </c>
       <c r="B107" s="31" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D107" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F107" s="29" t="n">
-        <v>40.33</v>
+        <v>33.15</v>
       </c>
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>차세대 광통신 부품 국산화 국책 사업 수행기관 선정.</t>
+          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
         </is>
       </c>
     </row>
@@ -3492,42 +3492,42 @@
       </c>
       <c r="B108" s="31" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D108" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F108" s="29" t="n">
-        <v>42.89</v>
+        <v>29.56</v>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 추진 기대감에 따른 수주 기대.</t>
+          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="31" customHeight="1" s="15">
       <c r="A109" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B109" s="31" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
@@ -3546,33 +3546,33 @@
         </is>
       </c>
       <c r="F109" s="29" t="n">
-        <v>35.16</v>
+        <v>119.31</v>
       </c>
       <c r="G109" s="17" t="inlineStr">
         <is>
-          <t>한미 원전 협력 가시화 및 대미 투자 프로젝트 내 원전 건설 기대.</t>
+          <t>범LG가 구본호 회장 측의 최대주주 등극 소식에 따른 경영권 변화 기대.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="31" customHeight="1" s="15">
       <c r="A110" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B110" s="31" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D110" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -3581,151 +3581,152 @@
         </is>
       </c>
       <c r="F110" s="29" t="n">
-        <v>32.47</v>
+        <v>37.43</v>
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>미국 내 대형 원전 8기 건설 협의 소식에 따른 수주 기대.</t>
+          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="31" customHeight="1" s="15">
       <c r="A111" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B111" s="31" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D111" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F111" s="29" t="n">
-        <v>29.56</v>
+        <v>35.74</v>
       </c>
       <c r="G111" s="17" t="inlineStr">
         <is>
-          <t>임신중지약 미프진의 연내 출시 기대감 및 탈모 치료제 성장.</t>
+          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="15">
       <c r="A112" s="31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B112" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="C112" s="31" t="inlineStr">
         <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F112" s="29" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="31" customHeight="1" s="15">
+      <c r="A113" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="C113" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D113" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F113" s="29" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>항암 후보물질 비교 평가 1차 연구 결과 발표에 따른 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="44.5" customHeight="1" s="15">
+      <c r="A114" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀 (2회)</t>
+        </is>
+      </c>
+      <c r="C114" s="31" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F112" s="29" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>가덕도 신공항 기본설계 제출 및 미국 원전 건설 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1" s="15">
-      <c r="A113" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B113" s="31" t="inlineStr">
-        <is>
-          <t>머큐리</t>
-        </is>
-      </c>
-      <c r="C113" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D113" s="34" t="inlineStr">
+      <c r="D114" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E113" s="14" t="inlineStr">
+      <c r="E114" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F113" s="29" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="G113" s="17" t="inlineStr">
-        <is>
-          <t>미국 버라이즌-코닝 광섬유 공급 계약에 따른 인프라 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="31" customHeight="1" s="15">
-      <c r="A114" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>페니트리움바이오</t>
-        </is>
-      </c>
-      <c r="C114" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D114" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
       <c r="F114" s="29" t="n">
-        <v>26.84</v>
+        <v>24.45</v>
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>항암 후보물질 비교 평가 1차 연구 결과 발표에 따른 기대감.</t>
+          <t>미국 AI 데이터센터용 연료전지 대규모 공급 계약 체결.
+(09-07) 미국 AI 데이터센터용 5,000억원대 대규모 연료전지 공급 계약 체결.</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3738,12 @@
       </c>
       <c r="B115" s="31" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D115" s="34" t="inlineStr">
@@ -3756,11 +3757,11 @@
         </is>
       </c>
       <c r="F115" s="29" t="n">
-        <v>119.31</v>
+        <v>24.41</v>
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>범LG가 구본호 회장 측의 최대주주 등극 소식에 따른 경영권 변화 기대.</t>
+          <t>캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3773,7 @@
       </c>
       <c r="B116" s="31" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C116" s="31" t="inlineStr">
@@ -3782,7 +3783,7 @@
       </c>
       <c r="D116" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
@@ -3791,11 +3792,11 @@
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>35.74</v>
+        <v>24.23</v>
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 투자 및 AI 광통신 관련주로 시장 관심 집중.</t>
+          <t>미국 광통신 시장 대규모 공급 계약에 따른 동반 수혜 기대.</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3808,7 @@
       </c>
       <c r="B117" s="31" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>에스엠벡셀</t>
         </is>
       </c>
       <c r="C117" s="31" t="inlineStr">
@@ -3817,125 +3818,128 @@
       </c>
       <c r="D117" s="34" t="inlineStr">
         <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F117" s="29" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="44.5" customHeight="1" s="15">
+      <c r="A118" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B118" s="31" t="inlineStr">
+        <is>
+          <t>DB하이텍 (2회)</t>
+        </is>
+      </c>
+      <c r="C118" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D118" s="34" t="inlineStr">
+        <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E117" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F117" s="29" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="G117" s="17" t="inlineStr">
-        <is>
-          <t>AI 데이터센터 전력원으로서 연료전지 수요 급증에 따른 수혜.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="31" customHeight="1" s="15">
-      <c r="A118" s="31" t="inlineStr">
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F118" s="29" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>파운드리 가격 상승 전망에 따른 실적 개선 기대감.
+(09-07) 차세대 전력반도체 양산 체제 구축 및 AI 모델 공개에 따른 파운드리 수혜 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="44.5" customHeight="1" s="15">
+      <c r="A119" s="31" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B118" s="31" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="C118" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D118" s="34" t="inlineStr">
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 (2회)</t>
+        </is>
+      </c>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D119" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="F119" s="29" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="G119" s="17" t="inlineStr">
+        <is>
+          <t>미국 AI 전력난에 따른 원전 및 가스터빈 수주 기대감 지속.
+(09-07) 원전 및 가스터빈 수주 기대감과 SMR 생산거점 육성 이슈 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="44.5" customHeight="1" s="15">
+      <c r="A120" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>SK하이닉스 (2회)</t>
+        </is>
+      </c>
+      <c r="C120" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F118" s="29" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="G118" s="17" t="inlineStr">
-        <is>
-          <t>미국 광통신 시장 대규모 공급 계약에 따른 동반 수혜 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="31" customHeight="1" s="15">
-      <c r="A119" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B119" s="31" t="inlineStr">
-        <is>
-          <t>에스엠벡셀</t>
-        </is>
-      </c>
-      <c r="C119" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D119" s="34" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E119" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F119" s="29" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="G119" s="17" t="inlineStr">
-        <is>
-          <t>미국 글로벌 자동차 기업과 차세대 LMR 배터리 기술 협력.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="31" customHeight="1" s="15">
-      <c r="A120" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B120" s="31" t="inlineStr">
-        <is>
-          <t>가온전선</t>
-        </is>
-      </c>
-      <c r="C120" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D120" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F120" s="29" t="n">
-        <v>24.41</v>
+        <v>11.43</v>
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>캐나다 공공 전력망 시장 첫 진출 및 북미 사업 확대 가시화.</t>
+          <t>AI 반도체 및 HBM 수요 확대에 따른 외국인·기관 매수세 집중.
+(09-07) AI 메모리 수요 확대 및 반도체 업황 회복 기대감에 따른 외국인·기관 매수세 유입.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3986,7 @@
       </c>
       <c r="B122" s="31" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C122" s="31" t="inlineStr">
@@ -3992,7 +3996,7 @@
       </c>
       <c r="D122" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -4001,222 +4005,83 @@
         </is>
       </c>
       <c r="F122" s="29" t="n">
-        <v>24.45</v>
+        <v>1.03</v>
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터용 연료전지 대규모 공급 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="15">
-      <c r="A123" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B123" s="31" t="inlineStr">
-        <is>
-          <t>DB하이텍</t>
-        </is>
-      </c>
-      <c r="C123" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D123" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E123" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F123" s="29" t="n">
-        <v>23.48</v>
-      </c>
-      <c r="G123" s="17" t="inlineStr">
-        <is>
-          <t>파운드리 가격 상승 전망에 따른 실적 개선 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="31" customHeight="1" s="15">
-      <c r="A124" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B124" s="31" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="C124" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D124" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F124" s="29" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>AI 반도체 및 HBM 수요 확대에 따른 외국인·기관 매수세 집중.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="31" customHeight="1" s="15">
-      <c r="A125" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B125" s="31" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="C125" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D125" s="34" t="inlineStr">
-        <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="E125" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F125" s="29" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="G125" s="17" t="inlineStr">
-        <is>
-          <t>미국 AI 전력난에 따른 원전 및 가스터빈 수주 기대감 지속.</t>
+          <t>태국 왕립해군 차세대 호위함 사업 우선협상대상자 선정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>다음 주 프리뷰</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr"/>
+      <c r="F124" s="3" t="inlineStr"/>
+      <c r="G124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="15">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 물가 지표가 예상치를 하회하면 금리 인하 기대감으로 기술주 중심의 상승세 지속</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="15">
-      <c r="A126" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B126" s="31" t="inlineStr">
-        <is>
-          <t>한화오션</t>
-        </is>
-      </c>
-      <c r="C126" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D126" s="34" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F126" s="29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>태국 왕립해군 차세대 호위함 사업 우선협상대상자 선정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>다음 주 프리뷰</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr"/>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="3" t="inlineStr"/>
-      <c r="F128" s="3" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr"/>
-      <c r="H128" s="3" t="inlineStr"/>
-      <c r="I128" s="3" t="inlineStr"/>
-      <c r="J128" s="3" t="inlineStr"/>
-      <c r="K128" s="3" t="inlineStr"/>
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 물가 지표가 예상치를 상회하면 금리 인상 우려 재점화로 인한 외국인 수급 이탈 및 지수 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="15">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>- 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI)의 전월 대비 등락폭</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="15">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 생산자물가지수(PPI)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="15">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>- 미국 물가 지표가 예상치를 하회하면 금리 인하 기대감으로 기술주 중심의 상승세 지속</t>
+          <t>- 미국 소비자물가지수(CPI)</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="15">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t>- 미국 물가 지표가 예상치를 상회하면 금리 인상 우려 재점화로 인한 외국인 수급 이탈 및 지수 조정</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="15">
-      <c r="A131" s="17" t="inlineStr">
-        <is>
-          <t>- 10일 발표되는 미국 생산자물가지수(PPI)와 11일 소비자물가지수(CPI)의 전월 대비 등락폭</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="15">
-      <c r="A132" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 생산자물가지수(PPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="15">
-      <c r="A133" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 소비자물가지수(CPI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15" customHeight="1" s="15">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
           <t>- 한국 무역수지</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="64">
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="G105:K105"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A73:E73"/>
@@ -4230,9 +4095,7 @@
     <mergeCell ref="G120:K120"/>
     <mergeCell ref="G98:K98"/>
     <mergeCell ref="G107:K107"/>
-    <mergeCell ref="G126:K126"/>
     <mergeCell ref="A94:K94"/>
-    <mergeCell ref="A132:K132"/>
     <mergeCell ref="G70:K70"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A88:K88"/>
@@ -4240,16 +4103,15 @@
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="G116:K116"/>
     <mergeCell ref="A87:K87"/>
-    <mergeCell ref="G125:K125"/>
     <mergeCell ref="G101:K101"/>
     <mergeCell ref="G103:K103"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="G112:K112"/>
+    <mergeCell ref="A128:K128"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="G37:K37"/>
     <mergeCell ref="A90:K90"/>
-    <mergeCell ref="A133:K133"/>
     <mergeCell ref="G118:K118"/>
     <mergeCell ref="G69:K69"/>
     <mergeCell ref="A89:K89"/>
@@ -4259,24 +4121,22 @@
     <mergeCell ref="A95:K95"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:K129"/>
-    <mergeCell ref="G124:K124"/>
     <mergeCell ref="G104:K104"/>
     <mergeCell ref="A42:K42"/>
     <mergeCell ref="G114:K114"/>
     <mergeCell ref="B86:K86"/>
     <mergeCell ref="G110:K110"/>
     <mergeCell ref="G79:K79"/>
-    <mergeCell ref="G123:K123"/>
+    <mergeCell ref="A126:K126"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G35:K35"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="G100:K100"/>
     <mergeCell ref="G113:K113"/>
-    <mergeCell ref="A131:K131"/>
     <mergeCell ref="G109:K109"/>
-    <mergeCell ref="A134:K134"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="G119:K119"/>
+    <mergeCell ref="A125:K125"/>
     <mergeCell ref="A93:K93"/>
     <mergeCell ref="G99:K99"/>
     <mergeCell ref="G106:K106"/>
